--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="56">
   <si>
     <t>NpcID</t>
   </si>
@@ -33,6 +33,24 @@
     <t>수상한 꽃</t>
   </si>
   <si>
+    <t>N003</t>
+  </si>
+  <si>
+    <t>시루</t>
+  </si>
+  <si>
+    <t>N004</t>
+  </si>
+  <si>
+    <t>오래된 풍선</t>
+  </si>
+  <si>
+    <t>N005</t>
+  </si>
+  <si>
+    <t>오래된 문</t>
+  </si>
+  <si>
     <t>LogID</t>
   </si>
   <si>
@@ -90,17 +108,87 @@
     <t>C003</t>
   </si>
   <si>
+    <t>시루야!!!!</t>
+  </si>
+  <si>
+    <t>왕왕!!!!</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>Monologue</t>
+  </si>
+  <si>
+    <t>보고 싶었어..시루야..</t>
+  </si>
+  <si>
+    <t>끼이잉..</t>
+  </si>
+  <si>
+    <t>내 말에 대답하는 거 같네, 알아듣는건가?</t>
+  </si>
+  <si>
+    <t>시루야 내가 하는 말 알아들을 수 있어?</t>
+  </si>
+  <si>
+    <t>왕왕왕!!!</t>
+  </si>
+  <si>
+    <t>진짜야 이거?</t>
+  </si>
+  <si>
+    <t>정말 보고 싶었어...</t>
+  </si>
+  <si>
+    <t>왕!!</t>
+  </si>
+  <si>
+    <t>오랜만에 봐서 너무 행복하지만,, 이제 가봐야 할 거 같아.</t>
+  </si>
+  <si>
+    <t>끼잉..끼이잉..</t>
+  </si>
+  <si>
+    <t>우리 다음에.. 또 볼 수 있겠지?</t>
+  </si>
+  <si>
+    <t>왕왕!</t>
+  </si>
+  <si>
+    <t>그래, 다음에 다시 만나자!</t>
+  </si>
+  <si>
+    <t>어렸을 땐 엄마랑 풍선만 있어도 행복했는데..</t>
+  </si>
+  <si>
+    <t>근데 이 풍선... 왜 여기에 있는 걸까?</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>왜 이런 곳에 문이 있지?</t>
+  </si>
+  <si>
+    <t>열쇠가 필요한 거 같은데..
+여기 어딘가에 떨어져 있으려나?</t>
+  </si>
+  <si>
+    <t>일단 이 주변을 한번 둘러봐야겠다..</t>
+  </si>
+  <si>
     <t>......................</t>
   </si>
   <si>
-    <t>Extra</t>
+    <t>왕왕!!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -116,8 +204,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -130,6 +222,18 @@
         <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -137,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -145,16 +249,92 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="2" pivot="0" name="NpcDialog-style">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -168,6 +348,21 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:I29" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="7">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
+    <tableColumn name="Column6" id="6"/>
+    <tableColumn name="Column7" id="7"/>
+  </tableColumns>
+  <tableStyleInfo name="NpcDialog-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -395,6 +590,30 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -415,194 +634,3706 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
         <v>1001.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1">
         <v>1002.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>1002.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1">
         <v>1003.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1003.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1">
         <v>-1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>2001.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>2002.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>2002.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1">
         <v>2003.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I6" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1">
         <v>2003.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>-1.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1">
         <v>-1.0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3001.0</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3002.0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3002.0</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="11">
+        <v>3003.0</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="13">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>3003.0</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="7">
+        <v>3004.0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="9">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3004.0</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="11">
+        <v>3005.0</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="13">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5">
+        <v>3005.0</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="7">
+        <v>3006.0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3006.0</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="11">
+        <v>3007.0</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="5">
+        <v>3007.0</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3008.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="5">
+        <v>3008.0</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="11">
+        <v>3009.0</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="13">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5">
+        <v>3009.0</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="7">
+        <v>3010.0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3010.0</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="11">
+        <v>3011.0</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="13">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="5">
+        <v>3011.0</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="7">
+        <v>3012.0</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="5">
+        <v>3012.0</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3013.0</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="13">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5">
+        <v>3013.0</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="7">
+        <v>3014.0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5">
+        <v>3014.0</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="11">
+        <v>3015.0</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="5">
+        <v>3015.0</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="7">
+        <v>3016.0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5">
+        <v>3016.0</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="11">
+        <v>3017.0</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="5">
+        <v>3017.0</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="9">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4001.0</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="7">
+        <v>4002.0</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="7">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4002.0</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-1.0</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="5">
+        <v>5001.0</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="7">
+        <v>5002.0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5">
+        <v>5002.0</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="11">
+        <v>5003.0</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="5">
+        <v>5003.0</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="9">
+        <v>-1.0</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="16"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="16"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="16"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="16"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="16"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="16"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="16"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="16"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="16"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="16"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="16"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="16"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="16"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="16"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="16"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="16"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="16"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="16"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="16"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="16"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="16"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="16"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="16"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="16"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="16"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="16"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="16"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="16"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="16"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="16"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="16"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="16"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="16"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="16"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="16"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="16"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="16"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="16"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="16"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="16"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="16"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="16"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="16"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="16"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="16"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="16"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="16"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="16"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="16"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="16"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="16"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="16"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="16"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="16"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="16"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="16"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="16"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="16"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="16"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="16"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="16"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="16"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="16"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="16"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="16"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="16"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="16"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="16"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="16"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="16"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="16"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="16"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="16"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="16"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="16"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="16"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="16"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="16"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="16"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="16"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="16"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="16"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="16"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="16"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="16"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="16"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="16"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="16"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="16"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="16"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="16"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="16"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="16"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="16"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="16"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="16"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="16"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="16"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="16"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="16"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="16"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="16"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="16"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="16"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="16"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="16"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="16"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="16"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="16"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="16"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="16"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="16"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="16"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="16"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="16"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="16"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="16"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="16"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="16"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="16"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="16"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="16"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="16"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="16"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="16"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="16"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="16"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="16"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="16"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="16"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="16"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="16"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="16"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="16"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="16"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="16"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="16"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="16"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="16"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="16"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="16"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="16"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="16"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="16"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="16"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="16"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="16"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="16"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="16"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="16"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="16"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="16"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="16"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="16"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="16"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="16"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="16"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="16"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="16"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="16"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="16"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="16"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="16"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="16"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="16"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="16"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="16"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="16"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="16"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="16"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="16"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="16"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="16"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="16"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="16"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="16"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="16"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="16"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="16"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="16"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="16"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="16"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="16"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="16"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="16"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="16"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="16"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="16"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="16"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="16"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="16"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="16"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="16"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="16"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="16"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="16"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="16"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="16"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="16"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="16"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="16"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="16"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="16"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="16"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="16"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="16"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="16"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="16"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="16"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="16"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="16"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="16"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="16"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="16"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="16"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="16"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="16"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="16"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="16"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="16"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="16"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="16"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="16"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="16"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="16"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="16"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="16"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="16"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="16"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="16"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="16"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="16"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="16"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="16"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="16"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="16"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="16"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="16"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="16"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="16"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="16"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="16"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="16"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="16"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="16"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="16"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="16"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="16"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="16"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="16"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="16"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="16"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="16"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="16"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="16"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="16"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="16"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="16"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="16"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="16"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="16"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="16"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="16"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="16"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="16"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="16"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="16"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="16"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="16"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="16"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="16"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="16"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="16"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="16"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="16"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="16"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="16"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="16"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="16"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="16"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="16"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="16"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="16"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="16"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="16"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="16"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="16"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="16"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="16"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="16"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="16"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="16"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="16"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="16"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="16"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="16"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="16"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="16"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="16"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="16"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="16"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="16"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="16"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="16"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="16"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="16"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="16"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="16"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="16"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="16"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="16"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="16"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="16"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="16"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="16"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="16"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="16"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="16"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="16"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="16"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="16"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="16"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="16"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="16"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="16"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="16"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="16"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="16"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="16"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="16"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="16"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="16"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="16"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="16"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="16"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="16"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="16"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="16"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="16"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="16"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="16"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="16"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="16"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="16"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="16"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="16"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="16"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="16"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="16"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="16"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="16"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="16"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="16"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="16"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="16"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="16"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="16"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="16"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="16"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="16"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="16"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="16"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="16"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="16"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="16"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="16"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="16"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="16"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="16"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="16"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="16"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="16"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="16"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="16"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="16"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="16"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="16"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="16"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="16"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="16"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="16"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="16"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="16"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="16"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="16"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="16"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="16"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="16"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="16"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="16"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="16"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="16"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="16"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="16"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="16"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="16"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="16"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="16"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="16"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="16"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="16"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="16"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="16"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="16"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="16"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="16"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="16"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="16"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="16"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="16"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="16"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="16"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="16"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="16"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="16"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="16"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="16"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="16"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="16"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="16"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="16"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="16"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="16"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="16"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="16"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="16"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="16"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="16"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="16"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="16"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="16"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="16"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="16"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="16"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="16"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="16"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="16"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="16"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="16"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="16"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="16"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="16"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="16"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="16"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="16"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="16"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="16"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="16"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="16"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="16"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="16"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="16"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="16"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="16"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="16"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="16"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="16"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="16"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="16"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="16"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="16"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="16"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="16"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="16"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="16"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="16"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="16"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="16"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="16"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="16"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="16"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="16"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="16"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="16"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="16"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="16"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="16"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="16"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="16"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="16"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="16"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="16"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="16"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="16"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="16"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="16"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="16"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="16"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="16"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="16"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="16"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="16"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="16"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="16"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="16"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="16"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="16"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="16"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="16"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="16"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="16"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="16"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="16"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="16"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="16"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="16"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="16"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="16"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="16"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="16"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="16"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="16"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="16"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="16"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="16"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="16"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="16"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="16"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="16"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="16"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="16"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="16"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="16"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="16"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="16"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="16"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="16"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="16"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="16"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="16"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="16"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="16"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="16"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="16"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="16"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="16"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="16"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="16"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="16"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="16"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="16"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="16"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="16"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="16"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="16"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="16"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="16"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="16"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="16"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="16"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="16"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="16"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="16"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="16"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="16"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="16"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="16"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="16"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="16"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="16"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="16"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="16"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="16"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="16"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="16"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="16"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="16"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="16"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="16"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="16"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="16"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="16"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="16"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="16"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="16"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="16"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="16"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="16"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="16"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="16"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="16"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="16"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="16"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="16"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="16"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="16"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="16"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="16"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="16"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="16"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="16"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="16"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="16"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="16"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="16"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="16"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="16"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="16"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="16"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="16"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="16"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="16"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="16"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="16"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="16"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="16"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="16"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="16"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="16"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="16"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="16"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="16"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="16"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="16"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="16"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="16"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="16"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="16"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="16"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="16"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="16"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="16"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="16"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="16"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="16"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="16"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="16"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="16"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="16"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="16"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="16"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="16"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="16"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="16"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="16"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="16"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="16"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="16"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="16"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="16"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="16"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="16"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="16"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="16"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="16"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="16"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="16"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="16"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="16"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="16"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="16"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="16"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="16"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="16"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="16"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="16"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="16"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="16"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="16"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="16"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="16"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="16"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="16"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="16"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="16"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="16"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="16"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="16"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="16"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="16"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="16"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="16"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="16"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="16"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="16"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="16"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="16"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="16"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="16"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="16"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="16"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="16"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="16"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="16"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="16"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="16"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="16"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="16"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="16"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="16"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="16"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="16"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="16"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="16"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="16"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="16"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="16"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="16"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="16"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="16"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="16"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="16"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="16"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="16"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="16"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="16"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="16"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="16"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="16"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="16"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="16"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="16"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="16"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="16"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="16"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="16"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="16"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="16"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="16"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="16"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="16"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="16"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="16"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="16"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="16"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="16"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="16"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="16"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="16"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="16"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="16"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="16"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="16"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="16"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="16"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="16"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="16"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="16"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="16"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="16"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="16"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="16"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="16"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="16"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="16"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="16"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="16"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="16"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="16"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="16"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="16"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="16"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="16"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="16"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="16"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="16"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="16"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="16"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="16"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="16"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="16"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="16"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="16"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="16"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="16"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="16"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="16"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="16"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="16"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="16"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="16"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="16"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="16"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="16"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="16"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="16"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="16"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="16"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="16"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="16"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="16"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="16"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="16"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="16"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="16"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="16"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="16"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="16"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="16"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="16"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="16"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="16"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="16"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="16"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="16"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="16"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="16"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="16"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="16"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="16"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="16"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="16"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="16"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="16"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="16"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="16"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="16"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="16"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="16"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="16"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="16"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="16"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="16"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="16"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="16"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="16"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="16"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="16"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="16"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="16"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="16"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="16"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="16"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="16"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="16"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="16"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="16"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="16"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="16"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="16"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="16"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="16"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="16"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="16"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="16"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="16"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="16"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="16"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="16"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="16"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="16"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="16"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="16"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="16"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="16"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="16"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="16"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="16"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="16"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="16"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="16"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="16"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="16"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="16"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="16"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="16"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="16"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="16"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="16"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="16"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="16"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="16"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="16"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="16"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="16"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="16"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="16"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="16"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="16"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="16"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="16"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="16"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="16"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="16"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="16"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="16"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="16"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="16"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="16"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="16"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="16"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="16"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="16"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="16"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="16"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="16"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="16"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="16"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="16"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="16"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="16"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="16"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="16"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="16"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="16"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="16"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="16"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="16"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="16"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="16"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="16"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="16"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="16"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="16"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="16"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="16"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="16"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="16"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="16"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="16"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="16"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="16"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="16"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="16"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="16"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="16"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="16"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="16"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="16"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="16"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="16"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="16"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="16"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="16"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="16"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="16"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="16"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="16"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="16"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="16"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="16"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="16"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="16"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="16"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="16"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="16"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="16"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="16"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="16"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="16"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="16"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -614,23 +4345,23 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -638,16 +4369,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -658,18 +4389,78 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
   <si>
     <t>NpcID</t>
   </si>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>오래된 문</t>
+  </si>
+  <si>
+    <t>N006</t>
+  </si>
+  <si>
+    <t>의문의 분수</t>
+  </si>
+  <si>
+    <t>N007</t>
+  </si>
+  <si>
+    <t>N008</t>
   </si>
   <si>
     <t>LogID</t>
@@ -178,10 +190,99 @@
     <t>일단 이 주변을 한번 둘러봐야겠다..</t>
   </si>
   <si>
+    <t>이건... 분수..?</t>
+  </si>
+  <si>
+    <t>분수가 왜 이런 곳에 있지?</t>
+  </si>
+  <si>
+    <t>어이!! 거기 너!!</t>
+  </si>
+  <si>
+    <t>분수</t>
+  </si>
+  <si>
+    <t>어...? 분수가 말을..?</t>
+  </si>
+  <si>
+    <t>거기 너! 수수께끼 좀 풀 줄 아나?</t>
+  </si>
+  <si>
+    <t>수수께끼... 잘 모르는데.</t>
+  </si>
+  <si>
+    <t>내가 내는 수수께끼를 맞히면 좋은 걸 줄게!</t>
+  </si>
+  <si>
+    <t>그렇다면.. 풀어볼게..</t>
+  </si>
+  <si>
+    <t>아침엔 네발 점심엔 두발 저녁엔 세발로 서있는 게 뭘까?</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>거기, 당신 날 좀 도와줄 수 있나요?</t>
+  </si>
+  <si>
+    <t>응? 뭘 도와주면 되는데?</t>
+  </si>
+  <si>
+    <t>수학 문제 라는데 저는 도저히 모르겠어요</t>
+  </si>
+  <si>
+    <t>나도 수학은 잘 모르는데..</t>
+  </si>
+  <si>
+    <t>절 도와주시면 당신에게 필요한 걸 줄게요.</t>
+  </si>
+  <si>
+    <t>그럼.. 일단 들어볼게.</t>
+  </si>
+  <si>
+    <t>3+5 가 뭐죠? 난 도저히 모르겠어요.</t>
+  </si>
+  <si>
+    <t>이 정도면 유치원생도 풀 수 있는 문제 아닌가..?</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>세상에서 제일 뜨거운 과일이 뭔지 맞춰봐.</t>
+  </si>
+  <si>
+    <t>천도복숭아..?</t>
+  </si>
+  <si>
+    <t>그렇다면, 왕이 넘어지면 뭘까?</t>
+  </si>
+  <si>
+    <t>....킹콩?</t>
+  </si>
+  <si>
+    <t>똑똑하군, 그럼 마지막 문제.</t>
+  </si>
+  <si>
+    <t>198265x0x257445x789545의 답은?</t>
+  </si>
+  <si>
+    <t>C007</t>
+  </si>
+  <si>
     <t>......................</t>
   </si>
   <si>
     <t>왕왕!!</t>
+  </si>
+  <si>
+    <t>정답이야! 
+너 똑똑하다!</t>
+  </si>
+  <si>
+    <t>그렇군요!!
+정말 고마워요</t>
   </si>
 </sst>
 </file>
@@ -241,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -289,6 +390,9 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
@@ -351,7 +455,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:I29" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:I52" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -614,6 +718,30 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -634,28 +762,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -666,19 +794,19 @@
         <v>1001.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1">
         <v>1002.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1">
         <v>-1.0</v>
@@ -692,19 +820,19 @@
         <v>1002.0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1">
         <v>1003.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1">
         <v>-1.0</v>
@@ -718,22 +846,22 @@
         <v>1003.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1">
         <v>-1.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1">
         <v>-1.0</v>
@@ -747,19 +875,19 @@
         <v>2001.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
         <v>2002.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1">
         <v>-1.0</v>
@@ -773,19 +901,19 @@
         <v>2002.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <v>2003.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1">
         <v>-1.0</v>
@@ -799,22 +927,22 @@
         <v>2003.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1">
         <v>-1.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1">
         <v>-1.0</v>
@@ -828,20 +956,20 @@
         <v>3001.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7">
         <v>3002.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" s="9">
         <v>0.0</v>
@@ -855,20 +983,20 @@
         <v>3002.0</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D9" s="11">
         <v>3003.0</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I9" s="13">
         <v>-1.0</v>
@@ -882,20 +1010,20 @@
         <v>3003.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D10" s="7">
         <v>3004.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" s="9">
         <v>4.0</v>
@@ -909,20 +1037,20 @@
         <v>3004.0</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="11">
         <v>3005.0</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I11" s="13">
         <v>-1.0</v>
@@ -936,20 +1064,20 @@
         <v>3005.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D12" s="7">
         <v>3006.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I12" s="9">
         <v>0.0</v>
@@ -963,20 +1091,20 @@
         <v>3006.0</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" s="11">
         <v>3007.0</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I13" s="13">
         <v>0.0</v>
@@ -990,20 +1118,20 @@
         <v>3007.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D14" s="7">
         <v>3008.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I14" s="9">
         <v>-1.0</v>
@@ -1017,20 +1145,20 @@
         <v>3008.0</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D15" s="11">
         <v>3009.0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I15" s="13">
         <v>2.0</v>
@@ -1044,20 +1172,20 @@
         <v>3009.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D16" s="7">
         <v>3010.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I16" s="9">
         <v>-1.0</v>
@@ -1071,20 +1199,20 @@
         <v>3010.0</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D17" s="11">
         <v>3011.0</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I17" s="13">
         <v>4.0</v>
@@ -1098,20 +1226,20 @@
         <v>3011.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D18" s="7">
         <v>3012.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I18" s="9">
         <v>-1.0</v>
@@ -1125,20 +1253,20 @@
         <v>3012.0</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D19" s="11">
         <v>3013.0</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I19" s="13">
         <v>4.0</v>
@@ -1152,20 +1280,20 @@
         <v>3013.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D20" s="7">
         <v>3014.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I20" s="9">
         <v>-1.0</v>
@@ -1179,20 +1307,20 @@
         <v>3014.0</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D21" s="11">
         <v>3015.0</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I21" s="13">
         <v>0.0</v>
@@ -1206,20 +1334,20 @@
         <v>3015.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D22" s="7">
         <v>3016.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I22" s="9">
         <v>-1.0</v>
@@ -1233,20 +1361,20 @@
         <v>3016.0</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D23" s="11">
         <v>3017.0</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I23" s="13">
         <v>0.0</v>
@@ -1260,20 +1388,20 @@
         <v>3017.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D24" s="7">
         <v>-1.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I24" s="9">
         <v>-1.0</v>
@@ -1287,20 +1415,20 @@
         <v>4001.0</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D25" s="7">
         <v>4002.0</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I25" s="7">
         <v>4.0</v>
@@ -1314,22 +1442,22 @@
         <v>4002.0</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D26" s="7">
         <v>-1.0</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I26" s="7">
         <v>0.0</v>
@@ -1343,20 +1471,20 @@
         <v>5001.0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D27" s="7">
         <v>5002.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I27" s="9">
         <v>0.0</v>
@@ -1370,20 +1498,20 @@
         <v>5002.0</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D28" s="11">
         <v>5003.0</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I28" s="13">
         <v>0.0</v>
@@ -1397,2937 +1525,3495 @@
         <v>5003.0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29" s="9">
         <v>-1.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I29" s="9">
         <v>0.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16"/>
+      <c r="A30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="1">
+        <v>6001.0</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="7">
+        <v>6002.0</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16"/>
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="1">
+        <v>6002.0</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="7">
+        <v>6003.0</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16"/>
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="1">
+        <v>6003.0</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6004.0</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16"/>
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="1">
+        <v>6004.0</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="7">
+        <v>6005.0</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="16"/>
+      <c r="A34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="1">
+        <v>6005.0</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6006.0</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16"/>
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1">
+        <v>6006.0</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="7">
+        <v>6007.0</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="16"/>
+      <c r="A36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="1">
+        <v>6007.0</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6008.0</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="16"/>
+      <c r="A37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="1">
+        <v>6008.0</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="7">
+        <v>6009.0</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="16"/>
+      <c r="A38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="1">
+        <v>6009.0</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-1.0</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="16"/>
+      <c r="A39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="1">
+        <v>7001.0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="7">
+        <v>7002.0</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="16"/>
+      <c r="H39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="16"/>
+      <c r="A40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1">
+        <v>7002.0</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="7">
+        <v>7003.0</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="16"/>
+      <c r="H40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16"/>
+      <c r="A41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="1">
+        <v>7003.0</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="7">
+        <v>7004.0</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="16"/>
+      <c r="H41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="16"/>
+      <c r="A42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="1">
+        <v>7004.0</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="7">
+        <v>7005.0</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="16"/>
+      <c r="A43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="1">
+        <v>7005.0</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="7">
+        <v>7006.0</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" s="16"/>
+      <c r="H43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="16"/>
+      <c r="A44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="1">
+        <v>7006.0</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" s="7">
+        <v>7007.0</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="16"/>
+      <c r="A45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="1">
+        <v>7007.0</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="7">
+        <v>7008.0</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="16"/>
+      <c r="H45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="16"/>
+      <c r="A46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="1">
+        <v>7008.0</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-1.0</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I46" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="16"/>
+      <c r="A47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1">
+        <v>8001.0</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="7">
+        <v>8002.0</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="16"/>
+      <c r="H47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="16"/>
+      <c r="A48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1">
+        <v>8002.0</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="7">
+        <v>8003.0</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="16"/>
+      <c r="H48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="16"/>
+      <c r="A49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1">
+        <v>8003.0</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="7">
+        <v>8004.0</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" s="16"/>
+      <c r="H49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="16"/>
+      <c r="A50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="1">
+        <v>8004.0</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="7">
+        <v>8005.0</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="16"/>
+      <c r="H50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="7">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="16"/>
+      <c r="A51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="1">
+        <v>8005.0</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="7">
+        <v>8006.0</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" s="16"/>
+      <c r="H51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="16"/>
+      <c r="A52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="1">
+        <v>8006.0</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-1.0</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" s="7">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="16"/>
+      <c r="A53" s="17"/>
     </row>
     <row r="54">
-      <c r="A54" s="16"/>
+      <c r="A54" s="17"/>
     </row>
     <row r="55">
-      <c r="A55" s="16"/>
+      <c r="A55" s="17"/>
     </row>
     <row r="56">
-      <c r="A56" s="16"/>
+      <c r="A56" s="17"/>
     </row>
     <row r="57">
-      <c r="A57" s="16"/>
+      <c r="A57" s="17"/>
     </row>
     <row r="58">
-      <c r="A58" s="16"/>
+      <c r="A58" s="17"/>
     </row>
     <row r="59">
-      <c r="A59" s="16"/>
+      <c r="A59" s="17"/>
     </row>
     <row r="60">
-      <c r="A60" s="16"/>
+      <c r="A60" s="17"/>
     </row>
     <row r="61">
-      <c r="A61" s="16"/>
+      <c r="A61" s="17"/>
     </row>
     <row r="62">
-      <c r="A62" s="16"/>
+      <c r="A62" s="17"/>
     </row>
     <row r="63">
-      <c r="A63" s="16"/>
+      <c r="A63" s="17"/>
     </row>
     <row r="64">
-      <c r="A64" s="16"/>
+      <c r="A64" s="17"/>
     </row>
     <row r="65">
-      <c r="A65" s="16"/>
+      <c r="A65" s="17"/>
     </row>
     <row r="66">
-      <c r="A66" s="16"/>
+      <c r="A66" s="17"/>
     </row>
     <row r="67">
-      <c r="A67" s="16"/>
+      <c r="A67" s="17"/>
     </row>
     <row r="68">
-      <c r="A68" s="16"/>
+      <c r="A68" s="17"/>
     </row>
     <row r="69">
-      <c r="A69" s="16"/>
+      <c r="A69" s="17"/>
     </row>
     <row r="70">
-      <c r="A70" s="16"/>
+      <c r="A70" s="17"/>
     </row>
     <row r="71">
-      <c r="A71" s="16"/>
+      <c r="A71" s="17"/>
     </row>
     <row r="72">
-      <c r="A72" s="16"/>
+      <c r="A72" s="17"/>
     </row>
     <row r="73">
-      <c r="A73" s="16"/>
+      <c r="A73" s="17"/>
     </row>
     <row r="74">
-      <c r="A74" s="16"/>
+      <c r="A74" s="17"/>
     </row>
     <row r="75">
-      <c r="A75" s="16"/>
+      <c r="A75" s="17"/>
     </row>
     <row r="76">
-      <c r="A76" s="16"/>
+      <c r="A76" s="17"/>
     </row>
     <row r="77">
-      <c r="A77" s="16"/>
+      <c r="A77" s="17"/>
     </row>
     <row r="78">
-      <c r="A78" s="16"/>
+      <c r="A78" s="17"/>
     </row>
     <row r="79">
-      <c r="A79" s="16"/>
+      <c r="A79" s="17"/>
     </row>
     <row r="80">
-      <c r="A80" s="16"/>
+      <c r="A80" s="17"/>
     </row>
     <row r="81">
-      <c r="A81" s="16"/>
+      <c r="A81" s="17"/>
     </row>
     <row r="82">
-      <c r="A82" s="16"/>
+      <c r="A82" s="17"/>
     </row>
     <row r="83">
-      <c r="A83" s="16"/>
+      <c r="A83" s="17"/>
     </row>
     <row r="84">
-      <c r="A84" s="16"/>
+      <c r="A84" s="17"/>
     </row>
     <row r="85">
-      <c r="A85" s="16"/>
+      <c r="A85" s="17"/>
     </row>
     <row r="86">
-      <c r="A86" s="16"/>
+      <c r="A86" s="17"/>
     </row>
     <row r="87">
-      <c r="A87" s="16"/>
+      <c r="A87" s="17"/>
     </row>
     <row r="88">
-      <c r="A88" s="16"/>
+      <c r="A88" s="17"/>
     </row>
     <row r="89">
-      <c r="A89" s="16"/>
+      <c r="A89" s="17"/>
     </row>
     <row r="90">
-      <c r="A90" s="16"/>
+      <c r="A90" s="17"/>
     </row>
     <row r="91">
-      <c r="A91" s="16"/>
+      <c r="A91" s="17"/>
     </row>
     <row r="92">
-      <c r="A92" s="16"/>
+      <c r="A92" s="17"/>
     </row>
     <row r="93">
-      <c r="A93" s="16"/>
+      <c r="A93" s="17"/>
     </row>
     <row r="94">
-      <c r="A94" s="16"/>
+      <c r="A94" s="17"/>
     </row>
     <row r="95">
-      <c r="A95" s="16"/>
+      <c r="A95" s="17"/>
     </row>
     <row r="96">
-      <c r="A96" s="16"/>
+      <c r="A96" s="17"/>
     </row>
     <row r="97">
-      <c r="A97" s="16"/>
+      <c r="A97" s="17"/>
     </row>
     <row r="98">
-      <c r="A98" s="16"/>
+      <c r="A98" s="17"/>
     </row>
     <row r="99">
-      <c r="A99" s="16"/>
+      <c r="A99" s="17"/>
     </row>
     <row r="100">
-      <c r="A100" s="16"/>
+      <c r="A100" s="17"/>
     </row>
     <row r="101">
-      <c r="A101" s="16"/>
+      <c r="A101" s="17"/>
     </row>
     <row r="102">
-      <c r="A102" s="16"/>
+      <c r="A102" s="17"/>
     </row>
     <row r="103">
-      <c r="A103" s="16"/>
+      <c r="A103" s="17"/>
     </row>
     <row r="104">
-      <c r="A104" s="16"/>
+      <c r="A104" s="17"/>
     </row>
     <row r="105">
-      <c r="A105" s="16"/>
+      <c r="A105" s="17"/>
     </row>
     <row r="106">
-      <c r="A106" s="16"/>
+      <c r="A106" s="17"/>
     </row>
     <row r="107">
-      <c r="A107" s="16"/>
+      <c r="A107" s="17"/>
     </row>
     <row r="108">
-      <c r="A108" s="16"/>
+      <c r="A108" s="17"/>
     </row>
     <row r="109">
-      <c r="A109" s="16"/>
+      <c r="A109" s="17"/>
     </row>
     <row r="110">
-      <c r="A110" s="16"/>
+      <c r="A110" s="17"/>
     </row>
     <row r="111">
-      <c r="A111" s="16"/>
+      <c r="A111" s="17"/>
     </row>
     <row r="112">
-      <c r="A112" s="16"/>
+      <c r="A112" s="17"/>
     </row>
     <row r="113">
-      <c r="A113" s="16"/>
+      <c r="A113" s="17"/>
     </row>
     <row r="114">
-      <c r="A114" s="16"/>
+      <c r="A114" s="17"/>
     </row>
     <row r="115">
-      <c r="A115" s="16"/>
+      <c r="A115" s="17"/>
     </row>
     <row r="116">
-      <c r="A116" s="16"/>
+      <c r="A116" s="17"/>
     </row>
     <row r="117">
-      <c r="A117" s="16"/>
+      <c r="A117" s="17"/>
     </row>
     <row r="118">
-      <c r="A118" s="16"/>
+      <c r="A118" s="17"/>
     </row>
     <row r="119">
-      <c r="A119" s="16"/>
+      <c r="A119" s="17"/>
     </row>
     <row r="120">
-      <c r="A120" s="16"/>
+      <c r="A120" s="17"/>
     </row>
     <row r="121">
-      <c r="A121" s="16"/>
+      <c r="A121" s="17"/>
     </row>
     <row r="122">
-      <c r="A122" s="16"/>
+      <c r="A122" s="17"/>
     </row>
     <row r="123">
-      <c r="A123" s="16"/>
+      <c r="A123" s="17"/>
     </row>
     <row r="124">
-      <c r="A124" s="16"/>
+      <c r="A124" s="17"/>
     </row>
     <row r="125">
-      <c r="A125" s="16"/>
+      <c r="A125" s="17"/>
     </row>
     <row r="126">
-      <c r="A126" s="16"/>
+      <c r="A126" s="17"/>
     </row>
     <row r="127">
-      <c r="A127" s="16"/>
+      <c r="A127" s="17"/>
     </row>
     <row r="128">
-      <c r="A128" s="16"/>
+      <c r="A128" s="17"/>
     </row>
     <row r="129">
-      <c r="A129" s="16"/>
+      <c r="A129" s="17"/>
     </row>
     <row r="130">
-      <c r="A130" s="16"/>
+      <c r="A130" s="17"/>
     </row>
     <row r="131">
-      <c r="A131" s="16"/>
+      <c r="A131" s="17"/>
     </row>
     <row r="132">
-      <c r="A132" s="16"/>
+      <c r="A132" s="17"/>
     </row>
     <row r="133">
-      <c r="A133" s="16"/>
+      <c r="A133" s="17"/>
     </row>
     <row r="134">
-      <c r="A134" s="16"/>
+      <c r="A134" s="17"/>
     </row>
     <row r="135">
-      <c r="A135" s="16"/>
+      <c r="A135" s="17"/>
     </row>
     <row r="136">
-      <c r="A136" s="16"/>
+      <c r="A136" s="17"/>
     </row>
     <row r="137">
-      <c r="A137" s="16"/>
+      <c r="A137" s="17"/>
     </row>
     <row r="138">
-      <c r="A138" s="16"/>
+      <c r="A138" s="17"/>
     </row>
     <row r="139">
-      <c r="A139" s="16"/>
+      <c r="A139" s="17"/>
     </row>
     <row r="140">
-      <c r="A140" s="16"/>
+      <c r="A140" s="17"/>
     </row>
     <row r="141">
-      <c r="A141" s="16"/>
+      <c r="A141" s="17"/>
     </row>
     <row r="142">
-      <c r="A142" s="16"/>
+      <c r="A142" s="17"/>
     </row>
     <row r="143">
-      <c r="A143" s="16"/>
+      <c r="A143" s="17"/>
     </row>
     <row r="144">
-      <c r="A144" s="16"/>
+      <c r="A144" s="17"/>
     </row>
     <row r="145">
-      <c r="A145" s="16"/>
+      <c r="A145" s="17"/>
     </row>
     <row r="146">
-      <c r="A146" s="16"/>
+      <c r="A146" s="17"/>
     </row>
     <row r="147">
-      <c r="A147" s="16"/>
+      <c r="A147" s="17"/>
     </row>
     <row r="148">
-      <c r="A148" s="16"/>
+      <c r="A148" s="17"/>
     </row>
     <row r="149">
-      <c r="A149" s="16"/>
+      <c r="A149" s="17"/>
     </row>
     <row r="150">
-      <c r="A150" s="16"/>
+      <c r="A150" s="17"/>
     </row>
     <row r="151">
-      <c r="A151" s="16"/>
+      <c r="A151" s="17"/>
     </row>
     <row r="152">
-      <c r="A152" s="16"/>
+      <c r="A152" s="17"/>
     </row>
     <row r="153">
-      <c r="A153" s="16"/>
+      <c r="A153" s="17"/>
     </row>
     <row r="154">
-      <c r="A154" s="16"/>
+      <c r="A154" s="17"/>
     </row>
     <row r="155">
-      <c r="A155" s="16"/>
+      <c r="A155" s="17"/>
     </row>
     <row r="156">
-      <c r="A156" s="16"/>
+      <c r="A156" s="17"/>
     </row>
     <row r="157">
-      <c r="A157" s="16"/>
+      <c r="A157" s="17"/>
     </row>
     <row r="158">
-      <c r="A158" s="16"/>
+      <c r="A158" s="17"/>
     </row>
     <row r="159">
-      <c r="A159" s="16"/>
+      <c r="A159" s="17"/>
     </row>
     <row r="160">
-      <c r="A160" s="16"/>
+      <c r="A160" s="17"/>
     </row>
     <row r="161">
-      <c r="A161" s="16"/>
+      <c r="A161" s="17"/>
     </row>
     <row r="162">
-      <c r="A162" s="16"/>
+      <c r="A162" s="17"/>
     </row>
     <row r="163">
-      <c r="A163" s="16"/>
+      <c r="A163" s="17"/>
     </row>
     <row r="164">
-      <c r="A164" s="16"/>
+      <c r="A164" s="17"/>
     </row>
     <row r="165">
-      <c r="A165" s="16"/>
+      <c r="A165" s="17"/>
     </row>
     <row r="166">
-      <c r="A166" s="16"/>
+      <c r="A166" s="17"/>
     </row>
     <row r="167">
-      <c r="A167" s="16"/>
+      <c r="A167" s="17"/>
     </row>
     <row r="168">
-      <c r="A168" s="16"/>
+      <c r="A168" s="17"/>
     </row>
     <row r="169">
-      <c r="A169" s="16"/>
+      <c r="A169" s="17"/>
     </row>
     <row r="170">
-      <c r="A170" s="16"/>
+      <c r="A170" s="17"/>
     </row>
     <row r="171">
-      <c r="A171" s="16"/>
+      <c r="A171" s="17"/>
     </row>
     <row r="172">
-      <c r="A172" s="16"/>
+      <c r="A172" s="17"/>
     </row>
     <row r="173">
-      <c r="A173" s="16"/>
+      <c r="A173" s="17"/>
     </row>
     <row r="174">
-      <c r="A174" s="16"/>
+      <c r="A174" s="17"/>
     </row>
     <row r="175">
-      <c r="A175" s="16"/>
+      <c r="A175" s="17"/>
     </row>
     <row r="176">
-      <c r="A176" s="16"/>
+      <c r="A176" s="17"/>
     </row>
     <row r="177">
-      <c r="A177" s="16"/>
+      <c r="A177" s="17"/>
     </row>
     <row r="178">
-      <c r="A178" s="16"/>
+      <c r="A178" s="17"/>
     </row>
     <row r="179">
-      <c r="A179" s="16"/>
+      <c r="A179" s="17"/>
     </row>
     <row r="180">
-      <c r="A180" s="16"/>
+      <c r="A180" s="17"/>
     </row>
     <row r="181">
-      <c r="A181" s="16"/>
+      <c r="A181" s="17"/>
     </row>
     <row r="182">
-      <c r="A182" s="16"/>
+      <c r="A182" s="17"/>
     </row>
     <row r="183">
-      <c r="A183" s="16"/>
+      <c r="A183" s="17"/>
     </row>
     <row r="184">
-      <c r="A184" s="16"/>
+      <c r="A184" s="17"/>
     </row>
     <row r="185">
-      <c r="A185" s="16"/>
+      <c r="A185" s="17"/>
     </row>
     <row r="186">
-      <c r="A186" s="16"/>
+      <c r="A186" s="17"/>
     </row>
     <row r="187">
-      <c r="A187" s="16"/>
+      <c r="A187" s="17"/>
     </row>
     <row r="188">
-      <c r="A188" s="16"/>
+      <c r="A188" s="17"/>
     </row>
     <row r="189">
-      <c r="A189" s="16"/>
+      <c r="A189" s="17"/>
     </row>
     <row r="190">
-      <c r="A190" s="16"/>
+      <c r="A190" s="17"/>
     </row>
     <row r="191">
-      <c r="A191" s="16"/>
+      <c r="A191" s="17"/>
     </row>
     <row r="192">
-      <c r="A192" s="16"/>
+      <c r="A192" s="17"/>
     </row>
     <row r="193">
-      <c r="A193" s="16"/>
+      <c r="A193" s="17"/>
     </row>
     <row r="194">
-      <c r="A194" s="16"/>
+      <c r="A194" s="17"/>
     </row>
     <row r="195">
-      <c r="A195" s="16"/>
+      <c r="A195" s="17"/>
     </row>
     <row r="196">
-      <c r="A196" s="16"/>
+      <c r="A196" s="17"/>
     </row>
     <row r="197">
-      <c r="A197" s="16"/>
+      <c r="A197" s="17"/>
     </row>
     <row r="198">
-      <c r="A198" s="16"/>
+      <c r="A198" s="17"/>
     </row>
     <row r="199">
-      <c r="A199" s="16"/>
+      <c r="A199" s="17"/>
     </row>
     <row r="200">
-      <c r="A200" s="16"/>
+      <c r="A200" s="17"/>
     </row>
     <row r="201">
-      <c r="A201" s="16"/>
+      <c r="A201" s="17"/>
     </row>
     <row r="202">
-      <c r="A202" s="16"/>
+      <c r="A202" s="17"/>
     </row>
     <row r="203">
-      <c r="A203" s="16"/>
+      <c r="A203" s="17"/>
     </row>
     <row r="204">
-      <c r="A204" s="16"/>
+      <c r="A204" s="17"/>
     </row>
     <row r="205">
-      <c r="A205" s="16"/>
+      <c r="A205" s="17"/>
     </row>
     <row r="206">
-      <c r="A206" s="16"/>
+      <c r="A206" s="17"/>
     </row>
     <row r="207">
-      <c r="A207" s="16"/>
+      <c r="A207" s="17"/>
     </row>
     <row r="208">
-      <c r="A208" s="16"/>
+      <c r="A208" s="17"/>
     </row>
     <row r="209">
-      <c r="A209" s="16"/>
+      <c r="A209" s="17"/>
     </row>
     <row r="210">
-      <c r="A210" s="16"/>
+      <c r="A210" s="17"/>
     </row>
     <row r="211">
-      <c r="A211" s="16"/>
+      <c r="A211" s="17"/>
     </row>
     <row r="212">
-      <c r="A212" s="16"/>
+      <c r="A212" s="17"/>
     </row>
     <row r="213">
-      <c r="A213" s="16"/>
+      <c r="A213" s="17"/>
     </row>
     <row r="214">
-      <c r="A214" s="16"/>
+      <c r="A214" s="17"/>
     </row>
     <row r="215">
-      <c r="A215" s="16"/>
+      <c r="A215" s="17"/>
     </row>
     <row r="216">
-      <c r="A216" s="16"/>
+      <c r="A216" s="17"/>
     </row>
     <row r="217">
-      <c r="A217" s="16"/>
+      <c r="A217" s="17"/>
     </row>
     <row r="218">
-      <c r="A218" s="16"/>
+      <c r="A218" s="17"/>
     </row>
     <row r="219">
-      <c r="A219" s="16"/>
+      <c r="A219" s="17"/>
     </row>
     <row r="220">
-      <c r="A220" s="16"/>
+      <c r="A220" s="17"/>
     </row>
     <row r="221">
-      <c r="A221" s="16"/>
+      <c r="A221" s="17"/>
     </row>
     <row r="222">
-      <c r="A222" s="16"/>
+      <c r="A222" s="17"/>
     </row>
     <row r="223">
-      <c r="A223" s="16"/>
+      <c r="A223" s="17"/>
     </row>
     <row r="224">
-      <c r="A224" s="16"/>
+      <c r="A224" s="17"/>
     </row>
     <row r="225">
-      <c r="A225" s="16"/>
+      <c r="A225" s="17"/>
     </row>
     <row r="226">
-      <c r="A226" s="16"/>
+      <c r="A226" s="17"/>
     </row>
     <row r="227">
-      <c r="A227" s="16"/>
+      <c r="A227" s="17"/>
     </row>
     <row r="228">
-      <c r="A228" s="16"/>
+      <c r="A228" s="17"/>
     </row>
     <row r="229">
-      <c r="A229" s="16"/>
+      <c r="A229" s="17"/>
     </row>
     <row r="230">
-      <c r="A230" s="16"/>
+      <c r="A230" s="17"/>
     </row>
     <row r="231">
-      <c r="A231" s="16"/>
+      <c r="A231" s="17"/>
     </row>
     <row r="232">
-      <c r="A232" s="16"/>
+      <c r="A232" s="17"/>
     </row>
     <row r="233">
-      <c r="A233" s="16"/>
+      <c r="A233" s="17"/>
     </row>
     <row r="234">
-      <c r="A234" s="16"/>
+      <c r="A234" s="17"/>
     </row>
     <row r="235">
-      <c r="A235" s="16"/>
+      <c r="A235" s="17"/>
     </row>
     <row r="236">
-      <c r="A236" s="16"/>
+      <c r="A236" s="17"/>
     </row>
     <row r="237">
-      <c r="A237" s="16"/>
+      <c r="A237" s="17"/>
     </row>
     <row r="238">
-      <c r="A238" s="16"/>
+      <c r="A238" s="17"/>
     </row>
     <row r="239">
-      <c r="A239" s="16"/>
+      <c r="A239" s="17"/>
     </row>
     <row r="240">
-      <c r="A240" s="16"/>
+      <c r="A240" s="17"/>
     </row>
     <row r="241">
-      <c r="A241" s="16"/>
+      <c r="A241" s="17"/>
     </row>
     <row r="242">
-      <c r="A242" s="16"/>
+      <c r="A242" s="17"/>
     </row>
     <row r="243">
-      <c r="A243" s="16"/>
+      <c r="A243" s="17"/>
     </row>
     <row r="244">
-      <c r="A244" s="16"/>
+      <c r="A244" s="17"/>
     </row>
     <row r="245">
-      <c r="A245" s="16"/>
+      <c r="A245" s="17"/>
     </row>
     <row r="246">
-      <c r="A246" s="16"/>
+      <c r="A246" s="17"/>
     </row>
     <row r="247">
-      <c r="A247" s="16"/>
+      <c r="A247" s="17"/>
     </row>
     <row r="248">
-      <c r="A248" s="16"/>
+      <c r="A248" s="17"/>
     </row>
     <row r="249">
-      <c r="A249" s="16"/>
+      <c r="A249" s="17"/>
     </row>
     <row r="250">
-      <c r="A250" s="16"/>
+      <c r="A250" s="17"/>
     </row>
     <row r="251">
-      <c r="A251" s="16"/>
+      <c r="A251" s="17"/>
     </row>
     <row r="252">
-      <c r="A252" s="16"/>
+      <c r="A252" s="17"/>
     </row>
     <row r="253">
-      <c r="A253" s="16"/>
+      <c r="A253" s="17"/>
     </row>
     <row r="254">
-      <c r="A254" s="16"/>
+      <c r="A254" s="17"/>
     </row>
     <row r="255">
-      <c r="A255" s="16"/>
+      <c r="A255" s="17"/>
     </row>
     <row r="256">
-      <c r="A256" s="16"/>
+      <c r="A256" s="17"/>
     </row>
     <row r="257">
-      <c r="A257" s="16"/>
+      <c r="A257" s="17"/>
     </row>
     <row r="258">
-      <c r="A258" s="16"/>
+      <c r="A258" s="17"/>
     </row>
     <row r="259">
-      <c r="A259" s="16"/>
+      <c r="A259" s="17"/>
     </row>
     <row r="260">
-      <c r="A260" s="16"/>
+      <c r="A260" s="17"/>
     </row>
     <row r="261">
-      <c r="A261" s="16"/>
+      <c r="A261" s="17"/>
     </row>
     <row r="262">
-      <c r="A262" s="16"/>
+      <c r="A262" s="17"/>
     </row>
     <row r="263">
-      <c r="A263" s="16"/>
+      <c r="A263" s="17"/>
     </row>
     <row r="264">
-      <c r="A264" s="16"/>
+      <c r="A264" s="17"/>
     </row>
     <row r="265">
-      <c r="A265" s="16"/>
+      <c r="A265" s="17"/>
     </row>
     <row r="266">
-      <c r="A266" s="16"/>
+      <c r="A266" s="17"/>
     </row>
     <row r="267">
-      <c r="A267" s="16"/>
+      <c r="A267" s="17"/>
     </row>
     <row r="268">
-      <c r="A268" s="16"/>
+      <c r="A268" s="17"/>
     </row>
     <row r="269">
-      <c r="A269" s="16"/>
+      <c r="A269" s="17"/>
     </row>
     <row r="270">
-      <c r="A270" s="16"/>
+      <c r="A270" s="17"/>
     </row>
     <row r="271">
-      <c r="A271" s="16"/>
+      <c r="A271" s="17"/>
     </row>
     <row r="272">
-      <c r="A272" s="16"/>
+      <c r="A272" s="17"/>
     </row>
     <row r="273">
-      <c r="A273" s="16"/>
+      <c r="A273" s="17"/>
     </row>
     <row r="274">
-      <c r="A274" s="16"/>
+      <c r="A274" s="17"/>
     </row>
     <row r="275">
-      <c r="A275" s="16"/>
+      <c r="A275" s="17"/>
     </row>
     <row r="276">
-      <c r="A276" s="16"/>
+      <c r="A276" s="17"/>
     </row>
     <row r="277">
-      <c r="A277" s="16"/>
+      <c r="A277" s="17"/>
     </row>
     <row r="278">
-      <c r="A278" s="16"/>
+      <c r="A278" s="17"/>
     </row>
     <row r="279">
-      <c r="A279" s="16"/>
+      <c r="A279" s="17"/>
     </row>
     <row r="280">
-      <c r="A280" s="16"/>
+      <c r="A280" s="17"/>
     </row>
     <row r="281">
-      <c r="A281" s="16"/>
+      <c r="A281" s="17"/>
     </row>
     <row r="282">
-      <c r="A282" s="16"/>
+      <c r="A282" s="17"/>
     </row>
     <row r="283">
-      <c r="A283" s="16"/>
+      <c r="A283" s="17"/>
     </row>
     <row r="284">
-      <c r="A284" s="16"/>
+      <c r="A284" s="17"/>
     </row>
     <row r="285">
-      <c r="A285" s="16"/>
+      <c r="A285" s="17"/>
     </row>
     <row r="286">
-      <c r="A286" s="16"/>
+      <c r="A286" s="17"/>
     </row>
     <row r="287">
-      <c r="A287" s="16"/>
+      <c r="A287" s="17"/>
     </row>
     <row r="288">
-      <c r="A288" s="16"/>
+      <c r="A288" s="17"/>
     </row>
     <row r="289">
-      <c r="A289" s="16"/>
+      <c r="A289" s="17"/>
     </row>
     <row r="290">
-      <c r="A290" s="16"/>
+      <c r="A290" s="17"/>
     </row>
     <row r="291">
-      <c r="A291" s="16"/>
+      <c r="A291" s="17"/>
     </row>
     <row r="292">
-      <c r="A292" s="16"/>
+      <c r="A292" s="17"/>
     </row>
     <row r="293">
-      <c r="A293" s="16"/>
+      <c r="A293" s="17"/>
     </row>
     <row r="294">
-      <c r="A294" s="16"/>
+      <c r="A294" s="17"/>
     </row>
     <row r="295">
-      <c r="A295" s="16"/>
+      <c r="A295" s="17"/>
     </row>
     <row r="296">
-      <c r="A296" s="16"/>
+      <c r="A296" s="17"/>
     </row>
     <row r="297">
-      <c r="A297" s="16"/>
+      <c r="A297" s="17"/>
     </row>
     <row r="298">
-      <c r="A298" s="16"/>
+      <c r="A298" s="17"/>
     </row>
     <row r="299">
-      <c r="A299" s="16"/>
+      <c r="A299" s="17"/>
     </row>
     <row r="300">
-      <c r="A300" s="16"/>
+      <c r="A300" s="17"/>
     </row>
     <row r="301">
-      <c r="A301" s="16"/>
+      <c r="A301" s="17"/>
     </row>
     <row r="302">
-      <c r="A302" s="16"/>
+      <c r="A302" s="17"/>
     </row>
     <row r="303">
-      <c r="A303" s="16"/>
+      <c r="A303" s="17"/>
     </row>
     <row r="304">
-      <c r="A304" s="16"/>
+      <c r="A304" s="17"/>
     </row>
     <row r="305">
-      <c r="A305" s="16"/>
+      <c r="A305" s="17"/>
     </row>
     <row r="306">
-      <c r="A306" s="16"/>
+      <c r="A306" s="17"/>
     </row>
     <row r="307">
-      <c r="A307" s="16"/>
+      <c r="A307" s="17"/>
     </row>
     <row r="308">
-      <c r="A308" s="16"/>
+      <c r="A308" s="17"/>
     </row>
     <row r="309">
-      <c r="A309" s="16"/>
+      <c r="A309" s="17"/>
     </row>
     <row r="310">
-      <c r="A310" s="16"/>
+      <c r="A310" s="17"/>
     </row>
     <row r="311">
-      <c r="A311" s="16"/>
+      <c r="A311" s="17"/>
     </row>
     <row r="312">
-      <c r="A312" s="16"/>
+      <c r="A312" s="17"/>
     </row>
     <row r="313">
-      <c r="A313" s="16"/>
+      <c r="A313" s="17"/>
     </row>
     <row r="314">
-      <c r="A314" s="16"/>
+      <c r="A314" s="17"/>
     </row>
     <row r="315">
-      <c r="A315" s="16"/>
+      <c r="A315" s="17"/>
     </row>
     <row r="316">
-      <c r="A316" s="16"/>
+      <c r="A316" s="17"/>
     </row>
     <row r="317">
-      <c r="A317" s="16"/>
+      <c r="A317" s="17"/>
     </row>
     <row r="318">
-      <c r="A318" s="16"/>
+      <c r="A318" s="17"/>
     </row>
     <row r="319">
-      <c r="A319" s="16"/>
+      <c r="A319" s="17"/>
     </row>
     <row r="320">
-      <c r="A320" s="16"/>
+      <c r="A320" s="17"/>
     </row>
     <row r="321">
-      <c r="A321" s="16"/>
+      <c r="A321" s="17"/>
     </row>
     <row r="322">
-      <c r="A322" s="16"/>
+      <c r="A322" s="17"/>
     </row>
     <row r="323">
-      <c r="A323" s="16"/>
+      <c r="A323" s="17"/>
     </row>
     <row r="324">
-      <c r="A324" s="16"/>
+      <c r="A324" s="17"/>
     </row>
     <row r="325">
-      <c r="A325" s="16"/>
+      <c r="A325" s="17"/>
     </row>
     <row r="326">
-      <c r="A326" s="16"/>
+      <c r="A326" s="17"/>
     </row>
     <row r="327">
-      <c r="A327" s="16"/>
+      <c r="A327" s="17"/>
     </row>
     <row r="328">
-      <c r="A328" s="16"/>
+      <c r="A328" s="17"/>
     </row>
     <row r="329">
-      <c r="A329" s="16"/>
+      <c r="A329" s="17"/>
     </row>
     <row r="330">
-      <c r="A330" s="16"/>
+      <c r="A330" s="17"/>
     </row>
     <row r="331">
-      <c r="A331" s="16"/>
+      <c r="A331" s="17"/>
     </row>
     <row r="332">
-      <c r="A332" s="16"/>
+      <c r="A332" s="17"/>
     </row>
     <row r="333">
-      <c r="A333" s="16"/>
+      <c r="A333" s="17"/>
     </row>
     <row r="334">
-      <c r="A334" s="16"/>
+      <c r="A334" s="17"/>
     </row>
     <row r="335">
-      <c r="A335" s="16"/>
+      <c r="A335" s="17"/>
     </row>
     <row r="336">
-      <c r="A336" s="16"/>
+      <c r="A336" s="17"/>
     </row>
     <row r="337">
-      <c r="A337" s="16"/>
+      <c r="A337" s="17"/>
     </row>
     <row r="338">
-      <c r="A338" s="16"/>
+      <c r="A338" s="17"/>
     </row>
     <row r="339">
-      <c r="A339" s="16"/>
+      <c r="A339" s="17"/>
     </row>
     <row r="340">
-      <c r="A340" s="16"/>
+      <c r="A340" s="17"/>
     </row>
     <row r="341">
-      <c r="A341" s="16"/>
+      <c r="A341" s="17"/>
     </row>
     <row r="342">
-      <c r="A342" s="16"/>
+      <c r="A342" s="17"/>
     </row>
     <row r="343">
-      <c r="A343" s="16"/>
+      <c r="A343" s="17"/>
     </row>
     <row r="344">
-      <c r="A344" s="16"/>
+      <c r="A344" s="17"/>
     </row>
     <row r="345">
-      <c r="A345" s="16"/>
+      <c r="A345" s="17"/>
     </row>
     <row r="346">
-      <c r="A346" s="16"/>
+      <c r="A346" s="17"/>
     </row>
     <row r="347">
-      <c r="A347" s="16"/>
+      <c r="A347" s="17"/>
     </row>
     <row r="348">
-      <c r="A348" s="16"/>
+      <c r="A348" s="17"/>
     </row>
     <row r="349">
-      <c r="A349" s="16"/>
+      <c r="A349" s="17"/>
     </row>
     <row r="350">
-      <c r="A350" s="16"/>
+      <c r="A350" s="17"/>
     </row>
     <row r="351">
-      <c r="A351" s="16"/>
+      <c r="A351" s="17"/>
     </row>
     <row r="352">
-      <c r="A352" s="16"/>
+      <c r="A352" s="17"/>
     </row>
     <row r="353">
-      <c r="A353" s="16"/>
+      <c r="A353" s="17"/>
     </row>
     <row r="354">
-      <c r="A354" s="16"/>
+      <c r="A354" s="17"/>
     </row>
     <row r="355">
-      <c r="A355" s="16"/>
+      <c r="A355" s="17"/>
     </row>
     <row r="356">
-      <c r="A356" s="16"/>
+      <c r="A356" s="17"/>
     </row>
     <row r="357">
-      <c r="A357" s="16"/>
+      <c r="A357" s="17"/>
     </row>
     <row r="358">
-      <c r="A358" s="16"/>
+      <c r="A358" s="17"/>
     </row>
     <row r="359">
-      <c r="A359" s="16"/>
+      <c r="A359" s="17"/>
     </row>
     <row r="360">
-      <c r="A360" s="16"/>
+      <c r="A360" s="17"/>
     </row>
     <row r="361">
-      <c r="A361" s="16"/>
+      <c r="A361" s="17"/>
     </row>
     <row r="362">
-      <c r="A362" s="16"/>
+      <c r="A362" s="17"/>
     </row>
     <row r="363">
-      <c r="A363" s="16"/>
+      <c r="A363" s="17"/>
     </row>
     <row r="364">
-      <c r="A364" s="16"/>
+      <c r="A364" s="17"/>
     </row>
     <row r="365">
-      <c r="A365" s="16"/>
+      <c r="A365" s="17"/>
     </row>
     <row r="366">
-      <c r="A366" s="16"/>
+      <c r="A366" s="17"/>
     </row>
     <row r="367">
-      <c r="A367" s="16"/>
+      <c r="A367" s="17"/>
     </row>
     <row r="368">
-      <c r="A368" s="16"/>
+      <c r="A368" s="17"/>
     </row>
     <row r="369">
-      <c r="A369" s="16"/>
+      <c r="A369" s="17"/>
     </row>
     <row r="370">
-      <c r="A370" s="16"/>
+      <c r="A370" s="17"/>
     </row>
     <row r="371">
-      <c r="A371" s="16"/>
+      <c r="A371" s="17"/>
     </row>
     <row r="372">
-      <c r="A372" s="16"/>
+      <c r="A372" s="17"/>
     </row>
     <row r="373">
-      <c r="A373" s="16"/>
+      <c r="A373" s="17"/>
     </row>
     <row r="374">
-      <c r="A374" s="16"/>
+      <c r="A374" s="17"/>
     </row>
     <row r="375">
-      <c r="A375" s="16"/>
+      <c r="A375" s="17"/>
     </row>
     <row r="376">
-      <c r="A376" s="16"/>
+      <c r="A376" s="17"/>
     </row>
     <row r="377">
-      <c r="A377" s="16"/>
+      <c r="A377" s="17"/>
     </row>
     <row r="378">
-      <c r="A378" s="16"/>
+      <c r="A378" s="17"/>
     </row>
     <row r="379">
-      <c r="A379" s="16"/>
+      <c r="A379" s="17"/>
     </row>
     <row r="380">
-      <c r="A380" s="16"/>
+      <c r="A380" s="17"/>
     </row>
     <row r="381">
-      <c r="A381" s="16"/>
+      <c r="A381" s="17"/>
     </row>
     <row r="382">
-      <c r="A382" s="16"/>
+      <c r="A382" s="17"/>
     </row>
     <row r="383">
-      <c r="A383" s="16"/>
+      <c r="A383" s="17"/>
     </row>
     <row r="384">
-      <c r="A384" s="16"/>
+      <c r="A384" s="17"/>
     </row>
     <row r="385">
-      <c r="A385" s="16"/>
+      <c r="A385" s="17"/>
     </row>
     <row r="386">
-      <c r="A386" s="16"/>
+      <c r="A386" s="17"/>
     </row>
     <row r="387">
-      <c r="A387" s="16"/>
+      <c r="A387" s="17"/>
     </row>
     <row r="388">
-      <c r="A388" s="16"/>
+      <c r="A388" s="17"/>
     </row>
     <row r="389">
-      <c r="A389" s="16"/>
+      <c r="A389" s="17"/>
     </row>
     <row r="390">
-      <c r="A390" s="16"/>
+      <c r="A390" s="17"/>
     </row>
     <row r="391">
-      <c r="A391" s="16"/>
+      <c r="A391" s="17"/>
     </row>
     <row r="392">
-      <c r="A392" s="16"/>
+      <c r="A392" s="17"/>
     </row>
     <row r="393">
-      <c r="A393" s="16"/>
+      <c r="A393" s="17"/>
     </row>
     <row r="394">
-      <c r="A394" s="16"/>
+      <c r="A394" s="17"/>
     </row>
     <row r="395">
-      <c r="A395" s="16"/>
+      <c r="A395" s="17"/>
     </row>
     <row r="396">
-      <c r="A396" s="16"/>
+      <c r="A396" s="17"/>
     </row>
     <row r="397">
-      <c r="A397" s="16"/>
+      <c r="A397" s="17"/>
     </row>
     <row r="398">
-      <c r="A398" s="16"/>
+      <c r="A398" s="17"/>
     </row>
     <row r="399">
-      <c r="A399" s="16"/>
+      <c r="A399" s="17"/>
     </row>
     <row r="400">
-      <c r="A400" s="16"/>
+      <c r="A400" s="17"/>
     </row>
     <row r="401">
-      <c r="A401" s="16"/>
+      <c r="A401" s="17"/>
     </row>
     <row r="402">
-      <c r="A402" s="16"/>
+      <c r="A402" s="17"/>
     </row>
     <row r="403">
-      <c r="A403" s="16"/>
+      <c r="A403" s="17"/>
     </row>
     <row r="404">
-      <c r="A404" s="16"/>
+      <c r="A404" s="17"/>
     </row>
     <row r="405">
-      <c r="A405" s="16"/>
+      <c r="A405" s="17"/>
     </row>
     <row r="406">
-      <c r="A406" s="16"/>
+      <c r="A406" s="17"/>
     </row>
     <row r="407">
-      <c r="A407" s="16"/>
+      <c r="A407" s="17"/>
     </row>
     <row r="408">
-      <c r="A408" s="16"/>
+      <c r="A408" s="17"/>
     </row>
     <row r="409">
-      <c r="A409" s="16"/>
+      <c r="A409" s="17"/>
     </row>
     <row r="410">
-      <c r="A410" s="16"/>
+      <c r="A410" s="17"/>
     </row>
     <row r="411">
-      <c r="A411" s="16"/>
+      <c r="A411" s="17"/>
     </row>
     <row r="412">
-      <c r="A412" s="16"/>
+      <c r="A412" s="17"/>
     </row>
     <row r="413">
-      <c r="A413" s="16"/>
+      <c r="A413" s="17"/>
     </row>
     <row r="414">
-      <c r="A414" s="16"/>
+      <c r="A414" s="17"/>
     </row>
     <row r="415">
-      <c r="A415" s="16"/>
+      <c r="A415" s="17"/>
     </row>
     <row r="416">
-      <c r="A416" s="16"/>
+      <c r="A416" s="17"/>
     </row>
     <row r="417">
-      <c r="A417" s="16"/>
+      <c r="A417" s="17"/>
     </row>
     <row r="418">
-      <c r="A418" s="16"/>
+      <c r="A418" s="17"/>
     </row>
     <row r="419">
-      <c r="A419" s="16"/>
+      <c r="A419" s="17"/>
     </row>
     <row r="420">
-      <c r="A420" s="16"/>
+      <c r="A420" s="17"/>
     </row>
     <row r="421">
-      <c r="A421" s="16"/>
+      <c r="A421" s="17"/>
     </row>
     <row r="422">
-      <c r="A422" s="16"/>
+      <c r="A422" s="17"/>
     </row>
     <row r="423">
-      <c r="A423" s="16"/>
+      <c r="A423" s="17"/>
     </row>
     <row r="424">
-      <c r="A424" s="16"/>
+      <c r="A424" s="17"/>
     </row>
     <row r="425">
-      <c r="A425" s="16"/>
+      <c r="A425" s="17"/>
     </row>
     <row r="426">
-      <c r="A426" s="16"/>
+      <c r="A426" s="17"/>
     </row>
     <row r="427">
-      <c r="A427" s="16"/>
+      <c r="A427" s="17"/>
     </row>
     <row r="428">
-      <c r="A428" s="16"/>
+      <c r="A428" s="17"/>
     </row>
     <row r="429">
-      <c r="A429" s="16"/>
+      <c r="A429" s="17"/>
     </row>
     <row r="430">
-      <c r="A430" s="16"/>
+      <c r="A430" s="17"/>
     </row>
     <row r="431">
-      <c r="A431" s="16"/>
+      <c r="A431" s="17"/>
     </row>
     <row r="432">
-      <c r="A432" s="16"/>
+      <c r="A432" s="17"/>
     </row>
     <row r="433">
-      <c r="A433" s="16"/>
+      <c r="A433" s="17"/>
     </row>
     <row r="434">
-      <c r="A434" s="16"/>
+      <c r="A434" s="17"/>
     </row>
     <row r="435">
-      <c r="A435" s="16"/>
+      <c r="A435" s="17"/>
     </row>
     <row r="436">
-      <c r="A436" s="16"/>
+      <c r="A436" s="17"/>
     </row>
     <row r="437">
-      <c r="A437" s="16"/>
+      <c r="A437" s="17"/>
     </row>
     <row r="438">
-      <c r="A438" s="16"/>
+      <c r="A438" s="17"/>
     </row>
     <row r="439">
-      <c r="A439" s="16"/>
+      <c r="A439" s="17"/>
     </row>
     <row r="440">
-      <c r="A440" s="16"/>
+      <c r="A440" s="17"/>
     </row>
     <row r="441">
-      <c r="A441" s="16"/>
+      <c r="A441" s="17"/>
     </row>
     <row r="442">
-      <c r="A442" s="16"/>
+      <c r="A442" s="17"/>
     </row>
     <row r="443">
-      <c r="A443" s="16"/>
+      <c r="A443" s="17"/>
     </row>
     <row r="444">
-      <c r="A444" s="16"/>
+      <c r="A444" s="17"/>
     </row>
     <row r="445">
-      <c r="A445" s="16"/>
+      <c r="A445" s="17"/>
     </row>
     <row r="446">
-      <c r="A446" s="16"/>
+      <c r="A446" s="17"/>
     </row>
     <row r="447">
-      <c r="A447" s="16"/>
+      <c r="A447" s="17"/>
     </row>
     <row r="448">
-      <c r="A448" s="16"/>
+      <c r="A448" s="17"/>
     </row>
     <row r="449">
-      <c r="A449" s="16"/>
+      <c r="A449" s="17"/>
     </row>
     <row r="450">
-      <c r="A450" s="16"/>
+      <c r="A450" s="17"/>
     </row>
     <row r="451">
-      <c r="A451" s="16"/>
+      <c r="A451" s="17"/>
     </row>
     <row r="452">
-      <c r="A452" s="16"/>
+      <c r="A452" s="17"/>
     </row>
     <row r="453">
-      <c r="A453" s="16"/>
+      <c r="A453" s="17"/>
     </row>
     <row r="454">
-      <c r="A454" s="16"/>
+      <c r="A454" s="17"/>
     </row>
     <row r="455">
-      <c r="A455" s="16"/>
+      <c r="A455" s="17"/>
     </row>
     <row r="456">
-      <c r="A456" s="16"/>
+      <c r="A456" s="17"/>
     </row>
     <row r="457">
-      <c r="A457" s="16"/>
+      <c r="A457" s="17"/>
     </row>
     <row r="458">
-      <c r="A458" s="16"/>
+      <c r="A458" s="17"/>
     </row>
     <row r="459">
-      <c r="A459" s="16"/>
+      <c r="A459" s="17"/>
     </row>
     <row r="460">
-      <c r="A460" s="16"/>
+      <c r="A460" s="17"/>
     </row>
     <row r="461">
-      <c r="A461" s="16"/>
+      <c r="A461" s="17"/>
     </row>
     <row r="462">
-      <c r="A462" s="16"/>
+      <c r="A462" s="17"/>
     </row>
     <row r="463">
-      <c r="A463" s="16"/>
+      <c r="A463" s="17"/>
     </row>
     <row r="464">
-      <c r="A464" s="16"/>
+      <c r="A464" s="17"/>
     </row>
     <row r="465">
-      <c r="A465" s="16"/>
+      <c r="A465" s="17"/>
     </row>
     <row r="466">
-      <c r="A466" s="16"/>
+      <c r="A466" s="17"/>
     </row>
     <row r="467">
-      <c r="A467" s="16"/>
+      <c r="A467" s="17"/>
     </row>
     <row r="468">
-      <c r="A468" s="16"/>
+      <c r="A468" s="17"/>
     </row>
     <row r="469">
-      <c r="A469" s="16"/>
+      <c r="A469" s="17"/>
     </row>
     <row r="470">
-      <c r="A470" s="16"/>
+      <c r="A470" s="17"/>
     </row>
     <row r="471">
-      <c r="A471" s="16"/>
+      <c r="A471" s="17"/>
     </row>
     <row r="472">
-      <c r="A472" s="16"/>
+      <c r="A472" s="17"/>
     </row>
     <row r="473">
-      <c r="A473" s="16"/>
+      <c r="A473" s="17"/>
     </row>
     <row r="474">
-      <c r="A474" s="16"/>
+      <c r="A474" s="17"/>
     </row>
     <row r="475">
-      <c r="A475" s="16"/>
+      <c r="A475" s="17"/>
     </row>
     <row r="476">
-      <c r="A476" s="16"/>
+      <c r="A476" s="17"/>
     </row>
     <row r="477">
-      <c r="A477" s="16"/>
+      <c r="A477" s="17"/>
     </row>
     <row r="478">
-      <c r="A478" s="16"/>
+      <c r="A478" s="17"/>
     </row>
     <row r="479">
-      <c r="A479" s="16"/>
+      <c r="A479" s="17"/>
     </row>
     <row r="480">
-      <c r="A480" s="16"/>
+      <c r="A480" s="17"/>
     </row>
     <row r="481">
-      <c r="A481" s="16"/>
+      <c r="A481" s="17"/>
     </row>
     <row r="482">
-      <c r="A482" s="16"/>
+      <c r="A482" s="17"/>
     </row>
     <row r="483">
-      <c r="A483" s="16"/>
+      <c r="A483" s="17"/>
     </row>
     <row r="484">
-      <c r="A484" s="16"/>
+      <c r="A484" s="17"/>
     </row>
     <row r="485">
-      <c r="A485" s="16"/>
+      <c r="A485" s="17"/>
     </row>
     <row r="486">
-      <c r="A486" s="16"/>
+      <c r="A486" s="17"/>
     </row>
     <row r="487">
-      <c r="A487" s="16"/>
+      <c r="A487" s="17"/>
     </row>
     <row r="488">
-      <c r="A488" s="16"/>
+      <c r="A488" s="17"/>
     </row>
     <row r="489">
-      <c r="A489" s="16"/>
+      <c r="A489" s="17"/>
     </row>
     <row r="490">
-      <c r="A490" s="16"/>
+      <c r="A490" s="17"/>
     </row>
     <row r="491">
-      <c r="A491" s="16"/>
+      <c r="A491" s="17"/>
     </row>
     <row r="492">
-      <c r="A492" s="16"/>
+      <c r="A492" s="17"/>
     </row>
     <row r="493">
-      <c r="A493" s="16"/>
+      <c r="A493" s="17"/>
     </row>
     <row r="494">
-      <c r="A494" s="16"/>
+      <c r="A494" s="17"/>
     </row>
     <row r="495">
-      <c r="A495" s="16"/>
+      <c r="A495" s="17"/>
     </row>
     <row r="496">
-      <c r="A496" s="16"/>
+      <c r="A496" s="17"/>
     </row>
     <row r="497">
-      <c r="A497" s="16"/>
+      <c r="A497" s="17"/>
     </row>
     <row r="498">
-      <c r="A498" s="16"/>
+      <c r="A498" s="17"/>
     </row>
     <row r="499">
-      <c r="A499" s="16"/>
+      <c r="A499" s="17"/>
     </row>
     <row r="500">
-      <c r="A500" s="16"/>
+      <c r="A500" s="17"/>
     </row>
     <row r="501">
-      <c r="A501" s="16"/>
+      <c r="A501" s="17"/>
     </row>
     <row r="502">
-      <c r="A502" s="16"/>
+      <c r="A502" s="17"/>
     </row>
     <row r="503">
-      <c r="A503" s="16"/>
+      <c r="A503" s="17"/>
     </row>
     <row r="504">
-      <c r="A504" s="16"/>
+      <c r="A504" s="17"/>
     </row>
     <row r="505">
-      <c r="A505" s="16"/>
+      <c r="A505" s="17"/>
     </row>
     <row r="506">
-      <c r="A506" s="16"/>
+      <c r="A506" s="17"/>
     </row>
     <row r="507">
-      <c r="A507" s="16"/>
+      <c r="A507" s="17"/>
     </row>
     <row r="508">
-      <c r="A508" s="16"/>
+      <c r="A508" s="17"/>
     </row>
     <row r="509">
-      <c r="A509" s="16"/>
+      <c r="A509" s="17"/>
     </row>
     <row r="510">
-      <c r="A510" s="16"/>
+      <c r="A510" s="17"/>
     </row>
     <row r="511">
-      <c r="A511" s="16"/>
+      <c r="A511" s="17"/>
     </row>
     <row r="512">
-      <c r="A512" s="16"/>
+      <c r="A512" s="17"/>
     </row>
     <row r="513">
-      <c r="A513" s="16"/>
+      <c r="A513" s="17"/>
     </row>
     <row r="514">
-      <c r="A514" s="16"/>
+      <c r="A514" s="17"/>
     </row>
     <row r="515">
-      <c r="A515" s="16"/>
+      <c r="A515" s="17"/>
     </row>
     <row r="516">
-      <c r="A516" s="16"/>
+      <c r="A516" s="17"/>
     </row>
     <row r="517">
-      <c r="A517" s="16"/>
+      <c r="A517" s="17"/>
     </row>
     <row r="518">
-      <c r="A518" s="16"/>
+      <c r="A518" s="17"/>
     </row>
     <row r="519">
-      <c r="A519" s="16"/>
+      <c r="A519" s="17"/>
     </row>
     <row r="520">
-      <c r="A520" s="16"/>
+      <c r="A520" s="17"/>
     </row>
     <row r="521">
-      <c r="A521" s="16"/>
+      <c r="A521" s="17"/>
     </row>
     <row r="522">
-      <c r="A522" s="16"/>
+      <c r="A522" s="17"/>
     </row>
     <row r="523">
-      <c r="A523" s="16"/>
+      <c r="A523" s="17"/>
     </row>
     <row r="524">
-      <c r="A524" s="16"/>
+      <c r="A524" s="17"/>
     </row>
     <row r="525">
-      <c r="A525" s="16"/>
+      <c r="A525" s="17"/>
     </row>
     <row r="526">
-      <c r="A526" s="16"/>
+      <c r="A526" s="17"/>
     </row>
     <row r="527">
-      <c r="A527" s="16"/>
+      <c r="A527" s="17"/>
     </row>
     <row r="528">
-      <c r="A528" s="16"/>
+      <c r="A528" s="17"/>
     </row>
     <row r="529">
-      <c r="A529" s="16"/>
+      <c r="A529" s="17"/>
     </row>
     <row r="530">
-      <c r="A530" s="16"/>
+      <c r="A530" s="17"/>
     </row>
     <row r="531">
-      <c r="A531" s="16"/>
+      <c r="A531" s="17"/>
     </row>
     <row r="532">
-      <c r="A532" s="16"/>
+      <c r="A532" s="17"/>
     </row>
     <row r="533">
-      <c r="A533" s="16"/>
+      <c r="A533" s="17"/>
     </row>
     <row r="534">
-      <c r="A534" s="16"/>
+      <c r="A534" s="17"/>
     </row>
     <row r="535">
-      <c r="A535" s="16"/>
+      <c r="A535" s="17"/>
     </row>
     <row r="536">
-      <c r="A536" s="16"/>
+      <c r="A536" s="17"/>
     </row>
     <row r="537">
-      <c r="A537" s="16"/>
+      <c r="A537" s="17"/>
     </row>
     <row r="538">
-      <c r="A538" s="16"/>
+      <c r="A538" s="17"/>
     </row>
     <row r="539">
-      <c r="A539" s="16"/>
+      <c r="A539" s="17"/>
     </row>
     <row r="540">
-      <c r="A540" s="16"/>
+      <c r="A540" s="17"/>
     </row>
     <row r="541">
-      <c r="A541" s="16"/>
+      <c r="A541" s="17"/>
     </row>
     <row r="542">
-      <c r="A542" s="16"/>
+      <c r="A542" s="17"/>
     </row>
     <row r="543">
-      <c r="A543" s="16"/>
+      <c r="A543" s="17"/>
     </row>
     <row r="544">
-      <c r="A544" s="16"/>
+      <c r="A544" s="17"/>
     </row>
     <row r="545">
-      <c r="A545" s="16"/>
+      <c r="A545" s="17"/>
     </row>
     <row r="546">
-      <c r="A546" s="16"/>
+      <c r="A546" s="17"/>
     </row>
     <row r="547">
-      <c r="A547" s="16"/>
+      <c r="A547" s="17"/>
     </row>
     <row r="548">
-      <c r="A548" s="16"/>
+      <c r="A548" s="17"/>
     </row>
     <row r="549">
-      <c r="A549" s="16"/>
+      <c r="A549" s="17"/>
     </row>
     <row r="550">
-      <c r="A550" s="16"/>
+      <c r="A550" s="17"/>
     </row>
     <row r="551">
-      <c r="A551" s="16"/>
+      <c r="A551" s="17"/>
     </row>
     <row r="552">
-      <c r="A552" s="16"/>
+      <c r="A552" s="17"/>
     </row>
     <row r="553">
-      <c r="A553" s="16"/>
+      <c r="A553" s="17"/>
     </row>
     <row r="554">
-      <c r="A554" s="16"/>
+      <c r="A554" s="17"/>
     </row>
     <row r="555">
-      <c r="A555" s="16"/>
+      <c r="A555" s="17"/>
     </row>
     <row r="556">
-      <c r="A556" s="16"/>
+      <c r="A556" s="17"/>
     </row>
     <row r="557">
-      <c r="A557" s="16"/>
+      <c r="A557" s="17"/>
     </row>
     <row r="558">
-      <c r="A558" s="16"/>
+      <c r="A558" s="17"/>
     </row>
     <row r="559">
-      <c r="A559" s="16"/>
+      <c r="A559" s="17"/>
     </row>
     <row r="560">
-      <c r="A560" s="16"/>
+      <c r="A560" s="17"/>
     </row>
     <row r="561">
-      <c r="A561" s="16"/>
+      <c r="A561" s="17"/>
     </row>
     <row r="562">
-      <c r="A562" s="16"/>
+      <c r="A562" s="17"/>
     </row>
     <row r="563">
-      <c r="A563" s="16"/>
+      <c r="A563" s="17"/>
     </row>
     <row r="564">
-      <c r="A564" s="16"/>
+      <c r="A564" s="17"/>
     </row>
     <row r="565">
-      <c r="A565" s="16"/>
+      <c r="A565" s="17"/>
     </row>
     <row r="566">
-      <c r="A566" s="16"/>
+      <c r="A566" s="17"/>
     </row>
     <row r="567">
-      <c r="A567" s="16"/>
+      <c r="A567" s="17"/>
     </row>
     <row r="568">
-      <c r="A568" s="16"/>
+      <c r="A568" s="17"/>
     </row>
     <row r="569">
-      <c r="A569" s="16"/>
+      <c r="A569" s="17"/>
     </row>
     <row r="570">
-      <c r="A570" s="16"/>
+      <c r="A570" s="17"/>
     </row>
     <row r="571">
-      <c r="A571" s="16"/>
+      <c r="A571" s="17"/>
     </row>
     <row r="572">
-      <c r="A572" s="16"/>
+      <c r="A572" s="17"/>
     </row>
     <row r="573">
-      <c r="A573" s="16"/>
+      <c r="A573" s="17"/>
     </row>
     <row r="574">
-      <c r="A574" s="16"/>
+      <c r="A574" s="17"/>
     </row>
     <row r="575">
-      <c r="A575" s="16"/>
+      <c r="A575" s="17"/>
     </row>
     <row r="576">
-      <c r="A576" s="16"/>
+      <c r="A576" s="17"/>
     </row>
     <row r="577">
-      <c r="A577" s="16"/>
+      <c r="A577" s="17"/>
     </row>
     <row r="578">
-      <c r="A578" s="16"/>
+      <c r="A578" s="17"/>
     </row>
     <row r="579">
-      <c r="A579" s="16"/>
+      <c r="A579" s="17"/>
     </row>
     <row r="580">
-      <c r="A580" s="16"/>
+      <c r="A580" s="17"/>
     </row>
     <row r="581">
-      <c r="A581" s="16"/>
+      <c r="A581" s="17"/>
     </row>
     <row r="582">
-      <c r="A582" s="16"/>
+      <c r="A582" s="17"/>
     </row>
     <row r="583">
-      <c r="A583" s="16"/>
+      <c r="A583" s="17"/>
     </row>
     <row r="584">
-      <c r="A584" s="16"/>
+      <c r="A584" s="17"/>
     </row>
     <row r="585">
-      <c r="A585" s="16"/>
+      <c r="A585" s="17"/>
     </row>
     <row r="586">
-      <c r="A586" s="16"/>
+      <c r="A586" s="17"/>
     </row>
     <row r="587">
-      <c r="A587" s="16"/>
+      <c r="A587" s="17"/>
     </row>
     <row r="588">
-      <c r="A588" s="16"/>
+      <c r="A588" s="17"/>
     </row>
     <row r="589">
-      <c r="A589" s="16"/>
+      <c r="A589" s="17"/>
     </row>
     <row r="590">
-      <c r="A590" s="16"/>
+      <c r="A590" s="17"/>
     </row>
     <row r="591">
-      <c r="A591" s="16"/>
+      <c r="A591" s="17"/>
     </row>
     <row r="592">
-      <c r="A592" s="16"/>
+      <c r="A592" s="17"/>
     </row>
     <row r="593">
-      <c r="A593" s="16"/>
+      <c r="A593" s="17"/>
     </row>
     <row r="594">
-      <c r="A594" s="16"/>
+      <c r="A594" s="17"/>
     </row>
     <row r="595">
-      <c r="A595" s="16"/>
+      <c r="A595" s="17"/>
     </row>
     <row r="596">
-      <c r="A596" s="16"/>
+      <c r="A596" s="17"/>
     </row>
     <row r="597">
-      <c r="A597" s="16"/>
+      <c r="A597" s="17"/>
     </row>
     <row r="598">
-      <c r="A598" s="16"/>
+      <c r="A598" s="17"/>
     </row>
     <row r="599">
-      <c r="A599" s="16"/>
+      <c r="A599" s="17"/>
     </row>
     <row r="600">
-      <c r="A600" s="16"/>
+      <c r="A600" s="17"/>
     </row>
     <row r="601">
-      <c r="A601" s="16"/>
+      <c r="A601" s="17"/>
     </row>
     <row r="602">
-      <c r="A602" s="16"/>
+      <c r="A602" s="17"/>
     </row>
     <row r="603">
-      <c r="A603" s="16"/>
+      <c r="A603" s="17"/>
     </row>
     <row r="604">
-      <c r="A604" s="16"/>
+      <c r="A604" s="17"/>
     </row>
     <row r="605">
-      <c r="A605" s="16"/>
+      <c r="A605" s="17"/>
     </row>
     <row r="606">
-      <c r="A606" s="16"/>
+      <c r="A606" s="17"/>
     </row>
     <row r="607">
-      <c r="A607" s="16"/>
+      <c r="A607" s="17"/>
     </row>
     <row r="608">
-      <c r="A608" s="16"/>
+      <c r="A608" s="17"/>
     </row>
     <row r="609">
-      <c r="A609" s="16"/>
+      <c r="A609" s="17"/>
     </row>
     <row r="610">
-      <c r="A610" s="16"/>
+      <c r="A610" s="17"/>
     </row>
     <row r="611">
-      <c r="A611" s="16"/>
+      <c r="A611" s="17"/>
     </row>
     <row r="612">
-      <c r="A612" s="16"/>
+      <c r="A612" s="17"/>
     </row>
     <row r="613">
-      <c r="A613" s="16"/>
+      <c r="A613" s="17"/>
     </row>
     <row r="614">
-      <c r="A614" s="16"/>
+      <c r="A614" s="17"/>
     </row>
     <row r="615">
-      <c r="A615" s="16"/>
+      <c r="A615" s="17"/>
     </row>
     <row r="616">
-      <c r="A616" s="16"/>
+      <c r="A616" s="17"/>
     </row>
     <row r="617">
-      <c r="A617" s="16"/>
+      <c r="A617" s="17"/>
     </row>
     <row r="618">
-      <c r="A618" s="16"/>
+      <c r="A618" s="17"/>
     </row>
     <row r="619">
-      <c r="A619" s="16"/>
+      <c r="A619" s="17"/>
     </row>
     <row r="620">
-      <c r="A620" s="16"/>
+      <c r="A620" s="17"/>
     </row>
     <row r="621">
-      <c r="A621" s="16"/>
+      <c r="A621" s="17"/>
     </row>
     <row r="622">
-      <c r="A622" s="16"/>
+      <c r="A622" s="17"/>
     </row>
     <row r="623">
-      <c r="A623" s="16"/>
+      <c r="A623" s="17"/>
     </row>
     <row r="624">
-      <c r="A624" s="16"/>
+      <c r="A624" s="17"/>
     </row>
     <row r="625">
-      <c r="A625" s="16"/>
+      <c r="A625" s="17"/>
     </row>
     <row r="626">
-      <c r="A626" s="16"/>
+      <c r="A626" s="17"/>
     </row>
     <row r="627">
-      <c r="A627" s="16"/>
+      <c r="A627" s="17"/>
     </row>
     <row r="628">
-      <c r="A628" s="16"/>
+      <c r="A628" s="17"/>
     </row>
     <row r="629">
-      <c r="A629" s="16"/>
+      <c r="A629" s="17"/>
     </row>
     <row r="630">
-      <c r="A630" s="16"/>
+      <c r="A630" s="17"/>
     </row>
     <row r="631">
-      <c r="A631" s="16"/>
+      <c r="A631" s="17"/>
     </row>
     <row r="632">
-      <c r="A632" s="16"/>
+      <c r="A632" s="17"/>
     </row>
     <row r="633">
-      <c r="A633" s="16"/>
+      <c r="A633" s="17"/>
     </row>
     <row r="634">
-      <c r="A634" s="16"/>
+      <c r="A634" s="17"/>
     </row>
     <row r="635">
-      <c r="A635" s="16"/>
+      <c r="A635" s="17"/>
     </row>
     <row r="636">
-      <c r="A636" s="16"/>
+      <c r="A636" s="17"/>
     </row>
     <row r="637">
-      <c r="A637" s="16"/>
+      <c r="A637" s="17"/>
     </row>
     <row r="638">
-      <c r="A638" s="16"/>
+      <c r="A638" s="17"/>
     </row>
     <row r="639">
-      <c r="A639" s="16"/>
+      <c r="A639" s="17"/>
     </row>
     <row r="640">
-      <c r="A640" s="16"/>
+      <c r="A640" s="17"/>
     </row>
     <row r="641">
-      <c r="A641" s="16"/>
+      <c r="A641" s="17"/>
     </row>
     <row r="642">
-      <c r="A642" s="16"/>
+      <c r="A642" s="17"/>
     </row>
     <row r="643">
-      <c r="A643" s="16"/>
+      <c r="A643" s="17"/>
     </row>
     <row r="644">
-      <c r="A644" s="16"/>
+      <c r="A644" s="17"/>
     </row>
     <row r="645">
-      <c r="A645" s="16"/>
+      <c r="A645" s="17"/>
     </row>
     <row r="646">
-      <c r="A646" s="16"/>
+      <c r="A646" s="17"/>
     </row>
     <row r="647">
-      <c r="A647" s="16"/>
+      <c r="A647" s="17"/>
     </row>
     <row r="648">
-      <c r="A648" s="16"/>
+      <c r="A648" s="17"/>
     </row>
     <row r="649">
-      <c r="A649" s="16"/>
+      <c r="A649" s="17"/>
     </row>
     <row r="650">
-      <c r="A650" s="16"/>
+      <c r="A650" s="17"/>
     </row>
     <row r="651">
-      <c r="A651" s="16"/>
+      <c r="A651" s="17"/>
     </row>
     <row r="652">
-      <c r="A652" s="16"/>
+      <c r="A652" s="17"/>
     </row>
     <row r="653">
-      <c r="A653" s="16"/>
+      <c r="A653" s="17"/>
     </row>
     <row r="654">
-      <c r="A654" s="16"/>
+      <c r="A654" s="17"/>
     </row>
     <row r="655">
-      <c r="A655" s="16"/>
+      <c r="A655" s="17"/>
     </row>
     <row r="656">
-      <c r="A656" s="16"/>
+      <c r="A656" s="17"/>
     </row>
     <row r="657">
-      <c r="A657" s="16"/>
+      <c r="A657" s="17"/>
     </row>
     <row r="658">
-      <c r="A658" s="16"/>
+      <c r="A658" s="17"/>
     </row>
     <row r="659">
-      <c r="A659" s="16"/>
+      <c r="A659" s="17"/>
     </row>
     <row r="660">
-      <c r="A660" s="16"/>
+      <c r="A660" s="17"/>
     </row>
     <row r="661">
-      <c r="A661" s="16"/>
+      <c r="A661" s="17"/>
     </row>
     <row r="662">
-      <c r="A662" s="16"/>
+      <c r="A662" s="17"/>
     </row>
     <row r="663">
-      <c r="A663" s="16"/>
+      <c r="A663" s="17"/>
     </row>
     <row r="664">
-      <c r="A664" s="16"/>
+      <c r="A664" s="17"/>
     </row>
     <row r="665">
-      <c r="A665" s="16"/>
+      <c r="A665" s="17"/>
     </row>
     <row r="666">
-      <c r="A666" s="16"/>
+      <c r="A666" s="17"/>
     </row>
     <row r="667">
-      <c r="A667" s="16"/>
+      <c r="A667" s="17"/>
     </row>
     <row r="668">
-      <c r="A668" s="16"/>
+      <c r="A668" s="17"/>
     </row>
     <row r="669">
-      <c r="A669" s="16"/>
+      <c r="A669" s="17"/>
     </row>
     <row r="670">
-      <c r="A670" s="16"/>
+      <c r="A670" s="17"/>
     </row>
     <row r="671">
-      <c r="A671" s="16"/>
+      <c r="A671" s="17"/>
     </row>
     <row r="672">
-      <c r="A672" s="16"/>
+      <c r="A672" s="17"/>
     </row>
     <row r="673">
-      <c r="A673" s="16"/>
+      <c r="A673" s="17"/>
     </row>
     <row r="674">
-      <c r="A674" s="16"/>
+      <c r="A674" s="17"/>
     </row>
     <row r="675">
-      <c r="A675" s="16"/>
+      <c r="A675" s="17"/>
     </row>
     <row r="676">
-      <c r="A676" s="16"/>
+      <c r="A676" s="17"/>
     </row>
     <row r="677">
-      <c r="A677" s="16"/>
+      <c r="A677" s="17"/>
     </row>
     <row r="678">
-      <c r="A678" s="16"/>
+      <c r="A678" s="17"/>
     </row>
     <row r="679">
-      <c r="A679" s="16"/>
+      <c r="A679" s="17"/>
     </row>
     <row r="680">
-      <c r="A680" s="16"/>
+      <c r="A680" s="17"/>
     </row>
     <row r="681">
-      <c r="A681" s="16"/>
+      <c r="A681" s="17"/>
     </row>
     <row r="682">
-      <c r="A682" s="16"/>
+      <c r="A682" s="17"/>
     </row>
     <row r="683">
-      <c r="A683" s="16"/>
+      <c r="A683" s="17"/>
     </row>
     <row r="684">
-      <c r="A684" s="16"/>
+      <c r="A684" s="17"/>
     </row>
     <row r="685">
-      <c r="A685" s="16"/>
+      <c r="A685" s="17"/>
     </row>
     <row r="686">
-      <c r="A686" s="16"/>
+      <c r="A686" s="17"/>
     </row>
     <row r="687">
-      <c r="A687" s="16"/>
+      <c r="A687" s="17"/>
     </row>
     <row r="688">
-      <c r="A688" s="16"/>
+      <c r="A688" s="17"/>
     </row>
     <row r="689">
-      <c r="A689" s="16"/>
+      <c r="A689" s="17"/>
     </row>
     <row r="690">
-      <c r="A690" s="16"/>
+      <c r="A690" s="17"/>
     </row>
     <row r="691">
-      <c r="A691" s="16"/>
+      <c r="A691" s="17"/>
     </row>
     <row r="692">
-      <c r="A692" s="16"/>
+      <c r="A692" s="17"/>
     </row>
     <row r="693">
-      <c r="A693" s="16"/>
+      <c r="A693" s="17"/>
     </row>
     <row r="694">
-      <c r="A694" s="16"/>
+      <c r="A694" s="17"/>
     </row>
     <row r="695">
-      <c r="A695" s="16"/>
+      <c r="A695" s="17"/>
     </row>
     <row r="696">
-      <c r="A696" s="16"/>
+      <c r="A696" s="17"/>
     </row>
     <row r="697">
-      <c r="A697" s="16"/>
+      <c r="A697" s="17"/>
     </row>
     <row r="698">
-      <c r="A698" s="16"/>
+      <c r="A698" s="17"/>
     </row>
     <row r="699">
-      <c r="A699" s="16"/>
+      <c r="A699" s="17"/>
     </row>
     <row r="700">
-      <c r="A700" s="16"/>
+      <c r="A700" s="17"/>
     </row>
     <row r="701">
-      <c r="A701" s="16"/>
+      <c r="A701" s="17"/>
     </row>
     <row r="702">
-      <c r="A702" s="16"/>
+      <c r="A702" s="17"/>
     </row>
     <row r="703">
-      <c r="A703" s="16"/>
+      <c r="A703" s="17"/>
     </row>
     <row r="704">
-      <c r="A704" s="16"/>
+      <c r="A704" s="17"/>
     </row>
     <row r="705">
-      <c r="A705" s="16"/>
+      <c r="A705" s="17"/>
     </row>
     <row r="706">
-      <c r="A706" s="16"/>
+      <c r="A706" s="17"/>
     </row>
     <row r="707">
-      <c r="A707" s="16"/>
+      <c r="A707" s="17"/>
     </row>
     <row r="708">
-      <c r="A708" s="16"/>
+      <c r="A708" s="17"/>
     </row>
     <row r="709">
-      <c r="A709" s="16"/>
+      <c r="A709" s="17"/>
     </row>
     <row r="710">
-      <c r="A710" s="16"/>
+      <c r="A710" s="17"/>
     </row>
     <row r="711">
-      <c r="A711" s="16"/>
+      <c r="A711" s="17"/>
     </row>
     <row r="712">
-      <c r="A712" s="16"/>
+      <c r="A712" s="17"/>
     </row>
     <row r="713">
-      <c r="A713" s="16"/>
+      <c r="A713" s="17"/>
     </row>
     <row r="714">
-      <c r="A714" s="16"/>
+      <c r="A714" s="17"/>
     </row>
     <row r="715">
-      <c r="A715" s="16"/>
+      <c r="A715" s="17"/>
     </row>
     <row r="716">
-      <c r="A716" s="16"/>
+      <c r="A716" s="17"/>
     </row>
     <row r="717">
-      <c r="A717" s="16"/>
+      <c r="A717" s="17"/>
     </row>
     <row r="718">
-      <c r="A718" s="16"/>
+      <c r="A718" s="17"/>
     </row>
     <row r="719">
-      <c r="A719" s="16"/>
+      <c r="A719" s="17"/>
     </row>
     <row r="720">
-      <c r="A720" s="16"/>
+      <c r="A720" s="17"/>
     </row>
     <row r="721">
-      <c r="A721" s="16"/>
+      <c r="A721" s="17"/>
     </row>
     <row r="722">
-      <c r="A722" s="16"/>
+      <c r="A722" s="17"/>
     </row>
     <row r="723">
-      <c r="A723" s="16"/>
+      <c r="A723" s="17"/>
     </row>
     <row r="724">
-      <c r="A724" s="16"/>
+      <c r="A724" s="17"/>
     </row>
     <row r="725">
-      <c r="A725" s="16"/>
+      <c r="A725" s="17"/>
     </row>
     <row r="726">
-      <c r="A726" s="16"/>
+      <c r="A726" s="17"/>
     </row>
     <row r="727">
-      <c r="A727" s="16"/>
+      <c r="A727" s="17"/>
     </row>
     <row r="728">
-      <c r="A728" s="16"/>
+      <c r="A728" s="17"/>
     </row>
     <row r="729">
-      <c r="A729" s="16"/>
+      <c r="A729" s="17"/>
     </row>
     <row r="730">
-      <c r="A730" s="16"/>
+      <c r="A730" s="17"/>
     </row>
     <row r="731">
-      <c r="A731" s="16"/>
+      <c r="A731" s="17"/>
     </row>
     <row r="732">
-      <c r="A732" s="16"/>
+      <c r="A732" s="17"/>
     </row>
     <row r="733">
-      <c r="A733" s="16"/>
+      <c r="A733" s="17"/>
     </row>
     <row r="734">
-      <c r="A734" s="16"/>
+      <c r="A734" s="17"/>
     </row>
     <row r="735">
-      <c r="A735" s="16"/>
+      <c r="A735" s="17"/>
     </row>
     <row r="736">
-      <c r="A736" s="16"/>
+      <c r="A736" s="17"/>
     </row>
     <row r="737">
-      <c r="A737" s="16"/>
+      <c r="A737" s="17"/>
     </row>
     <row r="738">
-      <c r="A738" s="16"/>
+      <c r="A738" s="17"/>
     </row>
     <row r="739">
-      <c r="A739" s="16"/>
+      <c r="A739" s="17"/>
     </row>
     <row r="740">
-      <c r="A740" s="16"/>
+      <c r="A740" s="17"/>
     </row>
     <row r="741">
-      <c r="A741" s="16"/>
+      <c r="A741" s="17"/>
     </row>
     <row r="742">
-      <c r="A742" s="16"/>
+      <c r="A742" s="17"/>
     </row>
     <row r="743">
-      <c r="A743" s="16"/>
+      <c r="A743" s="17"/>
     </row>
     <row r="744">
-      <c r="A744" s="16"/>
+      <c r="A744" s="17"/>
     </row>
     <row r="745">
-      <c r="A745" s="16"/>
+      <c r="A745" s="17"/>
     </row>
     <row r="746">
-      <c r="A746" s="16"/>
+      <c r="A746" s="17"/>
     </row>
     <row r="747">
-      <c r="A747" s="16"/>
+      <c r="A747" s="17"/>
     </row>
     <row r="748">
-      <c r="A748" s="16"/>
+      <c r="A748" s="17"/>
     </row>
     <row r="749">
-      <c r="A749" s="16"/>
+      <c r="A749" s="17"/>
     </row>
     <row r="750">
-      <c r="A750" s="16"/>
+      <c r="A750" s="17"/>
     </row>
     <row r="751">
-      <c r="A751" s="16"/>
+      <c r="A751" s="17"/>
     </row>
     <row r="752">
-      <c r="A752" s="16"/>
+      <c r="A752" s="17"/>
     </row>
     <row r="753">
-      <c r="A753" s="16"/>
+      <c r="A753" s="17"/>
     </row>
     <row r="754">
-      <c r="A754" s="16"/>
+      <c r="A754" s="17"/>
     </row>
     <row r="755">
-      <c r="A755" s="16"/>
+      <c r="A755" s="17"/>
     </row>
     <row r="756">
-      <c r="A756" s="16"/>
+      <c r="A756" s="17"/>
     </row>
     <row r="757">
-      <c r="A757" s="16"/>
+      <c r="A757" s="17"/>
     </row>
     <row r="758">
-      <c r="A758" s="16"/>
+      <c r="A758" s="17"/>
     </row>
     <row r="759">
-      <c r="A759" s="16"/>
+      <c r="A759" s="17"/>
     </row>
     <row r="760">
-      <c r="A760" s="16"/>
+      <c r="A760" s="17"/>
     </row>
     <row r="761">
-      <c r="A761" s="16"/>
+      <c r="A761" s="17"/>
     </row>
     <row r="762">
-      <c r="A762" s="16"/>
+      <c r="A762" s="17"/>
     </row>
     <row r="763">
-      <c r="A763" s="16"/>
+      <c r="A763" s="17"/>
     </row>
     <row r="764">
-      <c r="A764" s="16"/>
+      <c r="A764" s="17"/>
     </row>
     <row r="765">
-      <c r="A765" s="16"/>
+      <c r="A765" s="17"/>
     </row>
     <row r="766">
-      <c r="A766" s="16"/>
+      <c r="A766" s="17"/>
     </row>
     <row r="767">
-      <c r="A767" s="16"/>
+      <c r="A767" s="17"/>
     </row>
     <row r="768">
-      <c r="A768" s="16"/>
+      <c r="A768" s="17"/>
     </row>
     <row r="769">
-      <c r="A769" s="16"/>
+      <c r="A769" s="17"/>
     </row>
     <row r="770">
-      <c r="A770" s="16"/>
+      <c r="A770" s="17"/>
     </row>
     <row r="771">
-      <c r="A771" s="16"/>
+      <c r="A771" s="17"/>
     </row>
     <row r="772">
-      <c r="A772" s="16"/>
+      <c r="A772" s="17"/>
     </row>
     <row r="773">
-      <c r="A773" s="16"/>
+      <c r="A773" s="17"/>
     </row>
     <row r="774">
-      <c r="A774" s="16"/>
+      <c r="A774" s="17"/>
     </row>
     <row r="775">
-      <c r="A775" s="16"/>
+      <c r="A775" s="17"/>
     </row>
     <row r="776">
-      <c r="A776" s="16"/>
+      <c r="A776" s="17"/>
     </row>
     <row r="777">
-      <c r="A777" s="16"/>
+      <c r="A777" s="17"/>
     </row>
     <row r="778">
-      <c r="A778" s="16"/>
+      <c r="A778" s="17"/>
     </row>
     <row r="779">
-      <c r="A779" s="16"/>
+      <c r="A779" s="17"/>
     </row>
     <row r="780">
-      <c r="A780" s="16"/>
+      <c r="A780" s="17"/>
     </row>
     <row r="781">
-      <c r="A781" s="16"/>
+      <c r="A781" s="17"/>
     </row>
     <row r="782">
-      <c r="A782" s="16"/>
+      <c r="A782" s="17"/>
     </row>
     <row r="783">
-      <c r="A783" s="16"/>
+      <c r="A783" s="17"/>
     </row>
     <row r="784">
-      <c r="A784" s="16"/>
+      <c r="A784" s="17"/>
     </row>
     <row r="785">
-      <c r="A785" s="16"/>
+      <c r="A785" s="17"/>
     </row>
     <row r="786">
-      <c r="A786" s="16"/>
+      <c r="A786" s="17"/>
     </row>
     <row r="787">
-      <c r="A787" s="16"/>
+      <c r="A787" s="17"/>
     </row>
     <row r="788">
-      <c r="A788" s="16"/>
+      <c r="A788" s="17"/>
     </row>
     <row r="789">
-      <c r="A789" s="16"/>
+      <c r="A789" s="17"/>
     </row>
     <row r="790">
-      <c r="A790" s="16"/>
+      <c r="A790" s="17"/>
     </row>
     <row r="791">
-      <c r="A791" s="16"/>
+      <c r="A791" s="17"/>
     </row>
     <row r="792">
-      <c r="A792" s="16"/>
+      <c r="A792" s="17"/>
     </row>
     <row r="793">
-      <c r="A793" s="16"/>
+      <c r="A793" s="17"/>
     </row>
     <row r="794">
-      <c r="A794" s="16"/>
+      <c r="A794" s="17"/>
     </row>
     <row r="795">
-      <c r="A795" s="16"/>
+      <c r="A795" s="17"/>
     </row>
     <row r="796">
-      <c r="A796" s="16"/>
+      <c r="A796" s="17"/>
     </row>
     <row r="797">
-      <c r="A797" s="16"/>
+      <c r="A797" s="17"/>
     </row>
     <row r="798">
-      <c r="A798" s="16"/>
+      <c r="A798" s="17"/>
     </row>
     <row r="799">
-      <c r="A799" s="16"/>
+      <c r="A799" s="17"/>
     </row>
     <row r="800">
-      <c r="A800" s="16"/>
+      <c r="A800" s="17"/>
     </row>
     <row r="801">
-      <c r="A801" s="16"/>
+      <c r="A801" s="17"/>
     </row>
     <row r="802">
-      <c r="A802" s="16"/>
+      <c r="A802" s="17"/>
     </row>
     <row r="803">
-      <c r="A803" s="16"/>
+      <c r="A803" s="17"/>
     </row>
     <row r="804">
-      <c r="A804" s="16"/>
+      <c r="A804" s="17"/>
     </row>
     <row r="805">
-      <c r="A805" s="16"/>
+      <c r="A805" s="17"/>
     </row>
     <row r="806">
-      <c r="A806" s="16"/>
+      <c r="A806" s="17"/>
     </row>
     <row r="807">
-      <c r="A807" s="16"/>
+      <c r="A807" s="17"/>
     </row>
     <row r="808">
-      <c r="A808" s="16"/>
+      <c r="A808" s="17"/>
     </row>
     <row r="809">
-      <c r="A809" s="16"/>
+      <c r="A809" s="17"/>
     </row>
     <row r="810">
-      <c r="A810" s="16"/>
+      <c r="A810" s="17"/>
     </row>
     <row r="811">
-      <c r="A811" s="16"/>
+      <c r="A811" s="17"/>
     </row>
     <row r="812">
-      <c r="A812" s="16"/>
+      <c r="A812" s="17"/>
     </row>
     <row r="813">
-      <c r="A813" s="16"/>
+      <c r="A813" s="17"/>
     </row>
     <row r="814">
-      <c r="A814" s="16"/>
+      <c r="A814" s="17"/>
     </row>
     <row r="815">
-      <c r="A815" s="16"/>
+      <c r="A815" s="17"/>
     </row>
     <row r="816">
-      <c r="A816" s="16"/>
+      <c r="A816" s="17"/>
     </row>
     <row r="817">
-      <c r="A817" s="16"/>
+      <c r="A817" s="17"/>
     </row>
     <row r="818">
-      <c r="A818" s="16"/>
+      <c r="A818" s="17"/>
     </row>
     <row r="819">
-      <c r="A819" s="16"/>
+      <c r="A819" s="17"/>
     </row>
     <row r="820">
-      <c r="A820" s="16"/>
+      <c r="A820" s="17"/>
     </row>
     <row r="821">
-      <c r="A821" s="16"/>
+      <c r="A821" s="17"/>
     </row>
     <row r="822">
-      <c r="A822" s="16"/>
+      <c r="A822" s="17"/>
     </row>
     <row r="823">
-      <c r="A823" s="16"/>
+      <c r="A823" s="17"/>
     </row>
     <row r="824">
-      <c r="A824" s="16"/>
+      <c r="A824" s="17"/>
     </row>
     <row r="825">
-      <c r="A825" s="16"/>
+      <c r="A825" s="17"/>
     </row>
     <row r="826">
-      <c r="A826" s="16"/>
+      <c r="A826" s="17"/>
     </row>
     <row r="827">
-      <c r="A827" s="16"/>
+      <c r="A827" s="17"/>
     </row>
     <row r="828">
-      <c r="A828" s="16"/>
+      <c r="A828" s="17"/>
     </row>
     <row r="829">
-      <c r="A829" s="16"/>
+      <c r="A829" s="17"/>
     </row>
     <row r="830">
-      <c r="A830" s="16"/>
+      <c r="A830" s="17"/>
     </row>
     <row r="831">
-      <c r="A831" s="16"/>
+      <c r="A831" s="17"/>
     </row>
     <row r="832">
-      <c r="A832" s="16"/>
+      <c r="A832" s="17"/>
     </row>
     <row r="833">
-      <c r="A833" s="16"/>
+      <c r="A833" s="17"/>
     </row>
     <row r="834">
-      <c r="A834" s="16"/>
+      <c r="A834" s="17"/>
     </row>
     <row r="835">
-      <c r="A835" s="16"/>
+      <c r="A835" s="17"/>
     </row>
     <row r="836">
-      <c r="A836" s="16"/>
+      <c r="A836" s="17"/>
     </row>
     <row r="837">
-      <c r="A837" s="16"/>
+      <c r="A837" s="17"/>
     </row>
     <row r="838">
-      <c r="A838" s="16"/>
+      <c r="A838" s="17"/>
     </row>
     <row r="839">
-      <c r="A839" s="16"/>
+      <c r="A839" s="17"/>
     </row>
     <row r="840">
-      <c r="A840" s="16"/>
+      <c r="A840" s="17"/>
     </row>
     <row r="841">
-      <c r="A841" s="16"/>
+      <c r="A841" s="17"/>
     </row>
     <row r="842">
-      <c r="A842" s="16"/>
+      <c r="A842" s="17"/>
     </row>
     <row r="843">
-      <c r="A843" s="16"/>
+      <c r="A843" s="17"/>
     </row>
     <row r="844">
-      <c r="A844" s="16"/>
+      <c r="A844" s="17"/>
     </row>
     <row r="845">
-      <c r="A845" s="16"/>
+      <c r="A845" s="17"/>
     </row>
     <row r="846">
-      <c r="A846" s="16"/>
+      <c r="A846" s="17"/>
     </row>
     <row r="847">
-      <c r="A847" s="16"/>
+      <c r="A847" s="17"/>
     </row>
     <row r="848">
-      <c r="A848" s="16"/>
+      <c r="A848" s="17"/>
     </row>
     <row r="849">
-      <c r="A849" s="16"/>
+      <c r="A849" s="17"/>
     </row>
     <row r="850">
-      <c r="A850" s="16"/>
+      <c r="A850" s="17"/>
     </row>
     <row r="851">
-      <c r="A851" s="16"/>
+      <c r="A851" s="17"/>
     </row>
     <row r="852">
-      <c r="A852" s="16"/>
+      <c r="A852" s="17"/>
     </row>
     <row r="853">
-      <c r="A853" s="16"/>
+      <c r="A853" s="17"/>
     </row>
     <row r="854">
-      <c r="A854" s="16"/>
+      <c r="A854" s="17"/>
     </row>
     <row r="855">
-      <c r="A855" s="16"/>
+      <c r="A855" s="17"/>
     </row>
     <row r="856">
-      <c r="A856" s="16"/>
+      <c r="A856" s="17"/>
     </row>
     <row r="857">
-      <c r="A857" s="16"/>
+      <c r="A857" s="17"/>
     </row>
     <row r="858">
-      <c r="A858" s="16"/>
+      <c r="A858" s="17"/>
     </row>
     <row r="859">
-      <c r="A859" s="16"/>
+      <c r="A859" s="17"/>
     </row>
     <row r="860">
-      <c r="A860" s="16"/>
+      <c r="A860" s="17"/>
     </row>
     <row r="861">
-      <c r="A861" s="16"/>
+      <c r="A861" s="17"/>
     </row>
     <row r="862">
-      <c r="A862" s="16"/>
+      <c r="A862" s="17"/>
     </row>
     <row r="863">
-      <c r="A863" s="16"/>
+      <c r="A863" s="17"/>
     </row>
     <row r="864">
-      <c r="A864" s="16"/>
+      <c r="A864" s="17"/>
     </row>
     <row r="865">
-      <c r="A865" s="16"/>
+      <c r="A865" s="17"/>
     </row>
     <row r="866">
-      <c r="A866" s="16"/>
+      <c r="A866" s="17"/>
     </row>
     <row r="867">
-      <c r="A867" s="16"/>
+      <c r="A867" s="17"/>
     </row>
     <row r="868">
-      <c r="A868" s="16"/>
+      <c r="A868" s="17"/>
     </row>
     <row r="869">
-      <c r="A869" s="16"/>
+      <c r="A869" s="17"/>
     </row>
     <row r="870">
-      <c r="A870" s="16"/>
+      <c r="A870" s="17"/>
     </row>
     <row r="871">
-      <c r="A871" s="16"/>
+      <c r="A871" s="17"/>
     </row>
     <row r="872">
-      <c r="A872" s="16"/>
+      <c r="A872" s="17"/>
     </row>
     <row r="873">
-      <c r="A873" s="16"/>
+      <c r="A873" s="17"/>
     </row>
     <row r="874">
-      <c r="A874" s="16"/>
+      <c r="A874" s="17"/>
     </row>
     <row r="875">
-      <c r="A875" s="16"/>
+      <c r="A875" s="17"/>
     </row>
     <row r="876">
-      <c r="A876" s="16"/>
+      <c r="A876" s="17"/>
     </row>
     <row r="877">
-      <c r="A877" s="16"/>
+      <c r="A877" s="17"/>
     </row>
     <row r="878">
-      <c r="A878" s="16"/>
+      <c r="A878" s="17"/>
     </row>
     <row r="879">
-      <c r="A879" s="16"/>
+      <c r="A879" s="17"/>
     </row>
     <row r="880">
-      <c r="A880" s="16"/>
+      <c r="A880" s="17"/>
     </row>
     <row r="881">
-      <c r="A881" s="16"/>
+      <c r="A881" s="17"/>
     </row>
     <row r="882">
-      <c r="A882" s="16"/>
+      <c r="A882" s="17"/>
     </row>
     <row r="883">
-      <c r="A883" s="16"/>
+      <c r="A883" s="17"/>
     </row>
     <row r="884">
-      <c r="A884" s="16"/>
+      <c r="A884" s="17"/>
     </row>
     <row r="885">
-      <c r="A885" s="16"/>
+      <c r="A885" s="17"/>
     </row>
     <row r="886">
-      <c r="A886" s="16"/>
+      <c r="A886" s="17"/>
     </row>
     <row r="887">
-      <c r="A887" s="16"/>
+      <c r="A887" s="17"/>
     </row>
     <row r="888">
-      <c r="A888" s="16"/>
+      <c r="A888" s="17"/>
     </row>
     <row r="889">
-      <c r="A889" s="16"/>
+      <c r="A889" s="17"/>
     </row>
     <row r="890">
-      <c r="A890" s="16"/>
+      <c r="A890" s="17"/>
     </row>
     <row r="891">
-      <c r="A891" s="16"/>
+      <c r="A891" s="17"/>
     </row>
     <row r="892">
-      <c r="A892" s="16"/>
+      <c r="A892" s="17"/>
     </row>
     <row r="893">
-      <c r="A893" s="16"/>
+      <c r="A893" s="17"/>
     </row>
     <row r="894">
-      <c r="A894" s="16"/>
+      <c r="A894" s="17"/>
     </row>
     <row r="895">
-      <c r="A895" s="16"/>
+      <c r="A895" s="17"/>
     </row>
     <row r="896">
-      <c r="A896" s="16"/>
+      <c r="A896" s="17"/>
     </row>
     <row r="897">
-      <c r="A897" s="16"/>
+      <c r="A897" s="17"/>
     </row>
     <row r="898">
-      <c r="A898" s="16"/>
+      <c r="A898" s="17"/>
     </row>
     <row r="899">
-      <c r="A899" s="16"/>
+      <c r="A899" s="17"/>
     </row>
     <row r="900">
-      <c r="A900" s="16"/>
+      <c r="A900" s="17"/>
     </row>
     <row r="901">
-      <c r="A901" s="16"/>
+      <c r="A901" s="17"/>
     </row>
     <row r="902">
-      <c r="A902" s="16"/>
+      <c r="A902" s="17"/>
     </row>
     <row r="903">
-      <c r="A903" s="16"/>
+      <c r="A903" s="17"/>
     </row>
     <row r="904">
-      <c r="A904" s="16"/>
+      <c r="A904" s="17"/>
     </row>
     <row r="905">
-      <c r="A905" s="16"/>
+      <c r="A905" s="17"/>
     </row>
     <row r="906">
-      <c r="A906" s="16"/>
+      <c r="A906" s="17"/>
     </row>
     <row r="907">
-      <c r="A907" s="16"/>
+      <c r="A907" s="17"/>
     </row>
     <row r="908">
-      <c r="A908" s="16"/>
+      <c r="A908" s="17"/>
     </row>
     <row r="909">
-      <c r="A909" s="16"/>
+      <c r="A909" s="17"/>
     </row>
     <row r="910">
-      <c r="A910" s="16"/>
+      <c r="A910" s="17"/>
     </row>
     <row r="911">
-      <c r="A911" s="16"/>
+      <c r="A911" s="17"/>
     </row>
     <row r="912">
-      <c r="A912" s="16"/>
+      <c r="A912" s="17"/>
     </row>
     <row r="913">
-      <c r="A913" s="16"/>
+      <c r="A913" s="17"/>
     </row>
     <row r="914">
-      <c r="A914" s="16"/>
+      <c r="A914" s="17"/>
     </row>
     <row r="915">
-      <c r="A915" s="16"/>
+      <c r="A915" s="17"/>
     </row>
     <row r="916">
-      <c r="A916" s="16"/>
+      <c r="A916" s="17"/>
     </row>
     <row r="917">
-      <c r="A917" s="16"/>
+      <c r="A917" s="17"/>
     </row>
     <row r="918">
-      <c r="A918" s="16"/>
+      <c r="A918" s="17"/>
     </row>
     <row r="919">
-      <c r="A919" s="16"/>
+      <c r="A919" s="17"/>
     </row>
     <row r="920">
-      <c r="A920" s="16"/>
+      <c r="A920" s="17"/>
     </row>
     <row r="921">
-      <c r="A921" s="16"/>
+      <c r="A921" s="17"/>
     </row>
     <row r="922">
-      <c r="A922" s="16"/>
+      <c r="A922" s="17"/>
     </row>
     <row r="923">
-      <c r="A923" s="16"/>
+      <c r="A923" s="17"/>
     </row>
     <row r="924">
-      <c r="A924" s="16"/>
+      <c r="A924" s="17"/>
     </row>
     <row r="925">
-      <c r="A925" s="16"/>
+      <c r="A925" s="17"/>
     </row>
     <row r="926">
-      <c r="A926" s="16"/>
+      <c r="A926" s="17"/>
     </row>
     <row r="927">
-      <c r="A927" s="16"/>
+      <c r="A927" s="17"/>
     </row>
     <row r="928">
-      <c r="A928" s="16"/>
+      <c r="A928" s="17"/>
     </row>
     <row r="929">
-      <c r="A929" s="16"/>
+      <c r="A929" s="17"/>
     </row>
     <row r="930">
-      <c r="A930" s="16"/>
+      <c r="A930" s="17"/>
     </row>
     <row r="931">
-      <c r="A931" s="16"/>
+      <c r="A931" s="17"/>
     </row>
     <row r="932">
-      <c r="A932" s="16"/>
+      <c r="A932" s="17"/>
     </row>
     <row r="933">
-      <c r="A933" s="16"/>
+      <c r="A933" s="17"/>
     </row>
     <row r="934">
-      <c r="A934" s="16"/>
+      <c r="A934" s="17"/>
     </row>
     <row r="935">
-      <c r="A935" s="16"/>
+      <c r="A935" s="17"/>
     </row>
     <row r="936">
-      <c r="A936" s="16"/>
+      <c r="A936" s="17"/>
     </row>
     <row r="937">
-      <c r="A937" s="16"/>
+      <c r="A937" s="17"/>
     </row>
     <row r="938">
-      <c r="A938" s="16"/>
+      <c r="A938" s="17"/>
     </row>
     <row r="939">
-      <c r="A939" s="16"/>
+      <c r="A939" s="17"/>
     </row>
     <row r="940">
-      <c r="A940" s="16"/>
+      <c r="A940" s="17"/>
     </row>
     <row r="941">
-      <c r="A941" s="16"/>
+      <c r="A941" s="17"/>
     </row>
     <row r="942">
-      <c r="A942" s="16"/>
+      <c r="A942" s="17"/>
     </row>
     <row r="943">
-      <c r="A943" s="16"/>
+      <c r="A943" s="17"/>
     </row>
     <row r="944">
-      <c r="A944" s="16"/>
+      <c r="A944" s="17"/>
     </row>
     <row r="945">
-      <c r="A945" s="16"/>
+      <c r="A945" s="17"/>
     </row>
     <row r="946">
-      <c r="A946" s="16"/>
+      <c r="A946" s="17"/>
     </row>
     <row r="947">
-      <c r="A947" s="16"/>
+      <c r="A947" s="17"/>
     </row>
     <row r="948">
-      <c r="A948" s="16"/>
+      <c r="A948" s="17"/>
     </row>
     <row r="949">
-      <c r="A949" s="16"/>
+      <c r="A949" s="17"/>
     </row>
     <row r="950">
-      <c r="A950" s="16"/>
+      <c r="A950" s="17"/>
     </row>
     <row r="951">
-      <c r="A951" s="16"/>
+      <c r="A951" s="17"/>
     </row>
     <row r="952">
-      <c r="A952" s="16"/>
+      <c r="A952" s="17"/>
     </row>
     <row r="953">
-      <c r="A953" s="16"/>
+      <c r="A953" s="17"/>
     </row>
     <row r="954">
-      <c r="A954" s="16"/>
+      <c r="A954" s="17"/>
     </row>
     <row r="955">
-      <c r="A955" s="16"/>
+      <c r="A955" s="17"/>
     </row>
     <row r="956">
-      <c r="A956" s="16"/>
+      <c r="A956" s="17"/>
     </row>
     <row r="957">
-      <c r="A957" s="16"/>
+      <c r="A957" s="17"/>
     </row>
     <row r="958">
-      <c r="A958" s="16"/>
+      <c r="A958" s="17"/>
     </row>
     <row r="959">
-      <c r="A959" s="16"/>
+      <c r="A959" s="17"/>
     </row>
     <row r="960">
-      <c r="A960" s="16"/>
+      <c r="A960" s="17"/>
     </row>
     <row r="961">
-      <c r="A961" s="16"/>
+      <c r="A961" s="17"/>
     </row>
     <row r="962">
-      <c r="A962" s="16"/>
+      <c r="A962" s="17"/>
     </row>
     <row r="963">
-      <c r="A963" s="16"/>
+      <c r="A963" s="17"/>
     </row>
     <row r="964">
-      <c r="A964" s="16"/>
+      <c r="A964" s="17"/>
     </row>
     <row r="965">
-      <c r="A965" s="16"/>
+      <c r="A965" s="17"/>
     </row>
     <row r="966">
-      <c r="A966" s="16"/>
+      <c r="A966" s="17"/>
     </row>
     <row r="967">
-      <c r="A967" s="16"/>
+      <c r="A967" s="17"/>
     </row>
     <row r="968">
-      <c r="A968" s="16"/>
+      <c r="A968" s="17"/>
     </row>
     <row r="969">
-      <c r="A969" s="16"/>
+      <c r="A969" s="17"/>
     </row>
     <row r="970">
-      <c r="A970" s="16"/>
+      <c r="A970" s="17"/>
     </row>
     <row r="971">
-      <c r="A971" s="16"/>
+      <c r="A971" s="17"/>
     </row>
     <row r="972">
-      <c r="A972" s="16"/>
+      <c r="A972" s="17"/>
     </row>
     <row r="973">
-      <c r="A973" s="16"/>
+      <c r="A973" s="17"/>
     </row>
     <row r="974">
-      <c r="A974" s="16"/>
+      <c r="A974" s="17"/>
     </row>
     <row r="975">
-      <c r="A975" s="16"/>
+      <c r="A975" s="17"/>
     </row>
     <row r="976">
-      <c r="A976" s="16"/>
+      <c r="A976" s="17"/>
     </row>
     <row r="977">
-      <c r="A977" s="16"/>
+      <c r="A977" s="17"/>
     </row>
     <row r="978">
-      <c r="A978" s="16"/>
+      <c r="A978" s="17"/>
     </row>
     <row r="979">
-      <c r="A979" s="16"/>
+      <c r="A979" s="17"/>
     </row>
     <row r="980">
-      <c r="A980" s="16"/>
+      <c r="A980" s="17"/>
     </row>
     <row r="981">
-      <c r="A981" s="16"/>
+      <c r="A981" s="17"/>
     </row>
     <row r="982">
-      <c r="A982" s="16"/>
+      <c r="A982" s="17"/>
     </row>
     <row r="983">
-      <c r="A983" s="16"/>
+      <c r="A983" s="17"/>
     </row>
     <row r="984">
-      <c r="A984" s="16"/>
+      <c r="A984" s="17"/>
     </row>
     <row r="985">
-      <c r="A985" s="16"/>
+      <c r="A985" s="17"/>
     </row>
     <row r="986">
-      <c r="A986" s="16"/>
+      <c r="A986" s="17"/>
     </row>
     <row r="987">
-      <c r="A987" s="16"/>
+      <c r="A987" s="17"/>
     </row>
     <row r="988">
-      <c r="A988" s="16"/>
+      <c r="A988" s="17"/>
     </row>
     <row r="989">
-      <c r="A989" s="16"/>
+      <c r="A989" s="17"/>
     </row>
     <row r="990">
-      <c r="A990" s="16"/>
+      <c r="A990" s="17"/>
     </row>
     <row r="991">
-      <c r="A991" s="16"/>
+      <c r="A991" s="17"/>
     </row>
     <row r="992">
-      <c r="A992" s="16"/>
+      <c r="A992" s="17"/>
     </row>
     <row r="993">
-      <c r="A993" s="16"/>
+      <c r="A993" s="17"/>
     </row>
     <row r="994">
-      <c r="A994" s="16"/>
+      <c r="A994" s="17"/>
     </row>
     <row r="995">
-      <c r="A995" s="16"/>
+      <c r="A995" s="17"/>
     </row>
     <row r="996">
-      <c r="A996" s="16"/>
+      <c r="A996" s="17"/>
     </row>
     <row r="997">
-      <c r="A997" s="16"/>
+      <c r="A997" s="17"/>
     </row>
     <row r="998">
-      <c r="A998" s="16"/>
+      <c r="A998" s="17"/>
     </row>
     <row r="999">
-      <c r="A999" s="16"/>
+      <c r="A999" s="17"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="16"/>
+      <c r="A1000" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4345,23 +5031,23 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -4369,16 +5055,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -4389,16 +5075,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -4409,16 +5095,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -4429,16 +5115,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -4449,18 +5135,58 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
   <si>
     <t>NpcID</t>
   </si>
@@ -63,6 +63,9 @@
     <t>N008</t>
   </si>
   <si>
+    <t>NpcEventID</t>
+  </si>
+  <si>
     <t>LogID</t>
   </si>
   <si>
@@ -106,6 +109,24 @@
   </si>
   <si>
     <t>C002</t>
+  </si>
+  <si>
+    <t>N001_0</t>
+  </si>
+  <si>
+    <t>그래...맞아. 엄마가 사주셨던 곰인형이었어.</t>
+  </si>
+  <si>
+    <t>낡아서 헤질 때마다 바느질하곤 했지. 소중했으니까.</t>
+  </si>
+  <si>
+    <t>N001_1</t>
+  </si>
+  <si>
+    <t>윽!</t>
+  </si>
+  <si>
+    <t>나 뭔가 잘못 선택한 걸까...?</t>
   </si>
   <si>
     <t>뭐지... 방금 이 꽃이 날 쳐다본 거 같은데</t>
@@ -342,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -351,6 +372,9 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -455,7 +479,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:I52" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D12:J56" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -754,7 +778,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="44.25"/>
+    <col customWidth="1" min="4" max="4" width="44.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,4256 +788,4532 @@
       <c r="B1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
         <v>1001.0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1">
         <v>1002.0</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
         <v>1002.0</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1">
         <v>1003.0</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
         <v>1003.0</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
         <v>-1.0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="1">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2001.0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2002.0</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1004.0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1005.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="1">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2002.0</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="1">
-        <v>2003.0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
+      <c r="C6" s="1">
+        <v>1005.0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-1.0</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="1">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2003.0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-1.0</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
+      <c r="A7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1006.0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1007.0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5">
-        <v>3001.0</v>
-      </c>
-      <c r="C8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="7">
-        <v>3002.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="C8" s="1">
+        <v>1007.0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-1.0</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="9">
-        <v>0.0</v>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5">
-        <v>3002.0</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="11">
-        <v>3003.0</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2001.0</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="13">
+      <c r="E9" s="1">
+        <v>2002.0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>3003.0</v>
-      </c>
-      <c r="C10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2002.0</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="7">
-        <v>3004.0</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="1">
+        <v>2003.0</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="9">
-        <v>4.0</v>
+      <c r="I10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2003.0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-1.0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3001.0</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3002.0</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3002.0</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="12">
+        <v>3003.0</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="14">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3003.0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="8">
         <v>3004.0</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="F14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="10">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3004.0</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="12">
         <v>3005.0</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="F15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="13">
+      <c r="H15" s="11"/>
+      <c r="I15" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="14">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+    <row r="16">
+      <c r="A16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6">
         <v>3005.0</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="D16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="8">
         <v>3006.0</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="9">
+      <c r="G16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="10">
         <v>0.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="17">
+      <c r="A17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="6">
         <v>3006.0</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="D17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="12">
         <v>3007.0</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
+      <c r="G17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="13">
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="14">
         <v>0.0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+    <row r="18">
+      <c r="A18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="6">
         <v>3007.0</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3008.0</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="10">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3008.0</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="12">
+        <v>3009.0</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="14">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3009.0</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="7">
-        <v>3008.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="E20" s="8">
+        <v>3010.0</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="9">
+      <c r="H20" s="7"/>
+      <c r="I20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="10">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+    <row r="21">
+      <c r="A21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="5">
-        <v>3008.0</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3010.0</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="12">
+        <v>3011.0</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="14">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3011.0</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3012.0</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="11">
-        <v>3009.0</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="G22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="10">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="6">
+        <v>3012.0</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="12">
+        <v>3013.0</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10" t="s">
+      <c r="G23" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="13">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="H23" s="11"/>
+      <c r="I23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="14">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="5">
-        <v>3009.0</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="7">
-        <v>3010.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3013.0</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3014.0</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16" s="9">
+      <c r="H24" s="7"/>
+      <c r="I24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="10">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+    <row r="25">
+      <c r="A25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="5">
-        <v>3010.0</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3014.0</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="12">
+        <v>3015.0</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="14">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3015.0</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3016.0</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="11">
-        <v>3011.0</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="12" t="s">
+      <c r="J26" s="10">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3016.0</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="12">
+        <v>3017.0</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10" t="s">
+      <c r="G27" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="13">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="H27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="14">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="5">
-        <v>3011.0</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7">
-        <v>3012.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3017.0</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="9">
+      <c r="H28" s="7"/>
+      <c r="I28" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="10">
         <v>-1.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="5">
-        <v>3012.0</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="11">
-        <v>3013.0</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="13">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5">
-        <v>3013.0</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="7">
-        <v>3014.0</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="9">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="5">
-        <v>3014.0</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="11">
-        <v>3015.0</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="5">
-        <v>3015.0</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3016.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="9">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="5">
-        <v>3016.0</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="11">
-        <v>3017.0</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="13">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="5">
-        <v>3017.0</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.0</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" s="9">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="1">
-        <v>4001.0</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="7">
-        <v>4002.0</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" s="7">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="1">
-        <v>4002.0</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-1.0</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="5">
-        <v>5001.0</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="7">
-        <v>5002.0</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="5">
-        <v>5002.0</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="11">
-        <v>5003.0</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="5">
-        <v>5003.0</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="9">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4001.0</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="8">
+        <v>4002.0</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="8">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4002.0</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="8">
         <v>-1.0</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="9">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="1">
-        <v>6001.0</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="7">
-        <v>6002.0</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6" t="s">
+      <c r="G30" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I30" s="7">
+      <c r="H30" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>5001.0</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="8">
+        <v>5002.0</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>5002.0</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="12">
+        <v>5003.0</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="14">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5003.0</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="10">
+        <v>-1.0</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1">
+        <v>6001.0</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="8">
         <v>6002.0</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="F34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1">
+        <v>6002.0</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="8">
         <v>6003.0</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="1">
-        <v>6003.0</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="7">
-        <v>6004.0</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" s="7">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="1">
-        <v>6004.0</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="7">
-        <v>6005.0</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="1">
-        <v>6005.0</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="7">
-        <v>6006.0</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="7">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="1">
-        <v>6006.0</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="7">
-        <v>6007.0</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6" t="s">
+      <c r="G35" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I35" s="7">
+      <c r="H35" s="7"/>
+      <c r="I35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="1">
-        <v>6007.0</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="7">
-        <v>6008.0</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>37</v>
+      <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1">
+        <v>6003.0</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="8">
+        <v>6004.0</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" s="7">
+        <v>44</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="8">
         <v>-1.0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="1">
-        <v>6008.0</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="7">
-        <v>6009.0</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>25</v>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1">
+        <v>6004.0</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="8">
+        <v>6005.0</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6" t="s">
+      <c r="G37" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I37" s="7">
+      <c r="H37" s="7"/>
+      <c r="I37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1">
+        <v>6005.0</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="8">
+        <v>6006.0</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6006.0</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="8">
+        <v>6007.0</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1">
+        <v>6007.0</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="8">
+        <v>6008.0</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1">
+        <v>6008.0</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="8">
         <v>6009.0</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="F41" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="1">
+        <v>6009.0</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="8">
         <v>-1.0</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G38" s="14" t="s">
+      <c r="F42" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="7">
+      <c r="H42" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="8">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="s">
+    <row r="43">
+      <c r="A43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="1">
         <v>7001.0</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="7">
+      <c r="D43" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="8">
         <v>7002.0</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39" s="16"/>
-      <c r="H39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="7">
+      <c r="F43" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="8">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="s">
+    <row r="44">
+      <c r="A44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1">
         <v>7002.0</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="7">
+      <c r="D44" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="8">
         <v>7003.0</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="16"/>
-      <c r="H40" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I40" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="1">
-        <v>7003.0</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D41" s="7">
-        <v>7004.0</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G41" s="16"/>
-      <c r="H41" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I41" s="7">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="1">
-        <v>7004.0</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="7">
-        <v>7005.0</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B43" s="1">
-        <v>7005.0</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D43" s="7">
-        <v>7006.0</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="7">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="1">
-        <v>7006.0</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="7">
-        <v>7007.0</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14" t="s">
+      <c r="G44" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I44" s="7">
+      <c r="H44" s="17"/>
+      <c r="I44" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B45" s="1">
-        <v>7007.0</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="7">
-        <v>7008.0</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>37</v>
+      <c r="B45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="1">
+        <v>7003.0</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="8">
+        <v>7004.0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G45" s="16"/>
-      <c r="H45" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I45" s="7">
+        <v>44</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" s="8">
         <v>-1.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B46" s="1">
-        <v>7008.0</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-1.0</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>25</v>
+      <c r="B46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="1">
+        <v>7004.0</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="8">
+        <v>7005.0</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I46" s="7">
+      <c r="G46" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="1">
-        <v>8001.0</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D47" s="7">
-        <v>8002.0</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>37</v>
+      <c r="A47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="1">
+        <v>7005.0</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="8">
+        <v>7006.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47" s="16"/>
-      <c r="H47" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I47" s="7">
+        <v>44</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="17"/>
+      <c r="I47" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J47" s="8">
         <v>-1.0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="1">
-        <v>8002.0</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="7">
-        <v>8003.0</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>25</v>
+      <c r="A48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="1">
+        <v>7006.0</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="8">
+        <v>7007.0</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G48" s="16"/>
-      <c r="H48" s="7" t="s">
+      <c r="G48" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="7">
+      <c r="H48" s="15"/>
+      <c r="I48" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J48" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="1">
-        <v>8003.0</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="7">
-        <v>8004.0</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>37</v>
+      <c r="A49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="1">
+        <v>7007.0</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="8">
+        <v>7008.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G49" s="16"/>
-      <c r="H49" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I49" s="7">
+        <v>44</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" s="8">
         <v>-1.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="1">
-        <v>8004.0</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="7">
-        <v>8005.0</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>25</v>
+      <c r="A50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="1">
+        <v>7008.0</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.0</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G50" s="16"/>
-      <c r="H50" s="7" t="s">
+      <c r="G50" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="7">
+      <c r="H50" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J50" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="1">
+        <v>8001.0</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="8">
+        <v>8002.0</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="1">
+        <v>8002.0</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="8">
+        <v>8003.0</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="1">
+        <v>8003.0</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="8">
+        <v>8004.0</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="1">
+        <v>8004.0</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="8">
         <v>8005.0</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="F54" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="1">
+        <v>8005.0</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="8">
         <v>8006.0</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G51" s="16"/>
-      <c r="H51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I51" s="7">
+      <c r="F55" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="8">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="s">
+    <row r="56">
+      <c r="A56" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="1">
         <v>8006.0</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="D56" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="8">
         <v>-1.0</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I52" s="7">
+      <c r="F56" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="8">
         <v>-1.0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="17"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="17"/>
-    </row>
     <row r="57">
-      <c r="A57" s="17"/>
+      <c r="A57" s="18"/>
     </row>
     <row r="58">
-      <c r="A58" s="17"/>
+      <c r="A58" s="18"/>
     </row>
     <row r="59">
-      <c r="A59" s="17"/>
+      <c r="A59" s="18"/>
     </row>
     <row r="60">
-      <c r="A60" s="17"/>
+      <c r="A60" s="18"/>
     </row>
     <row r="61">
-      <c r="A61" s="17"/>
+      <c r="A61" s="18"/>
     </row>
     <row r="62">
-      <c r="A62" s="17"/>
+      <c r="A62" s="18"/>
     </row>
     <row r="63">
-      <c r="A63" s="17"/>
+      <c r="A63" s="18"/>
     </row>
     <row r="64">
-      <c r="A64" s="17"/>
+      <c r="A64" s="18"/>
     </row>
     <row r="65">
-      <c r="A65" s="17"/>
+      <c r="A65" s="18"/>
     </row>
     <row r="66">
-      <c r="A66" s="17"/>
+      <c r="A66" s="18"/>
     </row>
     <row r="67">
-      <c r="A67" s="17"/>
+      <c r="A67" s="18"/>
     </row>
     <row r="68">
-      <c r="A68" s="17"/>
+      <c r="A68" s="18"/>
     </row>
     <row r="69">
-      <c r="A69" s="17"/>
+      <c r="A69" s="18"/>
     </row>
     <row r="70">
-      <c r="A70" s="17"/>
+      <c r="A70" s="18"/>
     </row>
     <row r="71">
-      <c r="A71" s="17"/>
+      <c r="A71" s="18"/>
     </row>
     <row r="72">
-      <c r="A72" s="17"/>
+      <c r="A72" s="18"/>
     </row>
     <row r="73">
-      <c r="A73" s="17"/>
+      <c r="A73" s="18"/>
     </row>
     <row r="74">
-      <c r="A74" s="17"/>
+      <c r="A74" s="18"/>
     </row>
     <row r="75">
-      <c r="A75" s="17"/>
+      <c r="A75" s="18"/>
     </row>
     <row r="76">
-      <c r="A76" s="17"/>
+      <c r="A76" s="18"/>
     </row>
     <row r="77">
-      <c r="A77" s="17"/>
+      <c r="A77" s="18"/>
     </row>
     <row r="78">
-      <c r="A78" s="17"/>
+      <c r="A78" s="18"/>
     </row>
     <row r="79">
-      <c r="A79" s="17"/>
+      <c r="A79" s="18"/>
     </row>
     <row r="80">
-      <c r="A80" s="17"/>
+      <c r="A80" s="18"/>
     </row>
     <row r="81">
-      <c r="A81" s="17"/>
+      <c r="A81" s="18"/>
     </row>
     <row r="82">
-      <c r="A82" s="17"/>
+      <c r="A82" s="18"/>
     </row>
     <row r="83">
-      <c r="A83" s="17"/>
+      <c r="A83" s="18"/>
     </row>
     <row r="84">
-      <c r="A84" s="17"/>
+      <c r="A84" s="18"/>
     </row>
     <row r="85">
-      <c r="A85" s="17"/>
+      <c r="A85" s="18"/>
     </row>
     <row r="86">
-      <c r="A86" s="17"/>
+      <c r="A86" s="18"/>
     </row>
     <row r="87">
-      <c r="A87" s="17"/>
+      <c r="A87" s="18"/>
     </row>
     <row r="88">
-      <c r="A88" s="17"/>
+      <c r="A88" s="18"/>
     </row>
     <row r="89">
-      <c r="A89" s="17"/>
+      <c r="A89" s="18"/>
     </row>
     <row r="90">
-      <c r="A90" s="17"/>
+      <c r="A90" s="18"/>
     </row>
     <row r="91">
-      <c r="A91" s="17"/>
+      <c r="A91" s="18"/>
     </row>
     <row r="92">
-      <c r="A92" s="17"/>
+      <c r="A92" s="18"/>
     </row>
     <row r="93">
-      <c r="A93" s="17"/>
+      <c r="A93" s="18"/>
     </row>
     <row r="94">
-      <c r="A94" s="17"/>
+      <c r="A94" s="18"/>
     </row>
     <row r="95">
-      <c r="A95" s="17"/>
+      <c r="A95" s="18"/>
     </row>
     <row r="96">
-      <c r="A96" s="17"/>
+      <c r="A96" s="18"/>
     </row>
     <row r="97">
-      <c r="A97" s="17"/>
+      <c r="A97" s="18"/>
     </row>
     <row r="98">
-      <c r="A98" s="17"/>
+      <c r="A98" s="18"/>
     </row>
     <row r="99">
-      <c r="A99" s="17"/>
+      <c r="A99" s="18"/>
     </row>
     <row r="100">
-      <c r="A100" s="17"/>
+      <c r="A100" s="18"/>
     </row>
     <row r="101">
-      <c r="A101" s="17"/>
+      <c r="A101" s="18"/>
     </row>
     <row r="102">
-      <c r="A102" s="17"/>
+      <c r="A102" s="18"/>
     </row>
     <row r="103">
-      <c r="A103" s="17"/>
+      <c r="A103" s="18"/>
     </row>
     <row r="104">
-      <c r="A104" s="17"/>
+      <c r="A104" s="18"/>
     </row>
     <row r="105">
-      <c r="A105" s="17"/>
+      <c r="A105" s="18"/>
     </row>
     <row r="106">
-      <c r="A106" s="17"/>
+      <c r="A106" s="18"/>
     </row>
     <row r="107">
-      <c r="A107" s="17"/>
+      <c r="A107" s="18"/>
     </row>
     <row r="108">
-      <c r="A108" s="17"/>
+      <c r="A108" s="18"/>
     </row>
     <row r="109">
-      <c r="A109" s="17"/>
+      <c r="A109" s="18"/>
     </row>
     <row r="110">
-      <c r="A110" s="17"/>
+      <c r="A110" s="18"/>
     </row>
     <row r="111">
-      <c r="A111" s="17"/>
+      <c r="A111" s="18"/>
     </row>
     <row r="112">
-      <c r="A112" s="17"/>
+      <c r="A112" s="18"/>
     </row>
     <row r="113">
-      <c r="A113" s="17"/>
+      <c r="A113" s="18"/>
     </row>
     <row r="114">
-      <c r="A114" s="17"/>
+      <c r="A114" s="18"/>
     </row>
     <row r="115">
-      <c r="A115" s="17"/>
+      <c r="A115" s="18"/>
     </row>
     <row r="116">
-      <c r="A116" s="17"/>
+      <c r="A116" s="18"/>
     </row>
     <row r="117">
-      <c r="A117" s="17"/>
+      <c r="A117" s="18"/>
     </row>
     <row r="118">
-      <c r="A118" s="17"/>
+      <c r="A118" s="18"/>
     </row>
     <row r="119">
-      <c r="A119" s="17"/>
+      <c r="A119" s="18"/>
     </row>
     <row r="120">
-      <c r="A120" s="17"/>
+      <c r="A120" s="18"/>
     </row>
     <row r="121">
-      <c r="A121" s="17"/>
+      <c r="A121" s="18"/>
     </row>
     <row r="122">
-      <c r="A122" s="17"/>
+      <c r="A122" s="18"/>
     </row>
     <row r="123">
-      <c r="A123" s="17"/>
+      <c r="A123" s="18"/>
     </row>
     <row r="124">
-      <c r="A124" s="17"/>
+      <c r="A124" s="18"/>
     </row>
     <row r="125">
-      <c r="A125" s="17"/>
+      <c r="A125" s="18"/>
     </row>
     <row r="126">
-      <c r="A126" s="17"/>
+      <c r="A126" s="18"/>
     </row>
     <row r="127">
-      <c r="A127" s="17"/>
+      <c r="A127" s="18"/>
     </row>
     <row r="128">
-      <c r="A128" s="17"/>
+      <c r="A128" s="18"/>
     </row>
     <row r="129">
-      <c r="A129" s="17"/>
+      <c r="A129" s="18"/>
     </row>
     <row r="130">
-      <c r="A130" s="17"/>
+      <c r="A130" s="18"/>
     </row>
     <row r="131">
-      <c r="A131" s="17"/>
+      <c r="A131" s="18"/>
     </row>
     <row r="132">
-      <c r="A132" s="17"/>
+      <c r="A132" s="18"/>
     </row>
     <row r="133">
-      <c r="A133" s="17"/>
+      <c r="A133" s="18"/>
     </row>
     <row r="134">
-      <c r="A134" s="17"/>
+      <c r="A134" s="18"/>
     </row>
     <row r="135">
-      <c r="A135" s="17"/>
+      <c r="A135" s="18"/>
     </row>
     <row r="136">
-      <c r="A136" s="17"/>
+      <c r="A136" s="18"/>
     </row>
     <row r="137">
-      <c r="A137" s="17"/>
+      <c r="A137" s="18"/>
     </row>
     <row r="138">
-      <c r="A138" s="17"/>
+      <c r="A138" s="18"/>
     </row>
     <row r="139">
-      <c r="A139" s="17"/>
+      <c r="A139" s="18"/>
     </row>
     <row r="140">
-      <c r="A140" s="17"/>
+      <c r="A140" s="18"/>
     </row>
     <row r="141">
-      <c r="A141" s="17"/>
+      <c r="A141" s="18"/>
     </row>
     <row r="142">
-      <c r="A142" s="17"/>
+      <c r="A142" s="18"/>
     </row>
     <row r="143">
-      <c r="A143" s="17"/>
+      <c r="A143" s="18"/>
     </row>
     <row r="144">
-      <c r="A144" s="17"/>
+      <c r="A144" s="18"/>
     </row>
     <row r="145">
-      <c r="A145" s="17"/>
+      <c r="A145" s="18"/>
     </row>
     <row r="146">
-      <c r="A146" s="17"/>
+      <c r="A146" s="18"/>
     </row>
     <row r="147">
-      <c r="A147" s="17"/>
+      <c r="A147" s="18"/>
     </row>
     <row r="148">
-      <c r="A148" s="17"/>
+      <c r="A148" s="18"/>
     </row>
     <row r="149">
-      <c r="A149" s="17"/>
+      <c r="A149" s="18"/>
     </row>
     <row r="150">
-      <c r="A150" s="17"/>
+      <c r="A150" s="18"/>
     </row>
     <row r="151">
-      <c r="A151" s="17"/>
+      <c r="A151" s="18"/>
     </row>
     <row r="152">
-      <c r="A152" s="17"/>
+      <c r="A152" s="18"/>
     </row>
     <row r="153">
-      <c r="A153" s="17"/>
+      <c r="A153" s="18"/>
     </row>
     <row r="154">
-      <c r="A154" s="17"/>
+      <c r="A154" s="18"/>
     </row>
     <row r="155">
-      <c r="A155" s="17"/>
+      <c r="A155" s="18"/>
     </row>
     <row r="156">
-      <c r="A156" s="17"/>
+      <c r="A156" s="18"/>
     </row>
     <row r="157">
-      <c r="A157" s="17"/>
+      <c r="A157" s="18"/>
     </row>
     <row r="158">
-      <c r="A158" s="17"/>
+      <c r="A158" s="18"/>
     </row>
     <row r="159">
-      <c r="A159" s="17"/>
+      <c r="A159" s="18"/>
     </row>
     <row r="160">
-      <c r="A160" s="17"/>
+      <c r="A160" s="18"/>
     </row>
     <row r="161">
-      <c r="A161" s="17"/>
+      <c r="A161" s="18"/>
     </row>
     <row r="162">
-      <c r="A162" s="17"/>
+      <c r="A162" s="18"/>
     </row>
     <row r="163">
-      <c r="A163" s="17"/>
+      <c r="A163" s="18"/>
     </row>
     <row r="164">
-      <c r="A164" s="17"/>
+      <c r="A164" s="18"/>
     </row>
     <row r="165">
-      <c r="A165" s="17"/>
+      <c r="A165" s="18"/>
     </row>
     <row r="166">
-      <c r="A166" s="17"/>
+      <c r="A166" s="18"/>
     </row>
     <row r="167">
-      <c r="A167" s="17"/>
+      <c r="A167" s="18"/>
     </row>
     <row r="168">
-      <c r="A168" s="17"/>
+      <c r="A168" s="18"/>
     </row>
     <row r="169">
-      <c r="A169" s="17"/>
+      <c r="A169" s="18"/>
     </row>
     <row r="170">
-      <c r="A170" s="17"/>
+      <c r="A170" s="18"/>
     </row>
     <row r="171">
-      <c r="A171" s="17"/>
+      <c r="A171" s="18"/>
     </row>
     <row r="172">
-      <c r="A172" s="17"/>
+      <c r="A172" s="18"/>
     </row>
     <row r="173">
-      <c r="A173" s="17"/>
+      <c r="A173" s="18"/>
     </row>
     <row r="174">
-      <c r="A174" s="17"/>
+      <c r="A174" s="18"/>
     </row>
     <row r="175">
-      <c r="A175" s="17"/>
+      <c r="A175" s="18"/>
     </row>
     <row r="176">
-      <c r="A176" s="17"/>
+      <c r="A176" s="18"/>
     </row>
     <row r="177">
-      <c r="A177" s="17"/>
+      <c r="A177" s="18"/>
     </row>
     <row r="178">
-      <c r="A178" s="17"/>
+      <c r="A178" s="18"/>
     </row>
     <row r="179">
-      <c r="A179" s="17"/>
+      <c r="A179" s="18"/>
     </row>
     <row r="180">
-      <c r="A180" s="17"/>
+      <c r="A180" s="18"/>
     </row>
     <row r="181">
-      <c r="A181" s="17"/>
+      <c r="A181" s="18"/>
     </row>
     <row r="182">
-      <c r="A182" s="17"/>
+      <c r="A182" s="18"/>
     </row>
     <row r="183">
-      <c r="A183" s="17"/>
+      <c r="A183" s="18"/>
     </row>
     <row r="184">
-      <c r="A184" s="17"/>
+      <c r="A184" s="18"/>
     </row>
     <row r="185">
-      <c r="A185" s="17"/>
+      <c r="A185" s="18"/>
     </row>
     <row r="186">
-      <c r="A186" s="17"/>
+      <c r="A186" s="18"/>
     </row>
     <row r="187">
-      <c r="A187" s="17"/>
+      <c r="A187" s="18"/>
     </row>
     <row r="188">
-      <c r="A188" s="17"/>
+      <c r="A188" s="18"/>
     </row>
     <row r="189">
-      <c r="A189" s="17"/>
+      <c r="A189" s="18"/>
     </row>
     <row r="190">
-      <c r="A190" s="17"/>
+      <c r="A190" s="18"/>
     </row>
     <row r="191">
-      <c r="A191" s="17"/>
+      <c r="A191" s="18"/>
     </row>
     <row r="192">
-      <c r="A192" s="17"/>
+      <c r="A192" s="18"/>
     </row>
     <row r="193">
-      <c r="A193" s="17"/>
+      <c r="A193" s="18"/>
     </row>
     <row r="194">
-      <c r="A194" s="17"/>
+      <c r="A194" s="18"/>
     </row>
     <row r="195">
-      <c r="A195" s="17"/>
+      <c r="A195" s="18"/>
     </row>
     <row r="196">
-      <c r="A196" s="17"/>
+      <c r="A196" s="18"/>
     </row>
     <row r="197">
-      <c r="A197" s="17"/>
+      <c r="A197" s="18"/>
     </row>
     <row r="198">
-      <c r="A198" s="17"/>
+      <c r="A198" s="18"/>
     </row>
     <row r="199">
-      <c r="A199" s="17"/>
+      <c r="A199" s="18"/>
     </row>
     <row r="200">
-      <c r="A200" s="17"/>
+      <c r="A200" s="18"/>
     </row>
     <row r="201">
-      <c r="A201" s="17"/>
+      <c r="A201" s="18"/>
     </row>
     <row r="202">
-      <c r="A202" s="17"/>
+      <c r="A202" s="18"/>
     </row>
     <row r="203">
-      <c r="A203" s="17"/>
+      <c r="A203" s="18"/>
     </row>
     <row r="204">
-      <c r="A204" s="17"/>
+      <c r="A204" s="18"/>
     </row>
     <row r="205">
-      <c r="A205" s="17"/>
+      <c r="A205" s="18"/>
     </row>
     <row r="206">
-      <c r="A206" s="17"/>
+      <c r="A206" s="18"/>
     </row>
     <row r="207">
-      <c r="A207" s="17"/>
+      <c r="A207" s="18"/>
     </row>
     <row r="208">
-      <c r="A208" s="17"/>
+      <c r="A208" s="18"/>
     </row>
     <row r="209">
-      <c r="A209" s="17"/>
+      <c r="A209" s="18"/>
     </row>
     <row r="210">
-      <c r="A210" s="17"/>
+      <c r="A210" s="18"/>
     </row>
     <row r="211">
-      <c r="A211" s="17"/>
+      <c r="A211" s="18"/>
     </row>
     <row r="212">
-      <c r="A212" s="17"/>
+      <c r="A212" s="18"/>
     </row>
     <row r="213">
-      <c r="A213" s="17"/>
+      <c r="A213" s="18"/>
     </row>
     <row r="214">
-      <c r="A214" s="17"/>
+      <c r="A214" s="18"/>
     </row>
     <row r="215">
-      <c r="A215" s="17"/>
+      <c r="A215" s="18"/>
     </row>
     <row r="216">
-      <c r="A216" s="17"/>
+      <c r="A216" s="18"/>
     </row>
     <row r="217">
-      <c r="A217" s="17"/>
+      <c r="A217" s="18"/>
     </row>
     <row r="218">
-      <c r="A218" s="17"/>
+      <c r="A218" s="18"/>
     </row>
     <row r="219">
-      <c r="A219" s="17"/>
+      <c r="A219" s="18"/>
     </row>
     <row r="220">
-      <c r="A220" s="17"/>
+      <c r="A220" s="18"/>
     </row>
     <row r="221">
-      <c r="A221" s="17"/>
+      <c r="A221" s="18"/>
     </row>
     <row r="222">
-      <c r="A222" s="17"/>
+      <c r="A222" s="18"/>
     </row>
     <row r="223">
-      <c r="A223" s="17"/>
+      <c r="A223" s="18"/>
     </row>
     <row r="224">
-      <c r="A224" s="17"/>
+      <c r="A224" s="18"/>
     </row>
     <row r="225">
-      <c r="A225" s="17"/>
+      <c r="A225" s="18"/>
     </row>
     <row r="226">
-      <c r="A226" s="17"/>
+      <c r="A226" s="18"/>
     </row>
     <row r="227">
-      <c r="A227" s="17"/>
+      <c r="A227" s="18"/>
     </row>
     <row r="228">
-      <c r="A228" s="17"/>
+      <c r="A228" s="18"/>
     </row>
     <row r="229">
-      <c r="A229" s="17"/>
+      <c r="A229" s="18"/>
     </row>
     <row r="230">
-      <c r="A230" s="17"/>
+      <c r="A230" s="18"/>
     </row>
     <row r="231">
-      <c r="A231" s="17"/>
+      <c r="A231" s="18"/>
     </row>
     <row r="232">
-      <c r="A232" s="17"/>
+      <c r="A232" s="18"/>
     </row>
     <row r="233">
-      <c r="A233" s="17"/>
+      <c r="A233" s="18"/>
     </row>
     <row r="234">
-      <c r="A234" s="17"/>
+      <c r="A234" s="18"/>
     </row>
     <row r="235">
-      <c r="A235" s="17"/>
+      <c r="A235" s="18"/>
     </row>
     <row r="236">
-      <c r="A236" s="17"/>
+      <c r="A236" s="18"/>
     </row>
     <row r="237">
-      <c r="A237" s="17"/>
+      <c r="A237" s="18"/>
     </row>
     <row r="238">
-      <c r="A238" s="17"/>
+      <c r="A238" s="18"/>
     </row>
     <row r="239">
-      <c r="A239" s="17"/>
+      <c r="A239" s="18"/>
     </row>
     <row r="240">
-      <c r="A240" s="17"/>
+      <c r="A240" s="18"/>
     </row>
     <row r="241">
-      <c r="A241" s="17"/>
+      <c r="A241" s="18"/>
     </row>
     <row r="242">
-      <c r="A242" s="17"/>
+      <c r="A242" s="18"/>
     </row>
     <row r="243">
-      <c r="A243" s="17"/>
+      <c r="A243" s="18"/>
     </row>
     <row r="244">
-      <c r="A244" s="17"/>
+      <c r="A244" s="18"/>
     </row>
     <row r="245">
-      <c r="A245" s="17"/>
+      <c r="A245" s="18"/>
     </row>
     <row r="246">
-      <c r="A246" s="17"/>
+      <c r="A246" s="18"/>
     </row>
     <row r="247">
-      <c r="A247" s="17"/>
+      <c r="A247" s="18"/>
     </row>
     <row r="248">
-      <c r="A248" s="17"/>
+      <c r="A248" s="18"/>
     </row>
     <row r="249">
-      <c r="A249" s="17"/>
+      <c r="A249" s="18"/>
     </row>
     <row r="250">
-      <c r="A250" s="17"/>
+      <c r="A250" s="18"/>
     </row>
     <row r="251">
-      <c r="A251" s="17"/>
+      <c r="A251" s="18"/>
     </row>
     <row r="252">
-      <c r="A252" s="17"/>
+      <c r="A252" s="18"/>
     </row>
     <row r="253">
-      <c r="A253" s="17"/>
+      <c r="A253" s="18"/>
     </row>
     <row r="254">
-      <c r="A254" s="17"/>
+      <c r="A254" s="18"/>
     </row>
     <row r="255">
-      <c r="A255" s="17"/>
+      <c r="A255" s="18"/>
     </row>
     <row r="256">
-      <c r="A256" s="17"/>
+      <c r="A256" s="18"/>
     </row>
     <row r="257">
-      <c r="A257" s="17"/>
+      <c r="A257" s="18"/>
     </row>
     <row r="258">
-      <c r="A258" s="17"/>
+      <c r="A258" s="18"/>
     </row>
     <row r="259">
-      <c r="A259" s="17"/>
+      <c r="A259" s="18"/>
     </row>
     <row r="260">
-      <c r="A260" s="17"/>
+      <c r="A260" s="18"/>
     </row>
     <row r="261">
-      <c r="A261" s="17"/>
+      <c r="A261" s="18"/>
     </row>
     <row r="262">
-      <c r="A262" s="17"/>
+      <c r="A262" s="18"/>
     </row>
     <row r="263">
-      <c r="A263" s="17"/>
+      <c r="A263" s="18"/>
     </row>
     <row r="264">
-      <c r="A264" s="17"/>
+      <c r="A264" s="18"/>
     </row>
     <row r="265">
-      <c r="A265" s="17"/>
+      <c r="A265" s="18"/>
     </row>
     <row r="266">
-      <c r="A266" s="17"/>
+      <c r="A266" s="18"/>
     </row>
     <row r="267">
-      <c r="A267" s="17"/>
+      <c r="A267" s="18"/>
     </row>
     <row r="268">
-      <c r="A268" s="17"/>
+      <c r="A268" s="18"/>
     </row>
     <row r="269">
-      <c r="A269" s="17"/>
+      <c r="A269" s="18"/>
     </row>
     <row r="270">
-      <c r="A270" s="17"/>
+      <c r="A270" s="18"/>
     </row>
     <row r="271">
-      <c r="A271" s="17"/>
+      <c r="A271" s="18"/>
     </row>
     <row r="272">
-      <c r="A272" s="17"/>
+      <c r="A272" s="18"/>
     </row>
     <row r="273">
-      <c r="A273" s="17"/>
+      <c r="A273" s="18"/>
     </row>
     <row r="274">
-      <c r="A274" s="17"/>
+      <c r="A274" s="18"/>
     </row>
     <row r="275">
-      <c r="A275" s="17"/>
+      <c r="A275" s="18"/>
     </row>
     <row r="276">
-      <c r="A276" s="17"/>
+      <c r="A276" s="18"/>
     </row>
     <row r="277">
-      <c r="A277" s="17"/>
+      <c r="A277" s="18"/>
     </row>
     <row r="278">
-      <c r="A278" s="17"/>
+      <c r="A278" s="18"/>
     </row>
     <row r="279">
-      <c r="A279" s="17"/>
+      <c r="A279" s="18"/>
     </row>
     <row r="280">
-      <c r="A280" s="17"/>
+      <c r="A280" s="18"/>
     </row>
     <row r="281">
-      <c r="A281" s="17"/>
+      <c r="A281" s="18"/>
     </row>
     <row r="282">
-      <c r="A282" s="17"/>
+      <c r="A282" s="18"/>
     </row>
     <row r="283">
-      <c r="A283" s="17"/>
+      <c r="A283" s="18"/>
     </row>
     <row r="284">
-      <c r="A284" s="17"/>
+      <c r="A284" s="18"/>
     </row>
     <row r="285">
-      <c r="A285" s="17"/>
+      <c r="A285" s="18"/>
     </row>
     <row r="286">
-      <c r="A286" s="17"/>
+      <c r="A286" s="18"/>
     </row>
     <row r="287">
-      <c r="A287" s="17"/>
+      <c r="A287" s="18"/>
     </row>
     <row r="288">
-      <c r="A288" s="17"/>
+      <c r="A288" s="18"/>
     </row>
     <row r="289">
-      <c r="A289" s="17"/>
+      <c r="A289" s="18"/>
     </row>
     <row r="290">
-      <c r="A290" s="17"/>
+      <c r="A290" s="18"/>
     </row>
     <row r="291">
-      <c r="A291" s="17"/>
+      <c r="A291" s="18"/>
     </row>
     <row r="292">
-      <c r="A292" s="17"/>
+      <c r="A292" s="18"/>
     </row>
     <row r="293">
-      <c r="A293" s="17"/>
+      <c r="A293" s="18"/>
     </row>
     <row r="294">
-      <c r="A294" s="17"/>
+      <c r="A294" s="18"/>
     </row>
     <row r="295">
-      <c r="A295" s="17"/>
+      <c r="A295" s="18"/>
     </row>
     <row r="296">
-      <c r="A296" s="17"/>
+      <c r="A296" s="18"/>
     </row>
     <row r="297">
-      <c r="A297" s="17"/>
+      <c r="A297" s="18"/>
     </row>
     <row r="298">
-      <c r="A298" s="17"/>
+      <c r="A298" s="18"/>
     </row>
     <row r="299">
-      <c r="A299" s="17"/>
+      <c r="A299" s="18"/>
     </row>
     <row r="300">
-      <c r="A300" s="17"/>
+      <c r="A300" s="18"/>
     </row>
     <row r="301">
-      <c r="A301" s="17"/>
+      <c r="A301" s="18"/>
     </row>
     <row r="302">
-      <c r="A302" s="17"/>
+      <c r="A302" s="18"/>
     </row>
     <row r="303">
-      <c r="A303" s="17"/>
+      <c r="A303" s="18"/>
     </row>
     <row r="304">
-      <c r="A304" s="17"/>
+      <c r="A304" s="18"/>
     </row>
     <row r="305">
-      <c r="A305" s="17"/>
+      <c r="A305" s="18"/>
     </row>
     <row r="306">
-      <c r="A306" s="17"/>
+      <c r="A306" s="18"/>
     </row>
     <row r="307">
-      <c r="A307" s="17"/>
+      <c r="A307" s="18"/>
     </row>
     <row r="308">
-      <c r="A308" s="17"/>
+      <c r="A308" s="18"/>
     </row>
     <row r="309">
-      <c r="A309" s="17"/>
+      <c r="A309" s="18"/>
     </row>
     <row r="310">
-      <c r="A310" s="17"/>
+      <c r="A310" s="18"/>
     </row>
     <row r="311">
-      <c r="A311" s="17"/>
+      <c r="A311" s="18"/>
     </row>
     <row r="312">
-      <c r="A312" s="17"/>
+      <c r="A312" s="18"/>
     </row>
     <row r="313">
-      <c r="A313" s="17"/>
+      <c r="A313" s="18"/>
     </row>
     <row r="314">
-      <c r="A314" s="17"/>
+      <c r="A314" s="18"/>
     </row>
     <row r="315">
-      <c r="A315" s="17"/>
+      <c r="A315" s="18"/>
     </row>
     <row r="316">
-      <c r="A316" s="17"/>
+      <c r="A316" s="18"/>
     </row>
     <row r="317">
-      <c r="A317" s="17"/>
+      <c r="A317" s="18"/>
     </row>
     <row r="318">
-      <c r="A318" s="17"/>
+      <c r="A318" s="18"/>
     </row>
     <row r="319">
-      <c r="A319" s="17"/>
+      <c r="A319" s="18"/>
     </row>
     <row r="320">
-      <c r="A320" s="17"/>
+      <c r="A320" s="18"/>
     </row>
     <row r="321">
-      <c r="A321" s="17"/>
+      <c r="A321" s="18"/>
     </row>
     <row r="322">
-      <c r="A322" s="17"/>
+      <c r="A322" s="18"/>
     </row>
     <row r="323">
-      <c r="A323" s="17"/>
+      <c r="A323" s="18"/>
     </row>
     <row r="324">
-      <c r="A324" s="17"/>
+      <c r="A324" s="18"/>
     </row>
     <row r="325">
-      <c r="A325" s="17"/>
+      <c r="A325" s="18"/>
     </row>
     <row r="326">
-      <c r="A326" s="17"/>
+      <c r="A326" s="18"/>
     </row>
     <row r="327">
-      <c r="A327" s="17"/>
+      <c r="A327" s="18"/>
     </row>
     <row r="328">
-      <c r="A328" s="17"/>
+      <c r="A328" s="18"/>
     </row>
     <row r="329">
-      <c r="A329" s="17"/>
+      <c r="A329" s="18"/>
     </row>
     <row r="330">
-      <c r="A330" s="17"/>
+      <c r="A330" s="18"/>
     </row>
     <row r="331">
-      <c r="A331" s="17"/>
+      <c r="A331" s="18"/>
     </row>
     <row r="332">
-      <c r="A332" s="17"/>
+      <c r="A332" s="18"/>
     </row>
     <row r="333">
-      <c r="A333" s="17"/>
+      <c r="A333" s="18"/>
     </row>
     <row r="334">
-      <c r="A334" s="17"/>
+      <c r="A334" s="18"/>
     </row>
     <row r="335">
-      <c r="A335" s="17"/>
+      <c r="A335" s="18"/>
     </row>
     <row r="336">
-      <c r="A336" s="17"/>
+      <c r="A336" s="18"/>
     </row>
     <row r="337">
-      <c r="A337" s="17"/>
+      <c r="A337" s="18"/>
     </row>
     <row r="338">
-      <c r="A338" s="17"/>
+      <c r="A338" s="18"/>
     </row>
     <row r="339">
-      <c r="A339" s="17"/>
+      <c r="A339" s="18"/>
     </row>
     <row r="340">
-      <c r="A340" s="17"/>
+      <c r="A340" s="18"/>
     </row>
     <row r="341">
-      <c r="A341" s="17"/>
+      <c r="A341" s="18"/>
     </row>
     <row r="342">
-      <c r="A342" s="17"/>
+      <c r="A342" s="18"/>
     </row>
     <row r="343">
-      <c r="A343" s="17"/>
+      <c r="A343" s="18"/>
     </row>
     <row r="344">
-      <c r="A344" s="17"/>
+      <c r="A344" s="18"/>
     </row>
     <row r="345">
-      <c r="A345" s="17"/>
+      <c r="A345" s="18"/>
     </row>
     <row r="346">
-      <c r="A346" s="17"/>
+      <c r="A346" s="18"/>
     </row>
     <row r="347">
-      <c r="A347" s="17"/>
+      <c r="A347" s="18"/>
     </row>
     <row r="348">
-      <c r="A348" s="17"/>
+      <c r="A348" s="18"/>
     </row>
     <row r="349">
-      <c r="A349" s="17"/>
+      <c r="A349" s="18"/>
     </row>
     <row r="350">
-      <c r="A350" s="17"/>
+      <c r="A350" s="18"/>
     </row>
     <row r="351">
-      <c r="A351" s="17"/>
+      <c r="A351" s="18"/>
     </row>
     <row r="352">
-      <c r="A352" s="17"/>
+      <c r="A352" s="18"/>
     </row>
     <row r="353">
-      <c r="A353" s="17"/>
+      <c r="A353" s="18"/>
     </row>
     <row r="354">
-      <c r="A354" s="17"/>
+      <c r="A354" s="18"/>
     </row>
     <row r="355">
-      <c r="A355" s="17"/>
+      <c r="A355" s="18"/>
     </row>
     <row r="356">
-      <c r="A356" s="17"/>
+      <c r="A356" s="18"/>
     </row>
     <row r="357">
-      <c r="A357" s="17"/>
+      <c r="A357" s="18"/>
     </row>
     <row r="358">
-      <c r="A358" s="17"/>
+      <c r="A358" s="18"/>
     </row>
     <row r="359">
-      <c r="A359" s="17"/>
+      <c r="A359" s="18"/>
     </row>
     <row r="360">
-      <c r="A360" s="17"/>
+      <c r="A360" s="18"/>
     </row>
     <row r="361">
-      <c r="A361" s="17"/>
+      <c r="A361" s="18"/>
     </row>
     <row r="362">
-      <c r="A362" s="17"/>
+      <c r="A362" s="18"/>
     </row>
     <row r="363">
-      <c r="A363" s="17"/>
+      <c r="A363" s="18"/>
     </row>
     <row r="364">
-      <c r="A364" s="17"/>
+      <c r="A364" s="18"/>
     </row>
     <row r="365">
-      <c r="A365" s="17"/>
+      <c r="A365" s="18"/>
     </row>
     <row r="366">
-      <c r="A366" s="17"/>
+      <c r="A366" s="18"/>
     </row>
     <row r="367">
-      <c r="A367" s="17"/>
+      <c r="A367" s="18"/>
     </row>
     <row r="368">
-      <c r="A368" s="17"/>
+      <c r="A368" s="18"/>
     </row>
     <row r="369">
-      <c r="A369" s="17"/>
+      <c r="A369" s="18"/>
     </row>
     <row r="370">
-      <c r="A370" s="17"/>
+      <c r="A370" s="18"/>
     </row>
     <row r="371">
-      <c r="A371" s="17"/>
+      <c r="A371" s="18"/>
     </row>
     <row r="372">
-      <c r="A372" s="17"/>
+      <c r="A372" s="18"/>
     </row>
     <row r="373">
-      <c r="A373" s="17"/>
+      <c r="A373" s="18"/>
     </row>
     <row r="374">
-      <c r="A374" s="17"/>
+      <c r="A374" s="18"/>
     </row>
     <row r="375">
-      <c r="A375" s="17"/>
+      <c r="A375" s="18"/>
     </row>
     <row r="376">
-      <c r="A376" s="17"/>
+      <c r="A376" s="18"/>
     </row>
     <row r="377">
-      <c r="A377" s="17"/>
+      <c r="A377" s="18"/>
     </row>
     <row r="378">
-      <c r="A378" s="17"/>
+      <c r="A378" s="18"/>
     </row>
     <row r="379">
-      <c r="A379" s="17"/>
+      <c r="A379" s="18"/>
     </row>
     <row r="380">
-      <c r="A380" s="17"/>
+      <c r="A380" s="18"/>
     </row>
     <row r="381">
-      <c r="A381" s="17"/>
+      <c r="A381" s="18"/>
     </row>
     <row r="382">
-      <c r="A382" s="17"/>
+      <c r="A382" s="18"/>
     </row>
     <row r="383">
-      <c r="A383" s="17"/>
+      <c r="A383" s="18"/>
     </row>
     <row r="384">
-      <c r="A384" s="17"/>
+      <c r="A384" s="18"/>
     </row>
     <row r="385">
-      <c r="A385" s="17"/>
+      <c r="A385" s="18"/>
     </row>
     <row r="386">
-      <c r="A386" s="17"/>
+      <c r="A386" s="18"/>
     </row>
     <row r="387">
-      <c r="A387" s="17"/>
+      <c r="A387" s="18"/>
     </row>
     <row r="388">
-      <c r="A388" s="17"/>
+      <c r="A388" s="18"/>
     </row>
     <row r="389">
-      <c r="A389" s="17"/>
+      <c r="A389" s="18"/>
     </row>
     <row r="390">
-      <c r="A390" s="17"/>
+      <c r="A390" s="18"/>
     </row>
     <row r="391">
-      <c r="A391" s="17"/>
+      <c r="A391" s="18"/>
     </row>
     <row r="392">
-      <c r="A392" s="17"/>
+      <c r="A392" s="18"/>
     </row>
     <row r="393">
-      <c r="A393" s="17"/>
+      <c r="A393" s="18"/>
     </row>
     <row r="394">
-      <c r="A394" s="17"/>
+      <c r="A394" s="18"/>
     </row>
     <row r="395">
-      <c r="A395" s="17"/>
+      <c r="A395" s="18"/>
     </row>
     <row r="396">
-      <c r="A396" s="17"/>
+      <c r="A396" s="18"/>
     </row>
     <row r="397">
-      <c r="A397" s="17"/>
+      <c r="A397" s="18"/>
     </row>
     <row r="398">
-      <c r="A398" s="17"/>
+      <c r="A398" s="18"/>
     </row>
     <row r="399">
-      <c r="A399" s="17"/>
+      <c r="A399" s="18"/>
     </row>
     <row r="400">
-      <c r="A400" s="17"/>
+      <c r="A400" s="18"/>
     </row>
     <row r="401">
-      <c r="A401" s="17"/>
+      <c r="A401" s="18"/>
     </row>
     <row r="402">
-      <c r="A402" s="17"/>
+      <c r="A402" s="18"/>
     </row>
     <row r="403">
-      <c r="A403" s="17"/>
+      <c r="A403" s="18"/>
     </row>
     <row r="404">
-      <c r="A404" s="17"/>
+      <c r="A404" s="18"/>
     </row>
     <row r="405">
-      <c r="A405" s="17"/>
+      <c r="A405" s="18"/>
     </row>
     <row r="406">
-      <c r="A406" s="17"/>
+      <c r="A406" s="18"/>
     </row>
     <row r="407">
-      <c r="A407" s="17"/>
+      <c r="A407" s="18"/>
     </row>
     <row r="408">
-      <c r="A408" s="17"/>
+      <c r="A408" s="18"/>
     </row>
     <row r="409">
-      <c r="A409" s="17"/>
+      <c r="A409" s="18"/>
     </row>
     <row r="410">
-      <c r="A410" s="17"/>
+      <c r="A410" s="18"/>
     </row>
     <row r="411">
-      <c r="A411" s="17"/>
+      <c r="A411" s="18"/>
     </row>
     <row r="412">
-      <c r="A412" s="17"/>
+      <c r="A412" s="18"/>
     </row>
     <row r="413">
-      <c r="A413" s="17"/>
+      <c r="A413" s="18"/>
     </row>
     <row r="414">
-      <c r="A414" s="17"/>
+      <c r="A414" s="18"/>
     </row>
     <row r="415">
-      <c r="A415" s="17"/>
+      <c r="A415" s="18"/>
     </row>
     <row r="416">
-      <c r="A416" s="17"/>
+      <c r="A416" s="18"/>
     </row>
     <row r="417">
-      <c r="A417" s="17"/>
+      <c r="A417" s="18"/>
     </row>
     <row r="418">
-      <c r="A418" s="17"/>
+      <c r="A418" s="18"/>
     </row>
     <row r="419">
-      <c r="A419" s="17"/>
+      <c r="A419" s="18"/>
     </row>
     <row r="420">
-      <c r="A420" s="17"/>
+      <c r="A420" s="18"/>
     </row>
     <row r="421">
-      <c r="A421" s="17"/>
+      <c r="A421" s="18"/>
     </row>
     <row r="422">
-      <c r="A422" s="17"/>
+      <c r="A422" s="18"/>
     </row>
     <row r="423">
-      <c r="A423" s="17"/>
+      <c r="A423" s="18"/>
     </row>
     <row r="424">
-      <c r="A424" s="17"/>
+      <c r="A424" s="18"/>
     </row>
     <row r="425">
-      <c r="A425" s="17"/>
+      <c r="A425" s="18"/>
     </row>
     <row r="426">
-      <c r="A426" s="17"/>
+      <c r="A426" s="18"/>
     </row>
     <row r="427">
-      <c r="A427" s="17"/>
+      <c r="A427" s="18"/>
     </row>
     <row r="428">
-      <c r="A428" s="17"/>
+      <c r="A428" s="18"/>
     </row>
     <row r="429">
-      <c r="A429" s="17"/>
+      <c r="A429" s="18"/>
     </row>
     <row r="430">
-      <c r="A430" s="17"/>
+      <c r="A430" s="18"/>
     </row>
     <row r="431">
-      <c r="A431" s="17"/>
+      <c r="A431" s="18"/>
     </row>
     <row r="432">
-      <c r="A432" s="17"/>
+      <c r="A432" s="18"/>
     </row>
     <row r="433">
-      <c r="A433" s="17"/>
+      <c r="A433" s="18"/>
     </row>
     <row r="434">
-      <c r="A434" s="17"/>
+      <c r="A434" s="18"/>
     </row>
     <row r="435">
-      <c r="A435" s="17"/>
+      <c r="A435" s="18"/>
     </row>
     <row r="436">
-      <c r="A436" s="17"/>
+      <c r="A436" s="18"/>
     </row>
     <row r="437">
-      <c r="A437" s="17"/>
+      <c r="A437" s="18"/>
     </row>
     <row r="438">
-      <c r="A438" s="17"/>
+      <c r="A438" s="18"/>
     </row>
     <row r="439">
-      <c r="A439" s="17"/>
+      <c r="A439" s="18"/>
     </row>
     <row r="440">
-      <c r="A440" s="17"/>
+      <c r="A440" s="18"/>
     </row>
     <row r="441">
-      <c r="A441" s="17"/>
+      <c r="A441" s="18"/>
     </row>
     <row r="442">
-      <c r="A442" s="17"/>
+      <c r="A442" s="18"/>
     </row>
     <row r="443">
-      <c r="A443" s="17"/>
+      <c r="A443" s="18"/>
     </row>
     <row r="444">
-      <c r="A444" s="17"/>
+      <c r="A444" s="18"/>
     </row>
     <row r="445">
-      <c r="A445" s="17"/>
+      <c r="A445" s="18"/>
     </row>
     <row r="446">
-      <c r="A446" s="17"/>
+      <c r="A446" s="18"/>
     </row>
     <row r="447">
-      <c r="A447" s="17"/>
+      <c r="A447" s="18"/>
     </row>
     <row r="448">
-      <c r="A448" s="17"/>
+      <c r="A448" s="18"/>
     </row>
     <row r="449">
-      <c r="A449" s="17"/>
+      <c r="A449" s="18"/>
     </row>
     <row r="450">
-      <c r="A450" s="17"/>
+      <c r="A450" s="18"/>
     </row>
     <row r="451">
-      <c r="A451" s="17"/>
+      <c r="A451" s="18"/>
     </row>
     <row r="452">
-      <c r="A452" s="17"/>
+      <c r="A452" s="18"/>
     </row>
     <row r="453">
-      <c r="A453" s="17"/>
+      <c r="A453" s="18"/>
     </row>
     <row r="454">
-      <c r="A454" s="17"/>
+      <c r="A454" s="18"/>
     </row>
     <row r="455">
-      <c r="A455" s="17"/>
+      <c r="A455" s="18"/>
     </row>
     <row r="456">
-      <c r="A456" s="17"/>
+      <c r="A456" s="18"/>
     </row>
     <row r="457">
-      <c r="A457" s="17"/>
+      <c r="A457" s="18"/>
     </row>
     <row r="458">
-      <c r="A458" s="17"/>
+      <c r="A458" s="18"/>
     </row>
     <row r="459">
-      <c r="A459" s="17"/>
+      <c r="A459" s="18"/>
     </row>
     <row r="460">
-      <c r="A460" s="17"/>
+      <c r="A460" s="18"/>
     </row>
     <row r="461">
-      <c r="A461" s="17"/>
+      <c r="A461" s="18"/>
     </row>
     <row r="462">
-      <c r="A462" s="17"/>
+      <c r="A462" s="18"/>
     </row>
     <row r="463">
-      <c r="A463" s="17"/>
+      <c r="A463" s="18"/>
     </row>
     <row r="464">
-      <c r="A464" s="17"/>
+      <c r="A464" s="18"/>
     </row>
     <row r="465">
-      <c r="A465" s="17"/>
+      <c r="A465" s="18"/>
     </row>
     <row r="466">
-      <c r="A466" s="17"/>
+      <c r="A466" s="18"/>
     </row>
     <row r="467">
-      <c r="A467" s="17"/>
+      <c r="A467" s="18"/>
     </row>
     <row r="468">
-      <c r="A468" s="17"/>
+      <c r="A468" s="18"/>
     </row>
     <row r="469">
-      <c r="A469" s="17"/>
+      <c r="A469" s="18"/>
     </row>
     <row r="470">
-      <c r="A470" s="17"/>
+      <c r="A470" s="18"/>
     </row>
     <row r="471">
-      <c r="A471" s="17"/>
+      <c r="A471" s="18"/>
     </row>
     <row r="472">
-      <c r="A472" s="17"/>
+      <c r="A472" s="18"/>
     </row>
     <row r="473">
-      <c r="A473" s="17"/>
+      <c r="A473" s="18"/>
     </row>
     <row r="474">
-      <c r="A474" s="17"/>
+      <c r="A474" s="18"/>
     </row>
     <row r="475">
-      <c r="A475" s="17"/>
+      <c r="A475" s="18"/>
     </row>
     <row r="476">
-      <c r="A476" s="17"/>
+      <c r="A476" s="18"/>
     </row>
     <row r="477">
-      <c r="A477" s="17"/>
+      <c r="A477" s="18"/>
     </row>
     <row r="478">
-      <c r="A478" s="17"/>
+      <c r="A478" s="18"/>
     </row>
     <row r="479">
-      <c r="A479" s="17"/>
+      <c r="A479" s="18"/>
     </row>
     <row r="480">
-      <c r="A480" s="17"/>
+      <c r="A480" s="18"/>
     </row>
     <row r="481">
-      <c r="A481" s="17"/>
+      <c r="A481" s="18"/>
     </row>
     <row r="482">
-      <c r="A482" s="17"/>
+      <c r="A482" s="18"/>
     </row>
     <row r="483">
-      <c r="A483" s="17"/>
+      <c r="A483" s="18"/>
     </row>
     <row r="484">
-      <c r="A484" s="17"/>
+      <c r="A484" s="18"/>
     </row>
     <row r="485">
-      <c r="A485" s="17"/>
+      <c r="A485" s="18"/>
     </row>
     <row r="486">
-      <c r="A486" s="17"/>
+      <c r="A486" s="18"/>
     </row>
     <row r="487">
-      <c r="A487" s="17"/>
+      <c r="A487" s="18"/>
     </row>
     <row r="488">
-      <c r="A488" s="17"/>
+      <c r="A488" s="18"/>
     </row>
     <row r="489">
-      <c r="A489" s="17"/>
+      <c r="A489" s="18"/>
     </row>
     <row r="490">
-      <c r="A490" s="17"/>
+      <c r="A490" s="18"/>
     </row>
     <row r="491">
-      <c r="A491" s="17"/>
+      <c r="A491" s="18"/>
     </row>
     <row r="492">
-      <c r="A492" s="17"/>
+      <c r="A492" s="18"/>
     </row>
     <row r="493">
-      <c r="A493" s="17"/>
+      <c r="A493" s="18"/>
     </row>
     <row r="494">
-      <c r="A494" s="17"/>
+      <c r="A494" s="18"/>
     </row>
     <row r="495">
-      <c r="A495" s="17"/>
+      <c r="A495" s="18"/>
     </row>
     <row r="496">
-      <c r="A496" s="17"/>
+      <c r="A496" s="18"/>
     </row>
     <row r="497">
-      <c r="A497" s="17"/>
+      <c r="A497" s="18"/>
     </row>
     <row r="498">
-      <c r="A498" s="17"/>
+      <c r="A498" s="18"/>
     </row>
     <row r="499">
-      <c r="A499" s="17"/>
+      <c r="A499" s="18"/>
     </row>
     <row r="500">
-      <c r="A500" s="17"/>
+      <c r="A500" s="18"/>
     </row>
     <row r="501">
-      <c r="A501" s="17"/>
+      <c r="A501" s="18"/>
     </row>
     <row r="502">
-      <c r="A502" s="17"/>
+      <c r="A502" s="18"/>
     </row>
     <row r="503">
-      <c r="A503" s="17"/>
+      <c r="A503" s="18"/>
     </row>
     <row r="504">
-      <c r="A504" s="17"/>
+      <c r="A504" s="18"/>
     </row>
     <row r="505">
-      <c r="A505" s="17"/>
+      <c r="A505" s="18"/>
     </row>
     <row r="506">
-      <c r="A506" s="17"/>
+      <c r="A506" s="18"/>
     </row>
     <row r="507">
-      <c r="A507" s="17"/>
+      <c r="A507" s="18"/>
     </row>
     <row r="508">
-      <c r="A508" s="17"/>
+      <c r="A508" s="18"/>
     </row>
     <row r="509">
-      <c r="A509" s="17"/>
+      <c r="A509" s="18"/>
     </row>
     <row r="510">
-      <c r="A510" s="17"/>
+      <c r="A510" s="18"/>
     </row>
     <row r="511">
-      <c r="A511" s="17"/>
+      <c r="A511" s="18"/>
     </row>
     <row r="512">
-      <c r="A512" s="17"/>
+      <c r="A512" s="18"/>
     </row>
     <row r="513">
-      <c r="A513" s="17"/>
+      <c r="A513" s="18"/>
     </row>
     <row r="514">
-      <c r="A514" s="17"/>
+      <c r="A514" s="18"/>
     </row>
     <row r="515">
-      <c r="A515" s="17"/>
+      <c r="A515" s="18"/>
     </row>
     <row r="516">
-      <c r="A516" s="17"/>
+      <c r="A516" s="18"/>
     </row>
     <row r="517">
-      <c r="A517" s="17"/>
+      <c r="A517" s="18"/>
     </row>
     <row r="518">
-      <c r="A518" s="17"/>
+      <c r="A518" s="18"/>
     </row>
     <row r="519">
-      <c r="A519" s="17"/>
+      <c r="A519" s="18"/>
     </row>
     <row r="520">
-      <c r="A520" s="17"/>
+      <c r="A520" s="18"/>
     </row>
     <row r="521">
-      <c r="A521" s="17"/>
+      <c r="A521" s="18"/>
     </row>
     <row r="522">
-      <c r="A522" s="17"/>
+      <c r="A522" s="18"/>
     </row>
     <row r="523">
-      <c r="A523" s="17"/>
+      <c r="A523" s="18"/>
     </row>
     <row r="524">
-      <c r="A524" s="17"/>
+      <c r="A524" s="18"/>
     </row>
     <row r="525">
-      <c r="A525" s="17"/>
+      <c r="A525" s="18"/>
     </row>
     <row r="526">
-      <c r="A526" s="17"/>
+      <c r="A526" s="18"/>
     </row>
     <row r="527">
-      <c r="A527" s="17"/>
+      <c r="A527" s="18"/>
     </row>
     <row r="528">
-      <c r="A528" s="17"/>
+      <c r="A528" s="18"/>
     </row>
     <row r="529">
-      <c r="A529" s="17"/>
+      <c r="A529" s="18"/>
     </row>
     <row r="530">
-      <c r="A530" s="17"/>
+      <c r="A530" s="18"/>
     </row>
     <row r="531">
-      <c r="A531" s="17"/>
+      <c r="A531" s="18"/>
     </row>
     <row r="532">
-      <c r="A532" s="17"/>
+      <c r="A532" s="18"/>
     </row>
     <row r="533">
-      <c r="A533" s="17"/>
+      <c r="A533" s="18"/>
     </row>
     <row r="534">
-      <c r="A534" s="17"/>
+      <c r="A534" s="18"/>
     </row>
     <row r="535">
-      <c r="A535" s="17"/>
+      <c r="A535" s="18"/>
     </row>
     <row r="536">
-      <c r="A536" s="17"/>
+      <c r="A536" s="18"/>
     </row>
     <row r="537">
-      <c r="A537" s="17"/>
+      <c r="A537" s="18"/>
     </row>
     <row r="538">
-      <c r="A538" s="17"/>
+      <c r="A538" s="18"/>
     </row>
     <row r="539">
-      <c r="A539" s="17"/>
+      <c r="A539" s="18"/>
     </row>
     <row r="540">
-      <c r="A540" s="17"/>
+      <c r="A540" s="18"/>
     </row>
     <row r="541">
-      <c r="A541" s="17"/>
+      <c r="A541" s="18"/>
     </row>
     <row r="542">
-      <c r="A542" s="17"/>
+      <c r="A542" s="18"/>
     </row>
     <row r="543">
-      <c r="A543" s="17"/>
+      <c r="A543" s="18"/>
     </row>
     <row r="544">
-      <c r="A544" s="17"/>
+      <c r="A544" s="18"/>
     </row>
     <row r="545">
-      <c r="A545" s="17"/>
+      <c r="A545" s="18"/>
     </row>
     <row r="546">
-      <c r="A546" s="17"/>
+      <c r="A546" s="18"/>
     </row>
     <row r="547">
-      <c r="A547" s="17"/>
+      <c r="A547" s="18"/>
     </row>
     <row r="548">
-      <c r="A548" s="17"/>
+      <c r="A548" s="18"/>
     </row>
     <row r="549">
-      <c r="A549" s="17"/>
+      <c r="A549" s="18"/>
     </row>
     <row r="550">
-      <c r="A550" s="17"/>
+      <c r="A550" s="18"/>
     </row>
     <row r="551">
-      <c r="A551" s="17"/>
+      <c r="A551" s="18"/>
     </row>
     <row r="552">
-      <c r="A552" s="17"/>
+      <c r="A552" s="18"/>
     </row>
     <row r="553">
-      <c r="A553" s="17"/>
+      <c r="A553" s="18"/>
     </row>
     <row r="554">
-      <c r="A554" s="17"/>
+      <c r="A554" s="18"/>
     </row>
     <row r="555">
-      <c r="A555" s="17"/>
+      <c r="A555" s="18"/>
     </row>
     <row r="556">
-      <c r="A556" s="17"/>
+      <c r="A556" s="18"/>
     </row>
     <row r="557">
-      <c r="A557" s="17"/>
+      <c r="A557" s="18"/>
     </row>
     <row r="558">
-      <c r="A558" s="17"/>
+      <c r="A558" s="18"/>
     </row>
     <row r="559">
-      <c r="A559" s="17"/>
+      <c r="A559" s="18"/>
     </row>
     <row r="560">
-      <c r="A560" s="17"/>
+      <c r="A560" s="18"/>
     </row>
     <row r="561">
-      <c r="A561" s="17"/>
+      <c r="A561" s="18"/>
     </row>
     <row r="562">
-      <c r="A562" s="17"/>
+      <c r="A562" s="18"/>
     </row>
     <row r="563">
-      <c r="A563" s="17"/>
+      <c r="A563" s="18"/>
     </row>
     <row r="564">
-      <c r="A564" s="17"/>
+      <c r="A564" s="18"/>
     </row>
     <row r="565">
-      <c r="A565" s="17"/>
+      <c r="A565" s="18"/>
     </row>
     <row r="566">
-      <c r="A566" s="17"/>
+      <c r="A566" s="18"/>
     </row>
     <row r="567">
-      <c r="A567" s="17"/>
+      <c r="A567" s="18"/>
     </row>
     <row r="568">
-      <c r="A568" s="17"/>
+      <c r="A568" s="18"/>
     </row>
     <row r="569">
-      <c r="A569" s="17"/>
+      <c r="A569" s="18"/>
     </row>
     <row r="570">
-      <c r="A570" s="17"/>
+      <c r="A570" s="18"/>
     </row>
     <row r="571">
-      <c r="A571" s="17"/>
+      <c r="A571" s="18"/>
     </row>
     <row r="572">
-      <c r="A572" s="17"/>
+      <c r="A572" s="18"/>
     </row>
     <row r="573">
-      <c r="A573" s="17"/>
+      <c r="A573" s="18"/>
     </row>
     <row r="574">
-      <c r="A574" s="17"/>
+      <c r="A574" s="18"/>
     </row>
     <row r="575">
-      <c r="A575" s="17"/>
+      <c r="A575" s="18"/>
     </row>
     <row r="576">
-      <c r="A576" s="17"/>
+      <c r="A576" s="18"/>
     </row>
     <row r="577">
-      <c r="A577" s="17"/>
+      <c r="A577" s="18"/>
     </row>
     <row r="578">
-      <c r="A578" s="17"/>
+      <c r="A578" s="18"/>
     </row>
     <row r="579">
-      <c r="A579" s="17"/>
+      <c r="A579" s="18"/>
     </row>
     <row r="580">
-      <c r="A580" s="17"/>
+      <c r="A580" s="18"/>
     </row>
     <row r="581">
-      <c r="A581" s="17"/>
+      <c r="A581" s="18"/>
     </row>
     <row r="582">
-      <c r="A582" s="17"/>
+      <c r="A582" s="18"/>
     </row>
     <row r="583">
-      <c r="A583" s="17"/>
+      <c r="A583" s="18"/>
     </row>
     <row r="584">
-      <c r="A584" s="17"/>
+      <c r="A584" s="18"/>
     </row>
     <row r="585">
-      <c r="A585" s="17"/>
+      <c r="A585" s="18"/>
     </row>
     <row r="586">
-      <c r="A586" s="17"/>
+      <c r="A586" s="18"/>
     </row>
     <row r="587">
-      <c r="A587" s="17"/>
+      <c r="A587" s="18"/>
     </row>
     <row r="588">
-      <c r="A588" s="17"/>
+      <c r="A588" s="18"/>
     </row>
     <row r="589">
-      <c r="A589" s="17"/>
+      <c r="A589" s="18"/>
     </row>
     <row r="590">
-      <c r="A590" s="17"/>
+      <c r="A590" s="18"/>
     </row>
     <row r="591">
-      <c r="A591" s="17"/>
+      <c r="A591" s="18"/>
     </row>
     <row r="592">
-      <c r="A592" s="17"/>
+      <c r="A592" s="18"/>
     </row>
     <row r="593">
-      <c r="A593" s="17"/>
+      <c r="A593" s="18"/>
     </row>
     <row r="594">
-      <c r="A594" s="17"/>
+      <c r="A594" s="18"/>
     </row>
     <row r="595">
-      <c r="A595" s="17"/>
+      <c r="A595" s="18"/>
     </row>
     <row r="596">
-      <c r="A596" s="17"/>
+      <c r="A596" s="18"/>
     </row>
     <row r="597">
-      <c r="A597" s="17"/>
+      <c r="A597" s="18"/>
     </row>
     <row r="598">
-      <c r="A598" s="17"/>
+      <c r="A598" s="18"/>
     </row>
     <row r="599">
-      <c r="A599" s="17"/>
+      <c r="A599" s="18"/>
     </row>
     <row r="600">
-      <c r="A600" s="17"/>
+      <c r="A600" s="18"/>
     </row>
     <row r="601">
-      <c r="A601" s="17"/>
+      <c r="A601" s="18"/>
     </row>
     <row r="602">
-      <c r="A602" s="17"/>
+      <c r="A602" s="18"/>
     </row>
     <row r="603">
-      <c r="A603" s="17"/>
+      <c r="A603" s="18"/>
     </row>
     <row r="604">
-      <c r="A604" s="17"/>
+      <c r="A604" s="18"/>
     </row>
     <row r="605">
-      <c r="A605" s="17"/>
+      <c r="A605" s="18"/>
     </row>
     <row r="606">
-      <c r="A606" s="17"/>
+      <c r="A606" s="18"/>
     </row>
     <row r="607">
-      <c r="A607" s="17"/>
+      <c r="A607" s="18"/>
     </row>
     <row r="608">
-      <c r="A608" s="17"/>
+      <c r="A608" s="18"/>
     </row>
     <row r="609">
-      <c r="A609" s="17"/>
+      <c r="A609" s="18"/>
     </row>
     <row r="610">
-      <c r="A610" s="17"/>
+      <c r="A610" s="18"/>
     </row>
     <row r="611">
-      <c r="A611" s="17"/>
+      <c r="A611" s="18"/>
     </row>
     <row r="612">
-      <c r="A612" s="17"/>
+      <c r="A612" s="18"/>
     </row>
     <row r="613">
-      <c r="A613" s="17"/>
+      <c r="A613" s="18"/>
     </row>
     <row r="614">
-      <c r="A614" s="17"/>
+      <c r="A614" s="18"/>
     </row>
     <row r="615">
-      <c r="A615" s="17"/>
+      <c r="A615" s="18"/>
     </row>
     <row r="616">
-      <c r="A616" s="17"/>
+      <c r="A616" s="18"/>
     </row>
     <row r="617">
-      <c r="A617" s="17"/>
+      <c r="A617" s="18"/>
     </row>
     <row r="618">
-      <c r="A618" s="17"/>
+      <c r="A618" s="18"/>
     </row>
     <row r="619">
-      <c r="A619" s="17"/>
+      <c r="A619" s="18"/>
     </row>
     <row r="620">
-      <c r="A620" s="17"/>
+      <c r="A620" s="18"/>
     </row>
     <row r="621">
-      <c r="A621" s="17"/>
+      <c r="A621" s="18"/>
     </row>
     <row r="622">
-      <c r="A622" s="17"/>
+      <c r="A622" s="18"/>
     </row>
     <row r="623">
-      <c r="A623" s="17"/>
+      <c r="A623" s="18"/>
     </row>
     <row r="624">
-      <c r="A624" s="17"/>
+      <c r="A624" s="18"/>
     </row>
     <row r="625">
-      <c r="A625" s="17"/>
+      <c r="A625" s="18"/>
     </row>
     <row r="626">
-      <c r="A626" s="17"/>
+      <c r="A626" s="18"/>
     </row>
     <row r="627">
-      <c r="A627" s="17"/>
+      <c r="A627" s="18"/>
     </row>
     <row r="628">
-      <c r="A628" s="17"/>
+      <c r="A628" s="18"/>
     </row>
     <row r="629">
-      <c r="A629" s="17"/>
+      <c r="A629" s="18"/>
     </row>
     <row r="630">
-      <c r="A630" s="17"/>
+      <c r="A630" s="18"/>
     </row>
     <row r="631">
-      <c r="A631" s="17"/>
+      <c r="A631" s="18"/>
     </row>
     <row r="632">
-      <c r="A632" s="17"/>
+      <c r="A632" s="18"/>
     </row>
     <row r="633">
-      <c r="A633" s="17"/>
+      <c r="A633" s="18"/>
     </row>
     <row r="634">
-      <c r="A634" s="17"/>
+      <c r="A634" s="18"/>
     </row>
     <row r="635">
-      <c r="A635" s="17"/>
+      <c r="A635" s="18"/>
     </row>
     <row r="636">
-      <c r="A636" s="17"/>
+      <c r="A636" s="18"/>
     </row>
     <row r="637">
-      <c r="A637" s="17"/>
+      <c r="A637" s="18"/>
     </row>
     <row r="638">
-      <c r="A638" s="17"/>
+      <c r="A638" s="18"/>
     </row>
     <row r="639">
-      <c r="A639" s="17"/>
+      <c r="A639" s="18"/>
     </row>
     <row r="640">
-      <c r="A640" s="17"/>
+      <c r="A640" s="18"/>
     </row>
     <row r="641">
-      <c r="A641" s="17"/>
+      <c r="A641" s="18"/>
     </row>
     <row r="642">
-      <c r="A642" s="17"/>
+      <c r="A642" s="18"/>
     </row>
     <row r="643">
-      <c r="A643" s="17"/>
+      <c r="A643" s="18"/>
     </row>
     <row r="644">
-      <c r="A644" s="17"/>
+      <c r="A644" s="18"/>
     </row>
     <row r="645">
-      <c r="A645" s="17"/>
+      <c r="A645" s="18"/>
     </row>
     <row r="646">
-      <c r="A646" s="17"/>
+      <c r="A646" s="18"/>
     </row>
     <row r="647">
-      <c r="A647" s="17"/>
+      <c r="A647" s="18"/>
     </row>
     <row r="648">
-      <c r="A648" s="17"/>
+      <c r="A648" s="18"/>
     </row>
     <row r="649">
-      <c r="A649" s="17"/>
+      <c r="A649" s="18"/>
     </row>
     <row r="650">
-      <c r="A650" s="17"/>
+      <c r="A650" s="18"/>
     </row>
     <row r="651">
-      <c r="A651" s="17"/>
+      <c r="A651" s="18"/>
     </row>
     <row r="652">
-      <c r="A652" s="17"/>
+      <c r="A652" s="18"/>
     </row>
     <row r="653">
-      <c r="A653" s="17"/>
+      <c r="A653" s="18"/>
     </row>
     <row r="654">
-      <c r="A654" s="17"/>
+      <c r="A654" s="18"/>
     </row>
     <row r="655">
-      <c r="A655" s="17"/>
+      <c r="A655" s="18"/>
     </row>
     <row r="656">
-      <c r="A656" s="17"/>
+      <c r="A656" s="18"/>
     </row>
     <row r="657">
-      <c r="A657" s="17"/>
+      <c r="A657" s="18"/>
     </row>
     <row r="658">
-      <c r="A658" s="17"/>
+      <c r="A658" s="18"/>
     </row>
     <row r="659">
-      <c r="A659" s="17"/>
+      <c r="A659" s="18"/>
     </row>
     <row r="660">
-      <c r="A660" s="17"/>
+      <c r="A660" s="18"/>
     </row>
     <row r="661">
-      <c r="A661" s="17"/>
+      <c r="A661" s="18"/>
     </row>
     <row r="662">
-      <c r="A662" s="17"/>
+      <c r="A662" s="18"/>
     </row>
     <row r="663">
-      <c r="A663" s="17"/>
+      <c r="A663" s="18"/>
     </row>
     <row r="664">
-      <c r="A664" s="17"/>
+      <c r="A664" s="18"/>
     </row>
     <row r="665">
-      <c r="A665" s="17"/>
+      <c r="A665" s="18"/>
     </row>
     <row r="666">
-      <c r="A666" s="17"/>
+      <c r="A666" s="18"/>
     </row>
     <row r="667">
-      <c r="A667" s="17"/>
+      <c r="A667" s="18"/>
     </row>
     <row r="668">
-      <c r="A668" s="17"/>
+      <c r="A668" s="18"/>
     </row>
     <row r="669">
-      <c r="A669" s="17"/>
+      <c r="A669" s="18"/>
     </row>
     <row r="670">
-      <c r="A670" s="17"/>
+      <c r="A670" s="18"/>
     </row>
     <row r="671">
-      <c r="A671" s="17"/>
+      <c r="A671" s="18"/>
     </row>
     <row r="672">
-      <c r="A672" s="17"/>
+      <c r="A672" s="18"/>
     </row>
     <row r="673">
-      <c r="A673" s="17"/>
+      <c r="A673" s="18"/>
     </row>
     <row r="674">
-      <c r="A674" s="17"/>
+      <c r="A674" s="18"/>
     </row>
     <row r="675">
-      <c r="A675" s="17"/>
+      <c r="A675" s="18"/>
     </row>
     <row r="676">
-      <c r="A676" s="17"/>
+      <c r="A676" s="18"/>
     </row>
     <row r="677">
-      <c r="A677" s="17"/>
+      <c r="A677" s="18"/>
     </row>
     <row r="678">
-      <c r="A678" s="17"/>
+      <c r="A678" s="18"/>
     </row>
     <row r="679">
-      <c r="A679" s="17"/>
+      <c r="A679" s="18"/>
     </row>
     <row r="680">
-      <c r="A680" s="17"/>
+      <c r="A680" s="18"/>
     </row>
     <row r="681">
-      <c r="A681" s="17"/>
+      <c r="A681" s="18"/>
     </row>
     <row r="682">
-      <c r="A682" s="17"/>
+      <c r="A682" s="18"/>
     </row>
     <row r="683">
-      <c r="A683" s="17"/>
+      <c r="A683" s="18"/>
     </row>
     <row r="684">
-      <c r="A684" s="17"/>
+      <c r="A684" s="18"/>
     </row>
     <row r="685">
-      <c r="A685" s="17"/>
+      <c r="A685" s="18"/>
     </row>
     <row r="686">
-      <c r="A686" s="17"/>
+      <c r="A686" s="18"/>
     </row>
     <row r="687">
-      <c r="A687" s="17"/>
+      <c r="A687" s="18"/>
     </row>
     <row r="688">
-      <c r="A688" s="17"/>
+      <c r="A688" s="18"/>
     </row>
     <row r="689">
-      <c r="A689" s="17"/>
+      <c r="A689" s="18"/>
     </row>
     <row r="690">
-      <c r="A690" s="17"/>
+      <c r="A690" s="18"/>
     </row>
     <row r="691">
-      <c r="A691" s="17"/>
+      <c r="A691" s="18"/>
     </row>
     <row r="692">
-      <c r="A692" s="17"/>
+      <c r="A692" s="18"/>
     </row>
     <row r="693">
-      <c r="A693" s="17"/>
+      <c r="A693" s="18"/>
     </row>
     <row r="694">
-      <c r="A694" s="17"/>
+      <c r="A694" s="18"/>
     </row>
     <row r="695">
-      <c r="A695" s="17"/>
+      <c r="A695" s="18"/>
     </row>
     <row r="696">
-      <c r="A696" s="17"/>
+      <c r="A696" s="18"/>
     </row>
     <row r="697">
-      <c r="A697" s="17"/>
+      <c r="A697" s="18"/>
     </row>
     <row r="698">
-      <c r="A698" s="17"/>
+      <c r="A698" s="18"/>
     </row>
     <row r="699">
-      <c r="A699" s="17"/>
+      <c r="A699" s="18"/>
     </row>
     <row r="700">
-      <c r="A700" s="17"/>
+      <c r="A700" s="18"/>
     </row>
     <row r="701">
-      <c r="A701" s="17"/>
+      <c r="A701" s="18"/>
     </row>
     <row r="702">
-      <c r="A702" s="17"/>
+      <c r="A702" s="18"/>
     </row>
     <row r="703">
-      <c r="A703" s="17"/>
+      <c r="A703" s="18"/>
     </row>
     <row r="704">
-      <c r="A704" s="17"/>
+      <c r="A704" s="18"/>
     </row>
     <row r="705">
-      <c r="A705" s="17"/>
+      <c r="A705" s="18"/>
     </row>
     <row r="706">
-      <c r="A706" s="17"/>
+      <c r="A706" s="18"/>
     </row>
     <row r="707">
-      <c r="A707" s="17"/>
+      <c r="A707" s="18"/>
     </row>
     <row r="708">
-      <c r="A708" s="17"/>
+      <c r="A708" s="18"/>
     </row>
     <row r="709">
-      <c r="A709" s="17"/>
+      <c r="A709" s="18"/>
     </row>
     <row r="710">
-      <c r="A710" s="17"/>
+      <c r="A710" s="18"/>
     </row>
     <row r="711">
-      <c r="A711" s="17"/>
+      <c r="A711" s="18"/>
     </row>
     <row r="712">
-      <c r="A712" s="17"/>
+      <c r="A712" s="18"/>
     </row>
     <row r="713">
-      <c r="A713" s="17"/>
+      <c r="A713" s="18"/>
     </row>
     <row r="714">
-      <c r="A714" s="17"/>
+      <c r="A714" s="18"/>
     </row>
     <row r="715">
-      <c r="A715" s="17"/>
+      <c r="A715" s="18"/>
     </row>
     <row r="716">
-      <c r="A716" s="17"/>
+      <c r="A716" s="18"/>
     </row>
     <row r="717">
-      <c r="A717" s="17"/>
+      <c r="A717" s="18"/>
     </row>
     <row r="718">
-      <c r="A718" s="17"/>
+      <c r="A718" s="18"/>
     </row>
     <row r="719">
-      <c r="A719" s="17"/>
+      <c r="A719" s="18"/>
     </row>
     <row r="720">
-      <c r="A720" s="17"/>
+      <c r="A720" s="18"/>
     </row>
     <row r="721">
-      <c r="A721" s="17"/>
+      <c r="A721" s="18"/>
     </row>
     <row r="722">
-      <c r="A722" s="17"/>
+      <c r="A722" s="18"/>
     </row>
     <row r="723">
-      <c r="A723" s="17"/>
+      <c r="A723" s="18"/>
     </row>
     <row r="724">
-      <c r="A724" s="17"/>
+      <c r="A724" s="18"/>
     </row>
     <row r="725">
-      <c r="A725" s="17"/>
+      <c r="A725" s="18"/>
     </row>
     <row r="726">
-      <c r="A726" s="17"/>
+      <c r="A726" s="18"/>
     </row>
     <row r="727">
-      <c r="A727" s="17"/>
+      <c r="A727" s="18"/>
     </row>
     <row r="728">
-      <c r="A728" s="17"/>
+      <c r="A728" s="18"/>
     </row>
     <row r="729">
-      <c r="A729" s="17"/>
+      <c r="A729" s="18"/>
     </row>
     <row r="730">
-      <c r="A730" s="17"/>
+      <c r="A730" s="18"/>
     </row>
     <row r="731">
-      <c r="A731" s="17"/>
+      <c r="A731" s="18"/>
     </row>
     <row r="732">
-      <c r="A732" s="17"/>
+      <c r="A732" s="18"/>
     </row>
     <row r="733">
-      <c r="A733" s="17"/>
+      <c r="A733" s="18"/>
     </row>
     <row r="734">
-      <c r="A734" s="17"/>
+      <c r="A734" s="18"/>
     </row>
     <row r="735">
-      <c r="A735" s="17"/>
+      <c r="A735" s="18"/>
     </row>
     <row r="736">
-      <c r="A736" s="17"/>
+      <c r="A736" s="18"/>
     </row>
     <row r="737">
-      <c r="A737" s="17"/>
+      <c r="A737" s="18"/>
     </row>
     <row r="738">
-      <c r="A738" s="17"/>
+      <c r="A738" s="18"/>
     </row>
     <row r="739">
-      <c r="A739" s="17"/>
+      <c r="A739" s="18"/>
     </row>
     <row r="740">
-      <c r="A740" s="17"/>
+      <c r="A740" s="18"/>
     </row>
     <row r="741">
-      <c r="A741" s="17"/>
+      <c r="A741" s="18"/>
     </row>
     <row r="742">
-      <c r="A742" s="17"/>
+      <c r="A742" s="18"/>
     </row>
     <row r="743">
-      <c r="A743" s="17"/>
+      <c r="A743" s="18"/>
     </row>
     <row r="744">
-      <c r="A744" s="17"/>
+      <c r="A744" s="18"/>
     </row>
     <row r="745">
-      <c r="A745" s="17"/>
+      <c r="A745" s="18"/>
     </row>
     <row r="746">
-      <c r="A746" s="17"/>
+      <c r="A746" s="18"/>
     </row>
     <row r="747">
-      <c r="A747" s="17"/>
+      <c r="A747" s="18"/>
     </row>
     <row r="748">
-      <c r="A748" s="17"/>
+      <c r="A748" s="18"/>
     </row>
     <row r="749">
-      <c r="A749" s="17"/>
+      <c r="A749" s="18"/>
     </row>
     <row r="750">
-      <c r="A750" s="17"/>
+      <c r="A750" s="18"/>
     </row>
     <row r="751">
-      <c r="A751" s="17"/>
+      <c r="A751" s="18"/>
     </row>
     <row r="752">
-      <c r="A752" s="17"/>
+      <c r="A752" s="18"/>
     </row>
     <row r="753">
-      <c r="A753" s="17"/>
+      <c r="A753" s="18"/>
     </row>
     <row r="754">
-      <c r="A754" s="17"/>
+      <c r="A754" s="18"/>
     </row>
     <row r="755">
-      <c r="A755" s="17"/>
+      <c r="A755" s="18"/>
     </row>
     <row r="756">
-      <c r="A756" s="17"/>
+      <c r="A756" s="18"/>
     </row>
     <row r="757">
-      <c r="A757" s="17"/>
+      <c r="A757" s="18"/>
     </row>
     <row r="758">
-      <c r="A758" s="17"/>
+      <c r="A758" s="18"/>
     </row>
     <row r="759">
-      <c r="A759" s="17"/>
+      <c r="A759" s="18"/>
     </row>
     <row r="760">
-      <c r="A760" s="17"/>
+      <c r="A760" s="18"/>
     </row>
     <row r="761">
-      <c r="A761" s="17"/>
+      <c r="A761" s="18"/>
     </row>
     <row r="762">
-      <c r="A762" s="17"/>
+      <c r="A762" s="18"/>
     </row>
     <row r="763">
-      <c r="A763" s="17"/>
+      <c r="A763" s="18"/>
     </row>
     <row r="764">
-      <c r="A764" s="17"/>
+      <c r="A764" s="18"/>
     </row>
     <row r="765">
-      <c r="A765" s="17"/>
+      <c r="A765" s="18"/>
     </row>
     <row r="766">
-      <c r="A766" s="17"/>
+      <c r="A766" s="18"/>
     </row>
     <row r="767">
-      <c r="A767" s="17"/>
+      <c r="A767" s="18"/>
     </row>
     <row r="768">
-      <c r="A768" s="17"/>
+      <c r="A768" s="18"/>
     </row>
     <row r="769">
-      <c r="A769" s="17"/>
+      <c r="A769" s="18"/>
     </row>
     <row r="770">
-      <c r="A770" s="17"/>
+      <c r="A770" s="18"/>
     </row>
     <row r="771">
-      <c r="A771" s="17"/>
+      <c r="A771" s="18"/>
     </row>
     <row r="772">
-      <c r="A772" s="17"/>
+      <c r="A772" s="18"/>
     </row>
     <row r="773">
-      <c r="A773" s="17"/>
+      <c r="A773" s="18"/>
     </row>
     <row r="774">
-      <c r="A774" s="17"/>
+      <c r="A774" s="18"/>
     </row>
     <row r="775">
-      <c r="A775" s="17"/>
+      <c r="A775" s="18"/>
     </row>
     <row r="776">
-      <c r="A776" s="17"/>
+      <c r="A776" s="18"/>
     </row>
     <row r="777">
-      <c r="A777" s="17"/>
+      <c r="A777" s="18"/>
     </row>
     <row r="778">
-      <c r="A778" s="17"/>
+      <c r="A778" s="18"/>
     </row>
     <row r="779">
-      <c r="A779" s="17"/>
+      <c r="A779" s="18"/>
     </row>
     <row r="780">
-      <c r="A780" s="17"/>
+      <c r="A780" s="18"/>
     </row>
     <row r="781">
-      <c r="A781" s="17"/>
+      <c r="A781" s="18"/>
     </row>
     <row r="782">
-      <c r="A782" s="17"/>
+      <c r="A782" s="18"/>
     </row>
     <row r="783">
-      <c r="A783" s="17"/>
+      <c r="A783" s="18"/>
     </row>
     <row r="784">
-      <c r="A784" s="17"/>
+      <c r="A784" s="18"/>
     </row>
     <row r="785">
-      <c r="A785" s="17"/>
+      <c r="A785" s="18"/>
     </row>
     <row r="786">
-      <c r="A786" s="17"/>
+      <c r="A786" s="18"/>
     </row>
     <row r="787">
-      <c r="A787" s="17"/>
+      <c r="A787" s="18"/>
     </row>
     <row r="788">
-      <c r="A788" s="17"/>
+      <c r="A788" s="18"/>
     </row>
     <row r="789">
-      <c r="A789" s="17"/>
+      <c r="A789" s="18"/>
     </row>
     <row r="790">
-      <c r="A790" s="17"/>
+      <c r="A790" s="18"/>
     </row>
     <row r="791">
-      <c r="A791" s="17"/>
+      <c r="A791" s="18"/>
     </row>
     <row r="792">
-      <c r="A792" s="17"/>
+      <c r="A792" s="18"/>
     </row>
     <row r="793">
-      <c r="A793" s="17"/>
+      <c r="A793" s="18"/>
     </row>
     <row r="794">
-      <c r="A794" s="17"/>
+      <c r="A794" s="18"/>
     </row>
     <row r="795">
-      <c r="A795" s="17"/>
+      <c r="A795" s="18"/>
     </row>
     <row r="796">
-      <c r="A796" s="17"/>
+      <c r="A796" s="18"/>
     </row>
     <row r="797">
-      <c r="A797" s="17"/>
+      <c r="A797" s="18"/>
     </row>
     <row r="798">
-      <c r="A798" s="17"/>
+      <c r="A798" s="18"/>
     </row>
     <row r="799">
-      <c r="A799" s="17"/>
+      <c r="A799" s="18"/>
     </row>
     <row r="800">
-      <c r="A800" s="17"/>
+      <c r="A800" s="18"/>
     </row>
     <row r="801">
-      <c r="A801" s="17"/>
+      <c r="A801" s="18"/>
     </row>
     <row r="802">
-      <c r="A802" s="17"/>
+      <c r="A802" s="18"/>
     </row>
     <row r="803">
-      <c r="A803" s="17"/>
+      <c r="A803" s="18"/>
     </row>
     <row r="804">
-      <c r="A804" s="17"/>
+      <c r="A804" s="18"/>
     </row>
     <row r="805">
-      <c r="A805" s="17"/>
+      <c r="A805" s="18"/>
     </row>
     <row r="806">
-      <c r="A806" s="17"/>
+      <c r="A806" s="18"/>
     </row>
     <row r="807">
-      <c r="A807" s="17"/>
+      <c r="A807" s="18"/>
     </row>
     <row r="808">
-      <c r="A808" s="17"/>
+      <c r="A808" s="18"/>
     </row>
     <row r="809">
-      <c r="A809" s="17"/>
+      <c r="A809" s="18"/>
     </row>
     <row r="810">
-      <c r="A810" s="17"/>
+      <c r="A810" s="18"/>
     </row>
     <row r="811">
-      <c r="A811" s="17"/>
+      <c r="A811" s="18"/>
     </row>
     <row r="812">
-      <c r="A812" s="17"/>
+      <c r="A812" s="18"/>
     </row>
     <row r="813">
-      <c r="A813" s="17"/>
+      <c r="A813" s="18"/>
     </row>
     <row r="814">
-      <c r="A814" s="17"/>
+      <c r="A814" s="18"/>
     </row>
     <row r="815">
-      <c r="A815" s="17"/>
+      <c r="A815" s="18"/>
     </row>
     <row r="816">
-      <c r="A816" s="17"/>
+      <c r="A816" s="18"/>
     </row>
     <row r="817">
-      <c r="A817" s="17"/>
+      <c r="A817" s="18"/>
     </row>
     <row r="818">
-      <c r="A818" s="17"/>
+      <c r="A818" s="18"/>
     </row>
     <row r="819">
-      <c r="A819" s="17"/>
+      <c r="A819" s="18"/>
     </row>
     <row r="820">
-      <c r="A820" s="17"/>
+      <c r="A820" s="18"/>
     </row>
     <row r="821">
-      <c r="A821" s="17"/>
+      <c r="A821" s="18"/>
     </row>
     <row r="822">
-      <c r="A822" s="17"/>
+      <c r="A822" s="18"/>
     </row>
     <row r="823">
-      <c r="A823" s="17"/>
+      <c r="A823" s="18"/>
     </row>
     <row r="824">
-      <c r="A824" s="17"/>
+      <c r="A824" s="18"/>
     </row>
     <row r="825">
-      <c r="A825" s="17"/>
+      <c r="A825" s="18"/>
     </row>
     <row r="826">
-      <c r="A826" s="17"/>
+      <c r="A826" s="18"/>
     </row>
     <row r="827">
-      <c r="A827" s="17"/>
+      <c r="A827" s="18"/>
     </row>
     <row r="828">
-      <c r="A828" s="17"/>
+      <c r="A828" s="18"/>
     </row>
     <row r="829">
-      <c r="A829" s="17"/>
+      <c r="A829" s="18"/>
     </row>
     <row r="830">
-      <c r="A830" s="17"/>
+      <c r="A830" s="18"/>
     </row>
     <row r="831">
-      <c r="A831" s="17"/>
+      <c r="A831" s="18"/>
     </row>
     <row r="832">
-      <c r="A832" s="17"/>
+      <c r="A832" s="18"/>
     </row>
     <row r="833">
-      <c r="A833" s="17"/>
+      <c r="A833" s="18"/>
     </row>
     <row r="834">
-      <c r="A834" s="17"/>
+      <c r="A834" s="18"/>
     </row>
     <row r="835">
-      <c r="A835" s="17"/>
+      <c r="A835" s="18"/>
     </row>
     <row r="836">
-      <c r="A836" s="17"/>
+      <c r="A836" s="18"/>
     </row>
     <row r="837">
-      <c r="A837" s="17"/>
+      <c r="A837" s="18"/>
     </row>
     <row r="838">
-      <c r="A838" s="17"/>
+      <c r="A838" s="18"/>
     </row>
     <row r="839">
-      <c r="A839" s="17"/>
+      <c r="A839" s="18"/>
     </row>
     <row r="840">
-      <c r="A840" s="17"/>
+      <c r="A840" s="18"/>
     </row>
     <row r="841">
-      <c r="A841" s="17"/>
+      <c r="A841" s="18"/>
     </row>
     <row r="842">
-      <c r="A842" s="17"/>
+      <c r="A842" s="18"/>
     </row>
     <row r="843">
-      <c r="A843" s="17"/>
+      <c r="A843" s="18"/>
     </row>
     <row r="844">
-      <c r="A844" s="17"/>
+      <c r="A844" s="18"/>
     </row>
     <row r="845">
-      <c r="A845" s="17"/>
+      <c r="A845" s="18"/>
     </row>
     <row r="846">
-      <c r="A846" s="17"/>
+      <c r="A846" s="18"/>
     </row>
     <row r="847">
-      <c r="A847" s="17"/>
+      <c r="A847" s="18"/>
     </row>
     <row r="848">
-      <c r="A848" s="17"/>
+      <c r="A848" s="18"/>
     </row>
     <row r="849">
-      <c r="A849" s="17"/>
+      <c r="A849" s="18"/>
     </row>
     <row r="850">
-      <c r="A850" s="17"/>
+      <c r="A850" s="18"/>
     </row>
     <row r="851">
-      <c r="A851" s="17"/>
+      <c r="A851" s="18"/>
     </row>
     <row r="852">
-      <c r="A852" s="17"/>
+      <c r="A852" s="18"/>
     </row>
     <row r="853">
-      <c r="A853" s="17"/>
+      <c r="A853" s="18"/>
     </row>
     <row r="854">
-      <c r="A854" s="17"/>
+      <c r="A854" s="18"/>
     </row>
     <row r="855">
-      <c r="A855" s="17"/>
+      <c r="A855" s="18"/>
     </row>
     <row r="856">
-      <c r="A856" s="17"/>
+      <c r="A856" s="18"/>
     </row>
     <row r="857">
-      <c r="A857" s="17"/>
+      <c r="A857" s="18"/>
     </row>
     <row r="858">
-      <c r="A858" s="17"/>
+      <c r="A858" s="18"/>
     </row>
     <row r="859">
-      <c r="A859" s="17"/>
+      <c r="A859" s="18"/>
     </row>
     <row r="860">
-      <c r="A860" s="17"/>
+      <c r="A860" s="18"/>
     </row>
     <row r="861">
-      <c r="A861" s="17"/>
+      <c r="A861" s="18"/>
     </row>
     <row r="862">
-      <c r="A862" s="17"/>
+      <c r="A862" s="18"/>
     </row>
     <row r="863">
-      <c r="A863" s="17"/>
+      <c r="A863" s="18"/>
     </row>
     <row r="864">
-      <c r="A864" s="17"/>
+      <c r="A864" s="18"/>
     </row>
     <row r="865">
-      <c r="A865" s="17"/>
+      <c r="A865" s="18"/>
     </row>
     <row r="866">
-      <c r="A866" s="17"/>
+      <c r="A866" s="18"/>
     </row>
     <row r="867">
-      <c r="A867" s="17"/>
+      <c r="A867" s="18"/>
     </row>
     <row r="868">
-      <c r="A868" s="17"/>
+      <c r="A868" s="18"/>
     </row>
     <row r="869">
-      <c r="A869" s="17"/>
+      <c r="A869" s="18"/>
     </row>
     <row r="870">
-      <c r="A870" s="17"/>
+      <c r="A870" s="18"/>
     </row>
     <row r="871">
-      <c r="A871" s="17"/>
+      <c r="A871" s="18"/>
     </row>
     <row r="872">
-      <c r="A872" s="17"/>
+      <c r="A872" s="18"/>
     </row>
     <row r="873">
-      <c r="A873" s="17"/>
+      <c r="A873" s="18"/>
     </row>
     <row r="874">
-      <c r="A874" s="17"/>
+      <c r="A874" s="18"/>
     </row>
     <row r="875">
-      <c r="A875" s="17"/>
+      <c r="A875" s="18"/>
     </row>
     <row r="876">
-      <c r="A876" s="17"/>
+      <c r="A876" s="18"/>
     </row>
     <row r="877">
-      <c r="A877" s="17"/>
+      <c r="A877" s="18"/>
     </row>
     <row r="878">
-      <c r="A878" s="17"/>
+      <c r="A878" s="18"/>
     </row>
     <row r="879">
-      <c r="A879" s="17"/>
+      <c r="A879" s="18"/>
     </row>
     <row r="880">
-      <c r="A880" s="17"/>
+      <c r="A880" s="18"/>
     </row>
     <row r="881">
-      <c r="A881" s="17"/>
+      <c r="A881" s="18"/>
     </row>
     <row r="882">
-      <c r="A882" s="17"/>
+      <c r="A882" s="18"/>
     </row>
     <row r="883">
-      <c r="A883" s="17"/>
+      <c r="A883" s="18"/>
     </row>
     <row r="884">
-      <c r="A884" s="17"/>
+      <c r="A884" s="18"/>
     </row>
     <row r="885">
-      <c r="A885" s="17"/>
+      <c r="A885" s="18"/>
     </row>
     <row r="886">
-      <c r="A886" s="17"/>
+      <c r="A886" s="18"/>
     </row>
     <row r="887">
-      <c r="A887" s="17"/>
+      <c r="A887" s="18"/>
     </row>
     <row r="888">
-      <c r="A888" s="17"/>
+      <c r="A888" s="18"/>
     </row>
     <row r="889">
-      <c r="A889" s="17"/>
+      <c r="A889" s="18"/>
     </row>
     <row r="890">
-      <c r="A890" s="17"/>
+      <c r="A890" s="18"/>
     </row>
     <row r="891">
-      <c r="A891" s="17"/>
+      <c r="A891" s="18"/>
     </row>
     <row r="892">
-      <c r="A892" s="17"/>
+      <c r="A892" s="18"/>
     </row>
     <row r="893">
-      <c r="A893" s="17"/>
+      <c r="A893" s="18"/>
     </row>
     <row r="894">
-      <c r="A894" s="17"/>
+      <c r="A894" s="18"/>
     </row>
     <row r="895">
-      <c r="A895" s="17"/>
+      <c r="A895" s="18"/>
     </row>
     <row r="896">
-      <c r="A896" s="17"/>
+      <c r="A896" s="18"/>
     </row>
     <row r="897">
-      <c r="A897" s="17"/>
+      <c r="A897" s="18"/>
     </row>
     <row r="898">
-      <c r="A898" s="17"/>
+      <c r="A898" s="18"/>
     </row>
     <row r="899">
-      <c r="A899" s="17"/>
+      <c r="A899" s="18"/>
     </row>
     <row r="900">
-      <c r="A900" s="17"/>
+      <c r="A900" s="18"/>
     </row>
     <row r="901">
-      <c r="A901" s="17"/>
+      <c r="A901" s="18"/>
     </row>
     <row r="902">
-      <c r="A902" s="17"/>
+      <c r="A902" s="18"/>
     </row>
     <row r="903">
-      <c r="A903" s="17"/>
+      <c r="A903" s="18"/>
     </row>
     <row r="904">
-      <c r="A904" s="17"/>
+      <c r="A904" s="18"/>
     </row>
     <row r="905">
-      <c r="A905" s="17"/>
+      <c r="A905" s="18"/>
     </row>
     <row r="906">
-      <c r="A906" s="17"/>
+      <c r="A906" s="18"/>
     </row>
     <row r="907">
-      <c r="A907" s="17"/>
+      <c r="A907" s="18"/>
     </row>
     <row r="908">
-      <c r="A908" s="17"/>
+      <c r="A908" s="18"/>
     </row>
     <row r="909">
-      <c r="A909" s="17"/>
+      <c r="A909" s="18"/>
     </row>
     <row r="910">
-      <c r="A910" s="17"/>
+      <c r="A910" s="18"/>
     </row>
     <row r="911">
-      <c r="A911" s="17"/>
+      <c r="A911" s="18"/>
     </row>
     <row r="912">
-      <c r="A912" s="17"/>
+      <c r="A912" s="18"/>
     </row>
     <row r="913">
-      <c r="A913" s="17"/>
+      <c r="A913" s="18"/>
     </row>
     <row r="914">
-      <c r="A914" s="17"/>
+      <c r="A914" s="18"/>
     </row>
     <row r="915">
-      <c r="A915" s="17"/>
+      <c r="A915" s="18"/>
     </row>
     <row r="916">
-      <c r="A916" s="17"/>
+      <c r="A916" s="18"/>
     </row>
     <row r="917">
-      <c r="A917" s="17"/>
+      <c r="A917" s="18"/>
     </row>
     <row r="918">
-      <c r="A918" s="17"/>
+      <c r="A918" s="18"/>
     </row>
     <row r="919">
-      <c r="A919" s="17"/>
+      <c r="A919" s="18"/>
     </row>
     <row r="920">
-      <c r="A920" s="17"/>
+      <c r="A920" s="18"/>
     </row>
     <row r="921">
-      <c r="A921" s="17"/>
+      <c r="A921" s="18"/>
     </row>
     <row r="922">
-      <c r="A922" s="17"/>
+      <c r="A922" s="18"/>
     </row>
     <row r="923">
-      <c r="A923" s="17"/>
+      <c r="A923" s="18"/>
     </row>
     <row r="924">
-      <c r="A924" s="17"/>
+      <c r="A924" s="18"/>
     </row>
     <row r="925">
-      <c r="A925" s="17"/>
+      <c r="A925" s="18"/>
     </row>
     <row r="926">
-      <c r="A926" s="17"/>
+      <c r="A926" s="18"/>
     </row>
     <row r="927">
-      <c r="A927" s="17"/>
+      <c r="A927" s="18"/>
     </row>
     <row r="928">
-      <c r="A928" s="17"/>
+      <c r="A928" s="18"/>
     </row>
     <row r="929">
-      <c r="A929" s="17"/>
+      <c r="A929" s="18"/>
     </row>
     <row r="930">
-      <c r="A930" s="17"/>
+      <c r="A930" s="18"/>
     </row>
     <row r="931">
-      <c r="A931" s="17"/>
+      <c r="A931" s="18"/>
     </row>
     <row r="932">
-      <c r="A932" s="17"/>
+      <c r="A932" s="18"/>
     </row>
     <row r="933">
-      <c r="A933" s="17"/>
+      <c r="A933" s="18"/>
     </row>
     <row r="934">
-      <c r="A934" s="17"/>
+      <c r="A934" s="18"/>
     </row>
     <row r="935">
-      <c r="A935" s="17"/>
+      <c r="A935" s="18"/>
     </row>
     <row r="936">
-      <c r="A936" s="17"/>
+      <c r="A936" s="18"/>
     </row>
     <row r="937">
-      <c r="A937" s="17"/>
+      <c r="A937" s="18"/>
     </row>
     <row r="938">
-      <c r="A938" s="17"/>
+      <c r="A938" s="18"/>
     </row>
     <row r="939">
-      <c r="A939" s="17"/>
+      <c r="A939" s="18"/>
     </row>
     <row r="940">
-      <c r="A940" s="17"/>
+      <c r="A940" s="18"/>
     </row>
     <row r="941">
-      <c r="A941" s="17"/>
+      <c r="A941" s="18"/>
     </row>
     <row r="942">
-      <c r="A942" s="17"/>
+      <c r="A942" s="18"/>
     </row>
     <row r="943">
-      <c r="A943" s="17"/>
+      <c r="A943" s="18"/>
     </row>
     <row r="944">
-      <c r="A944" s="17"/>
+      <c r="A944" s="18"/>
     </row>
     <row r="945">
-      <c r="A945" s="17"/>
+      <c r="A945" s="18"/>
     </row>
     <row r="946">
-      <c r="A946" s="17"/>
+      <c r="A946" s="18"/>
     </row>
     <row r="947">
-      <c r="A947" s="17"/>
+      <c r="A947" s="18"/>
     </row>
     <row r="948">
-      <c r="A948" s="17"/>
+      <c r="A948" s="18"/>
     </row>
     <row r="949">
-      <c r="A949" s="17"/>
+      <c r="A949" s="18"/>
     </row>
     <row r="950">
-      <c r="A950" s="17"/>
+      <c r="A950" s="18"/>
     </row>
     <row r="951">
-      <c r="A951" s="17"/>
+      <c r="A951" s="18"/>
     </row>
     <row r="952">
-      <c r="A952" s="17"/>
+      <c r="A952" s="18"/>
     </row>
     <row r="953">
-      <c r="A953" s="17"/>
+      <c r="A953" s="18"/>
     </row>
     <row r="954">
-      <c r="A954" s="17"/>
+      <c r="A954" s="18"/>
     </row>
     <row r="955">
-      <c r="A955" s="17"/>
+      <c r="A955" s="18"/>
     </row>
     <row r="956">
-      <c r="A956" s="17"/>
+      <c r="A956" s="18"/>
     </row>
     <row r="957">
-      <c r="A957" s="17"/>
+      <c r="A957" s="18"/>
     </row>
     <row r="958">
-      <c r="A958" s="17"/>
+      <c r="A958" s="18"/>
     </row>
     <row r="959">
-      <c r="A959" s="17"/>
+      <c r="A959" s="18"/>
     </row>
     <row r="960">
-      <c r="A960" s="17"/>
+      <c r="A960" s="18"/>
     </row>
     <row r="961">
-      <c r="A961" s="17"/>
+      <c r="A961" s="18"/>
     </row>
     <row r="962">
-      <c r="A962" s="17"/>
+      <c r="A962" s="18"/>
     </row>
     <row r="963">
-      <c r="A963" s="17"/>
+      <c r="A963" s="18"/>
     </row>
     <row r="964">
-      <c r="A964" s="17"/>
+      <c r="A964" s="18"/>
     </row>
     <row r="965">
-      <c r="A965" s="17"/>
+      <c r="A965" s="18"/>
     </row>
     <row r="966">
-      <c r="A966" s="17"/>
+      <c r="A966" s="18"/>
     </row>
     <row r="967">
-      <c r="A967" s="17"/>
+      <c r="A967" s="18"/>
     </row>
     <row r="968">
-      <c r="A968" s="17"/>
+      <c r="A968" s="18"/>
     </row>
     <row r="969">
-      <c r="A969" s="17"/>
+      <c r="A969" s="18"/>
     </row>
     <row r="970">
-      <c r="A970" s="17"/>
+      <c r="A970" s="18"/>
     </row>
     <row r="971">
-      <c r="A971" s="17"/>
+      <c r="A971" s="18"/>
     </row>
     <row r="972">
-      <c r="A972" s="17"/>
+      <c r="A972" s="18"/>
     </row>
     <row r="973">
-      <c r="A973" s="17"/>
+      <c r="A973" s="18"/>
     </row>
     <row r="974">
-      <c r="A974" s="17"/>
+      <c r="A974" s="18"/>
     </row>
     <row r="975">
-      <c r="A975" s="17"/>
+      <c r="A975" s="18"/>
     </row>
     <row r="976">
-      <c r="A976" s="17"/>
+      <c r="A976" s="18"/>
     </row>
     <row r="977">
-      <c r="A977" s="17"/>
+      <c r="A977" s="18"/>
     </row>
     <row r="978">
-      <c r="A978" s="17"/>
+      <c r="A978" s="18"/>
     </row>
     <row r="979">
-      <c r="A979" s="17"/>
+      <c r="A979" s="18"/>
     </row>
     <row r="980">
-      <c r="A980" s="17"/>
+      <c r="A980" s="18"/>
     </row>
     <row r="981">
-      <c r="A981" s="17"/>
+      <c r="A981" s="18"/>
     </row>
     <row r="982">
-      <c r="A982" s="17"/>
+      <c r="A982" s="18"/>
     </row>
     <row r="983">
-      <c r="A983" s="17"/>
+      <c r="A983" s="18"/>
     </row>
     <row r="984">
-      <c r="A984" s="17"/>
+      <c r="A984" s="18"/>
     </row>
     <row r="985">
-      <c r="A985" s="17"/>
+      <c r="A985" s="18"/>
     </row>
     <row r="986">
-      <c r="A986" s="17"/>
+      <c r="A986" s="18"/>
     </row>
     <row r="987">
-      <c r="A987" s="17"/>
+      <c r="A987" s="18"/>
     </row>
     <row r="988">
-      <c r="A988" s="17"/>
+      <c r="A988" s="18"/>
     </row>
     <row r="989">
-      <c r="A989" s="17"/>
+      <c r="A989" s="18"/>
     </row>
     <row r="990">
-      <c r="A990" s="17"/>
+      <c r="A990" s="18"/>
     </row>
     <row r="991">
-      <c r="A991" s="17"/>
+      <c r="A991" s="18"/>
     </row>
     <row r="992">
-      <c r="A992" s="17"/>
+      <c r="A992" s="18"/>
     </row>
     <row r="993">
-      <c r="A993" s="17"/>
+      <c r="A993" s="18"/>
     </row>
     <row r="994">
-      <c r="A994" s="17"/>
+      <c r="A994" s="18"/>
     </row>
     <row r="995">
-      <c r="A995" s="17"/>
+      <c r="A995" s="18"/>
     </row>
     <row r="996">
-      <c r="A996" s="17"/>
+      <c r="A996" s="18"/>
     </row>
     <row r="997">
-      <c r="A997" s="17"/>
+      <c r="A997" s="18"/>
     </row>
     <row r="998">
-      <c r="A998" s="17"/>
+      <c r="A998" s="18"/>
     </row>
     <row r="999">
-      <c r="A999" s="17"/>
+      <c r="A999" s="18"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="17"/>
+      <c r="A1000" s="18"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="18"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="18"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="18"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="18"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5031,23 +5331,23 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -5055,16 +5355,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -5075,16 +5375,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -5095,16 +5395,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -5115,16 +5415,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -5135,16 +5435,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1">
         <v>-1.0</v>
@@ -5155,16 +5455,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1">
         <v>-1.0</v>
@@ -5175,16 +5475,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>-1.0</v>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="131">
   <si>
     <t>NpcID</t>
   </si>
@@ -244,6 +244,38 @@
     <t>C005</t>
   </si>
   <si>
+    <t>N006_0</t>
+  </si>
+  <si>
+    <t>사람?? 맞아맞아, 내가 왜 그 생각을 못했지?</t>
+  </si>
+  <si>
+    <t>이제 됐지? 난 가볼게.</t>
+  </si>
+  <si>
+    <t>잠깐만!! 문제 푸는걸 도와줬으니 이걸 줄게. 필요할 거야.</t>
+  </si>
+  <si>
+    <t>열쇠 조각을 받았다.</t>
+  </si>
+  <si>
+    <t>N006_1</t>
+  </si>
+  <si>
+    <t>꺄악!!</t>
+  </si>
+  <si>
+    <t>땡땡땡!!! 
+틀린 답을 말했으니 대가를 치르도록 해!!!</t>
+  </si>
+  <si>
+    <t>그게 정말 정답이라고 생각한 건 아니지?</t>
+  </si>
+  <si>
+    <t>좀 더 신중하게 답을 골라야겠어...
+체력이 좀 닳은 것 같아..</t>
+  </si>
+  <si>
     <t>거기, 당신 날 좀 도와줄 수 있나요?</t>
   </si>
   <si>
@@ -271,6 +303,36 @@
     <t>C006</t>
   </si>
   <si>
+    <t>N007_0</t>
+  </si>
+  <si>
+    <t>틀렸어요!!
+이런 기본적인 산수도 못 하시다니!!</t>
+  </si>
+  <si>
+    <t>잠깐 실수한 거야... 다시 하면 잘할 수 있어.</t>
+  </si>
+  <si>
+    <t>실수 안 하도록 조심해야겠어..
+체력이 닳은 거 같아..</t>
+  </si>
+  <si>
+    <t>N007_1</t>
+  </si>
+  <si>
+    <t>8이라... 맞는것 같아요!!</t>
+  </si>
+  <si>
+    <t>당신 정말 똑똑하군요?
+저를 도와주셨으니 당신에게 필요한 걸 드릴게요!</t>
+  </si>
+  <si>
+    <t>어?? 고마워...</t>
+  </si>
+  <si>
+    <t>이걸 모르는 건.. 말이 안 되는데..</t>
+  </si>
+  <si>
     <t>세상에서 제일 뜨거운 과일이 뭔지 맞춰봐.</t>
   </si>
   <si>
@@ -290,6 +352,56 @@
   </si>
   <si>
     <t>C007</t>
+  </si>
+  <si>
+    <t>N008_0</t>
+  </si>
+  <si>
+    <t>너... 대단한데?
+이 문제를 풀다니..</t>
+  </si>
+  <si>
+    <t>지금까지 이 문제를 푼 사람은 아무도 없었지..</t>
+  </si>
+  <si>
+    <t>어려운 문제를 풀었으니 보상을 해주도록 하지.
+자 이거 받아!!</t>
+  </si>
+  <si>
+    <t>너에게 분명 필요할 거야.
+잘 쓰도록 해.</t>
+  </si>
+  <si>
+    <t>고마워.. 마침 필요하던 참이었어..</t>
+  </si>
+  <si>
+    <t>그렇게 어려운 문제는 아니었던 거 같은데..</t>
+  </si>
+  <si>
+    <t>N008_1</t>
+  </si>
+  <si>
+    <t>이 문제의 허점을 찾아내지 못했구나.</t>
+  </si>
+  <si>
+    <t>너도 다른 인간들이랑 같아.</t>
+  </si>
+  <si>
+    <t>틀린 답을 말하면 대가를 치르게 되지!</t>
+  </si>
+  <si>
+    <t>하지만 문제가 너무 어려운걸..</t>
+  </si>
+  <si>
+    <t>문제 속에 답이 있다. 
+잘 들여다보도록 해!</t>
+  </si>
+  <si>
+    <t>알겠어.. 어렵지만 다시 풀어볼게..</t>
+  </si>
+  <si>
+    <t>이번엔 좀 더 신중하게 대답해야 되겠어..
+체력이 좀 닳은 거 같아..</t>
   </si>
   <si>
     <t>......................</t>
@@ -302,8 +414,10 @@
 너 똑똑하다!</t>
   </si>
   <si>
-    <t>그렇군요!!
-정말 고마워요</t>
+    <t>행운을 빌어요.</t>
+  </si>
+  <si>
+    <t>잘가!</t>
   </si>
 </sst>
 </file>
@@ -479,7 +593,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D12:J56" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D12:J88" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2049,19 +2163,19 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C43" s="1">
-        <v>7001.0</v>
+        <v>6010.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E43" s="8">
-        <v>7002.0</v>
+        <v>6011.0</v>
       </c>
       <c r="F43" s="15" t="s">
         <v>44</v>
@@ -2069,8 +2183,8 @@
       <c r="G43" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="7" t="s">
+      <c r="H43" s="15"/>
+      <c r="I43" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J43" s="8">
@@ -2079,19 +2193,19 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C44" s="1">
-        <v>7002.0</v>
+        <v>6011.0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E44" s="8">
-        <v>7003.0</v>
+        <v>6012.0</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>26</v>
@@ -2099,8 +2213,8 @@
       <c r="G44" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="7" t="s">
+      <c r="H44" s="15"/>
+      <c r="I44" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J44" s="8">
@@ -2109,19 +2223,19 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1">
-        <v>7003.0</v>
+        <v>6012.0</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E45" s="8">
-        <v>7004.0</v>
+        <v>6013.0</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>44</v>
@@ -2129,8 +2243,8 @@
       <c r="G45" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="17"/>
-      <c r="I45" s="7" t="s">
+      <c r="H45" s="15"/>
+      <c r="I45" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J45" s="8">
@@ -2139,19 +2253,19 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C46" s="1">
-        <v>7004.0</v>
+        <v>6013.0</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E46" s="8">
-        <v>7005.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>26</v>
@@ -2160,88 +2274,88 @@
         <v>27</v>
       </c>
       <c r="H46" s="15"/>
-      <c r="I46" s="7" t="s">
-        <v>28</v>
+      <c r="I46" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="J46" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C47" s="1">
-        <v>7005.0</v>
+        <v>6014.0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E47" s="8">
-        <v>7006.0</v>
+        <v>6015.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H47" s="17"/>
+        <v>27</v>
+      </c>
+      <c r="H47" s="15"/>
       <c r="I47" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J47" s="8">
-        <v>-1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C48" s="1">
-        <v>7006.0</v>
+        <v>6015.0</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E48" s="8">
-        <v>7007.0</v>
+        <v>6016.0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J48" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C49" s="1">
-        <v>7007.0</v>
+        <v>6016.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E49" s="8">
-        <v>7008.0</v>
+        <v>6017.0</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>44</v>
@@ -2249,7 +2363,7 @@
       <c r="G49" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H49" s="17"/>
+      <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
         <v>28</v>
       </c>
@@ -2259,16 +2373,16 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C50" s="1">
-        <v>7008.0</v>
+        <v>6017.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E50" s="8">
         <v>-1.0</v>
@@ -2279,31 +2393,29 @@
       <c r="G50" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H50" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="H50" s="15"/>
+      <c r="I50" s="15" t="s">
         <v>45</v>
       </c>
       <c r="J50" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="1">
-        <v>8001.0</v>
+        <v>7001.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E51" s="8">
-        <v>8002.0</v>
+        <v>7002.0</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>44</v>
@@ -2312,7 +2424,7 @@
         <v>68</v>
       </c>
       <c r="H51" s="17"/>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J51" s="8">
@@ -2321,19 +2433,19 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" s="1">
-        <v>8002.0</v>
+        <v>7002.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E52" s="8">
-        <v>8003.0</v>
+        <v>7003.0</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>26</v>
@@ -2342,7 +2454,7 @@
         <v>27</v>
       </c>
       <c r="H52" s="17"/>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J52" s="8">
@@ -2351,19 +2463,19 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="1">
-        <v>8003.0</v>
+        <v>7003.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E53" s="8">
-        <v>8004.0</v>
+        <v>7004.0</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>44</v>
@@ -2372,7 +2484,7 @@
         <v>68</v>
       </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="8" t="s">
+      <c r="I53" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J53" s="8">
@@ -2381,19 +2493,19 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" s="1">
-        <v>8004.0</v>
+        <v>7004.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E54" s="8">
-        <v>8005.0</v>
+        <v>7005.0</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>26</v>
@@ -2401,8 +2513,8 @@
       <c r="G54" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H54" s="17"/>
-      <c r="I54" s="8" t="s">
+      <c r="H54" s="15"/>
+      <c r="I54" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J54" s="8">
@@ -2411,19 +2523,19 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" s="1">
-        <v>8005.0</v>
+        <v>7005.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E55" s="8">
-        <v>8006.0</v>
+        <v>7006.0</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>44</v>
@@ -2432,7 +2544,7 @@
         <v>68</v>
       </c>
       <c r="H55" s="17"/>
-      <c r="I55" s="8" t="s">
+      <c r="I55" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J55" s="8">
@@ -2441,131 +2553,997 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="1">
+        <v>7006.0</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="8">
+        <v>7007.0</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="1">
+        <v>7007.0</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E57" s="8">
+        <v>7008.0</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="1">
+        <v>7008.0</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" s="1">
+        <v>7009.0</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="8">
+        <v>7010.0</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="15"/>
+      <c r="I59" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J59" s="8">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="1">
+        <v>7010.0</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="8">
+        <v>7011.0</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="15"/>
+      <c r="I60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J60" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="1">
+        <v>7011.0</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" s="8">
+        <v>7012.0</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="15"/>
+      <c r="I61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="1">
+        <v>7012.0</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J62" s="8">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="1">
+        <v>7013.0</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E63" s="8">
+        <v>7014.0</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H63" s="15"/>
+      <c r="I63" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J63" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="1">
+        <v>7014.0</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="8">
+        <v>7015.0</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H64" s="15"/>
+      <c r="I64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="1">
+        <v>7015.0</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65" s="8">
+        <v>7016.0</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" s="1">
+        <v>7016.0</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" s="8">
+        <v>7017.0</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J66" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" s="1">
+        <v>7017.0</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J67" s="8">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C68" s="1">
+        <v>8001.0</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E68" s="8">
+        <v>8002.0</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J68" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="1">
+        <v>8002.0</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E69" s="8">
+        <v>8003.0</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="1">
+        <v>8003.0</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E70" s="8">
+        <v>8004.0</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" s="8">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="1">
+        <v>8004.0</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E71" s="8">
+        <v>8005.0</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="1">
+        <v>8005.0</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E72" s="8">
         <v>8006.0</v>
       </c>
-      <c r="D56" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.0</v>
-      </c>
-      <c r="F56" s="15" t="s">
+      <c r="F72" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G56" s="16" t="s">
+      <c r="G72" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" s="8">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="18"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="18"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="18"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="18"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="18"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="18"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="18"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="18"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="18"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="18"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="18"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="18"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="18"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="18"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="18"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="18"/>
+      <c r="A73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="1">
+        <v>8006.0</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J73" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="18"/>
+      <c r="A74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C74" s="1">
+        <v>8007.0</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74" s="8">
+        <v>8008.0</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" s="17"/>
+      <c r="I74" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J74" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="18"/>
+      <c r="A75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="1">
+        <v>8008.0</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" s="8">
+        <v>8009.0</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H75" s="17"/>
+      <c r="I75" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J75" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="18"/>
+      <c r="A76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="1">
+        <v>8009.0</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E76" s="8">
+        <v>8010.0</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H76" s="17"/>
+      <c r="I76" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J76" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="18"/>
+      <c r="A77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="1">
+        <v>8010.0</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" s="8">
+        <v>8011.0</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="17"/>
+      <c r="I77" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J77" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="18"/>
+      <c r="A78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="1">
+        <v>8011.0</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="8">
+        <v>8012.0</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H78" s="17"/>
+      <c r="I78" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="18"/>
+      <c r="A79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C79" s="1">
+        <v>8012.0</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E79" s="8">
+        <v>8013.0</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="17"/>
+      <c r="I79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J79" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="18"/>
+      <c r="A80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="1">
+        <v>8013.0</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="17"/>
+      <c r="I80" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J80" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="18"/>
+      <c r="A81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C81" s="1">
+        <v>8014.0</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E81" s="8">
+        <v>8014.0</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="I81" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J81" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="18"/>
+      <c r="A82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="1">
+        <v>8015.0</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="8">
+        <v>8015.0</v>
+      </c>
+      <c r="F82" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J82" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="18"/>
+      <c r="A83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="1">
+        <v>8016.0</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E83" s="8">
+        <v>8016.0</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H83" s="17"/>
+      <c r="I83" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J83" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="18"/>
+      <c r="A84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="1">
+        <v>8017.0</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" s="8">
+        <v>8017.0</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" s="17"/>
+      <c r="I84" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J84" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="18"/>
+      <c r="A85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="1">
+        <v>8018.0</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E85" s="8">
+        <v>8018.0</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H85" s="17"/>
+      <c r="I85" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J85" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="18"/>
+      <c r="A86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C86" s="1">
+        <v>8019.0</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E86" s="8">
+        <v>8019.0</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H86" s="17"/>
+      <c r="I86" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="18"/>
+      <c r="A87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" s="1">
+        <v>8020.0</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="8">
+        <v>8020.0</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H87" s="17"/>
+      <c r="I87" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="18"/>
+      <c r="A88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="1">
+        <v>8021.0</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H88" s="17"/>
+      <c r="I88" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J88" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="18"/>
@@ -5314,6 +6292,57 @@
     </row>
     <row r="1004">
       <c r="A1004" s="18"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="18"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="18"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="18"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="18"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="18"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="18"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="18"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="18"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="18"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="18"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="18"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="18"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="18"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="18"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="18"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="18"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="18"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5355,7 +6384,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>44</v>
@@ -5375,7 +6404,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>44</v>
@@ -5395,7 +6424,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>44</v>
@@ -5415,7 +6444,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>44</v>
@@ -5435,7 +6464,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>44</v>
@@ -5455,7 +6484,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>44</v>
@@ -5475,7 +6504,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>44</v>
@@ -5487,6 +6516,26 @@
         <v>28</v>
       </c>
       <c r="F8" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -3318,8 +3318,8 @@
       <c r="D81" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E81" s="8">
-        <v>8014.0</v>
+      <c r="E81" s="1">
+        <v>8015.0</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>26</v>
@@ -3348,8 +3348,8 @@
       <c r="D82" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E82" s="8">
-        <v>8015.0</v>
+      <c r="E82" s="1">
+        <v>8016.0</v>
       </c>
       <c r="F82" s="15" t="s">
         <v>44</v>
@@ -3378,8 +3378,8 @@
       <c r="D83" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E83" s="8">
-        <v>8016.0</v>
+      <c r="E83" s="1">
+        <v>8017.0</v>
       </c>
       <c r="F83" s="15" t="s">
         <v>44</v>
@@ -3408,8 +3408,8 @@
       <c r="D84" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E84" s="8">
-        <v>8017.0</v>
+      <c r="E84" s="1">
+        <v>8018.0</v>
       </c>
       <c r="F84" s="15" t="s">
         <v>44</v>
@@ -3438,8 +3438,8 @@
       <c r="D85" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E85" s="8">
-        <v>8018.0</v>
+      <c r="E85" s="1">
+        <v>8019.0</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>26</v>
@@ -3468,8 +3468,8 @@
       <c r="D86" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E86" s="8">
-        <v>8019.0</v>
+      <c r="E86" s="1">
+        <v>8020.0</v>
       </c>
       <c r="F86" s="15" t="s">
         <v>44</v>
@@ -3498,8 +3498,8 @@
       <c r="D87" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E87" s="8">
-        <v>8020.0</v>
+      <c r="E87" s="1">
+        <v>8021.0</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>26</v>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="198">
   <si>
     <t>NpcID</t>
   </si>
@@ -63,6 +63,24 @@
     <t>N008</t>
   </si>
   <si>
+    <t>N009</t>
+  </si>
+  <si>
+    <t>서린이 방 책상</t>
+  </si>
+  <si>
+    <t>N010</t>
+  </si>
+  <si>
+    <t>소미,세나</t>
+  </si>
+  <si>
+    <t>N011</t>
+  </si>
+  <si>
+    <t>혁이</t>
+  </si>
+  <si>
     <t>NpcEventID</t>
   </si>
   <si>
@@ -129,16 +147,32 @@
     <t>나 뭔가 잘못 선택한 걸까...?</t>
   </si>
   <si>
-    <t>뭐지... 방금 이 꽃이 날 쳐다본 거 같은데</t>
-  </si>
-  <si>
-    <t>뭔가.. 눈이 달린 것 같았어</t>
+    <t>뭐야 이꽃...?</t>
+  </si>
+  <si>
+    <t>눈...? 이거 분명 눈인데..?</t>
   </si>
   <si>
     <t>그럴 수가 있나?</t>
   </si>
   <si>
     <t>C003</t>
+  </si>
+  <si>
+    <t>N002_0</t>
+  </si>
+  <si>
+    <t>꺄악!!</t>
+  </si>
+  <si>
+    <t>뭐야 이거... 눈 맞잖아.. ?
+왜 자꾸 쳐다보는거야.. 소름끼쳐..</t>
+  </si>
+  <si>
+    <t>N002_1</t>
+  </si>
+  <si>
+    <t>역시.. 그럴리가 없지.</t>
   </si>
   <si>
     <t>시루야!!!!</t>
@@ -262,9 +296,6 @@
     <t>N006_1</t>
   </si>
   <si>
-    <t>꺄악!!</t>
-  </si>
-  <si>
     <t>땡땡땡!!! 
 틀린 답을 말했으니 대가를 치르도록 해!!!</t>
   </si>
@@ -404,6 +435,170 @@
 체력이 좀 닳은 거 같아..</t>
   </si>
   <si>
+    <t>엄마...아빠...</t>
+  </si>
+  <si>
+    <t>이제 사진을 보는게 아니면 얼굴도 잘 기억이 안나..</t>
+  </si>
+  <si>
+    <t>내가 혼자가 된지 얼마나 지났더라..</t>
+  </si>
+  <si>
+    <t>C008</t>
+  </si>
+  <si>
+    <t>N009_0</t>
+  </si>
+  <si>
+    <t>늦었다.. 어서 잠을 자야겠어..</t>
+  </si>
+  <si>
+    <t>N009_1</t>
+  </si>
+  <si>
+    <t>아무리 오래되도.. 잘 안잊혀지네..</t>
+  </si>
+  <si>
+    <t>어서 잠이나 자자..</t>
+  </si>
+  <si>
+    <t>늦어서 미안...</t>
+  </si>
+  <si>
+    <t>야, 네가 그러니까 안된다는 거야 알아?</t>
+  </si>
+  <si>
+    <t>소미</t>
+  </si>
+  <si>
+    <t>크큭...너무 그러진 마.</t>
+  </si>
+  <si>
+    <t>세나</t>
+  </si>
+  <si>
+    <t>부모도 없는 애가 뭘 알겠어?</t>
+  </si>
+  <si>
+    <t>.......</t>
+  </si>
+  <si>
+    <t>뭐야?? 뭐 불만 있어?</t>
+  </si>
+  <si>
+    <t>아니야....그런 거..</t>
+  </si>
+  <si>
+    <t>그래, 말 좀 잘 듣자.</t>
+  </si>
+  <si>
+    <t>우리 앞으로도 볼 날 많으니까 잘하자?</t>
+  </si>
+  <si>
+    <t>응...근데 나 뭐 하나만 물어봐도 될까..?</t>
+  </si>
+  <si>
+    <t>크큭...찐따가 이제 질문도 하네?</t>
+  </si>
+  <si>
+    <t>뭐, 이번만 특별히 들어줄게. 
+뭔데?</t>
+  </si>
+  <si>
+    <t>C009</t>
+  </si>
+  <si>
+    <t>N010_0</t>
+  </si>
+  <si>
+    <t>질문이 겨우 그거야??</t>
+  </si>
+  <si>
+    <t>왜 그렇게까지 하냐니.</t>
+  </si>
+  <si>
+    <t>그냥 재밌잖아.</t>
+  </si>
+  <si>
+    <t>.......그런거구나...</t>
+  </si>
+  <si>
+    <t>N010_1</t>
+  </si>
+  <si>
+    <t>이유? 그런 게 어디 있어.</t>
+  </si>
+  <si>
+    <t>그냥 네가 맘에 안 드니깐 그런 거야.</t>
+  </si>
+  <si>
+    <t>넌 평생 우리 장난감이야 알겠어?</t>
+  </si>
+  <si>
+    <t>...그렇구나...</t>
+  </si>
+  <si>
+    <t>서린이, 오랜만이다?</t>
+  </si>
+  <si>
+    <t>그동안 잘 지냈어?</t>
+  </si>
+  <si>
+    <t>....우리가 안부 물을 사이는 아닌거 같은데..</t>
+  </si>
+  <si>
+    <t>나 다 알고있어.. 네가 나 가지고 놀았다는거..</t>
+  </si>
+  <si>
+    <t>뭐야?? 다 알고 있었어?</t>
+  </si>
+  <si>
+    <t>어떻게 알았대?</t>
+  </si>
+  <si>
+    <t>어쩌다 보니.. 알게 됐어..</t>
+  </si>
+  <si>
+    <t>뭐야 그럼, 이제 잘 해줄 필요도 없네.</t>
+  </si>
+  <si>
+    <t>이제 볼일 없으니까 가봐.</t>
+  </si>
+  <si>
+    <t>마지막으로 하나 물어보고 싶은 게 있어..</t>
+  </si>
+  <si>
+    <t>뭔데, 들어는 줄게.</t>
+  </si>
+  <si>
+    <t>C010</t>
+  </si>
+  <si>
+    <t>N011_0</t>
+  </si>
+  <si>
+    <t>하하하하, 진심?
+그럴 리가 있겠어?</t>
+  </si>
+  <si>
+    <t>그냥 애들이랑 내기한 거 가지고?</t>
+  </si>
+  <si>
+    <t>그랬구나... 알겠어..</t>
+  </si>
+  <si>
+    <t>N011_1</t>
+  </si>
+  <si>
+    <t>그냥, 재밌잖아.</t>
+  </si>
+  <si>
+    <t>반응이 궁금하기도 했고.</t>
+  </si>
+  <si>
+    <t>재미... 그렇구나..</t>
+  </si>
+  <si>
     <t>......................</t>
   </si>
   <si>
@@ -418,6 +613,16 @@
   </si>
   <si>
     <t>잘가!</t>
+  </si>
+  <si>
+    <t>이러다 학교 늦겠어..
+어서 잠을 자야해..</t>
+  </si>
+  <si>
+    <t>뭘봐, 저리 안꺼져?</t>
+  </si>
+  <si>
+    <t>아직 할말 남았어?</t>
   </si>
 </sst>
 </file>
@@ -477,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -530,6 +735,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -593,7 +801,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D12:J88" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J134" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -880,6 +1088,30 @@
         <v>13</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -900,31 +1132,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -938,19 +1170,19 @@
         <v>1001.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1">
         <v>1002.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J2" s="1">
         <v>-1.0</v>
@@ -967,19 +1199,19 @@
         <v>1002.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1">
         <v>1003.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J3" s="1">
         <v>-1.0</v>
@@ -996,22 +1228,22 @@
         <v>1003.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1">
         <v>-1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J4" s="1">
         <v>-1.0</v>
@@ -1022,26 +1254,26 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1">
         <v>1004.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1">
         <v>1005.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J5" s="1">
         <v>-1.0</v>
@@ -1052,26 +1284,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1">
         <v>1005.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1">
         <v>-1.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J6" s="1">
         <v>-1.0</v>
@@ -1082,26 +1314,26 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1">
         <v>1006.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1">
         <v>1007.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1">
         <v>-1.0</v>
@@ -1112,26 +1344,26 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1">
         <v>1007.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1">
         <v>-1.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1">
         <v>-1.0</v>
@@ -1148,19 +1380,19 @@
         <v>2001.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1">
         <v>2002.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J9" s="1">
         <v>-1.0</v>
@@ -1177,19 +1409,19 @@
         <v>2002.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1">
         <v>2003.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1">
         <v>-1.0</v>
@@ -1206,115 +1438,115 @@
         <v>2003.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1">
         <v>-1.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1">
         <v>-1.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>6</v>
+      <c r="A12" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3001.0</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3002.0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="10">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2004.0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2005.0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2005.0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-1.0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="1">
         <v>0.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3002.0</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="12">
-        <v>3003.0</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="14">
-        <v>-1.0</v>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>6</v>
+      <c r="A14" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="6">
-        <v>3003.0</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3004.0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="10">
-        <v>4.0</v>
+        <v>51</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2006.0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-1.0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="15">
@@ -1325,26 +1557,26 @@
         <v>6</v>
       </c>
       <c r="C15" s="6">
-        <v>3004.0</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="12">
-        <v>3005.0</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="14">
-        <v>-1.0</v>
+        <v>3001.0</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3002.0</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -1355,26 +1587,26 @@
         <v>6</v>
       </c>
       <c r="C16" s="6">
-        <v>3005.0</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3006.0</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0.0</v>
+        <v>3002.0</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="12">
+        <v>3003.0</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="14">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="17">
@@ -1385,26 +1617,26 @@
         <v>6</v>
       </c>
       <c r="C17" s="6">
-        <v>3006.0</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="12">
-        <v>3007.0</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.0</v>
+        <v>3003.0</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3004.0</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="10">
+        <v>4.0</v>
       </c>
     </row>
     <row r="18">
@@ -1415,25 +1647,25 @@
         <v>6</v>
       </c>
       <c r="C18" s="6">
-        <v>3007.0</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3008.0</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="9" t="s">
+        <v>3004.0</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="12">
+        <v>3005.0</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="10">
+      <c r="H18" s="11"/>
+      <c r="I18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -1445,26 +1677,26 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>3008.0</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="12">
-        <v>3009.0</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="14">
-        <v>2.0</v>
+        <v>3005.0</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3006.0</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="10">
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -1475,26 +1707,26 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>3009.0</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3010.0</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="10">
-        <v>-1.0</v>
+        <v>3006.0</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="12">
+        <v>3007.0</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -1505,26 +1737,26 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>3010.0</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12">
-        <v>3011.0</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="14">
-        <v>4.0</v>
+        <v>3007.0</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3008.0</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" s="10">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="22">
@@ -1535,26 +1767,26 @@
         <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>3011.0</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3012.0</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="10">
-        <v>-1.0</v>
+        <v>3008.0</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="12">
+        <v>3009.0</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="14">
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -1565,26 +1797,26 @@
         <v>6</v>
       </c>
       <c r="C23" s="6">
-        <v>3012.0</v>
-      </c>
-      <c r="D23" s="11" t="s">
+        <v>3009.0</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="12">
-        <v>3013.0</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="14">
-        <v>4.0</v>
+      <c r="E23" s="8">
+        <v>3010.0</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="10">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="24">
@@ -1595,26 +1827,26 @@
         <v>6</v>
       </c>
       <c r="C24" s="6">
-        <v>3013.0</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="8">
-        <v>3014.0</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24" s="10">
-        <v>-1.0</v>
+        <v>3010.0</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="12">
+        <v>3011.0</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="14">
+        <v>4.0</v>
       </c>
     </row>
     <row r="25">
@@ -1625,26 +1857,26 @@
         <v>6</v>
       </c>
       <c r="C25" s="6">
-        <v>3014.0</v>
-      </c>
-      <c r="D25" s="11" t="s">
+        <v>3011.0</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3012.0</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="12">
-        <v>3015.0</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="14">
-        <v>0.0</v>
+      <c r="J25" s="10">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="26">
@@ -1655,26 +1887,26 @@
         <v>6</v>
       </c>
       <c r="C26" s="6">
-        <v>3015.0</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3016.0</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26" s="10">
-        <v>-1.0</v>
+        <v>3012.0</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="12">
+        <v>3013.0</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="14">
+        <v>4.0</v>
       </c>
     </row>
     <row r="27">
@@ -1685,26 +1917,26 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>3016.0</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="12">
-        <v>3017.0</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="14">
-        <v>0.0</v>
+        <v>3013.0</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3014.0</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="10">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="28">
@@ -1715,268 +1947,268 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
+        <v>3014.0</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="12">
+        <v>3015.0</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="14">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>3015.0</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3016.0</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="10">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>3016.0</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="12">
         <v>3017.0</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.0</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" s="10">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1">
-        <v>4001.0</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="8">
-        <v>4002.0</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="8">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1">
-        <v>4002.0</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.0</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="8">
+      <c r="F30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="14">
         <v>0.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3017.0</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="10">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4001.0</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="8">
+        <v>4002.0</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="8">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4002.0</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C34" s="6">
         <v>5001.0</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="D34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="8">
         <v>5002.0</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>5002.0</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="12">
-        <v>5003.0</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="14">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>5003.0</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="10">
-        <v>-1.0</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="1">
-        <v>6001.0</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="8">
-        <v>6002.0</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>27</v>
+      <c r="F34" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="8">
+        <v>34</v>
+      </c>
+      <c r="J34" s="10">
         <v>0.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="s">
-        <v>12</v>
+      <c r="A35" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="1">
-        <v>6002.0</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="8">
-        <v>6003.0</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="8">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>5002.0</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="12">
+        <v>5003.0</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="14">
         <v>0.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="s">
-        <v>12</v>
+      <c r="A36" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1">
-        <v>6003.0</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="8">
-        <v>6004.0</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>68</v>
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>5003.0</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-1.0</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="8">
-        <v>-1.0</v>
+        <v>34</v>
+      </c>
+      <c r="J36" s="10">
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -1987,23 +2219,23 @@
         <v>12</v>
       </c>
       <c r="C37" s="1">
-        <v>6004.0</v>
+        <v>6001.0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E37" s="8">
-        <v>6005.0</v>
+        <v>6002.0</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J37" s="8">
         <v>0.0</v>
@@ -2017,26 +2249,26 @@
         <v>12</v>
       </c>
       <c r="C38" s="1">
-        <v>6005.0</v>
+        <v>6002.0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E38" s="8">
-        <v>6006.0</v>
+        <v>6003.0</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J38" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -2047,26 +2279,26 @@
         <v>12</v>
       </c>
       <c r="C39" s="1">
-        <v>6006.0</v>
+        <v>6003.0</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E39" s="8">
-        <v>6007.0</v>
+        <v>6004.0</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J39" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="40">
@@ -2077,26 +2309,26 @@
         <v>12</v>
       </c>
       <c r="C40" s="1">
-        <v>6007.0</v>
+        <v>6004.0</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E40" s="8">
-        <v>6008.0</v>
+        <v>6005.0</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J40" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -2107,26 +2339,26 @@
         <v>12</v>
       </c>
       <c r="C41" s="1">
-        <v>6008.0</v>
+        <v>6005.0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E41" s="8">
-        <v>6009.0</v>
+        <v>6006.0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J41" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="42">
@@ -2137,28 +2369,26 @@
         <v>12</v>
       </c>
       <c r="C42" s="1">
-        <v>6009.0</v>
+        <v>6006.0</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.0</v>
+        <v>6007.0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>75</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J42" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -2166,26 +2396,26 @@
         <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1">
-        <v>6010.0</v>
+        <v>6007.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E43" s="8">
-        <v>6011.0</v>
+        <v>6008.0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J43" s="8">
         <v>-1.0</v>
@@ -2196,26 +2426,26 @@
         <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1">
-        <v>6011.0</v>
+        <v>6008.0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E44" s="8">
-        <v>6012.0</v>
+        <v>6009.0</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J44" s="8">
         <v>0.0</v>
@@ -2226,26 +2456,28 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1">
-        <v>6012.0</v>
+        <v>6009.0</v>
       </c>
       <c r="D45" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="8">
-        <v>6013.0</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15" t="s">
-        <v>28</v>
+      <c r="H45" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J45" s="8">
         <v>-1.0</v>
@@ -2256,26 +2488,26 @@
         <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1">
-        <v>6013.0</v>
+        <v>6010.0</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E46" s="8">
-        <v>-1.0</v>
+        <v>6011.0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="15" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J46" s="8">
         <v>-1.0</v>
@@ -2286,29 +2518,29 @@
         <v>12</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C47" s="1">
-        <v>6014.0</v>
+        <v>6011.0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E47" s="8">
-        <v>6015.0</v>
+        <v>6012.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H47" s="15"/>
       <c r="I47" s="15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J47" s="8">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -2316,26 +2548,26 @@
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C48" s="1">
-        <v>6015.0</v>
+        <v>6012.0</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E48" s="8">
-        <v>6016.0</v>
+        <v>6013.0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J48" s="8">
         <v>-1.0</v>
@@ -2346,26 +2578,26 @@
         <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C49" s="1">
-        <v>6016.0</v>
+        <v>6013.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E49" s="8">
-        <v>6017.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J49" s="8">
         <v>-1.0</v>
@@ -2376,56 +2608,56 @@
         <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C50" s="1">
-        <v>6017.0</v>
+        <v>6014.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="E50" s="8">
-        <v>-1.0</v>
+        <v>6015.0</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="15" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J50" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C51" s="1">
-        <v>7001.0</v>
+        <v>6015.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E51" s="8">
-        <v>7002.0</v>
+        <v>6016.0</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="7" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="J51" s="8">
         <v>-1.0</v>
@@ -2433,62 +2665,62 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C52" s="1">
-        <v>7002.0</v>
+        <v>6016.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E52" s="8">
-        <v>7003.0</v>
+        <v>6017.0</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="7" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="J52" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C53" s="1">
-        <v>7003.0</v>
+        <v>6017.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E53" s="8">
-        <v>7004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H53" s="17"/>
-      <c r="I53" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="J53" s="8">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
@@ -2499,26 +2731,26 @@
         <v>14</v>
       </c>
       <c r="C54" s="1">
-        <v>7004.0</v>
+        <v>7001.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E54" s="8">
-        <v>7005.0</v>
+        <v>7002.0</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H54" s="15"/>
+        <v>79</v>
+      </c>
+      <c r="H54" s="17"/>
       <c r="I54" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J54" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="55">
@@ -2529,26 +2761,26 @@
         <v>14</v>
       </c>
       <c r="C55" s="1">
-        <v>7005.0</v>
+        <v>7002.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E55" s="8">
-        <v>7006.0</v>
+        <v>7003.0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H55" s="17"/>
-      <c r="I55" s="15" t="s">
-        <v>28</v>
+      <c r="I55" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J55" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -2559,26 +2791,26 @@
         <v>14</v>
       </c>
       <c r="C56" s="1">
-        <v>7006.0</v>
+        <v>7003.0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E56" s="8">
-        <v>7007.0</v>
+        <v>7004.0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J56" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="57">
@@ -2589,26 +2821,26 @@
         <v>14</v>
       </c>
       <c r="C57" s="1">
-        <v>7007.0</v>
+        <v>7004.0</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E57" s="8">
-        <v>7008.0</v>
+        <v>7005.0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H57" s="17"/>
-      <c r="I57" s="15" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="H57" s="15"/>
+      <c r="I57" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="J57" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -2619,28 +2851,26 @@
         <v>14</v>
       </c>
       <c r="C58" s="1">
-        <v>7008.0</v>
+        <v>7005.0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E58" s="8">
-        <v>-1.0</v>
+        <v>7006.0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>45</v>
+        <v>79</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="J58" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="59">
@@ -2648,29 +2878,29 @@
         <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C59" s="1">
-        <v>7009.0</v>
+        <v>7006.0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="E59" s="8">
-        <v>7010.0</v>
+        <v>7007.0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H59" s="15"/>
-      <c r="I59" s="8" t="s">
-        <v>28</v>
+      <c r="I59" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="J59" s="8">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -2678,26 +2908,26 @@
         <v>14</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C60" s="1">
-        <v>7010.0</v>
+        <v>7007.0</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E60" s="8">
-        <v>7011.0</v>
+        <v>7008.0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H60" s="15"/>
-      <c r="I60" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="J60" s="8">
         <v>-1.0</v>
@@ -2708,26 +2938,28 @@
         <v>14</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C61" s="1">
-        <v>7011.0</v>
+        <v>7008.0</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E61" s="8">
-        <v>7012.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="15"/>
-      <c r="I61" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="J61" s="8">
         <v>0.0</v>
@@ -2738,29 +2970,29 @@
         <v>14</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C62" s="1">
-        <v>7012.0</v>
+        <v>7009.0</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="E62" s="8">
-        <v>-1.0</v>
+        <v>7010.0</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J62" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="63">
@@ -2768,26 +3000,26 @@
         <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1">
-        <v>7013.0</v>
+        <v>7010.0</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E63" s="8">
-        <v>7014.0</v>
+        <v>7011.0</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J63" s="8">
         <v>-1.0</v>
@@ -2798,29 +3030,29 @@
         <v>14</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C64" s="1">
-        <v>7014.0</v>
+        <v>7011.0</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E64" s="8">
-        <v>7015.0</v>
+        <v>7012.0</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J64" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -2828,29 +3060,29 @@
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C65" s="1">
-        <v>7015.0</v>
+        <v>7012.0</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E65" s="8">
-        <v>7016.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J65" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="66">
@@ -2858,26 +3090,26 @@
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C66" s="1">
-        <v>7016.0</v>
+        <v>7013.0</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E66" s="8">
-        <v>7017.0</v>
+        <v>7014.0</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J66" s="8">
         <v>-1.0</v>
@@ -2888,119 +3120,119 @@
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C67" s="1">
-        <v>7017.0</v>
+        <v>7014.0</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E67" s="8">
-        <v>-1.0</v>
+        <v>7015.0</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J67" s="8">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="C68" s="1">
-        <v>8001.0</v>
+        <v>7015.0</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E68" s="8">
-        <v>8002.0</v>
+        <v>7016.0</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H68" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="H68" s="15"/>
       <c r="I68" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J68" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="C69" s="1">
-        <v>8002.0</v>
+        <v>7016.0</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E69" s="8">
-        <v>8003.0</v>
+        <v>7017.0</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="H69" s="15"/>
       <c r="I69" s="8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J69" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="C70" s="1">
-        <v>8003.0</v>
+        <v>7017.0</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E70" s="8">
-        <v>8004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H70" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="H70" s="15"/>
       <c r="I70" s="8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J70" s="8">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="71">
@@ -3011,26 +3243,26 @@
         <v>15</v>
       </c>
       <c r="C71" s="1">
-        <v>8004.0</v>
+        <v>8001.0</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E71" s="8">
-        <v>8005.0</v>
+        <v>8002.0</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J71" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="72">
@@ -3041,26 +3273,26 @@
         <v>15</v>
       </c>
       <c r="C72" s="1">
-        <v>8005.0</v>
+        <v>8002.0</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E72" s="8">
-        <v>8006.0</v>
+        <v>8003.0</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J72" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -3071,25 +3303,23 @@
         <v>15</v>
       </c>
       <c r="C73" s="1">
-        <v>8006.0</v>
+        <v>8003.0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E73" s="8">
-        <v>-1.0</v>
+        <v>8004.0</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H73" s="17"/>
       <c r="I73" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J73" s="8">
         <v>-1.0</v>
@@ -3100,29 +3330,29 @@
         <v>15</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C74" s="1">
-        <v>8007.0</v>
+        <v>8004.0</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E74" s="8">
-        <v>8008.0</v>
+        <v>8005.0</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J74" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -3130,26 +3360,26 @@
         <v>15</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C75" s="1">
-        <v>8008.0</v>
+        <v>8005.0</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E75" s="8">
-        <v>8009.0</v>
+        <v>8006.0</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J75" s="8">
         <v>-1.0</v>
@@ -3160,26 +3390,28 @@
         <v>15</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C76" s="1">
-        <v>8009.0</v>
+        <v>8006.0</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E76" s="8">
-        <v>8010.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H76" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="I76" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J76" s="8">
         <v>-1.0</v>
@@ -3190,26 +3422,26 @@
         <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C77" s="1">
-        <v>8010.0</v>
+        <v>8007.0</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E77" s="8">
-        <v>8011.0</v>
+        <v>8008.0</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H77" s="17"/>
       <c r="I77" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J77" s="8">
         <v>-1.0</v>
@@ -3220,26 +3452,26 @@
         <v>15</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C78" s="1">
-        <v>8011.0</v>
+        <v>8008.0</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E78" s="8">
-        <v>8012.0</v>
+        <v>8009.0</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J78" s="8">
         <v>-1.0</v>
@@ -3250,29 +3482,29 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C79" s="1">
-        <v>8012.0</v>
+        <v>8009.0</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E79" s="8">
-        <v>8013.0</v>
+        <v>8010.0</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H79" s="17"/>
       <c r="I79" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J79" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="80">
@@ -3280,26 +3512,26 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C80" s="1">
-        <v>8013.0</v>
+        <v>8010.0</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="E80" s="8">
-        <v>-1.0</v>
+        <v>8011.0</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J80" s="8">
         <v>-1.0</v>
@@ -3310,29 +3542,29 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C81" s="1">
-        <v>8014.0</v>
+        <v>8011.0</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E81" s="1">
-        <v>8015.0</v>
+        <v>125</v>
+      </c>
+      <c r="E81" s="8">
+        <v>8012.0</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J81" s="8">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="82">
@@ -3340,29 +3572,29 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C82" s="1">
-        <v>8015.0</v>
+        <v>8012.0</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E82" s="1">
-        <v>8016.0</v>
+        <v>126</v>
+      </c>
+      <c r="E82" s="8">
+        <v>8013.0</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J82" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -3370,26 +3602,26 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C83" s="1">
-        <v>8016.0</v>
+        <v>8013.0</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E83" s="1">
-        <v>8017.0</v>
+        <v>127</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-1.0</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J83" s="8">
         <v>-1.0</v>
@@ -3400,29 +3632,29 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C84" s="1">
-        <v>8017.0</v>
+        <v>8014.0</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="E84" s="1">
-        <v>8018.0</v>
+        <v>8015.0</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J84" s="8">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
@@ -3430,29 +3662,29 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C85" s="1">
-        <v>8018.0</v>
+        <v>8015.0</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E85" s="1">
-        <v>8019.0</v>
+        <v>8016.0</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J85" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="86">
@@ -3460,26 +3692,26 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C86" s="1">
-        <v>8019.0</v>
+        <v>8016.0</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E86" s="1">
-        <v>8020.0</v>
+        <v>8017.0</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H86" s="17"/>
       <c r="I86" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J86" s="8">
         <v>-1.0</v>
@@ -3490,29 +3722,29 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C87" s="1">
-        <v>8020.0</v>
+        <v>8017.0</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E87" s="1">
-        <v>8021.0</v>
+        <v>8018.0</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="H87" s="17"/>
       <c r="I87" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J87" s="8">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="88">
@@ -3520,2829 +3752,4086 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C88" s="1">
-        <v>8021.0</v>
+        <v>8018.0</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-1.0</v>
+        <v>132</v>
+      </c>
+      <c r="E88" s="1">
+        <v>8019.0</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="8" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J88" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18"/>
+      <c r="A89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" s="1">
+        <v>8019.0</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="1">
+        <v>8020.0</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H89" s="17"/>
+      <c r="I89" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J89" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="18"/>
+      <c r="A90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="1">
+        <v>8020.0</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E90" s="1">
+        <v>8021.0</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H90" s="17"/>
+      <c r="I90" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J90" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="18"/>
+      <c r="A91" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C91" s="1">
+        <v>8021.0</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H91" s="17"/>
+      <c r="I91" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J91" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="18"/>
+      <c r="A92" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="1">
+        <v>9001.0</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E92" s="8">
+        <v>9002.0</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H92" s="17"/>
+      <c r="I92" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J92" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="18"/>
+      <c r="A93" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="1">
+        <v>9002.0</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E93" s="8">
+        <v>9003.0</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" s="17"/>
+      <c r="I93" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J93" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="18"/>
+      <c r="A94" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="1">
+        <v>9003.0</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J94" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="18"/>
+      <c r="A95" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C95" s="1">
+        <v>9004.0</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H95" s="17"/>
+      <c r="I95" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J95" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="18"/>
+      <c r="A96" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C96" s="1">
+        <v>9005.0</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E96" s="8">
+        <v>9006.0</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H96" s="17"/>
+      <c r="I96" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J96" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="18"/>
+      <c r="A97" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C97" s="1">
+        <v>9006.0</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" s="17"/>
+      <c r="I97" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J97" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="18"/>
+      <c r="A98" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="1">
+        <v>10001.0</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E98" s="8">
+        <v>10002.0</v>
+      </c>
+      <c r="F98" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="17"/>
+      <c r="I98" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="18"/>
+      <c r="A99" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="1">
+        <v>10002.0</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E99" s="8">
+        <v>10003.0</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H99" s="17"/>
+      <c r="I99" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J99" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="18"/>
+      <c r="A100" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="1">
+        <v>10003.0</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" s="8">
+        <v>10004.0</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H100" s="17"/>
+      <c r="I100" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J100" s="8">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="18"/>
+      <c r="A101" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="1">
+        <v>10004.0</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E101" s="8">
+        <v>10005.0</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H101" s="17"/>
+      <c r="I101" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J101" s="8">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="18"/>
+      <c r="A102" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="1">
+        <v>10005.0</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E102" s="8">
+        <v>10006.0</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H102" s="17"/>
+      <c r="I102" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J102" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="18"/>
+      <c r="A103" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="1">
+        <v>10006.0</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E103" s="8">
+        <v>10007.0</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G103" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H103" s="17"/>
+      <c r="I103" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J103" s="8">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="18"/>
+      <c r="A104" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="1">
+        <v>10007.0</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E104" s="8">
+        <v>10008.0</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G104" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H104" s="17"/>
+      <c r="I104" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J104" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="18"/>
+      <c r="A105" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="1">
+        <v>10008.0</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E105" s="8">
+        <v>10009.0</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H105" s="17"/>
+      <c r="I105" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J105" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="18"/>
+      <c r="A106" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="1">
+        <v>10009.0</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E106" s="8">
+        <v>10010.0</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H106" s="17"/>
+      <c r="I106" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J106" s="8">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="18"/>
+      <c r="A107" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10010.0</v>
+      </c>
+      <c r="D107" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E107" s="8">
+        <v>10011.0</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H107" s="17"/>
+      <c r="I107" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J107" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="18"/>
+      <c r="A108" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="1">
+        <v>10011.0</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E108" s="8">
+        <v>10012.0</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H108" s="17"/>
+      <c r="I108" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J108" s="8">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="18"/>
+      <c r="A109" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10012.0</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J109" s="8">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="18"/>
+      <c r="A110" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C110" s="1">
+        <v>10013.0</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E110" s="8">
+        <v>10014.0</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H110" s="17"/>
+      <c r="I110" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J110" s="8">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="18"/>
+      <c r="A111" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C111" s="1">
+        <v>10014.0</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E111" s="8">
+        <v>10015.0</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H111" s="17"/>
+      <c r="I111" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J111" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="18"/>
+      <c r="A112" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C112" s="1">
+        <v>10015.0</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="E112" s="8">
+        <v>10016.0</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H112" s="17"/>
+      <c r="I112" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J112" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="18"/>
+      <c r="A113" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C113" s="1">
+        <v>10016.0</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H113" s="17"/>
+      <c r="I113" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J113" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="18"/>
+      <c r="A114" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C114" s="1">
+        <v>10017.0</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E114" s="8">
+        <v>10018.0</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H114" s="17"/>
+      <c r="I114" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J114" s="8">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="18"/>
+      <c r="A115" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C115" s="1">
+        <v>10018.0</v>
+      </c>
+      <c r="D115" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E115" s="8">
+        <v>10019.0</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H115" s="17"/>
+      <c r="I115" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J115" s="8">
+        <v>7.0</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="18"/>
+      <c r="A116" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C116" s="1">
+        <v>10019.0</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E116" s="8">
+        <v>10020.0</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G116" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H116" s="17"/>
+      <c r="I116" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J116" s="8">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="18"/>
+      <c r="A117" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C117" s="1">
+        <v>10020.0</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G117" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H117" s="17"/>
+      <c r="I117" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J117" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="18"/>
+      <c r="A118" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="1">
+        <v>11001.0</v>
+      </c>
+      <c r="D118" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E118" s="8">
+        <v>11002.0</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H118" s="17"/>
+      <c r="I118" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J118" s="8">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="18"/>
+      <c r="A119" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="1">
+        <v>11002.0</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E119" s="8">
+        <v>11003.0</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G119" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H119" s="17"/>
+      <c r="I119" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J119" s="8">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="18"/>
+      <c r="A120" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="1">
+        <v>11003.0</v>
+      </c>
+      <c r="D120" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E120" s="8">
+        <v>11004.0</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G120" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H120" s="17"/>
+      <c r="I120" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J120" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="18"/>
+      <c r="A121" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="1">
+        <v>11004.0</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E121" s="8">
+        <v>11005.0</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H121" s="17"/>
+      <c r="I121" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J121" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="18"/>
+      <c r="A122" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="1">
+        <v>11005.0</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E122" s="8">
+        <v>11006.0</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H122" s="17"/>
+      <c r="I122" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J122" s="8">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="18"/>
+      <c r="A123" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="1">
+        <v>11006.0</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E123" s="8">
+        <v>11007.0</v>
+      </c>
+      <c r="F123" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G123" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H123" s="17"/>
+      <c r="I123" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J123" s="8">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="18"/>
+      <c r="A124" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="1">
+        <v>11007.0</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="E124" s="8">
+        <v>11008.0</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G124" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H124" s="17"/>
+      <c r="I124" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J124" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="18"/>
+      <c r="A125" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="1">
+        <v>11008.0</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E125" s="8">
+        <v>11009.0</v>
+      </c>
+      <c r="F125" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H125" s="17"/>
+      <c r="I125" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J125" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="18"/>
+      <c r="A126" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" s="1">
+        <v>11009.0</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E126" s="8">
+        <v>11010.0</v>
+      </c>
+      <c r="F126" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G126" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" s="17"/>
+      <c r="I126" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J126" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="18"/>
+      <c r="A127" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" s="1">
+        <v>11010.0</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E127" s="8">
+        <v>11011.0</v>
+      </c>
+      <c r="F127" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G127" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H127" s="17"/>
+      <c r="I127" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J127" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="18"/>
+      <c r="A128" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="1">
+        <v>11011.0</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F128" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G128" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H128" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J128" s="8">
+        <v>8.0</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="18"/>
+      <c r="A129" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C129" s="1">
+        <v>11012.0</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E129" s="8">
+        <v>11013.0</v>
+      </c>
+      <c r="F129" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G129" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H129" s="17"/>
+      <c r="I129" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J129" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="18"/>
+      <c r="A130" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C130" s="1">
+        <v>11013.0</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E130" s="8">
+        <v>11014.0</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G130" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H130" s="17"/>
+      <c r="I130" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J130" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="18"/>
+      <c r="A131" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C131" s="1">
+        <v>11014.0</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F131" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G131" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H131" s="17"/>
+      <c r="I131" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J131" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="18"/>
+      <c r="A132" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C132" s="1">
+        <v>11015.0</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E132" s="8">
+        <v>11016.0</v>
+      </c>
+      <c r="F132" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G132" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" s="17"/>
+      <c r="I132" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J132" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="18"/>
+      <c r="A133" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C133" s="1">
+        <v>11016.0</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E133" s="8">
+        <v>11017.0</v>
+      </c>
+      <c r="F133" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G133" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="17"/>
+      <c r="I133" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J133" s="8">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="18"/>
+      <c r="A134" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C134" s="1">
+        <v>11017.0</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F134" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G134" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H134" s="17"/>
+      <c r="I134" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J134" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="18"/>
+      <c r="A135" s="19"/>
     </row>
     <row r="136">
-      <c r="A136" s="18"/>
+      <c r="A136" s="19"/>
     </row>
     <row r="137">
-      <c r="A137" s="18"/>
+      <c r="A137" s="19"/>
     </row>
     <row r="138">
-      <c r="A138" s="18"/>
+      <c r="A138" s="19"/>
     </row>
     <row r="139">
-      <c r="A139" s="18"/>
+      <c r="A139" s="19"/>
     </row>
     <row r="140">
-      <c r="A140" s="18"/>
+      <c r="A140" s="19"/>
     </row>
     <row r="141">
-      <c r="A141" s="18"/>
+      <c r="A141" s="19"/>
     </row>
     <row r="142">
-      <c r="A142" s="18"/>
+      <c r="A142" s="19"/>
     </row>
     <row r="143">
-      <c r="A143" s="18"/>
+      <c r="A143" s="19"/>
     </row>
     <row r="144">
-      <c r="A144" s="18"/>
+      <c r="A144" s="19"/>
     </row>
     <row r="145">
-      <c r="A145" s="18"/>
+      <c r="A145" s="19"/>
     </row>
     <row r="146">
-      <c r="A146" s="18"/>
+      <c r="A146" s="19"/>
     </row>
     <row r="147">
-      <c r="A147" s="18"/>
+      <c r="A147" s="19"/>
     </row>
     <row r="148">
-      <c r="A148" s="18"/>
+      <c r="A148" s="19"/>
     </row>
     <row r="149">
-      <c r="A149" s="18"/>
+      <c r="A149" s="19"/>
     </row>
     <row r="150">
-      <c r="A150" s="18"/>
+      <c r="A150" s="19"/>
     </row>
     <row r="151">
-      <c r="A151" s="18"/>
+      <c r="A151" s="19"/>
     </row>
     <row r="152">
-      <c r="A152" s="18"/>
+      <c r="A152" s="19"/>
     </row>
     <row r="153">
-      <c r="A153" s="18"/>
+      <c r="A153" s="19"/>
     </row>
     <row r="154">
-      <c r="A154" s="18"/>
+      <c r="A154" s="19"/>
     </row>
     <row r="155">
-      <c r="A155" s="18"/>
+      <c r="A155" s="19"/>
     </row>
     <row r="156">
-      <c r="A156" s="18"/>
+      <c r="A156" s="19"/>
     </row>
     <row r="157">
-      <c r="A157" s="18"/>
+      <c r="A157" s="19"/>
     </row>
     <row r="158">
-      <c r="A158" s="18"/>
+      <c r="A158" s="19"/>
     </row>
     <row r="159">
-      <c r="A159" s="18"/>
+      <c r="A159" s="19"/>
     </row>
     <row r="160">
-      <c r="A160" s="18"/>
+      <c r="A160" s="19"/>
     </row>
     <row r="161">
-      <c r="A161" s="18"/>
+      <c r="A161" s="19"/>
     </row>
     <row r="162">
-      <c r="A162" s="18"/>
+      <c r="A162" s="19"/>
     </row>
     <row r="163">
-      <c r="A163" s="18"/>
+      <c r="A163" s="19"/>
     </row>
     <row r="164">
-      <c r="A164" s="18"/>
+      <c r="A164" s="19"/>
     </row>
     <row r="165">
-      <c r="A165" s="18"/>
+      <c r="A165" s="19"/>
     </row>
     <row r="166">
-      <c r="A166" s="18"/>
+      <c r="A166" s="19"/>
     </row>
     <row r="167">
-      <c r="A167" s="18"/>
+      <c r="A167" s="19"/>
     </row>
     <row r="168">
-      <c r="A168" s="18"/>
+      <c r="A168" s="19"/>
     </row>
     <row r="169">
-      <c r="A169" s="18"/>
+      <c r="A169" s="19"/>
     </row>
     <row r="170">
-      <c r="A170" s="18"/>
+      <c r="A170" s="19"/>
     </row>
     <row r="171">
-      <c r="A171" s="18"/>
+      <c r="A171" s="19"/>
     </row>
     <row r="172">
-      <c r="A172" s="18"/>
+      <c r="A172" s="19"/>
     </row>
     <row r="173">
-      <c r="A173" s="18"/>
+      <c r="A173" s="19"/>
     </row>
     <row r="174">
-      <c r="A174" s="18"/>
+      <c r="A174" s="19"/>
     </row>
     <row r="175">
-      <c r="A175" s="18"/>
+      <c r="A175" s="19"/>
     </row>
     <row r="176">
-      <c r="A176" s="18"/>
+      <c r="A176" s="19"/>
     </row>
     <row r="177">
-      <c r="A177" s="18"/>
+      <c r="A177" s="19"/>
     </row>
     <row r="178">
-      <c r="A178" s="18"/>
+      <c r="A178" s="19"/>
     </row>
     <row r="179">
-      <c r="A179" s="18"/>
+      <c r="A179" s="19"/>
     </row>
     <row r="180">
-      <c r="A180" s="18"/>
+      <c r="A180" s="19"/>
     </row>
     <row r="181">
-      <c r="A181" s="18"/>
+      <c r="A181" s="19"/>
     </row>
     <row r="182">
-      <c r="A182" s="18"/>
+      <c r="A182" s="19"/>
     </row>
     <row r="183">
-      <c r="A183" s="18"/>
+      <c r="A183" s="19"/>
     </row>
     <row r="184">
-      <c r="A184" s="18"/>
+      <c r="A184" s="19"/>
     </row>
     <row r="185">
-      <c r="A185" s="18"/>
+      <c r="A185" s="19"/>
     </row>
     <row r="186">
-      <c r="A186" s="18"/>
+      <c r="A186" s="19"/>
     </row>
     <row r="187">
-      <c r="A187" s="18"/>
+      <c r="A187" s="19"/>
     </row>
     <row r="188">
-      <c r="A188" s="18"/>
+      <c r="A188" s="19"/>
     </row>
     <row r="189">
-      <c r="A189" s="18"/>
+      <c r="A189" s="19"/>
     </row>
     <row r="190">
-      <c r="A190" s="18"/>
+      <c r="A190" s="19"/>
     </row>
     <row r="191">
-      <c r="A191" s="18"/>
+      <c r="A191" s="19"/>
     </row>
     <row r="192">
-      <c r="A192" s="18"/>
+      <c r="A192" s="19"/>
     </row>
     <row r="193">
-      <c r="A193" s="18"/>
+      <c r="A193" s="19"/>
     </row>
     <row r="194">
-      <c r="A194" s="18"/>
+      <c r="A194" s="19"/>
     </row>
     <row r="195">
-      <c r="A195" s="18"/>
+      <c r="A195" s="19"/>
     </row>
     <row r="196">
-      <c r="A196" s="18"/>
+      <c r="A196" s="19"/>
     </row>
     <row r="197">
-      <c r="A197" s="18"/>
+      <c r="A197" s="19"/>
     </row>
     <row r="198">
-      <c r="A198" s="18"/>
+      <c r="A198" s="19"/>
     </row>
     <row r="199">
-      <c r="A199" s="18"/>
+      <c r="A199" s="19"/>
     </row>
     <row r="200">
-      <c r="A200" s="18"/>
+      <c r="A200" s="19"/>
     </row>
     <row r="201">
-      <c r="A201" s="18"/>
+      <c r="A201" s="19"/>
     </row>
     <row r="202">
-      <c r="A202" s="18"/>
+      <c r="A202" s="19"/>
     </row>
     <row r="203">
-      <c r="A203" s="18"/>
+      <c r="A203" s="19"/>
     </row>
     <row r="204">
-      <c r="A204" s="18"/>
+      <c r="A204" s="19"/>
     </row>
     <row r="205">
-      <c r="A205" s="18"/>
+      <c r="A205" s="19"/>
     </row>
     <row r="206">
-      <c r="A206" s="18"/>
+      <c r="A206" s="19"/>
     </row>
     <row r="207">
-      <c r="A207" s="18"/>
+      <c r="A207" s="19"/>
     </row>
     <row r="208">
-      <c r="A208" s="18"/>
+      <c r="A208" s="19"/>
     </row>
     <row r="209">
-      <c r="A209" s="18"/>
+      <c r="A209" s="19"/>
     </row>
     <row r="210">
-      <c r="A210" s="18"/>
+      <c r="A210" s="19"/>
     </row>
     <row r="211">
-      <c r="A211" s="18"/>
+      <c r="A211" s="19"/>
     </row>
     <row r="212">
-      <c r="A212" s="18"/>
+      <c r="A212" s="19"/>
     </row>
     <row r="213">
-      <c r="A213" s="18"/>
+      <c r="A213" s="19"/>
     </row>
     <row r="214">
-      <c r="A214" s="18"/>
+      <c r="A214" s="19"/>
     </row>
     <row r="215">
-      <c r="A215" s="18"/>
+      <c r="A215" s="19"/>
     </row>
     <row r="216">
-      <c r="A216" s="18"/>
+      <c r="A216" s="19"/>
     </row>
     <row r="217">
-      <c r="A217" s="18"/>
+      <c r="A217" s="19"/>
     </row>
     <row r="218">
-      <c r="A218" s="18"/>
+      <c r="A218" s="19"/>
     </row>
     <row r="219">
-      <c r="A219" s="18"/>
+      <c r="A219" s="19"/>
     </row>
     <row r="220">
-      <c r="A220" s="18"/>
+      <c r="A220" s="19"/>
     </row>
     <row r="221">
-      <c r="A221" s="18"/>
+      <c r="A221" s="19"/>
     </row>
     <row r="222">
-      <c r="A222" s="18"/>
+      <c r="A222" s="19"/>
     </row>
     <row r="223">
-      <c r="A223" s="18"/>
+      <c r="A223" s="19"/>
     </row>
     <row r="224">
-      <c r="A224" s="18"/>
+      <c r="A224" s="19"/>
     </row>
     <row r="225">
-      <c r="A225" s="18"/>
+      <c r="A225" s="19"/>
     </row>
     <row r="226">
-      <c r="A226" s="18"/>
+      <c r="A226" s="19"/>
     </row>
     <row r="227">
-      <c r="A227" s="18"/>
+      <c r="A227" s="19"/>
     </row>
     <row r="228">
-      <c r="A228" s="18"/>
+      <c r="A228" s="19"/>
     </row>
     <row r="229">
-      <c r="A229" s="18"/>
+      <c r="A229" s="19"/>
     </row>
     <row r="230">
-      <c r="A230" s="18"/>
+      <c r="A230" s="19"/>
     </row>
     <row r="231">
-      <c r="A231" s="18"/>
+      <c r="A231" s="19"/>
     </row>
     <row r="232">
-      <c r="A232" s="18"/>
+      <c r="A232" s="19"/>
     </row>
     <row r="233">
-      <c r="A233" s="18"/>
+      <c r="A233" s="19"/>
     </row>
     <row r="234">
-      <c r="A234" s="18"/>
+      <c r="A234" s="19"/>
     </row>
     <row r="235">
-      <c r="A235" s="18"/>
+      <c r="A235" s="19"/>
     </row>
     <row r="236">
-      <c r="A236" s="18"/>
+      <c r="A236" s="19"/>
     </row>
     <row r="237">
-      <c r="A237" s="18"/>
+      <c r="A237" s="19"/>
     </row>
     <row r="238">
-      <c r="A238" s="18"/>
+      <c r="A238" s="19"/>
     </row>
     <row r="239">
-      <c r="A239" s="18"/>
+      <c r="A239" s="19"/>
     </row>
     <row r="240">
-      <c r="A240" s="18"/>
+      <c r="A240" s="19"/>
     </row>
     <row r="241">
-      <c r="A241" s="18"/>
+      <c r="A241" s="19"/>
     </row>
     <row r="242">
-      <c r="A242" s="18"/>
+      <c r="A242" s="19"/>
     </row>
     <row r="243">
-      <c r="A243" s="18"/>
+      <c r="A243" s="19"/>
     </row>
     <row r="244">
-      <c r="A244" s="18"/>
+      <c r="A244" s="19"/>
     </row>
     <row r="245">
-      <c r="A245" s="18"/>
+      <c r="A245" s="19"/>
     </row>
     <row r="246">
-      <c r="A246" s="18"/>
+      <c r="A246" s="19"/>
     </row>
     <row r="247">
-      <c r="A247" s="18"/>
+      <c r="A247" s="19"/>
     </row>
     <row r="248">
-      <c r="A248" s="18"/>
+      <c r="A248" s="19"/>
     </row>
     <row r="249">
-      <c r="A249" s="18"/>
+      <c r="A249" s="19"/>
     </row>
     <row r="250">
-      <c r="A250" s="18"/>
+      <c r="A250" s="19"/>
     </row>
     <row r="251">
-      <c r="A251" s="18"/>
+      <c r="A251" s="19"/>
     </row>
     <row r="252">
-      <c r="A252" s="18"/>
+      <c r="A252" s="19"/>
     </row>
     <row r="253">
-      <c r="A253" s="18"/>
+      <c r="A253" s="19"/>
     </row>
     <row r="254">
-      <c r="A254" s="18"/>
+      <c r="A254" s="19"/>
     </row>
     <row r="255">
-      <c r="A255" s="18"/>
+      <c r="A255" s="19"/>
     </row>
     <row r="256">
-      <c r="A256" s="18"/>
+      <c r="A256" s="19"/>
     </row>
     <row r="257">
-      <c r="A257" s="18"/>
+      <c r="A257" s="19"/>
     </row>
     <row r="258">
-      <c r="A258" s="18"/>
+      <c r="A258" s="19"/>
     </row>
     <row r="259">
-      <c r="A259" s="18"/>
+      <c r="A259" s="19"/>
     </row>
     <row r="260">
-      <c r="A260" s="18"/>
+      <c r="A260" s="19"/>
     </row>
     <row r="261">
-      <c r="A261" s="18"/>
+      <c r="A261" s="19"/>
     </row>
     <row r="262">
-      <c r="A262" s="18"/>
+      <c r="A262" s="19"/>
     </row>
     <row r="263">
-      <c r="A263" s="18"/>
+      <c r="A263" s="19"/>
     </row>
     <row r="264">
-      <c r="A264" s="18"/>
+      <c r="A264" s="19"/>
     </row>
     <row r="265">
-      <c r="A265" s="18"/>
+      <c r="A265" s="19"/>
     </row>
     <row r="266">
-      <c r="A266" s="18"/>
+      <c r="A266" s="19"/>
     </row>
     <row r="267">
-      <c r="A267" s="18"/>
+      <c r="A267" s="19"/>
     </row>
     <row r="268">
-      <c r="A268" s="18"/>
+      <c r="A268" s="19"/>
     </row>
     <row r="269">
-      <c r="A269" s="18"/>
+      <c r="A269" s="19"/>
     </row>
     <row r="270">
-      <c r="A270" s="18"/>
+      <c r="A270" s="19"/>
     </row>
     <row r="271">
-      <c r="A271" s="18"/>
+      <c r="A271" s="19"/>
     </row>
     <row r="272">
-      <c r="A272" s="18"/>
+      <c r="A272" s="19"/>
     </row>
     <row r="273">
-      <c r="A273" s="18"/>
+      <c r="A273" s="19"/>
     </row>
     <row r="274">
-      <c r="A274" s="18"/>
+      <c r="A274" s="19"/>
     </row>
     <row r="275">
-      <c r="A275" s="18"/>
+      <c r="A275" s="19"/>
     </row>
     <row r="276">
-      <c r="A276" s="18"/>
+      <c r="A276" s="19"/>
     </row>
     <row r="277">
-      <c r="A277" s="18"/>
+      <c r="A277" s="19"/>
     </row>
     <row r="278">
-      <c r="A278" s="18"/>
+      <c r="A278" s="19"/>
     </row>
     <row r="279">
-      <c r="A279" s="18"/>
+      <c r="A279" s="19"/>
     </row>
     <row r="280">
-      <c r="A280" s="18"/>
+      <c r="A280" s="19"/>
     </row>
     <row r="281">
-      <c r="A281" s="18"/>
+      <c r="A281" s="19"/>
     </row>
     <row r="282">
-      <c r="A282" s="18"/>
+      <c r="A282" s="19"/>
     </row>
     <row r="283">
-      <c r="A283" s="18"/>
+      <c r="A283" s="19"/>
     </row>
     <row r="284">
-      <c r="A284" s="18"/>
+      <c r="A284" s="19"/>
     </row>
     <row r="285">
-      <c r="A285" s="18"/>
+      <c r="A285" s="19"/>
     </row>
     <row r="286">
-      <c r="A286" s="18"/>
+      <c r="A286" s="19"/>
     </row>
     <row r="287">
-      <c r="A287" s="18"/>
+      <c r="A287" s="19"/>
     </row>
     <row r="288">
-      <c r="A288" s="18"/>
+      <c r="A288" s="19"/>
     </row>
     <row r="289">
-      <c r="A289" s="18"/>
+      <c r="A289" s="19"/>
     </row>
     <row r="290">
-      <c r="A290" s="18"/>
+      <c r="A290" s="19"/>
     </row>
     <row r="291">
-      <c r="A291" s="18"/>
+      <c r="A291" s="19"/>
     </row>
     <row r="292">
-      <c r="A292" s="18"/>
+      <c r="A292" s="19"/>
     </row>
     <row r="293">
-      <c r="A293" s="18"/>
+      <c r="A293" s="19"/>
     </row>
     <row r="294">
-      <c r="A294" s="18"/>
+      <c r="A294" s="19"/>
     </row>
     <row r="295">
-      <c r="A295" s="18"/>
+      <c r="A295" s="19"/>
     </row>
     <row r="296">
-      <c r="A296" s="18"/>
+      <c r="A296" s="19"/>
     </row>
     <row r="297">
-      <c r="A297" s="18"/>
+      <c r="A297" s="19"/>
     </row>
     <row r="298">
-      <c r="A298" s="18"/>
+      <c r="A298" s="19"/>
     </row>
     <row r="299">
-      <c r="A299" s="18"/>
+      <c r="A299" s="19"/>
     </row>
     <row r="300">
-      <c r="A300" s="18"/>
+      <c r="A300" s="19"/>
     </row>
     <row r="301">
-      <c r="A301" s="18"/>
+      <c r="A301" s="19"/>
     </row>
     <row r="302">
-      <c r="A302" s="18"/>
+      <c r="A302" s="19"/>
     </row>
     <row r="303">
-      <c r="A303" s="18"/>
+      <c r="A303" s="19"/>
     </row>
     <row r="304">
-      <c r="A304" s="18"/>
+      <c r="A304" s="19"/>
     </row>
     <row r="305">
-      <c r="A305" s="18"/>
+      <c r="A305" s="19"/>
     </row>
     <row r="306">
-      <c r="A306" s="18"/>
+      <c r="A306" s="19"/>
     </row>
     <row r="307">
-      <c r="A307" s="18"/>
+      <c r="A307" s="19"/>
     </row>
     <row r="308">
-      <c r="A308" s="18"/>
+      <c r="A308" s="19"/>
     </row>
     <row r="309">
-      <c r="A309" s="18"/>
+      <c r="A309" s="19"/>
     </row>
     <row r="310">
-      <c r="A310" s="18"/>
+      <c r="A310" s="19"/>
     </row>
     <row r="311">
-      <c r="A311" s="18"/>
+      <c r="A311" s="19"/>
     </row>
     <row r="312">
-      <c r="A312" s="18"/>
+      <c r="A312" s="19"/>
     </row>
     <row r="313">
-      <c r="A313" s="18"/>
+      <c r="A313" s="19"/>
     </row>
     <row r="314">
-      <c r="A314" s="18"/>
+      <c r="A314" s="19"/>
     </row>
     <row r="315">
-      <c r="A315" s="18"/>
+      <c r="A315" s="19"/>
     </row>
     <row r="316">
-      <c r="A316" s="18"/>
+      <c r="A316" s="19"/>
     </row>
     <row r="317">
-      <c r="A317" s="18"/>
+      <c r="A317" s="19"/>
     </row>
     <row r="318">
-      <c r="A318" s="18"/>
+      <c r="A318" s="19"/>
     </row>
     <row r="319">
-      <c r="A319" s="18"/>
+      <c r="A319" s="19"/>
     </row>
     <row r="320">
-      <c r="A320" s="18"/>
+      <c r="A320" s="19"/>
     </row>
     <row r="321">
-      <c r="A321" s="18"/>
+      <c r="A321" s="19"/>
     </row>
     <row r="322">
-      <c r="A322" s="18"/>
+      <c r="A322" s="19"/>
     </row>
     <row r="323">
-      <c r="A323" s="18"/>
+      <c r="A323" s="19"/>
     </row>
     <row r="324">
-      <c r="A324" s="18"/>
+      <c r="A324" s="19"/>
     </row>
     <row r="325">
-      <c r="A325" s="18"/>
+      <c r="A325" s="19"/>
     </row>
     <row r="326">
-      <c r="A326" s="18"/>
+      <c r="A326" s="19"/>
     </row>
     <row r="327">
-      <c r="A327" s="18"/>
+      <c r="A327" s="19"/>
     </row>
     <row r="328">
-      <c r="A328" s="18"/>
+      <c r="A328" s="19"/>
     </row>
     <row r="329">
-      <c r="A329" s="18"/>
+      <c r="A329" s="19"/>
     </row>
     <row r="330">
-      <c r="A330" s="18"/>
+      <c r="A330" s="19"/>
     </row>
     <row r="331">
-      <c r="A331" s="18"/>
+      <c r="A331" s="19"/>
     </row>
     <row r="332">
-      <c r="A332" s="18"/>
+      <c r="A332" s="19"/>
     </row>
     <row r="333">
-      <c r="A333" s="18"/>
+      <c r="A333" s="19"/>
     </row>
     <row r="334">
-      <c r="A334" s="18"/>
+      <c r="A334" s="19"/>
     </row>
     <row r="335">
-      <c r="A335" s="18"/>
+      <c r="A335" s="19"/>
     </row>
     <row r="336">
-      <c r="A336" s="18"/>
+      <c r="A336" s="19"/>
     </row>
     <row r="337">
-      <c r="A337" s="18"/>
+      <c r="A337" s="19"/>
     </row>
     <row r="338">
-      <c r="A338" s="18"/>
+      <c r="A338" s="19"/>
     </row>
     <row r="339">
-      <c r="A339" s="18"/>
+      <c r="A339" s="19"/>
     </row>
     <row r="340">
-      <c r="A340" s="18"/>
+      <c r="A340" s="19"/>
     </row>
     <row r="341">
-      <c r="A341" s="18"/>
+      <c r="A341" s="19"/>
     </row>
     <row r="342">
-      <c r="A342" s="18"/>
+      <c r="A342" s="19"/>
     </row>
     <row r="343">
-      <c r="A343" s="18"/>
+      <c r="A343" s="19"/>
     </row>
     <row r="344">
-      <c r="A344" s="18"/>
+      <c r="A344" s="19"/>
     </row>
     <row r="345">
-      <c r="A345" s="18"/>
+      <c r="A345" s="19"/>
     </row>
     <row r="346">
-      <c r="A346" s="18"/>
+      <c r="A346" s="19"/>
     </row>
     <row r="347">
-      <c r="A347" s="18"/>
+      <c r="A347" s="19"/>
     </row>
     <row r="348">
-      <c r="A348" s="18"/>
+      <c r="A348" s="19"/>
     </row>
     <row r="349">
-      <c r="A349" s="18"/>
+      <c r="A349" s="19"/>
     </row>
     <row r="350">
-      <c r="A350" s="18"/>
+      <c r="A350" s="19"/>
     </row>
     <row r="351">
-      <c r="A351" s="18"/>
+      <c r="A351" s="19"/>
     </row>
     <row r="352">
-      <c r="A352" s="18"/>
+      <c r="A352" s="19"/>
     </row>
     <row r="353">
-      <c r="A353" s="18"/>
+      <c r="A353" s="19"/>
     </row>
     <row r="354">
-      <c r="A354" s="18"/>
+      <c r="A354" s="19"/>
     </row>
     <row r="355">
-      <c r="A355" s="18"/>
+      <c r="A355" s="19"/>
     </row>
     <row r="356">
-      <c r="A356" s="18"/>
+      <c r="A356" s="19"/>
     </row>
     <row r="357">
-      <c r="A357" s="18"/>
+      <c r="A357" s="19"/>
     </row>
     <row r="358">
-      <c r="A358" s="18"/>
+      <c r="A358" s="19"/>
     </row>
     <row r="359">
-      <c r="A359" s="18"/>
+      <c r="A359" s="19"/>
     </row>
     <row r="360">
-      <c r="A360" s="18"/>
+      <c r="A360" s="19"/>
     </row>
     <row r="361">
-      <c r="A361" s="18"/>
+      <c r="A361" s="19"/>
     </row>
     <row r="362">
-      <c r="A362" s="18"/>
+      <c r="A362" s="19"/>
     </row>
     <row r="363">
-      <c r="A363" s="18"/>
+      <c r="A363" s="19"/>
     </row>
     <row r="364">
-      <c r="A364" s="18"/>
+      <c r="A364" s="19"/>
     </row>
     <row r="365">
-      <c r="A365" s="18"/>
+      <c r="A365" s="19"/>
     </row>
     <row r="366">
-      <c r="A366" s="18"/>
+      <c r="A366" s="19"/>
     </row>
     <row r="367">
-      <c r="A367" s="18"/>
+      <c r="A367" s="19"/>
     </row>
     <row r="368">
-      <c r="A368" s="18"/>
+      <c r="A368" s="19"/>
     </row>
     <row r="369">
-      <c r="A369" s="18"/>
+      <c r="A369" s="19"/>
     </row>
     <row r="370">
-      <c r="A370" s="18"/>
+      <c r="A370" s="19"/>
     </row>
     <row r="371">
-      <c r="A371" s="18"/>
+      <c r="A371" s="19"/>
     </row>
     <row r="372">
-      <c r="A372" s="18"/>
+      <c r="A372" s="19"/>
     </row>
     <row r="373">
-      <c r="A373" s="18"/>
+      <c r="A373" s="19"/>
     </row>
     <row r="374">
-      <c r="A374" s="18"/>
+      <c r="A374" s="19"/>
     </row>
     <row r="375">
-      <c r="A375" s="18"/>
+      <c r="A375" s="19"/>
     </row>
     <row r="376">
-      <c r="A376" s="18"/>
+      <c r="A376" s="19"/>
     </row>
     <row r="377">
-      <c r="A377" s="18"/>
+      <c r="A377" s="19"/>
     </row>
     <row r="378">
-      <c r="A378" s="18"/>
+      <c r="A378" s="19"/>
     </row>
     <row r="379">
-      <c r="A379" s="18"/>
+      <c r="A379" s="19"/>
     </row>
     <row r="380">
-      <c r="A380" s="18"/>
+      <c r="A380" s="19"/>
     </row>
     <row r="381">
-      <c r="A381" s="18"/>
+      <c r="A381" s="19"/>
     </row>
     <row r="382">
-      <c r="A382" s="18"/>
+      <c r="A382" s="19"/>
     </row>
     <row r="383">
-      <c r="A383" s="18"/>
+      <c r="A383" s="19"/>
     </row>
     <row r="384">
-      <c r="A384" s="18"/>
+      <c r="A384" s="19"/>
     </row>
     <row r="385">
-      <c r="A385" s="18"/>
+      <c r="A385" s="19"/>
     </row>
     <row r="386">
-      <c r="A386" s="18"/>
+      <c r="A386" s="19"/>
     </row>
     <row r="387">
-      <c r="A387" s="18"/>
+      <c r="A387" s="19"/>
     </row>
     <row r="388">
-      <c r="A388" s="18"/>
+      <c r="A388" s="19"/>
     </row>
     <row r="389">
-      <c r="A389" s="18"/>
+      <c r="A389" s="19"/>
     </row>
     <row r="390">
-      <c r="A390" s="18"/>
+      <c r="A390" s="19"/>
     </row>
     <row r="391">
-      <c r="A391" s="18"/>
+      <c r="A391" s="19"/>
     </row>
     <row r="392">
-      <c r="A392" s="18"/>
+      <c r="A392" s="19"/>
     </row>
     <row r="393">
-      <c r="A393" s="18"/>
+      <c r="A393" s="19"/>
     </row>
     <row r="394">
-      <c r="A394" s="18"/>
+      <c r="A394" s="19"/>
     </row>
     <row r="395">
-      <c r="A395" s="18"/>
+      <c r="A395" s="19"/>
     </row>
     <row r="396">
-      <c r="A396" s="18"/>
+      <c r="A396" s="19"/>
     </row>
     <row r="397">
-      <c r="A397" s="18"/>
+      <c r="A397" s="19"/>
     </row>
     <row r="398">
-      <c r="A398" s="18"/>
+      <c r="A398" s="19"/>
     </row>
     <row r="399">
-      <c r="A399" s="18"/>
+      <c r="A399" s="19"/>
     </row>
     <row r="400">
-      <c r="A400" s="18"/>
+      <c r="A400" s="19"/>
     </row>
     <row r="401">
-      <c r="A401" s="18"/>
+      <c r="A401" s="19"/>
     </row>
     <row r="402">
-      <c r="A402" s="18"/>
+      <c r="A402" s="19"/>
     </row>
     <row r="403">
-      <c r="A403" s="18"/>
+      <c r="A403" s="19"/>
     </row>
     <row r="404">
-      <c r="A404" s="18"/>
+      <c r="A404" s="19"/>
     </row>
     <row r="405">
-      <c r="A405" s="18"/>
+      <c r="A405" s="19"/>
     </row>
     <row r="406">
-      <c r="A406" s="18"/>
+      <c r="A406" s="19"/>
     </row>
     <row r="407">
-      <c r="A407" s="18"/>
+      <c r="A407" s="19"/>
     </row>
     <row r="408">
-      <c r="A408" s="18"/>
+      <c r="A408" s="19"/>
     </row>
     <row r="409">
-      <c r="A409" s="18"/>
+      <c r="A409" s="19"/>
     </row>
     <row r="410">
-      <c r="A410" s="18"/>
+      <c r="A410" s="19"/>
     </row>
     <row r="411">
-      <c r="A411" s="18"/>
+      <c r="A411" s="19"/>
     </row>
     <row r="412">
-      <c r="A412" s="18"/>
+      <c r="A412" s="19"/>
     </row>
     <row r="413">
-      <c r="A413" s="18"/>
+      <c r="A413" s="19"/>
     </row>
     <row r="414">
-      <c r="A414" s="18"/>
+      <c r="A414" s="19"/>
     </row>
     <row r="415">
-      <c r="A415" s="18"/>
+      <c r="A415" s="19"/>
     </row>
     <row r="416">
-      <c r="A416" s="18"/>
+      <c r="A416" s="19"/>
     </row>
     <row r="417">
-      <c r="A417" s="18"/>
+      <c r="A417" s="19"/>
     </row>
     <row r="418">
-      <c r="A418" s="18"/>
+      <c r="A418" s="19"/>
     </row>
     <row r="419">
-      <c r="A419" s="18"/>
+      <c r="A419" s="19"/>
     </row>
     <row r="420">
-      <c r="A420" s="18"/>
+      <c r="A420" s="19"/>
     </row>
     <row r="421">
-      <c r="A421" s="18"/>
+      <c r="A421" s="19"/>
     </row>
     <row r="422">
-      <c r="A422" s="18"/>
+      <c r="A422" s="19"/>
     </row>
     <row r="423">
-      <c r="A423" s="18"/>
+      <c r="A423" s="19"/>
     </row>
     <row r="424">
-      <c r="A424" s="18"/>
+      <c r="A424" s="19"/>
     </row>
     <row r="425">
-      <c r="A425" s="18"/>
+      <c r="A425" s="19"/>
     </row>
     <row r="426">
-      <c r="A426" s="18"/>
+      <c r="A426" s="19"/>
     </row>
     <row r="427">
-      <c r="A427" s="18"/>
+      <c r="A427" s="19"/>
     </row>
     <row r="428">
-      <c r="A428" s="18"/>
+      <c r="A428" s="19"/>
     </row>
     <row r="429">
-      <c r="A429" s="18"/>
+      <c r="A429" s="19"/>
     </row>
     <row r="430">
-      <c r="A430" s="18"/>
+      <c r="A430" s="19"/>
     </row>
     <row r="431">
-      <c r="A431" s="18"/>
+      <c r="A431" s="19"/>
     </row>
     <row r="432">
-      <c r="A432" s="18"/>
+      <c r="A432" s="19"/>
     </row>
     <row r="433">
-      <c r="A433" s="18"/>
+      <c r="A433" s="19"/>
     </row>
     <row r="434">
-      <c r="A434" s="18"/>
+      <c r="A434" s="19"/>
     </row>
     <row r="435">
-      <c r="A435" s="18"/>
+      <c r="A435" s="19"/>
     </row>
     <row r="436">
-      <c r="A436" s="18"/>
+      <c r="A436" s="19"/>
     </row>
     <row r="437">
-      <c r="A437" s="18"/>
+      <c r="A437" s="19"/>
     </row>
     <row r="438">
-      <c r="A438" s="18"/>
+      <c r="A438" s="19"/>
     </row>
     <row r="439">
-      <c r="A439" s="18"/>
+      <c r="A439" s="19"/>
     </row>
     <row r="440">
-      <c r="A440" s="18"/>
+      <c r="A440" s="19"/>
     </row>
     <row r="441">
-      <c r="A441" s="18"/>
+      <c r="A441" s="19"/>
     </row>
     <row r="442">
-      <c r="A442" s="18"/>
+      <c r="A442" s="19"/>
     </row>
     <row r="443">
-      <c r="A443" s="18"/>
+      <c r="A443" s="19"/>
     </row>
     <row r="444">
-      <c r="A444" s="18"/>
+      <c r="A444" s="19"/>
     </row>
     <row r="445">
-      <c r="A445" s="18"/>
+      <c r="A445" s="19"/>
     </row>
     <row r="446">
-      <c r="A446" s="18"/>
+      <c r="A446" s="19"/>
     </row>
     <row r="447">
-      <c r="A447" s="18"/>
+      <c r="A447" s="19"/>
     </row>
     <row r="448">
-      <c r="A448" s="18"/>
+      <c r="A448" s="19"/>
     </row>
     <row r="449">
-      <c r="A449" s="18"/>
+      <c r="A449" s="19"/>
     </row>
     <row r="450">
-      <c r="A450" s="18"/>
+      <c r="A450" s="19"/>
     </row>
     <row r="451">
-      <c r="A451" s="18"/>
+      <c r="A451" s="19"/>
     </row>
     <row r="452">
-      <c r="A452" s="18"/>
+      <c r="A452" s="19"/>
     </row>
     <row r="453">
-      <c r="A453" s="18"/>
+      <c r="A453" s="19"/>
     </row>
     <row r="454">
-      <c r="A454" s="18"/>
+      <c r="A454" s="19"/>
     </row>
     <row r="455">
-      <c r="A455" s="18"/>
+      <c r="A455" s="19"/>
     </row>
     <row r="456">
-      <c r="A456" s="18"/>
+      <c r="A456" s="19"/>
     </row>
     <row r="457">
-      <c r="A457" s="18"/>
+      <c r="A457" s="19"/>
     </row>
     <row r="458">
-      <c r="A458" s="18"/>
+      <c r="A458" s="19"/>
     </row>
     <row r="459">
-      <c r="A459" s="18"/>
+      <c r="A459" s="19"/>
     </row>
     <row r="460">
-      <c r="A460" s="18"/>
+      <c r="A460" s="19"/>
     </row>
     <row r="461">
-      <c r="A461" s="18"/>
+      <c r="A461" s="19"/>
     </row>
     <row r="462">
-      <c r="A462" s="18"/>
+      <c r="A462" s="19"/>
     </row>
     <row r="463">
-      <c r="A463" s="18"/>
+      <c r="A463" s="19"/>
     </row>
     <row r="464">
-      <c r="A464" s="18"/>
+      <c r="A464" s="19"/>
     </row>
     <row r="465">
-      <c r="A465" s="18"/>
+      <c r="A465" s="19"/>
     </row>
     <row r="466">
-      <c r="A466" s="18"/>
+      <c r="A466" s="19"/>
     </row>
     <row r="467">
-      <c r="A467" s="18"/>
+      <c r="A467" s="19"/>
     </row>
     <row r="468">
-      <c r="A468" s="18"/>
+      <c r="A468" s="19"/>
     </row>
     <row r="469">
-      <c r="A469" s="18"/>
+      <c r="A469" s="19"/>
     </row>
     <row r="470">
-      <c r="A470" s="18"/>
+      <c r="A470" s="19"/>
     </row>
     <row r="471">
-      <c r="A471" s="18"/>
+      <c r="A471" s="19"/>
     </row>
     <row r="472">
-      <c r="A472" s="18"/>
+      <c r="A472" s="19"/>
     </row>
     <row r="473">
-      <c r="A473" s="18"/>
+      <c r="A473" s="19"/>
     </row>
     <row r="474">
-      <c r="A474" s="18"/>
+      <c r="A474" s="19"/>
     </row>
     <row r="475">
-      <c r="A475" s="18"/>
+      <c r="A475" s="19"/>
     </row>
     <row r="476">
-      <c r="A476" s="18"/>
+      <c r="A476" s="19"/>
     </row>
     <row r="477">
-      <c r="A477" s="18"/>
+      <c r="A477" s="19"/>
     </row>
     <row r="478">
-      <c r="A478" s="18"/>
+      <c r="A478" s="19"/>
     </row>
     <row r="479">
-      <c r="A479" s="18"/>
+      <c r="A479" s="19"/>
     </row>
     <row r="480">
-      <c r="A480" s="18"/>
+      <c r="A480" s="19"/>
     </row>
     <row r="481">
-      <c r="A481" s="18"/>
+      <c r="A481" s="19"/>
     </row>
     <row r="482">
-      <c r="A482" s="18"/>
+      <c r="A482" s="19"/>
     </row>
     <row r="483">
-      <c r="A483" s="18"/>
+      <c r="A483" s="19"/>
     </row>
     <row r="484">
-      <c r="A484" s="18"/>
+      <c r="A484" s="19"/>
     </row>
     <row r="485">
-      <c r="A485" s="18"/>
+      <c r="A485" s="19"/>
     </row>
     <row r="486">
-      <c r="A486" s="18"/>
+      <c r="A486" s="19"/>
     </row>
     <row r="487">
-      <c r="A487" s="18"/>
+      <c r="A487" s="19"/>
     </row>
     <row r="488">
-      <c r="A488" s="18"/>
+      <c r="A488" s="19"/>
     </row>
     <row r="489">
-      <c r="A489" s="18"/>
+      <c r="A489" s="19"/>
     </row>
     <row r="490">
-      <c r="A490" s="18"/>
+      <c r="A490" s="19"/>
     </row>
     <row r="491">
-      <c r="A491" s="18"/>
+      <c r="A491" s="19"/>
     </row>
     <row r="492">
-      <c r="A492" s="18"/>
+      <c r="A492" s="19"/>
     </row>
     <row r="493">
-      <c r="A493" s="18"/>
+      <c r="A493" s="19"/>
     </row>
     <row r="494">
-      <c r="A494" s="18"/>
+      <c r="A494" s="19"/>
     </row>
     <row r="495">
-      <c r="A495" s="18"/>
+      <c r="A495" s="19"/>
     </row>
     <row r="496">
-      <c r="A496" s="18"/>
+      <c r="A496" s="19"/>
     </row>
     <row r="497">
-      <c r="A497" s="18"/>
+      <c r="A497" s="19"/>
     </row>
     <row r="498">
-      <c r="A498" s="18"/>
+      <c r="A498" s="19"/>
     </row>
     <row r="499">
-      <c r="A499" s="18"/>
+      <c r="A499" s="19"/>
     </row>
     <row r="500">
-      <c r="A500" s="18"/>
+      <c r="A500" s="19"/>
     </row>
     <row r="501">
-      <c r="A501" s="18"/>
+      <c r="A501" s="19"/>
     </row>
     <row r="502">
-      <c r="A502" s="18"/>
+      <c r="A502" s="19"/>
     </row>
     <row r="503">
-      <c r="A503" s="18"/>
+      <c r="A503" s="19"/>
     </row>
     <row r="504">
-      <c r="A504" s="18"/>
+      <c r="A504" s="19"/>
     </row>
     <row r="505">
-      <c r="A505" s="18"/>
+      <c r="A505" s="19"/>
     </row>
     <row r="506">
-      <c r="A506" s="18"/>
+      <c r="A506" s="19"/>
     </row>
     <row r="507">
-      <c r="A507" s="18"/>
+      <c r="A507" s="19"/>
     </row>
     <row r="508">
-      <c r="A508" s="18"/>
+      <c r="A508" s="19"/>
     </row>
     <row r="509">
-      <c r="A509" s="18"/>
+      <c r="A509" s="19"/>
     </row>
     <row r="510">
-      <c r="A510" s="18"/>
+      <c r="A510" s="19"/>
     </row>
     <row r="511">
-      <c r="A511" s="18"/>
+      <c r="A511" s="19"/>
     </row>
     <row r="512">
-      <c r="A512" s="18"/>
+      <c r="A512" s="19"/>
     </row>
     <row r="513">
-      <c r="A513" s="18"/>
+      <c r="A513" s="19"/>
     </row>
     <row r="514">
-      <c r="A514" s="18"/>
+      <c r="A514" s="19"/>
     </row>
     <row r="515">
-      <c r="A515" s="18"/>
+      <c r="A515" s="19"/>
     </row>
     <row r="516">
-      <c r="A516" s="18"/>
+      <c r="A516" s="19"/>
     </row>
     <row r="517">
-      <c r="A517" s="18"/>
+      <c r="A517" s="19"/>
     </row>
     <row r="518">
-      <c r="A518" s="18"/>
+      <c r="A518" s="19"/>
     </row>
     <row r="519">
-      <c r="A519" s="18"/>
+      <c r="A519" s="19"/>
     </row>
     <row r="520">
-      <c r="A520" s="18"/>
+      <c r="A520" s="19"/>
     </row>
     <row r="521">
-      <c r="A521" s="18"/>
+      <c r="A521" s="19"/>
     </row>
     <row r="522">
-      <c r="A522" s="18"/>
+      <c r="A522" s="19"/>
     </row>
     <row r="523">
-      <c r="A523" s="18"/>
+      <c r="A523" s="19"/>
     </row>
     <row r="524">
-      <c r="A524" s="18"/>
+      <c r="A524" s="19"/>
     </row>
     <row r="525">
-      <c r="A525" s="18"/>
+      <c r="A525" s="19"/>
     </row>
     <row r="526">
-      <c r="A526" s="18"/>
+      <c r="A526" s="19"/>
     </row>
     <row r="527">
-      <c r="A527" s="18"/>
+      <c r="A527" s="19"/>
     </row>
     <row r="528">
-      <c r="A528" s="18"/>
+      <c r="A528" s="19"/>
     </row>
     <row r="529">
-      <c r="A529" s="18"/>
+      <c r="A529" s="19"/>
     </row>
     <row r="530">
-      <c r="A530" s="18"/>
+      <c r="A530" s="19"/>
     </row>
     <row r="531">
-      <c r="A531" s="18"/>
+      <c r="A531" s="19"/>
     </row>
     <row r="532">
-      <c r="A532" s="18"/>
+      <c r="A532" s="19"/>
     </row>
     <row r="533">
-      <c r="A533" s="18"/>
+      <c r="A533" s="19"/>
     </row>
     <row r="534">
-      <c r="A534" s="18"/>
+      <c r="A534" s="19"/>
     </row>
     <row r="535">
-      <c r="A535" s="18"/>
+      <c r="A535" s="19"/>
     </row>
     <row r="536">
-      <c r="A536" s="18"/>
+      <c r="A536" s="19"/>
     </row>
     <row r="537">
-      <c r="A537" s="18"/>
+      <c r="A537" s="19"/>
     </row>
     <row r="538">
-      <c r="A538" s="18"/>
+      <c r="A538" s="19"/>
     </row>
     <row r="539">
-      <c r="A539" s="18"/>
+      <c r="A539" s="19"/>
     </row>
     <row r="540">
-      <c r="A540" s="18"/>
+      <c r="A540" s="19"/>
     </row>
     <row r="541">
-      <c r="A541" s="18"/>
+      <c r="A541" s="19"/>
     </row>
     <row r="542">
-      <c r="A542" s="18"/>
+      <c r="A542" s="19"/>
     </row>
     <row r="543">
-      <c r="A543" s="18"/>
+      <c r="A543" s="19"/>
     </row>
     <row r="544">
-      <c r="A544" s="18"/>
+      <c r="A544" s="19"/>
     </row>
     <row r="545">
-      <c r="A545" s="18"/>
+      <c r="A545" s="19"/>
     </row>
     <row r="546">
-      <c r="A546" s="18"/>
+      <c r="A546" s="19"/>
     </row>
     <row r="547">
-      <c r="A547" s="18"/>
+      <c r="A547" s="19"/>
     </row>
     <row r="548">
-      <c r="A548" s="18"/>
+      <c r="A548" s="19"/>
     </row>
     <row r="549">
-      <c r="A549" s="18"/>
+      <c r="A549" s="19"/>
     </row>
     <row r="550">
-      <c r="A550" s="18"/>
+      <c r="A550" s="19"/>
     </row>
     <row r="551">
-      <c r="A551" s="18"/>
+      <c r="A551" s="19"/>
     </row>
     <row r="552">
-      <c r="A552" s="18"/>
+      <c r="A552" s="19"/>
     </row>
     <row r="553">
-      <c r="A553" s="18"/>
+      <c r="A553" s="19"/>
     </row>
     <row r="554">
-      <c r="A554" s="18"/>
+      <c r="A554" s="19"/>
     </row>
     <row r="555">
-      <c r="A555" s="18"/>
+      <c r="A555" s="19"/>
     </row>
     <row r="556">
-      <c r="A556" s="18"/>
+      <c r="A556" s="19"/>
     </row>
     <row r="557">
-      <c r="A557" s="18"/>
+      <c r="A557" s="19"/>
     </row>
     <row r="558">
-      <c r="A558" s="18"/>
+      <c r="A558" s="19"/>
     </row>
     <row r="559">
-      <c r="A559" s="18"/>
+      <c r="A559" s="19"/>
     </row>
     <row r="560">
-      <c r="A560" s="18"/>
+      <c r="A560" s="19"/>
     </row>
     <row r="561">
-      <c r="A561" s="18"/>
+      <c r="A561" s="19"/>
     </row>
     <row r="562">
-      <c r="A562" s="18"/>
+      <c r="A562" s="19"/>
     </row>
     <row r="563">
-      <c r="A563" s="18"/>
+      <c r="A563" s="19"/>
     </row>
     <row r="564">
-      <c r="A564" s="18"/>
+      <c r="A564" s="19"/>
     </row>
     <row r="565">
-      <c r="A565" s="18"/>
+      <c r="A565" s="19"/>
     </row>
     <row r="566">
-      <c r="A566" s="18"/>
+      <c r="A566" s="19"/>
     </row>
     <row r="567">
-      <c r="A567" s="18"/>
+      <c r="A567" s="19"/>
     </row>
     <row r="568">
-      <c r="A568" s="18"/>
+      <c r="A568" s="19"/>
     </row>
     <row r="569">
-      <c r="A569" s="18"/>
+      <c r="A569" s="19"/>
     </row>
     <row r="570">
-      <c r="A570" s="18"/>
+      <c r="A570" s="19"/>
     </row>
     <row r="571">
-      <c r="A571" s="18"/>
+      <c r="A571" s="19"/>
     </row>
     <row r="572">
-      <c r="A572" s="18"/>
+      <c r="A572" s="19"/>
     </row>
     <row r="573">
-      <c r="A573" s="18"/>
+      <c r="A573" s="19"/>
     </row>
     <row r="574">
-      <c r="A574" s="18"/>
+      <c r="A574" s="19"/>
     </row>
     <row r="575">
-      <c r="A575" s="18"/>
+      <c r="A575" s="19"/>
     </row>
     <row r="576">
-      <c r="A576" s="18"/>
+      <c r="A576" s="19"/>
     </row>
     <row r="577">
-      <c r="A577" s="18"/>
+      <c r="A577" s="19"/>
     </row>
     <row r="578">
-      <c r="A578" s="18"/>
+      <c r="A578" s="19"/>
     </row>
     <row r="579">
-      <c r="A579" s="18"/>
+      <c r="A579" s="19"/>
     </row>
     <row r="580">
-      <c r="A580" s="18"/>
+      <c r="A580" s="19"/>
     </row>
     <row r="581">
-      <c r="A581" s="18"/>
+      <c r="A581" s="19"/>
     </row>
     <row r="582">
-      <c r="A582" s="18"/>
+      <c r="A582" s="19"/>
     </row>
     <row r="583">
-      <c r="A583" s="18"/>
+      <c r="A583" s="19"/>
     </row>
     <row r="584">
-      <c r="A584" s="18"/>
+      <c r="A584" s="19"/>
     </row>
     <row r="585">
-      <c r="A585" s="18"/>
+      <c r="A585" s="19"/>
     </row>
     <row r="586">
-      <c r="A586" s="18"/>
+      <c r="A586" s="19"/>
     </row>
     <row r="587">
-      <c r="A587" s="18"/>
+      <c r="A587" s="19"/>
     </row>
     <row r="588">
-      <c r="A588" s="18"/>
+      <c r="A588" s="19"/>
     </row>
     <row r="589">
-      <c r="A589" s="18"/>
+      <c r="A589" s="19"/>
     </row>
     <row r="590">
-      <c r="A590" s="18"/>
+      <c r="A590" s="19"/>
     </row>
     <row r="591">
-      <c r="A591" s="18"/>
+      <c r="A591" s="19"/>
     </row>
     <row r="592">
-      <c r="A592" s="18"/>
+      <c r="A592" s="19"/>
     </row>
     <row r="593">
-      <c r="A593" s="18"/>
+      <c r="A593" s="19"/>
     </row>
     <row r="594">
-      <c r="A594" s="18"/>
+      <c r="A594" s="19"/>
     </row>
     <row r="595">
-      <c r="A595" s="18"/>
+      <c r="A595" s="19"/>
     </row>
     <row r="596">
-      <c r="A596" s="18"/>
+      <c r="A596" s="19"/>
     </row>
     <row r="597">
-      <c r="A597" s="18"/>
+      <c r="A597" s="19"/>
     </row>
     <row r="598">
-      <c r="A598" s="18"/>
+      <c r="A598" s="19"/>
     </row>
     <row r="599">
-      <c r="A599" s="18"/>
+      <c r="A599" s="19"/>
     </row>
     <row r="600">
-      <c r="A600" s="18"/>
+      <c r="A600" s="19"/>
     </row>
     <row r="601">
-      <c r="A601" s="18"/>
+      <c r="A601" s="19"/>
     </row>
     <row r="602">
-      <c r="A602" s="18"/>
+      <c r="A602" s="19"/>
     </row>
     <row r="603">
-      <c r="A603" s="18"/>
+      <c r="A603" s="19"/>
     </row>
     <row r="604">
-      <c r="A604" s="18"/>
+      <c r="A604" s="19"/>
     </row>
     <row r="605">
-      <c r="A605" s="18"/>
+      <c r="A605" s="19"/>
     </row>
     <row r="606">
-      <c r="A606" s="18"/>
+      <c r="A606" s="19"/>
     </row>
     <row r="607">
-      <c r="A607" s="18"/>
+      <c r="A607" s="19"/>
     </row>
     <row r="608">
-      <c r="A608" s="18"/>
+      <c r="A608" s="19"/>
     </row>
     <row r="609">
-      <c r="A609" s="18"/>
+      <c r="A609" s="19"/>
     </row>
     <row r="610">
-      <c r="A610" s="18"/>
+      <c r="A610" s="19"/>
     </row>
     <row r="611">
-      <c r="A611" s="18"/>
+      <c r="A611" s="19"/>
     </row>
     <row r="612">
-      <c r="A612" s="18"/>
+      <c r="A612" s="19"/>
     </row>
     <row r="613">
-      <c r="A613" s="18"/>
+      <c r="A613" s="19"/>
     </row>
     <row r="614">
-      <c r="A614" s="18"/>
+      <c r="A614" s="19"/>
     </row>
     <row r="615">
-      <c r="A615" s="18"/>
+      <c r="A615" s="19"/>
     </row>
     <row r="616">
-      <c r="A616" s="18"/>
+      <c r="A616" s="19"/>
     </row>
     <row r="617">
-      <c r="A617" s="18"/>
+      <c r="A617" s="19"/>
     </row>
     <row r="618">
-      <c r="A618" s="18"/>
+      <c r="A618" s="19"/>
     </row>
     <row r="619">
-      <c r="A619" s="18"/>
+      <c r="A619" s="19"/>
     </row>
     <row r="620">
-      <c r="A620" s="18"/>
+      <c r="A620" s="19"/>
     </row>
     <row r="621">
-      <c r="A621" s="18"/>
+      <c r="A621" s="19"/>
     </row>
     <row r="622">
-      <c r="A622" s="18"/>
+      <c r="A622" s="19"/>
     </row>
     <row r="623">
-      <c r="A623" s="18"/>
+      <c r="A623" s="19"/>
     </row>
     <row r="624">
-      <c r="A624" s="18"/>
+      <c r="A624" s="19"/>
     </row>
     <row r="625">
-      <c r="A625" s="18"/>
+      <c r="A625" s="19"/>
     </row>
     <row r="626">
-      <c r="A626" s="18"/>
+      <c r="A626" s="19"/>
     </row>
     <row r="627">
-      <c r="A627" s="18"/>
+      <c r="A627" s="19"/>
     </row>
     <row r="628">
-      <c r="A628" s="18"/>
+      <c r="A628" s="19"/>
     </row>
     <row r="629">
-      <c r="A629" s="18"/>
+      <c r="A629" s="19"/>
     </row>
     <row r="630">
-      <c r="A630" s="18"/>
+      <c r="A630" s="19"/>
     </row>
     <row r="631">
-      <c r="A631" s="18"/>
+      <c r="A631" s="19"/>
     </row>
     <row r="632">
-      <c r="A632" s="18"/>
+      <c r="A632" s="19"/>
     </row>
     <row r="633">
-      <c r="A633" s="18"/>
+      <c r="A633" s="19"/>
     </row>
     <row r="634">
-      <c r="A634" s="18"/>
+      <c r="A634" s="19"/>
     </row>
     <row r="635">
-      <c r="A635" s="18"/>
+      <c r="A635" s="19"/>
     </row>
     <row r="636">
-      <c r="A636" s="18"/>
+      <c r="A636" s="19"/>
     </row>
     <row r="637">
-      <c r="A637" s="18"/>
+      <c r="A637" s="19"/>
     </row>
     <row r="638">
-      <c r="A638" s="18"/>
+      <c r="A638" s="19"/>
     </row>
     <row r="639">
-      <c r="A639" s="18"/>
+      <c r="A639" s="19"/>
     </row>
     <row r="640">
-      <c r="A640" s="18"/>
+      <c r="A640" s="19"/>
     </row>
     <row r="641">
-      <c r="A641" s="18"/>
+      <c r="A641" s="19"/>
     </row>
     <row r="642">
-      <c r="A642" s="18"/>
+      <c r="A642" s="19"/>
     </row>
     <row r="643">
-      <c r="A643" s="18"/>
+      <c r="A643" s="19"/>
     </row>
     <row r="644">
-      <c r="A644" s="18"/>
+      <c r="A644" s="19"/>
     </row>
     <row r="645">
-      <c r="A645" s="18"/>
+      <c r="A645" s="19"/>
     </row>
     <row r="646">
-      <c r="A646" s="18"/>
+      <c r="A646" s="19"/>
     </row>
     <row r="647">
-      <c r="A647" s="18"/>
+      <c r="A647" s="19"/>
     </row>
     <row r="648">
-      <c r="A648" s="18"/>
+      <c r="A648" s="19"/>
     </row>
     <row r="649">
-      <c r="A649" s="18"/>
+      <c r="A649" s="19"/>
     </row>
     <row r="650">
-      <c r="A650" s="18"/>
+      <c r="A650" s="19"/>
     </row>
     <row r="651">
-      <c r="A651" s="18"/>
+      <c r="A651" s="19"/>
     </row>
     <row r="652">
-      <c r="A652" s="18"/>
+      <c r="A652" s="19"/>
     </row>
     <row r="653">
-      <c r="A653" s="18"/>
+      <c r="A653" s="19"/>
     </row>
     <row r="654">
-      <c r="A654" s="18"/>
+      <c r="A654" s="19"/>
     </row>
     <row r="655">
-      <c r="A655" s="18"/>
+      <c r="A655" s="19"/>
     </row>
     <row r="656">
-      <c r="A656" s="18"/>
+      <c r="A656" s="19"/>
     </row>
     <row r="657">
-      <c r="A657" s="18"/>
+      <c r="A657" s="19"/>
     </row>
     <row r="658">
-      <c r="A658" s="18"/>
+      <c r="A658" s="19"/>
     </row>
     <row r="659">
-      <c r="A659" s="18"/>
+      <c r="A659" s="19"/>
     </row>
     <row r="660">
-      <c r="A660" s="18"/>
+      <c r="A660" s="19"/>
     </row>
     <row r="661">
-      <c r="A661" s="18"/>
+      <c r="A661" s="19"/>
     </row>
     <row r="662">
-      <c r="A662" s="18"/>
+      <c r="A662" s="19"/>
     </row>
     <row r="663">
-      <c r="A663" s="18"/>
+      <c r="A663" s="19"/>
     </row>
     <row r="664">
-      <c r="A664" s="18"/>
+      <c r="A664" s="19"/>
     </row>
     <row r="665">
-      <c r="A665" s="18"/>
+      <c r="A665" s="19"/>
     </row>
     <row r="666">
-      <c r="A666" s="18"/>
+      <c r="A666" s="19"/>
     </row>
     <row r="667">
-      <c r="A667" s="18"/>
+      <c r="A667" s="19"/>
     </row>
     <row r="668">
-      <c r="A668" s="18"/>
+      <c r="A668" s="19"/>
     </row>
     <row r="669">
-      <c r="A669" s="18"/>
+      <c r="A669" s="19"/>
     </row>
     <row r="670">
-      <c r="A670" s="18"/>
+      <c r="A670" s="19"/>
     </row>
     <row r="671">
-      <c r="A671" s="18"/>
+      <c r="A671" s="19"/>
     </row>
     <row r="672">
-      <c r="A672" s="18"/>
+      <c r="A672" s="19"/>
     </row>
     <row r="673">
-      <c r="A673" s="18"/>
+      <c r="A673" s="19"/>
     </row>
     <row r="674">
-      <c r="A674" s="18"/>
+      <c r="A674" s="19"/>
     </row>
     <row r="675">
-      <c r="A675" s="18"/>
+      <c r="A675" s="19"/>
     </row>
     <row r="676">
-      <c r="A676" s="18"/>
+      <c r="A676" s="19"/>
     </row>
     <row r="677">
-      <c r="A677" s="18"/>
+      <c r="A677" s="19"/>
     </row>
     <row r="678">
-      <c r="A678" s="18"/>
+      <c r="A678" s="19"/>
     </row>
     <row r="679">
-      <c r="A679" s="18"/>
+      <c r="A679" s="19"/>
     </row>
     <row r="680">
-      <c r="A680" s="18"/>
+      <c r="A680" s="19"/>
     </row>
     <row r="681">
-      <c r="A681" s="18"/>
+      <c r="A681" s="19"/>
     </row>
     <row r="682">
-      <c r="A682" s="18"/>
+      <c r="A682" s="19"/>
     </row>
     <row r="683">
-      <c r="A683" s="18"/>
+      <c r="A683" s="19"/>
     </row>
     <row r="684">
-      <c r="A684" s="18"/>
+      <c r="A684" s="19"/>
     </row>
     <row r="685">
-      <c r="A685" s="18"/>
+      <c r="A685" s="19"/>
     </row>
     <row r="686">
-      <c r="A686" s="18"/>
+      <c r="A686" s="19"/>
     </row>
     <row r="687">
-      <c r="A687" s="18"/>
+      <c r="A687" s="19"/>
     </row>
     <row r="688">
-      <c r="A688" s="18"/>
+      <c r="A688" s="19"/>
     </row>
     <row r="689">
-      <c r="A689" s="18"/>
+      <c r="A689" s="19"/>
     </row>
     <row r="690">
-      <c r="A690" s="18"/>
+      <c r="A690" s="19"/>
     </row>
     <row r="691">
-      <c r="A691" s="18"/>
+      <c r="A691" s="19"/>
     </row>
     <row r="692">
-      <c r="A692" s="18"/>
+      <c r="A692" s="19"/>
     </row>
     <row r="693">
-      <c r="A693" s="18"/>
+      <c r="A693" s="19"/>
     </row>
     <row r="694">
-      <c r="A694" s="18"/>
+      <c r="A694" s="19"/>
     </row>
     <row r="695">
-      <c r="A695" s="18"/>
+      <c r="A695" s="19"/>
     </row>
     <row r="696">
-      <c r="A696" s="18"/>
+      <c r="A696" s="19"/>
     </row>
     <row r="697">
-      <c r="A697" s="18"/>
+      <c r="A697" s="19"/>
     </row>
     <row r="698">
-      <c r="A698" s="18"/>
+      <c r="A698" s="19"/>
     </row>
     <row r="699">
-      <c r="A699" s="18"/>
+      <c r="A699" s="19"/>
     </row>
     <row r="700">
-      <c r="A700" s="18"/>
+      <c r="A700" s="19"/>
     </row>
     <row r="701">
-      <c r="A701" s="18"/>
+      <c r="A701" s="19"/>
     </row>
     <row r="702">
-      <c r="A702" s="18"/>
+      <c r="A702" s="19"/>
     </row>
     <row r="703">
-      <c r="A703" s="18"/>
+      <c r="A703" s="19"/>
     </row>
     <row r="704">
-      <c r="A704" s="18"/>
+      <c r="A704" s="19"/>
     </row>
     <row r="705">
-      <c r="A705" s="18"/>
+      <c r="A705" s="19"/>
     </row>
     <row r="706">
-      <c r="A706" s="18"/>
+      <c r="A706" s="19"/>
     </row>
     <row r="707">
-      <c r="A707" s="18"/>
+      <c r="A707" s="19"/>
     </row>
     <row r="708">
-      <c r="A708" s="18"/>
+      <c r="A708" s="19"/>
     </row>
     <row r="709">
-      <c r="A709" s="18"/>
+      <c r="A709" s="19"/>
     </row>
     <row r="710">
-      <c r="A710" s="18"/>
+      <c r="A710" s="19"/>
     </row>
     <row r="711">
-      <c r="A711" s="18"/>
+      <c r="A711" s="19"/>
     </row>
     <row r="712">
-      <c r="A712" s="18"/>
+      <c r="A712" s="19"/>
     </row>
     <row r="713">
-      <c r="A713" s="18"/>
+      <c r="A713" s="19"/>
     </row>
     <row r="714">
-      <c r="A714" s="18"/>
+      <c r="A714" s="19"/>
     </row>
     <row r="715">
-      <c r="A715" s="18"/>
+      <c r="A715" s="19"/>
     </row>
     <row r="716">
-      <c r="A716" s="18"/>
+      <c r="A716" s="19"/>
     </row>
     <row r="717">
-      <c r="A717" s="18"/>
+      <c r="A717" s="19"/>
     </row>
     <row r="718">
-      <c r="A718" s="18"/>
+      <c r="A718" s="19"/>
     </row>
     <row r="719">
-      <c r="A719" s="18"/>
+      <c r="A719" s="19"/>
     </row>
     <row r="720">
-      <c r="A720" s="18"/>
+      <c r="A720" s="19"/>
     </row>
     <row r="721">
-      <c r="A721" s="18"/>
+      <c r="A721" s="19"/>
     </row>
     <row r="722">
-      <c r="A722" s="18"/>
+      <c r="A722" s="19"/>
     </row>
     <row r="723">
-      <c r="A723" s="18"/>
+      <c r="A723" s="19"/>
     </row>
     <row r="724">
-      <c r="A724" s="18"/>
+      <c r="A724" s="19"/>
     </row>
     <row r="725">
-      <c r="A725" s="18"/>
+      <c r="A725" s="19"/>
     </row>
     <row r="726">
-      <c r="A726" s="18"/>
+      <c r="A726" s="19"/>
     </row>
     <row r="727">
-      <c r="A727" s="18"/>
+      <c r="A727" s="19"/>
     </row>
     <row r="728">
-      <c r="A728" s="18"/>
+      <c r="A728" s="19"/>
     </row>
     <row r="729">
-      <c r="A729" s="18"/>
+      <c r="A729" s="19"/>
     </row>
     <row r="730">
-      <c r="A730" s="18"/>
+      <c r="A730" s="19"/>
     </row>
     <row r="731">
-      <c r="A731" s="18"/>
+      <c r="A731" s="19"/>
     </row>
     <row r="732">
-      <c r="A732" s="18"/>
+      <c r="A732" s="19"/>
     </row>
     <row r="733">
-      <c r="A733" s="18"/>
+      <c r="A733" s="19"/>
     </row>
     <row r="734">
-      <c r="A734" s="18"/>
+      <c r="A734" s="19"/>
     </row>
     <row r="735">
-      <c r="A735" s="18"/>
+      <c r="A735" s="19"/>
     </row>
     <row r="736">
-      <c r="A736" s="18"/>
+      <c r="A736" s="19"/>
     </row>
     <row r="737">
-      <c r="A737" s="18"/>
+      <c r="A737" s="19"/>
     </row>
     <row r="738">
-      <c r="A738" s="18"/>
+      <c r="A738" s="19"/>
     </row>
     <row r="739">
-      <c r="A739" s="18"/>
+      <c r="A739" s="19"/>
     </row>
     <row r="740">
-      <c r="A740" s="18"/>
+      <c r="A740" s="19"/>
     </row>
     <row r="741">
-      <c r="A741" s="18"/>
+      <c r="A741" s="19"/>
     </row>
     <row r="742">
-      <c r="A742" s="18"/>
+      <c r="A742" s="19"/>
     </row>
     <row r="743">
-      <c r="A743" s="18"/>
+      <c r="A743" s="19"/>
     </row>
     <row r="744">
-      <c r="A744" s="18"/>
+      <c r="A744" s="19"/>
     </row>
     <row r="745">
-      <c r="A745" s="18"/>
+      <c r="A745" s="19"/>
     </row>
     <row r="746">
-      <c r="A746" s="18"/>
+      <c r="A746" s="19"/>
     </row>
     <row r="747">
-      <c r="A747" s="18"/>
+      <c r="A747" s="19"/>
     </row>
     <row r="748">
-      <c r="A748" s="18"/>
+      <c r="A748" s="19"/>
     </row>
     <row r="749">
-      <c r="A749" s="18"/>
+      <c r="A749" s="19"/>
     </row>
     <row r="750">
-      <c r="A750" s="18"/>
+      <c r="A750" s="19"/>
     </row>
     <row r="751">
-      <c r="A751" s="18"/>
+      <c r="A751" s="19"/>
     </row>
     <row r="752">
-      <c r="A752" s="18"/>
+      <c r="A752" s="19"/>
     </row>
     <row r="753">
-      <c r="A753" s="18"/>
+      <c r="A753" s="19"/>
     </row>
     <row r="754">
-      <c r="A754" s="18"/>
+      <c r="A754" s="19"/>
     </row>
     <row r="755">
-      <c r="A755" s="18"/>
+      <c r="A755" s="19"/>
     </row>
     <row r="756">
-      <c r="A756" s="18"/>
+      <c r="A756" s="19"/>
     </row>
     <row r="757">
-      <c r="A757" s="18"/>
+      <c r="A757" s="19"/>
     </row>
     <row r="758">
-      <c r="A758" s="18"/>
+      <c r="A758" s="19"/>
     </row>
     <row r="759">
-      <c r="A759" s="18"/>
+      <c r="A759" s="19"/>
     </row>
     <row r="760">
-      <c r="A760" s="18"/>
+      <c r="A760" s="19"/>
     </row>
     <row r="761">
-      <c r="A761" s="18"/>
+      <c r="A761" s="19"/>
     </row>
     <row r="762">
-      <c r="A762" s="18"/>
+      <c r="A762" s="19"/>
     </row>
     <row r="763">
-      <c r="A763" s="18"/>
+      <c r="A763" s="19"/>
     </row>
     <row r="764">
-      <c r="A764" s="18"/>
+      <c r="A764" s="19"/>
     </row>
     <row r="765">
-      <c r="A765" s="18"/>
+      <c r="A765" s="19"/>
     </row>
     <row r="766">
-      <c r="A766" s="18"/>
+      <c r="A766" s="19"/>
     </row>
     <row r="767">
-      <c r="A767" s="18"/>
+      <c r="A767" s="19"/>
     </row>
     <row r="768">
-      <c r="A768" s="18"/>
+      <c r="A768" s="19"/>
     </row>
     <row r="769">
-      <c r="A769" s="18"/>
+      <c r="A769" s="19"/>
     </row>
     <row r="770">
-      <c r="A770" s="18"/>
+      <c r="A770" s="19"/>
     </row>
     <row r="771">
-      <c r="A771" s="18"/>
+      <c r="A771" s="19"/>
     </row>
     <row r="772">
-      <c r="A772" s="18"/>
+      <c r="A772" s="19"/>
     </row>
     <row r="773">
-      <c r="A773" s="18"/>
+      <c r="A773" s="19"/>
     </row>
     <row r="774">
-      <c r="A774" s="18"/>
+      <c r="A774" s="19"/>
     </row>
     <row r="775">
-      <c r="A775" s="18"/>
+      <c r="A775" s="19"/>
     </row>
     <row r="776">
-      <c r="A776" s="18"/>
+      <c r="A776" s="19"/>
     </row>
     <row r="777">
-      <c r="A777" s="18"/>
+      <c r="A777" s="19"/>
     </row>
     <row r="778">
-      <c r="A778" s="18"/>
+      <c r="A778" s="19"/>
     </row>
     <row r="779">
-      <c r="A779" s="18"/>
+      <c r="A779" s="19"/>
     </row>
     <row r="780">
-      <c r="A780" s="18"/>
+      <c r="A780" s="19"/>
     </row>
     <row r="781">
-      <c r="A781" s="18"/>
+      <c r="A781" s="19"/>
     </row>
     <row r="782">
-      <c r="A782" s="18"/>
+      <c r="A782" s="19"/>
     </row>
     <row r="783">
-      <c r="A783" s="18"/>
+      <c r="A783" s="19"/>
     </row>
     <row r="784">
-      <c r="A784" s="18"/>
+      <c r="A784" s="19"/>
     </row>
     <row r="785">
-      <c r="A785" s="18"/>
+      <c r="A785" s="19"/>
     </row>
     <row r="786">
-      <c r="A786" s="18"/>
+      <c r="A786" s="19"/>
     </row>
     <row r="787">
-      <c r="A787" s="18"/>
+      <c r="A787" s="19"/>
     </row>
     <row r="788">
-      <c r="A788" s="18"/>
+      <c r="A788" s="19"/>
     </row>
     <row r="789">
-      <c r="A789" s="18"/>
+      <c r="A789" s="19"/>
     </row>
     <row r="790">
-      <c r="A790" s="18"/>
+      <c r="A790" s="19"/>
     </row>
     <row r="791">
-      <c r="A791" s="18"/>
+      <c r="A791" s="19"/>
     </row>
     <row r="792">
-      <c r="A792" s="18"/>
+      <c r="A792" s="19"/>
     </row>
     <row r="793">
-      <c r="A793" s="18"/>
+      <c r="A793" s="19"/>
     </row>
     <row r="794">
-      <c r="A794" s="18"/>
+      <c r="A794" s="19"/>
     </row>
     <row r="795">
-      <c r="A795" s="18"/>
+      <c r="A795" s="19"/>
     </row>
     <row r="796">
-      <c r="A796" s="18"/>
+      <c r="A796" s="19"/>
     </row>
     <row r="797">
-      <c r="A797" s="18"/>
+      <c r="A797" s="19"/>
     </row>
     <row r="798">
-      <c r="A798" s="18"/>
+      <c r="A798" s="19"/>
     </row>
     <row r="799">
-      <c r="A799" s="18"/>
+      <c r="A799" s="19"/>
     </row>
     <row r="800">
-      <c r="A800" s="18"/>
+      <c r="A800" s="19"/>
     </row>
     <row r="801">
-      <c r="A801" s="18"/>
+      <c r="A801" s="19"/>
     </row>
     <row r="802">
-      <c r="A802" s="18"/>
+      <c r="A802" s="19"/>
     </row>
     <row r="803">
-      <c r="A803" s="18"/>
+      <c r="A803" s="19"/>
     </row>
     <row r="804">
-      <c r="A804" s="18"/>
+      <c r="A804" s="19"/>
     </row>
     <row r="805">
-      <c r="A805" s="18"/>
+      <c r="A805" s="19"/>
     </row>
     <row r="806">
-      <c r="A806" s="18"/>
+      <c r="A806" s="19"/>
     </row>
     <row r="807">
-      <c r="A807" s="18"/>
+      <c r="A807" s="19"/>
     </row>
     <row r="808">
-      <c r="A808" s="18"/>
+      <c r="A808" s="19"/>
     </row>
     <row r="809">
-      <c r="A809" s="18"/>
+      <c r="A809" s="19"/>
     </row>
     <row r="810">
-      <c r="A810" s="18"/>
+      <c r="A810" s="19"/>
     </row>
     <row r="811">
-      <c r="A811" s="18"/>
+      <c r="A811" s="19"/>
     </row>
     <row r="812">
-      <c r="A812" s="18"/>
+      <c r="A812" s="19"/>
     </row>
     <row r="813">
-      <c r="A813" s="18"/>
+      <c r="A813" s="19"/>
     </row>
     <row r="814">
-      <c r="A814" s="18"/>
+      <c r="A814" s="19"/>
     </row>
     <row r="815">
-      <c r="A815" s="18"/>
+      <c r="A815" s="19"/>
     </row>
     <row r="816">
-      <c r="A816" s="18"/>
+      <c r="A816" s="19"/>
     </row>
     <row r="817">
-      <c r="A817" s="18"/>
+      <c r="A817" s="19"/>
     </row>
     <row r="818">
-      <c r="A818" s="18"/>
+      <c r="A818" s="19"/>
     </row>
     <row r="819">
-      <c r="A819" s="18"/>
+      <c r="A819" s="19"/>
     </row>
     <row r="820">
-      <c r="A820" s="18"/>
+      <c r="A820" s="19"/>
     </row>
     <row r="821">
-      <c r="A821" s="18"/>
+      <c r="A821" s="19"/>
     </row>
     <row r="822">
-      <c r="A822" s="18"/>
+      <c r="A822" s="19"/>
     </row>
     <row r="823">
-      <c r="A823" s="18"/>
+      <c r="A823" s="19"/>
     </row>
     <row r="824">
-      <c r="A824" s="18"/>
+      <c r="A824" s="19"/>
     </row>
     <row r="825">
-      <c r="A825" s="18"/>
+      <c r="A825" s="19"/>
     </row>
     <row r="826">
-      <c r="A826" s="18"/>
+      <c r="A826" s="19"/>
     </row>
     <row r="827">
-      <c r="A827" s="18"/>
+      <c r="A827" s="19"/>
     </row>
     <row r="828">
-      <c r="A828" s="18"/>
+      <c r="A828" s="19"/>
     </row>
     <row r="829">
-      <c r="A829" s="18"/>
+      <c r="A829" s="19"/>
     </row>
     <row r="830">
-      <c r="A830" s="18"/>
+      <c r="A830" s="19"/>
     </row>
     <row r="831">
-      <c r="A831" s="18"/>
+      <c r="A831" s="19"/>
     </row>
     <row r="832">
-      <c r="A832" s="18"/>
+      <c r="A832" s="19"/>
     </row>
     <row r="833">
-      <c r="A833" s="18"/>
+      <c r="A833" s="19"/>
     </row>
     <row r="834">
-      <c r="A834" s="18"/>
+      <c r="A834" s="19"/>
     </row>
     <row r="835">
-      <c r="A835" s="18"/>
+      <c r="A835" s="19"/>
     </row>
     <row r="836">
-      <c r="A836" s="18"/>
+      <c r="A836" s="19"/>
     </row>
     <row r="837">
-      <c r="A837" s="18"/>
+      <c r="A837" s="19"/>
     </row>
     <row r="838">
-      <c r="A838" s="18"/>
+      <c r="A838" s="19"/>
     </row>
     <row r="839">
-      <c r="A839" s="18"/>
+      <c r="A839" s="19"/>
     </row>
     <row r="840">
-      <c r="A840" s="18"/>
+      <c r="A840" s="19"/>
     </row>
     <row r="841">
-      <c r="A841" s="18"/>
+      <c r="A841" s="19"/>
     </row>
     <row r="842">
-      <c r="A842" s="18"/>
+      <c r="A842" s="19"/>
     </row>
     <row r="843">
-      <c r="A843" s="18"/>
+      <c r="A843" s="19"/>
     </row>
     <row r="844">
-      <c r="A844" s="18"/>
+      <c r="A844" s="19"/>
     </row>
     <row r="845">
-      <c r="A845" s="18"/>
+      <c r="A845" s="19"/>
     </row>
     <row r="846">
-      <c r="A846" s="18"/>
+      <c r="A846" s="19"/>
     </row>
     <row r="847">
-      <c r="A847" s="18"/>
+      <c r="A847" s="19"/>
     </row>
     <row r="848">
-      <c r="A848" s="18"/>
+      <c r="A848" s="19"/>
     </row>
     <row r="849">
-      <c r="A849" s="18"/>
+      <c r="A849" s="19"/>
     </row>
     <row r="850">
-      <c r="A850" s="18"/>
+      <c r="A850" s="19"/>
     </row>
     <row r="851">
-      <c r="A851" s="18"/>
+      <c r="A851" s="19"/>
     </row>
     <row r="852">
-      <c r="A852" s="18"/>
+      <c r="A852" s="19"/>
     </row>
     <row r="853">
-      <c r="A853" s="18"/>
+      <c r="A853" s="19"/>
     </row>
     <row r="854">
-      <c r="A854" s="18"/>
+      <c r="A854" s="19"/>
     </row>
     <row r="855">
-      <c r="A855" s="18"/>
+      <c r="A855" s="19"/>
     </row>
     <row r="856">
-      <c r="A856" s="18"/>
+      <c r="A856" s="19"/>
     </row>
     <row r="857">
-      <c r="A857" s="18"/>
+      <c r="A857" s="19"/>
     </row>
     <row r="858">
-      <c r="A858" s="18"/>
+      <c r="A858" s="19"/>
     </row>
     <row r="859">
-      <c r="A859" s="18"/>
+      <c r="A859" s="19"/>
     </row>
     <row r="860">
-      <c r="A860" s="18"/>
+      <c r="A860" s="19"/>
     </row>
     <row r="861">
-      <c r="A861" s="18"/>
+      <c r="A861" s="19"/>
     </row>
     <row r="862">
-      <c r="A862" s="18"/>
+      <c r="A862" s="19"/>
     </row>
     <row r="863">
-      <c r="A863" s="18"/>
+      <c r="A863" s="19"/>
     </row>
     <row r="864">
-      <c r="A864" s="18"/>
+      <c r="A864" s="19"/>
     </row>
     <row r="865">
-      <c r="A865" s="18"/>
+      <c r="A865" s="19"/>
     </row>
     <row r="866">
-      <c r="A866" s="18"/>
+      <c r="A866" s="19"/>
     </row>
     <row r="867">
-      <c r="A867" s="18"/>
+      <c r="A867" s="19"/>
     </row>
     <row r="868">
-      <c r="A868" s="18"/>
+      <c r="A868" s="19"/>
     </row>
     <row r="869">
-      <c r="A869" s="18"/>
+      <c r="A869" s="19"/>
     </row>
     <row r="870">
-      <c r="A870" s="18"/>
+      <c r="A870" s="19"/>
     </row>
     <row r="871">
-      <c r="A871" s="18"/>
+      <c r="A871" s="19"/>
     </row>
     <row r="872">
-      <c r="A872" s="18"/>
+      <c r="A872" s="19"/>
     </row>
     <row r="873">
-      <c r="A873" s="18"/>
+      <c r="A873" s="19"/>
     </row>
     <row r="874">
-      <c r="A874" s="18"/>
+      <c r="A874" s="19"/>
     </row>
     <row r="875">
-      <c r="A875" s="18"/>
+      <c r="A875" s="19"/>
     </row>
     <row r="876">
-      <c r="A876" s="18"/>
+      <c r="A876" s="19"/>
     </row>
     <row r="877">
-      <c r="A877" s="18"/>
+      <c r="A877" s="19"/>
     </row>
     <row r="878">
-      <c r="A878" s="18"/>
+      <c r="A878" s="19"/>
     </row>
     <row r="879">
-      <c r="A879" s="18"/>
+      <c r="A879" s="19"/>
     </row>
     <row r="880">
-      <c r="A880" s="18"/>
+      <c r="A880" s="19"/>
     </row>
     <row r="881">
-      <c r="A881" s="18"/>
+      <c r="A881" s="19"/>
     </row>
     <row r="882">
-      <c r="A882" s="18"/>
+      <c r="A882" s="19"/>
     </row>
     <row r="883">
-      <c r="A883" s="18"/>
+      <c r="A883" s="19"/>
     </row>
     <row r="884">
-      <c r="A884" s="18"/>
+      <c r="A884" s="19"/>
     </row>
     <row r="885">
-      <c r="A885" s="18"/>
+      <c r="A885" s="19"/>
     </row>
     <row r="886">
-      <c r="A886" s="18"/>
+      <c r="A886" s="19"/>
     </row>
     <row r="887">
-      <c r="A887" s="18"/>
+      <c r="A887" s="19"/>
     </row>
     <row r="888">
-      <c r="A888" s="18"/>
+      <c r="A888" s="19"/>
     </row>
     <row r="889">
-      <c r="A889" s="18"/>
+      <c r="A889" s="19"/>
     </row>
     <row r="890">
-      <c r="A890" s="18"/>
+      <c r="A890" s="19"/>
     </row>
     <row r="891">
-      <c r="A891" s="18"/>
+      <c r="A891" s="19"/>
     </row>
     <row r="892">
-      <c r="A892" s="18"/>
+      <c r="A892" s="19"/>
     </row>
     <row r="893">
-      <c r="A893" s="18"/>
+      <c r="A893" s="19"/>
     </row>
     <row r="894">
-      <c r="A894" s="18"/>
+      <c r="A894" s="19"/>
     </row>
     <row r="895">
-      <c r="A895" s="18"/>
+      <c r="A895" s="19"/>
     </row>
     <row r="896">
-      <c r="A896" s="18"/>
+      <c r="A896" s="19"/>
     </row>
     <row r="897">
-      <c r="A897" s="18"/>
+      <c r="A897" s="19"/>
     </row>
     <row r="898">
-      <c r="A898" s="18"/>
+      <c r="A898" s="19"/>
     </row>
     <row r="899">
-      <c r="A899" s="18"/>
+      <c r="A899" s="19"/>
     </row>
     <row r="900">
-      <c r="A900" s="18"/>
+      <c r="A900" s="19"/>
     </row>
     <row r="901">
-      <c r="A901" s="18"/>
+      <c r="A901" s="19"/>
     </row>
     <row r="902">
-      <c r="A902" s="18"/>
+      <c r="A902" s="19"/>
     </row>
     <row r="903">
-      <c r="A903" s="18"/>
+      <c r="A903" s="19"/>
     </row>
     <row r="904">
-      <c r="A904" s="18"/>
+      <c r="A904" s="19"/>
     </row>
     <row r="905">
-      <c r="A905" s="18"/>
+      <c r="A905" s="19"/>
     </row>
     <row r="906">
-      <c r="A906" s="18"/>
+      <c r="A906" s="19"/>
     </row>
     <row r="907">
-      <c r="A907" s="18"/>
+      <c r="A907" s="19"/>
     </row>
     <row r="908">
-      <c r="A908" s="18"/>
+      <c r="A908" s="19"/>
     </row>
     <row r="909">
-      <c r="A909" s="18"/>
+      <c r="A909" s="19"/>
     </row>
     <row r="910">
-      <c r="A910" s="18"/>
+      <c r="A910" s="19"/>
     </row>
     <row r="911">
-      <c r="A911" s="18"/>
+      <c r="A911" s="19"/>
     </row>
     <row r="912">
-      <c r="A912" s="18"/>
+      <c r="A912" s="19"/>
     </row>
     <row r="913">
-      <c r="A913" s="18"/>
+      <c r="A913" s="19"/>
     </row>
     <row r="914">
-      <c r="A914" s="18"/>
+      <c r="A914" s="19"/>
     </row>
     <row r="915">
-      <c r="A915" s="18"/>
+      <c r="A915" s="19"/>
     </row>
     <row r="916">
-      <c r="A916" s="18"/>
+      <c r="A916" s="19"/>
     </row>
     <row r="917">
-      <c r="A917" s="18"/>
+      <c r="A917" s="19"/>
     </row>
     <row r="918">
-      <c r="A918" s="18"/>
+      <c r="A918" s="19"/>
     </row>
     <row r="919">
-      <c r="A919" s="18"/>
+      <c r="A919" s="19"/>
     </row>
     <row r="920">
-      <c r="A920" s="18"/>
+      <c r="A920" s="19"/>
     </row>
     <row r="921">
-      <c r="A921" s="18"/>
+      <c r="A921" s="19"/>
     </row>
     <row r="922">
-      <c r="A922" s="18"/>
+      <c r="A922" s="19"/>
     </row>
     <row r="923">
-      <c r="A923" s="18"/>
+      <c r="A923" s="19"/>
     </row>
     <row r="924">
-      <c r="A924" s="18"/>
+      <c r="A924" s="19"/>
     </row>
     <row r="925">
-      <c r="A925" s="18"/>
+      <c r="A925" s="19"/>
     </row>
     <row r="926">
-      <c r="A926" s="18"/>
+      <c r="A926" s="19"/>
     </row>
     <row r="927">
-      <c r="A927" s="18"/>
+      <c r="A927" s="19"/>
     </row>
     <row r="928">
-      <c r="A928" s="18"/>
+      <c r="A928" s="19"/>
     </row>
     <row r="929">
-      <c r="A929" s="18"/>
+      <c r="A929" s="19"/>
     </row>
     <row r="930">
-      <c r="A930" s="18"/>
+      <c r="A930" s="19"/>
     </row>
     <row r="931">
-      <c r="A931" s="18"/>
+      <c r="A931" s="19"/>
     </row>
     <row r="932">
-      <c r="A932" s="18"/>
+      <c r="A932" s="19"/>
     </row>
     <row r="933">
-      <c r="A933" s="18"/>
+      <c r="A933" s="19"/>
     </row>
     <row r="934">
-      <c r="A934" s="18"/>
+      <c r="A934" s="19"/>
     </row>
     <row r="935">
-      <c r="A935" s="18"/>
+      <c r="A935" s="19"/>
     </row>
     <row r="936">
-      <c r="A936" s="18"/>
+      <c r="A936" s="19"/>
     </row>
     <row r="937">
-      <c r="A937" s="18"/>
+      <c r="A937" s="19"/>
     </row>
     <row r="938">
-      <c r="A938" s="18"/>
+      <c r="A938" s="19"/>
     </row>
     <row r="939">
-      <c r="A939" s="18"/>
+      <c r="A939" s="19"/>
     </row>
     <row r="940">
-      <c r="A940" s="18"/>
+      <c r="A940" s="19"/>
     </row>
     <row r="941">
-      <c r="A941" s="18"/>
+      <c r="A941" s="19"/>
     </row>
     <row r="942">
-      <c r="A942" s="18"/>
+      <c r="A942" s="19"/>
     </row>
     <row r="943">
-      <c r="A943" s="18"/>
+      <c r="A943" s="19"/>
     </row>
     <row r="944">
-      <c r="A944" s="18"/>
+      <c r="A944" s="19"/>
     </row>
     <row r="945">
-      <c r="A945" s="18"/>
+      <c r="A945" s="19"/>
     </row>
     <row r="946">
-      <c r="A946" s="18"/>
+      <c r="A946" s="19"/>
     </row>
     <row r="947">
-      <c r="A947" s="18"/>
+      <c r="A947" s="19"/>
     </row>
     <row r="948">
-      <c r="A948" s="18"/>
+      <c r="A948" s="19"/>
     </row>
     <row r="949">
-      <c r="A949" s="18"/>
+      <c r="A949" s="19"/>
     </row>
     <row r="950">
-      <c r="A950" s="18"/>
+      <c r="A950" s="19"/>
     </row>
     <row r="951">
-      <c r="A951" s="18"/>
+      <c r="A951" s="19"/>
     </row>
     <row r="952">
-      <c r="A952" s="18"/>
+      <c r="A952" s="19"/>
     </row>
     <row r="953">
-      <c r="A953" s="18"/>
+      <c r="A953" s="19"/>
     </row>
     <row r="954">
-      <c r="A954" s="18"/>
+      <c r="A954" s="19"/>
     </row>
     <row r="955">
-      <c r="A955" s="18"/>
+      <c r="A955" s="19"/>
     </row>
     <row r="956">
-      <c r="A956" s="18"/>
+      <c r="A956" s="19"/>
     </row>
     <row r="957">
-      <c r="A957" s="18"/>
+      <c r="A957" s="19"/>
     </row>
     <row r="958">
-      <c r="A958" s="18"/>
+      <c r="A958" s="19"/>
     </row>
     <row r="959">
-      <c r="A959" s="18"/>
+      <c r="A959" s="19"/>
     </row>
     <row r="960">
-      <c r="A960" s="18"/>
+      <c r="A960" s="19"/>
     </row>
     <row r="961">
-      <c r="A961" s="18"/>
+      <c r="A961" s="19"/>
     </row>
     <row r="962">
-      <c r="A962" s="18"/>
+      <c r="A962" s="19"/>
     </row>
     <row r="963">
-      <c r="A963" s="18"/>
+      <c r="A963" s="19"/>
     </row>
     <row r="964">
-      <c r="A964" s="18"/>
+      <c r="A964" s="19"/>
     </row>
     <row r="965">
-      <c r="A965" s="18"/>
+      <c r="A965" s="19"/>
     </row>
     <row r="966">
-      <c r="A966" s="18"/>
+      <c r="A966" s="19"/>
     </row>
     <row r="967">
-      <c r="A967" s="18"/>
+      <c r="A967" s="19"/>
     </row>
     <row r="968">
-      <c r="A968" s="18"/>
+      <c r="A968" s="19"/>
     </row>
     <row r="969">
-      <c r="A969" s="18"/>
+      <c r="A969" s="19"/>
     </row>
     <row r="970">
-      <c r="A970" s="18"/>
+      <c r="A970" s="19"/>
     </row>
     <row r="971">
-      <c r="A971" s="18"/>
+      <c r="A971" s="19"/>
     </row>
     <row r="972">
-      <c r="A972" s="18"/>
+      <c r="A972" s="19"/>
     </row>
     <row r="973">
-      <c r="A973" s="18"/>
+      <c r="A973" s="19"/>
     </row>
     <row r="974">
-      <c r="A974" s="18"/>
+      <c r="A974" s="19"/>
     </row>
     <row r="975">
-      <c r="A975" s="18"/>
+      <c r="A975" s="19"/>
     </row>
     <row r="976">
-      <c r="A976" s="18"/>
+      <c r="A976" s="19"/>
     </row>
     <row r="977">
-      <c r="A977" s="18"/>
+      <c r="A977" s="19"/>
     </row>
     <row r="978">
-      <c r="A978" s="18"/>
+      <c r="A978" s="19"/>
     </row>
     <row r="979">
-      <c r="A979" s="18"/>
+      <c r="A979" s="19"/>
     </row>
     <row r="980">
-      <c r="A980" s="18"/>
+      <c r="A980" s="19"/>
     </row>
     <row r="981">
-      <c r="A981" s="18"/>
+      <c r="A981" s="19"/>
     </row>
     <row r="982">
-      <c r="A982" s="18"/>
+      <c r="A982" s="19"/>
     </row>
     <row r="983">
-      <c r="A983" s="18"/>
+      <c r="A983" s="19"/>
     </row>
     <row r="984">
-      <c r="A984" s="18"/>
+      <c r="A984" s="19"/>
     </row>
     <row r="985">
-      <c r="A985" s="18"/>
+      <c r="A985" s="19"/>
     </row>
     <row r="986">
-      <c r="A986" s="18"/>
+      <c r="A986" s="19"/>
     </row>
     <row r="987">
-      <c r="A987" s="18"/>
+      <c r="A987" s="19"/>
     </row>
     <row r="988">
-      <c r="A988" s="18"/>
+      <c r="A988" s="19"/>
     </row>
     <row r="989">
-      <c r="A989" s="18"/>
+      <c r="A989" s="19"/>
     </row>
     <row r="990">
-      <c r="A990" s="18"/>
+      <c r="A990" s="19"/>
     </row>
     <row r="991">
-      <c r="A991" s="18"/>
+      <c r="A991" s="19"/>
     </row>
     <row r="992">
-      <c r="A992" s="18"/>
+      <c r="A992" s="19"/>
     </row>
     <row r="993">
-      <c r="A993" s="18"/>
+      <c r="A993" s="19"/>
     </row>
     <row r="994">
-      <c r="A994" s="18"/>
+      <c r="A994" s="19"/>
     </row>
     <row r="995">
-      <c r="A995" s="18"/>
+      <c r="A995" s="19"/>
     </row>
     <row r="996">
-      <c r="A996" s="18"/>
+      <c r="A996" s="19"/>
     </row>
     <row r="997">
-      <c r="A997" s="18"/>
+      <c r="A997" s="19"/>
     </row>
     <row r="998">
-      <c r="A998" s="18"/>
+      <c r="A998" s="19"/>
     </row>
     <row r="999">
-      <c r="A999" s="18"/>
+      <c r="A999" s="19"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="18"/>
+      <c r="A1000" s="19"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="18"/>
+      <c r="A1001" s="19"/>
     </row>
     <row r="1002">
-      <c r="A1002" s="18"/>
+      <c r="A1002" s="19"/>
     </row>
     <row r="1003">
-      <c r="A1003" s="18"/>
+      <c r="A1003" s="19"/>
     </row>
     <row r="1004">
-      <c r="A1004" s="18"/>
+      <c r="A1004" s="19"/>
     </row>
     <row r="1005">
-      <c r="A1005" s="18"/>
+      <c r="A1005" s="19"/>
     </row>
     <row r="1006">
-      <c r="A1006" s="18"/>
+      <c r="A1006" s="19"/>
     </row>
     <row r="1007">
-      <c r="A1007" s="18"/>
+      <c r="A1007" s="19"/>
     </row>
     <row r="1008">
-      <c r="A1008" s="18"/>
+      <c r="A1008" s="19"/>
     </row>
     <row r="1009">
-      <c r="A1009" s="18"/>
+      <c r="A1009" s="19"/>
     </row>
     <row r="1010">
-      <c r="A1010" s="18"/>
+      <c r="A1010" s="19"/>
     </row>
     <row r="1011">
-      <c r="A1011" s="18"/>
+      <c r="A1011" s="19"/>
     </row>
     <row r="1012">
-      <c r="A1012" s="18"/>
+      <c r="A1012" s="19"/>
     </row>
     <row r="1013">
-      <c r="A1013" s="18"/>
+      <c r="A1013" s="19"/>
     </row>
     <row r="1014">
-      <c r="A1014" s="18"/>
+      <c r="A1014" s="19"/>
     </row>
     <row r="1015">
-      <c r="A1015" s="18"/>
+      <c r="A1015" s="19"/>
     </row>
     <row r="1016">
-      <c r="A1016" s="18"/>
+      <c r="A1016" s="19"/>
     </row>
     <row r="1017">
-      <c r="A1017" s="18"/>
+      <c r="A1017" s="19"/>
     </row>
     <row r="1018">
-      <c r="A1018" s="18"/>
+      <c r="A1018" s="19"/>
     </row>
     <row r="1019">
-      <c r="A1019" s="18"/>
+      <c r="A1019" s="19"/>
     </row>
     <row r="1020">
-      <c r="A1020" s="18"/>
+      <c r="A1020" s="19"/>
     </row>
     <row r="1021">
-      <c r="A1021" s="18"/>
+      <c r="A1021" s="19"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="19"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="19"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6358,25 +7847,28 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="15.13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -6384,16 +7876,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -6404,16 +7896,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -6424,16 +7916,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -6444,16 +7936,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -6464,16 +7956,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1">
         <v>-1.0</v>
@@ -6484,16 +7976,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1">
         <v>-1.0</v>
@@ -6504,16 +7996,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1">
         <v>-1.0</v>
@@ -6524,18 +8016,78 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="206">
   <si>
     <t>NpcID</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>혁이</t>
+  </si>
+  <si>
+    <t>N012</t>
+  </si>
+  <si>
+    <t>서린이 방 침대</t>
   </si>
   <si>
     <t>NpcEventID</t>
@@ -599,6 +605,21 @@
     <t>재미... 그렇구나..</t>
   </si>
   <si>
+    <t>자고 일어나면 내일도 학교를 가야겠지...</t>
+  </si>
+  <si>
+    <t>학교...그만두고 싶다..</t>
+  </si>
+  <si>
+    <t>엄마....아빠....보고 싶어요...</t>
+  </si>
+  <si>
+    <t>꿈속에서라도 볼 수 있으면 참 좋을 텐데...</t>
+  </si>
+  <si>
+    <t>어서 잠이나 자야지...</t>
+  </si>
+  <si>
     <t>......................</t>
   </si>
   <si>
@@ -623,6 +644,9 @@
   </si>
   <si>
     <t>아직 할말 남았어?</t>
+  </si>
+  <si>
+    <t>침대</t>
   </si>
 </sst>
 </file>
@@ -801,7 +825,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J134" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J139" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1112,6 +1136,14 @@
         <v>21</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1132,31 +1164,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1170,19 +1202,19 @@
         <v>1001.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1">
         <v>1002.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" s="1">
         <v>-1.0</v>
@@ -1199,19 +1231,19 @@
         <v>1002.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1">
         <v>1003.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" s="1">
         <v>-1.0</v>
@@ -1228,22 +1260,22 @@
         <v>1003.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1">
         <v>-1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" s="1">
         <v>-1.0</v>
@@ -1254,26 +1286,26 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1">
         <v>1004.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1">
         <v>1005.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" s="1">
         <v>-1.0</v>
@@ -1284,26 +1316,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1">
         <v>1005.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1">
         <v>-1.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1">
         <v>-1.0</v>
@@ -1314,26 +1346,26 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1">
         <v>1006.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1">
         <v>1007.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1">
         <v>-1.0</v>
@@ -1344,26 +1376,26 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1">
         <v>1007.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1">
         <v>-1.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J8" s="1">
         <v>-1.0</v>
@@ -1380,19 +1412,19 @@
         <v>2001.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1">
         <v>2002.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J9" s="1">
         <v>-1.0</v>
@@ -1409,19 +1441,19 @@
         <v>2002.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1">
         <v>2003.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" s="1">
         <v>-1.0</v>
@@ -1438,22 +1470,22 @@
         <v>2003.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1">
         <v>-1.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" s="1">
         <v>-1.0</v>
@@ -1464,26 +1496,26 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1">
         <v>2004.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="1">
         <v>2005.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J12" s="1">
         <v>2.0</v>
@@ -1494,26 +1526,26 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1">
         <v>2005.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" s="1">
         <v>-1.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J13" s="1">
         <v>0.0</v>
@@ -1524,26 +1556,26 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1">
         <v>2006.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1">
         <v>-1.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J14" s="1">
         <v>-1.0</v>
@@ -1560,20 +1592,20 @@
         <v>3001.0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" s="8">
         <v>3002.0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J15" s="10">
         <v>0.0</v>
@@ -1590,20 +1622,20 @@
         <v>3002.0</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="12">
         <v>3003.0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J16" s="14">
         <v>-1.0</v>
@@ -1620,20 +1652,20 @@
         <v>3003.0</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="8">
         <v>3004.0</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J17" s="10">
         <v>4.0</v>
@@ -1650,20 +1682,20 @@
         <v>3004.0</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" s="12">
         <v>3005.0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J18" s="14">
         <v>-1.0</v>
@@ -1680,20 +1712,20 @@
         <v>3005.0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E19" s="8">
         <v>3006.0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J19" s="10">
         <v>0.0</v>
@@ -1710,20 +1742,20 @@
         <v>3006.0</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" s="12">
         <v>3007.0</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
         <v>0.0</v>
@@ -1740,20 +1772,20 @@
         <v>3007.0</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E21" s="8">
         <v>3008.0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J21" s="10">
         <v>-1.0</v>
@@ -1770,20 +1802,20 @@
         <v>3008.0</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" s="12">
         <v>3009.0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J22" s="14">
         <v>2.0</v>
@@ -1800,20 +1832,20 @@
         <v>3009.0</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E23" s="8">
         <v>3010.0</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J23" s="10">
         <v>-1.0</v>
@@ -1830,20 +1862,20 @@
         <v>3010.0</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="12">
         <v>3011.0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J24" s="14">
         <v>4.0</v>
@@ -1860,20 +1892,20 @@
         <v>3011.0</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E25" s="8">
         <v>3012.0</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J25" s="10">
         <v>-1.0</v>
@@ -1890,20 +1922,20 @@
         <v>3012.0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" s="12">
         <v>3013.0</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J26" s="14">
         <v>4.0</v>
@@ -1920,20 +1952,20 @@
         <v>3013.0</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E27" s="8">
         <v>3014.0</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J27" s="10">
         <v>-1.0</v>
@@ -1950,20 +1982,20 @@
         <v>3014.0</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E28" s="12">
         <v>3015.0</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
         <v>0.0</v>
@@ -1980,20 +2012,20 @@
         <v>3015.0</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E29" s="8">
         <v>3016.0</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J29" s="10">
         <v>-1.0</v>
@@ -2010,20 +2042,20 @@
         <v>3016.0</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E30" s="12">
         <v>3017.0</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J30" s="14">
         <v>0.0</v>
@@ -2040,20 +2072,20 @@
         <v>3017.0</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="8">
         <v>-1.0</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J31" s="10">
         <v>-1.0</v>
@@ -2070,20 +2102,20 @@
         <v>4001.0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32" s="8">
         <v>4002.0</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J32" s="8">
         <v>4.0</v>
@@ -2100,22 +2132,22 @@
         <v>4002.0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E33" s="8">
         <v>-1.0</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J33" s="8">
         <v>0.0</v>
@@ -2132,20 +2164,20 @@
         <v>5001.0</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E34" s="8">
         <v>5002.0</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J34" s="10">
         <v>0.0</v>
@@ -2162,20 +2194,20 @@
         <v>5002.0</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E35" s="12">
         <v>5003.0</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J35" s="14">
         <v>0.0</v>
@@ -2192,20 +2224,20 @@
         <v>5003.0</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E36" s="10">
         <v>-1.0</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J36" s="10">
         <v>0.0</v>
@@ -2222,20 +2254,20 @@
         <v>6001.0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E37" s="8">
         <v>6002.0</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J37" s="8">
         <v>0.0</v>
@@ -2252,20 +2284,20 @@
         <v>6002.0</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E38" s="8">
         <v>6003.0</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J38" s="8">
         <v>0.0</v>
@@ -2282,20 +2314,20 @@
         <v>6003.0</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E39" s="8">
         <v>6004.0</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J39" s="8">
         <v>-1.0</v>
@@ -2312,20 +2344,20 @@
         <v>6004.0</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E40" s="8">
         <v>6005.0</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J40" s="8">
         <v>0.0</v>
@@ -2342,20 +2374,20 @@
         <v>6005.0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E41" s="8">
         <v>6006.0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J41" s="8">
         <v>-1.0</v>
@@ -2372,20 +2404,20 @@
         <v>6006.0</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E42" s="8">
         <v>6007.0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J42" s="8">
         <v>0.0</v>
@@ -2402,20 +2434,20 @@
         <v>6007.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E43" s="8">
         <v>6008.0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J43" s="8">
         <v>-1.0</v>
@@ -2432,20 +2464,20 @@
         <v>6008.0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E44" s="8">
         <v>6009.0</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J44" s="8">
         <v>0.0</v>
@@ -2462,22 +2494,22 @@
         <v>6009.0</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E45" s="8">
         <v>-1.0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J45" s="8">
         <v>-1.0</v>
@@ -2488,26 +2520,26 @@
         <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C46" s="1">
         <v>6010.0</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E46" s="8">
         <v>6011.0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J46" s="8">
         <v>-1.0</v>
@@ -2518,26 +2550,26 @@
         <v>12</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" s="1">
         <v>6011.0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E47" s="8">
         <v>6012.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H47" s="15"/>
       <c r="I47" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J47" s="8">
         <v>0.0</v>
@@ -2548,26 +2580,26 @@
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C48" s="1">
         <v>6012.0</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E48" s="8">
         <v>6013.0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J48" s="8">
         <v>-1.0</v>
@@ -2578,26 +2610,26 @@
         <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C49" s="1">
         <v>6013.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E49" s="8">
         <v>-1.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J49" s="8">
         <v>-1.0</v>
@@ -2608,26 +2640,26 @@
         <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C50" s="1">
         <v>6014.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E50" s="8">
         <v>6015.0</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J50" s="8">
         <v>3.0</v>
@@ -2638,26 +2670,26 @@
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C51" s="1">
         <v>6015.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E51" s="8">
         <v>6016.0</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J51" s="8">
         <v>-1.0</v>
@@ -2668,26 +2700,26 @@
         <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C52" s="1">
         <v>6016.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E52" s="8">
         <v>6017.0</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J52" s="8">
         <v>-1.0</v>
@@ -2698,26 +2730,26 @@
         <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C53" s="1">
         <v>6017.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E53" s="8">
         <v>-1.0</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J53" s="8">
         <v>1.0</v>
@@ -2734,20 +2766,20 @@
         <v>7001.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E54" s="8">
         <v>7002.0</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J54" s="8">
         <v>-1.0</v>
@@ -2764,20 +2796,20 @@
         <v>7002.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E55" s="8">
         <v>7003.0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J55" s="8">
         <v>0.0</v>
@@ -2794,20 +2826,20 @@
         <v>7003.0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E56" s="8">
         <v>7004.0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H56" s="17"/>
       <c r="I56" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J56" s="8">
         <v>-1.0</v>
@@ -2824,20 +2856,20 @@
         <v>7004.0</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E57" s="8">
         <v>7005.0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H57" s="15"/>
       <c r="I57" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J57" s="8">
         <v>0.0</v>
@@ -2854,20 +2886,20 @@
         <v>7005.0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E58" s="8">
         <v>7006.0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J58" s="8">
         <v>-1.0</v>
@@ -2884,20 +2916,20 @@
         <v>7006.0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E59" s="8">
         <v>7007.0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J59" s="8">
         <v>0.0</v>
@@ -2914,20 +2946,20 @@
         <v>7007.0</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E60" s="8">
         <v>7008.0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J60" s="8">
         <v>-1.0</v>
@@ -2944,22 +2976,22 @@
         <v>7008.0</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E61" s="8">
         <v>-1.0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H61" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J61" s="8">
         <v>0.0</v>
@@ -2970,26 +3002,26 @@
         <v>14</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C62" s="1">
         <v>7009.0</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E62" s="8">
         <v>7010.0</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J62" s="8">
         <v>3.0</v>
@@ -3000,26 +3032,26 @@
         <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C63" s="1">
         <v>7010.0</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E63" s="8">
         <v>7011.0</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J63" s="8">
         <v>-1.0</v>
@@ -3030,26 +3062,26 @@
         <v>14</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C64" s="1">
         <v>7011.0</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E64" s="8">
         <v>7012.0</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J64" s="8">
         <v>0.0</v>
@@ -3060,26 +3092,26 @@
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C65" s="1">
         <v>7012.0</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E65" s="8">
         <v>-1.0</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J65" s="8">
         <v>1.0</v>
@@ -3090,26 +3122,26 @@
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C66" s="1">
         <v>7013.0</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E66" s="8">
         <v>7014.0</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J66" s="8">
         <v>-1.0</v>
@@ -3120,26 +3152,26 @@
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C67" s="1">
         <v>7014.0</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E67" s="8">
         <v>7015.0</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J67" s="8">
         <v>-1.0</v>
@@ -3150,26 +3182,26 @@
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C68" s="1">
         <v>7015.0</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E68" s="8">
         <v>7016.0</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J68" s="8">
         <v>0.0</v>
@@ -3180,26 +3212,26 @@
         <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C69" s="1">
         <v>7016.0</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E69" s="8">
         <v>7017.0</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J69" s="8">
         <v>-1.0</v>
@@ -3210,26 +3242,26 @@
         <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C70" s="1">
         <v>7017.0</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E70" s="8">
         <v>-1.0</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H70" s="15"/>
       <c r="I70" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J70" s="8">
         <v>2.0</v>
@@ -3246,20 +3278,20 @@
         <v>8001.0</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E71" s="8">
         <v>8002.0</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J71" s="8">
         <v>-1.0</v>
@@ -3276,20 +3308,20 @@
         <v>8002.0</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E72" s="8">
         <v>8003.0</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J72" s="8">
         <v>0.0</v>
@@ -3306,20 +3338,20 @@
         <v>8003.0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E73" s="8">
         <v>8004.0</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H73" s="17"/>
       <c r="I73" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J73" s="8">
         <v>-1.0</v>
@@ -3336,20 +3368,20 @@
         <v>8004.0</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E74" s="8">
         <v>8005.0</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J74" s="8">
         <v>0.0</v>
@@ -3366,20 +3398,20 @@
         <v>8005.0</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E75" s="8">
         <v>8006.0</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J75" s="8">
         <v>-1.0</v>
@@ -3396,22 +3428,22 @@
         <v>8006.0</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E76" s="8">
         <v>-1.0</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J76" s="8">
         <v>-1.0</v>
@@ -3422,26 +3454,26 @@
         <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C77" s="1">
         <v>8007.0</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E77" s="8">
         <v>8008.0</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H77" s="17"/>
       <c r="I77" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J77" s="8">
         <v>-1.0</v>
@@ -3452,26 +3484,26 @@
         <v>15</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C78" s="1">
         <v>8008.0</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E78" s="8">
         <v>8009.0</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J78" s="8">
         <v>-1.0</v>
@@ -3482,26 +3514,26 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C79" s="1">
         <v>8009.0</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E79" s="8">
         <v>8010.0</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H79" s="17"/>
       <c r="I79" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J79" s="8">
         <v>-1.0</v>
@@ -3512,26 +3544,26 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C80" s="1">
         <v>8010.0</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E80" s="8">
         <v>8011.0</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J80" s="8">
         <v>-1.0</v>
@@ -3542,26 +3574,26 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C81" s="1">
         <v>8011.0</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E81" s="8">
         <v>8012.0</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J81" s="8">
         <v>-1.0</v>
@@ -3572,26 +3604,26 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C82" s="1">
         <v>8012.0</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E82" s="8">
         <v>8013.0</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J82" s="8">
         <v>0.0</v>
@@ -3602,26 +3634,26 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C83" s="1">
         <v>8013.0</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E83" s="8">
         <v>-1.0</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J83" s="8">
         <v>-1.0</v>
@@ -3632,26 +3664,26 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C84" s="1">
         <v>8014.0</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E84" s="1">
         <v>8015.0</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J84" s="8">
         <v>2.0</v>
@@ -3662,26 +3694,26 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C85" s="1">
         <v>8015.0</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E85" s="1">
         <v>8016.0</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J85" s="8">
         <v>-1.0</v>
@@ -3692,26 +3724,26 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C86" s="1">
         <v>8016.0</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E86" s="1">
         <v>8017.0</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H86" s="17"/>
       <c r="I86" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J86" s="8">
         <v>-1.0</v>
@@ -3722,26 +3754,26 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C87" s="1">
         <v>8017.0</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E87" s="1">
         <v>8018.0</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H87" s="17"/>
       <c r="I87" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J87" s="8">
         <v>-1.0</v>
@@ -3752,26 +3784,26 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C88" s="1">
         <v>8018.0</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E88" s="1">
         <v>8019.0</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J88" s="8">
         <v>0.0</v>
@@ -3782,26 +3814,26 @@
         <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C89" s="1">
         <v>8019.0</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E89" s="1">
         <v>8020.0</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H89" s="17"/>
       <c r="I89" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J89" s="8">
         <v>-1.0</v>
@@ -3812,26 +3844,26 @@
         <v>15</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C90" s="1">
         <v>8020.0</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E90" s="1">
         <v>8021.0</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H90" s="17"/>
       <c r="I90" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J90" s="8">
         <v>1.0</v>
@@ -3842,26 +3874,26 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C91" s="1">
         <v>8021.0</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E91" s="8">
         <v>-1.0</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H91" s="17"/>
       <c r="I91" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J91" s="8">
         <v>0.0</v>
@@ -3878,20 +3910,20 @@
         <v>9001.0</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E92" s="8">
         <v>9002.0</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H92" s="17"/>
       <c r="I92" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J92" s="8">
         <v>1.0</v>
@@ -3908,20 +3940,20 @@
         <v>9002.0</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E93" s="8">
         <v>9003.0</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H93" s="17"/>
       <c r="I93" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J93" s="8">
         <v>0.0</v>
@@ -3938,22 +3970,22 @@
         <v>9003.0</v>
       </c>
       <c r="D94" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E94" s="8">
         <v>-1.0</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H94" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J94" s="8">
         <v>0.0</v>
@@ -3964,26 +3996,26 @@
         <v>16</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C95" s="1">
         <v>9004.0</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E95" s="8">
         <v>-1.0</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H95" s="17"/>
       <c r="I95" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J95" s="8">
         <v>0.0</v>
@@ -3994,26 +4026,26 @@
         <v>16</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C96" s="1">
         <v>9005.0</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E96" s="8">
         <v>9006.0</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H96" s="17"/>
       <c r="I96" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J96" s="8">
         <v>0.0</v>
@@ -4024,26 +4056,26 @@
         <v>16</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C97" s="1">
         <v>9006.0</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E97" s="8">
         <v>-1.0</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H97" s="17"/>
       <c r="I97" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J97" s="8">
         <v>0.0</v>
@@ -4060,20 +4092,20 @@
         <v>10001.0</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E98" s="8">
         <v>10002.0</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H98" s="17"/>
       <c r="I98" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J98" s="8">
         <v>0.0</v>
@@ -4090,20 +4122,20 @@
         <v>10002.0</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E99" s="8">
         <v>10003.0</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H99" s="17"/>
       <c r="I99" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J99" s="8">
         <v>2.0</v>
@@ -4120,20 +4152,20 @@
         <v>10003.0</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E100" s="8">
         <v>10004.0</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H100" s="17"/>
       <c r="I100" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J100" s="8">
         <v>4.0</v>
@@ -4150,20 +4182,20 @@
         <v>10004.0</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E101" s="8">
         <v>10005.0</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H101" s="17"/>
       <c r="I101" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J101" s="8">
         <v>5.0</v>
@@ -4180,20 +4212,20 @@
         <v>10005.0</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E102" s="8">
         <v>10006.0</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H102" s="17"/>
       <c r="I102" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J102" s="8">
         <v>1.0</v>
@@ -4210,20 +4242,20 @@
         <v>10006.0</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E103" s="8">
         <v>10007.0</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J103" s="8">
         <v>3.0</v>
@@ -4240,20 +4272,20 @@
         <v>10007.0</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E104" s="8">
         <v>10008.0</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J104" s="8">
         <v>1.0</v>
@@ -4270,20 +4302,20 @@
         <v>10008.0</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E105" s="8">
         <v>10009.0</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J105" s="8">
         <v>2.0</v>
@@ -4300,20 +4332,20 @@
         <v>10009.0</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E106" s="8">
         <v>10010.0</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J106" s="8">
         <v>6.0</v>
@@ -4330,20 +4362,20 @@
         <v>10010.0</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E107" s="8">
         <v>10011.0</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J107" s="8">
         <v>1.0</v>
@@ -4360,20 +4392,20 @@
         <v>10011.0</v>
       </c>
       <c r="D108" s="18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E108" s="8">
         <v>10012.0</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H108" s="17"/>
       <c r="I108" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J108" s="8">
         <v>4.0</v>
@@ -4390,22 +4422,22 @@
         <v>10012.0</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E109" s="8">
         <v>-1.0</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J109" s="8">
         <v>3.0</v>
@@ -4416,26 +4448,26 @@
         <v>18</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C110" s="1">
         <v>10013.0</v>
       </c>
       <c r="D110" s="18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E110" s="8">
         <v>10014.0</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H110" s="17"/>
       <c r="I110" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J110" s="8">
         <v>3.0</v>
@@ -4446,26 +4478,26 @@
         <v>18</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C111" s="1">
         <v>10014.0</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E111" s="8">
         <v>10015.0</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H111" s="17"/>
       <c r="I111" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J111" s="8">
         <v>2.0</v>
@@ -4476,26 +4508,26 @@
         <v>18</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C112" s="1">
         <v>10015.0</v>
       </c>
       <c r="D112" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E112" s="8">
         <v>10016.0</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H112" s="17"/>
       <c r="I112" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J112" s="8">
         <v>1.0</v>
@@ -4506,26 +4538,26 @@
         <v>18</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C113" s="1">
         <v>10016.0</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E113" s="8">
         <v>-1.0</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H113" s="17"/>
       <c r="I113" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J113" s="8">
         <v>1.0</v>
@@ -4536,26 +4568,26 @@
         <v>18</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C114" s="1">
         <v>10017.0</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E114" s="8">
         <v>10018.0</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H114" s="17"/>
       <c r="I114" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J114" s="8">
         <v>6.0</v>
@@ -4566,26 +4598,26 @@
         <v>18</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C115" s="1">
         <v>10018.0</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E115" s="8">
         <v>10019.0</v>
       </c>
       <c r="F115" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J115" s="8">
         <v>7.0</v>
@@ -4596,26 +4628,26 @@
         <v>18</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C116" s="1">
         <v>10019.0</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E116" s="8">
         <v>10020.0</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H116" s="17"/>
       <c r="I116" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J116" s="8">
         <v>5.0</v>
@@ -4626,26 +4658,26 @@
         <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C117" s="1">
         <v>10020.0</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E117" s="8">
         <v>-1.0</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H117" s="17"/>
       <c r="I117" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J117" s="8">
         <v>1.0</v>
@@ -4662,20 +4694,20 @@
         <v>11001.0</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E118" s="8">
         <v>11002.0</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G118" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J118" s="8">
         <v>10.0</v>
@@ -4692,20 +4724,20 @@
         <v>11002.0</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E119" s="8">
         <v>11003.0</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G119" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H119" s="17"/>
       <c r="I119" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J119" s="8">
         <v>10.0</v>
@@ -4722,20 +4754,20 @@
         <v>11003.0</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E120" s="8">
         <v>11004.0</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H120" s="17"/>
       <c r="I120" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J120" s="8">
         <v>0.0</v>
@@ -4752,20 +4784,20 @@
         <v>11004.0</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E121" s="8">
         <v>11005.0</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H121" s="17"/>
       <c r="I121" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J121" s="8">
         <v>0.0</v>
@@ -4782,20 +4814,20 @@
         <v>11005.0</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E122" s="8">
         <v>11006.0</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G122" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H122" s="17"/>
       <c r="I122" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J122" s="8">
         <v>11.0</v>
@@ -4812,20 +4844,20 @@
         <v>11006.0</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E123" s="8">
         <v>11007.0</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G123" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H123" s="17"/>
       <c r="I123" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J123" s="8">
         <v>11.0</v>
@@ -4842,20 +4874,20 @@
         <v>11007.0</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E124" s="8">
         <v>11008.0</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H124" s="17"/>
       <c r="I124" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J124" s="8">
         <v>0.0</v>
@@ -4872,20 +4904,20 @@
         <v>11008.0</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E125" s="8">
         <v>11009.0</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G125" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H125" s="17"/>
       <c r="I125" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J125" s="8">
         <v>9.0</v>
@@ -4902,20 +4934,20 @@
         <v>11009.0</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E126" s="8">
         <v>11010.0</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G126" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H126" s="17"/>
       <c r="I126" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J126" s="8">
         <v>9.0</v>
@@ -4932,20 +4964,20 @@
         <v>11010.0</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E127" s="8">
         <v>11011.0</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J127" s="8">
         <v>0.0</v>
@@ -4962,22 +4994,22 @@
         <v>11011.0</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E128" s="8">
         <v>-1.0</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G128" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H128" s="15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J128" s="8">
         <v>8.0</v>
@@ -4988,26 +5020,26 @@
         <v>20</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C129" s="1">
         <v>11012.0</v>
       </c>
       <c r="D129" s="18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E129" s="8">
         <v>11013.0</v>
       </c>
       <c r="F129" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G129" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J129" s="8">
         <v>9.0</v>
@@ -5018,26 +5050,26 @@
         <v>20</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C130" s="1">
         <v>11013.0</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E130" s="8">
         <v>11014.0</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G130" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J130" s="8">
         <v>9.0</v>
@@ -5048,26 +5080,26 @@
         <v>20</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C131" s="1">
         <v>11014.0</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E131" s="8">
         <v>-1.0</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H131" s="17"/>
       <c r="I131" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J131" s="8">
         <v>1.0</v>
@@ -5078,26 +5110,26 @@
         <v>20</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C132" s="1">
         <v>11015.0</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E132" s="8">
         <v>11016.0</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G132" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H132" s="17"/>
       <c r="I132" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J132" s="8">
         <v>9.0</v>
@@ -5108,26 +5140,26 @@
         <v>20</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C133" s="1">
         <v>11016.0</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E133" s="8">
         <v>11017.0</v>
       </c>
       <c r="F133" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G133" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H133" s="17"/>
       <c r="I133" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J133" s="8">
         <v>9.0</v>
@@ -5138,45 +5170,180 @@
         <v>20</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C134" s="1">
         <v>11017.0</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E134" s="8">
         <v>-1.0</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J134" s="8">
         <v>1.0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="19"/>
+      <c r="A135" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C135" s="1">
+        <v>12001.0</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="E135" s="8">
+        <v>12002.0</v>
+      </c>
+      <c r="F135" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G135" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H135" s="17"/>
+      <c r="I135" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J135" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="19"/>
+      <c r="A136" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136" s="1">
+        <v>12002.0</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E136" s="8">
+        <v>12003.0</v>
+      </c>
+      <c r="F136" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G136" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H136" s="17"/>
+      <c r="I136" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J136" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="19"/>
+      <c r="A137" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C137" s="1">
+        <v>12003.0</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="E137" s="8">
+        <v>12004.0</v>
+      </c>
+      <c r="F137" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G137" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H137" s="17"/>
+      <c r="I137" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J137" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="19"/>
+      <c r="A138" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" s="1">
+        <v>12004.0</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E138" s="8">
+        <v>12005.0</v>
+      </c>
+      <c r="F138" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G138" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H138" s="17"/>
+      <c r="I138" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J138" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="19"/>
+      <c r="A139" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" s="1">
+        <v>12005.0</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F139" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G139" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H139" s="17"/>
+      <c r="I139" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J139" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="19"/>
@@ -7856,19 +8023,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -7876,16 +8043,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -7896,16 +8063,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -7916,16 +8083,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -7936,16 +8103,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -7956,16 +8123,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1">
         <v>-1.0</v>
@@ -7976,16 +8143,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1">
         <v>-1.0</v>
@@ -7996,16 +8163,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1">
         <v>-1.0</v>
@@ -8016,16 +8183,16 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1">
         <v>-1.0</v>
@@ -8036,16 +8203,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1">
         <v>-1.0</v>
@@ -8056,16 +8223,16 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1">
         <v>-1.0</v>
@@ -8076,18 +8243,38 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="211">
   <si>
     <t>NpcID</t>
   </si>
@@ -239,6 +239,21 @@
   </si>
   <si>
     <t>C004</t>
+  </si>
+  <si>
+    <t>N004_0</t>
+  </si>
+  <si>
+    <t>꺄악!!!</t>
+  </si>
+  <si>
+    <t>이번에도 뭔가 잘못 생각한걸까..?</t>
+  </si>
+  <si>
+    <t>N004_1</t>
+  </si>
+  <si>
+    <t>아무래도 그렇겠지..</t>
   </si>
   <si>
     <t>왜 이런 곳에 문이 있지?</t>
@@ -825,7 +840,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J139" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J142" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2154,183 +2169,183 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4003.0</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="8">
+        <v>4004.0</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J34" s="8">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="1">
+        <v>4004.0</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4005.0</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C37" s="6">
         <v>5001.0</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="8">
+      <c r="D37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="8">
         <v>5002.0</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J34" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>5002.0</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="12">
-        <v>5003.0</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J35" s="14">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>5003.0</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-1.0</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" s="10">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="1">
-        <v>6001.0</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E37" s="8">
-        <v>6002.0</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="9" t="s">
         <v>35</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="10">
         <v>0.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="s">
-        <v>12</v>
+      <c r="A38" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="1">
-        <v>6002.0</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E38" s="8">
-        <v>6003.0</v>
-      </c>
-      <c r="F38" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>5002.0</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="12">
+        <v>5003.0</v>
+      </c>
+      <c r="F38" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J38" s="8">
+      <c r="H38" s="11"/>
+      <c r="I38" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" s="14">
         <v>0.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="s">
-        <v>12</v>
+      <c r="A39" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="1">
-        <v>6003.0</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="8">
-        <v>6004.0</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>81</v>
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5003.0</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="10">
+        <v>-1.0</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J39" s="8">
-        <v>-1.0</v>
+      <c r="J39" s="10">
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -2341,13 +2356,13 @@
         <v>12</v>
       </c>
       <c r="C40" s="1">
-        <v>6004.0</v>
+        <v>6001.0</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="8">
-        <v>6005.0</v>
+        <v>6002.0</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>34</v>
@@ -2371,26 +2386,26 @@
         <v>12</v>
       </c>
       <c r="C41" s="1">
-        <v>6005.0</v>
+        <v>6002.0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="8">
-        <v>6006.0</v>
+        <v>6003.0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J41" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -2401,26 +2416,26 @@
         <v>12</v>
       </c>
       <c r="C42" s="1">
-        <v>6006.0</v>
+        <v>6003.0</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="8">
-        <v>6007.0</v>
+        <v>6004.0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J42" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="43">
@@ -2431,26 +2446,26 @@
         <v>12</v>
       </c>
       <c r="C43" s="1">
-        <v>6007.0</v>
+        <v>6004.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E43" s="8">
-        <v>6008.0</v>
+        <v>6005.0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J43" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -2461,26 +2476,26 @@
         <v>12</v>
       </c>
       <c r="C44" s="1">
-        <v>6008.0</v>
+        <v>6005.0</v>
       </c>
       <c r="D44" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E44" s="8">
+        <v>6006.0</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="E44" s="8">
-        <v>6009.0</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>35</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J44" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="45">
@@ -2491,28 +2506,26 @@
         <v>12</v>
       </c>
       <c r="C45" s="1">
-        <v>6009.0</v>
+        <v>6006.0</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E45" s="8">
-        <v>-1.0</v>
+        <v>6007.0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>88</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J45" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2533,25 @@
         <v>12</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C46" s="1">
-        <v>6010.0</v>
+        <v>6007.0</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E46" s="8">
-        <v>6011.0</v>
+        <v>6008.0</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J46" s="8">
@@ -2550,16 +2563,16 @@
         <v>12</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1">
-        <v>6011.0</v>
+        <v>6008.0</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>91</v>
       </c>
       <c r="E47" s="8">
-        <v>6012.0</v>
+        <v>6009.0</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>34</v>
@@ -2567,8 +2580,8 @@
       <c r="G47" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15" t="s">
+      <c r="H47" s="7"/>
+      <c r="I47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J47" s="8">
@@ -2580,25 +2593,27 @@
         <v>12</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1">
-        <v>6012.0</v>
+        <v>6009.0</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>92</v>
       </c>
       <c r="E48" s="8">
-        <v>6013.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J48" s="8">
@@ -2610,26 +2625,26 @@
         <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C49" s="1">
-        <v>6013.0</v>
+        <v>6010.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E49" s="8">
-        <v>-1.0</v>
+        <v>6011.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J49" s="8">
         <v>-1.0</v>
@@ -2643,13 +2658,13 @@
         <v>94</v>
       </c>
       <c r="C50" s="1">
-        <v>6014.0</v>
+        <v>6011.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="E50" s="8">
-        <v>6015.0</v>
+        <v>6012.0</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>34</v>
@@ -2662,7 +2677,7 @@
         <v>36</v>
       </c>
       <c r="J50" s="8">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -2673,19 +2688,19 @@
         <v>94</v>
       </c>
       <c r="C51" s="1">
-        <v>6015.0</v>
+        <v>6012.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E51" s="8">
-        <v>6016.0</v>
+        <v>6013.0</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15" t="s">
@@ -2703,23 +2718,23 @@
         <v>94</v>
       </c>
       <c r="C52" s="1">
-        <v>6016.0</v>
+        <v>6013.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E52" s="8">
-        <v>6017.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J52" s="8">
         <v>-1.0</v>
@@ -2730,16 +2745,16 @@
         <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1">
-        <v>6017.0</v>
+        <v>6014.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="E53" s="8">
-        <v>-1.0</v>
+        <v>6015.0</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>34</v>
@@ -2749,36 +2764,36 @@
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J53" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="C54" s="1">
-        <v>7001.0</v>
+        <v>6015.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E54" s="8">
-        <v>7002.0</v>
+        <v>6016.0</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H54" s="17"/>
-      <c r="I54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="J54" s="8">
@@ -2787,62 +2802,62 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="C55" s="1">
-        <v>7002.0</v>
+        <v>6016.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55" s="8">
-        <v>7003.0</v>
+        <v>6017.0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15" t="s">
         <v>36</v>
       </c>
       <c r="J55" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="C56" s="1">
-        <v>7003.0</v>
+        <v>6017.0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E56" s="8">
-        <v>7004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="J56" s="8">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
@@ -2853,26 +2868,26 @@
         <v>14</v>
       </c>
       <c r="C57" s="1">
-        <v>7004.0</v>
+        <v>7001.0</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E57" s="8">
-        <v>7005.0</v>
+        <v>7002.0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57" s="15"/>
+        <v>86</v>
+      </c>
+      <c r="H57" s="17"/>
       <c r="I57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J57" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="58">
@@ -2883,26 +2898,26 @@
         <v>14</v>
       </c>
       <c r="C58" s="1">
-        <v>7005.0</v>
+        <v>7002.0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E58" s="8">
-        <v>7006.0</v>
+        <v>7003.0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H58" s="17"/>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J58" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -2913,26 +2928,26 @@
         <v>14</v>
       </c>
       <c r="C59" s="1">
-        <v>7006.0</v>
+        <v>7003.0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E59" s="8">
-        <v>7007.0</v>
+        <v>7004.0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J59" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="60">
@@ -2943,26 +2958,26 @@
         <v>14</v>
       </c>
       <c r="C60" s="1">
-        <v>7007.0</v>
+        <v>7004.0</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E60" s="8">
-        <v>7008.0</v>
+        <v>7005.0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H60" s="17"/>
-      <c r="I60" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" s="15"/>
+      <c r="I60" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J60" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -2973,28 +2988,26 @@
         <v>14</v>
       </c>
       <c r="C61" s="1">
-        <v>7008.0</v>
+        <v>7005.0</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E61" s="8">
-        <v>-1.0</v>
+        <v>7006.0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>58</v>
+        <v>86</v>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="J61" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="62">
@@ -3002,16 +3015,16 @@
         <v>14</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C62" s="1">
-        <v>7009.0</v>
+        <v>7006.0</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="E62" s="8">
-        <v>7010.0</v>
+        <v>7007.0</v>
       </c>
       <c r="F62" s="15" t="s">
         <v>34</v>
@@ -3020,11 +3033,11 @@
         <v>35</v>
       </c>
       <c r="H62" s="15"/>
-      <c r="I62" s="8" t="s">
+      <c r="I62" s="15" t="s">
         <v>36</v>
       </c>
       <c r="J62" s="8">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -3032,25 +3045,25 @@
         <v>14</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C63" s="1">
-        <v>7010.0</v>
+        <v>7007.0</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63" s="8">
-        <v>7011.0</v>
+        <v>7008.0</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H63" s="15"/>
-      <c r="I63" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="15" t="s">
         <v>36</v>
       </c>
       <c r="J63" s="8">
@@ -3062,16 +3075,16 @@
         <v>14</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C64" s="1">
-        <v>7011.0</v>
+        <v>7008.0</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64" s="8">
-        <v>7012.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>34</v>
@@ -3079,9 +3092,11 @@
       <c r="G64" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H64" s="15"/>
-      <c r="I64" s="8" t="s">
-        <v>36</v>
+      <c r="H64" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="J64" s="8">
         <v>0.0</v>
@@ -3092,16 +3107,16 @@
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C65" s="1">
-        <v>7012.0</v>
+        <v>7009.0</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="E65" s="8">
-        <v>-1.0</v>
+        <v>7010.0</v>
       </c>
       <c r="F65" s="15" t="s">
         <v>34</v>
@@ -3111,10 +3126,10 @@
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J65" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="66">
@@ -3122,22 +3137,22 @@
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="1">
-        <v>7013.0</v>
+        <v>7010.0</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E66" s="8">
-        <v>7014.0</v>
+        <v>7011.0</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="8" t="s">
@@ -3152,29 +3167,29 @@
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C67" s="1">
-        <v>7014.0</v>
+        <v>7011.0</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E67" s="8">
-        <v>7015.0</v>
+        <v>7012.0</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J67" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -3182,16 +3197,16 @@
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C68" s="1">
-        <v>7015.0</v>
+        <v>7012.0</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E68" s="8">
-        <v>7016.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F68" s="15" t="s">
         <v>34</v>
@@ -3201,10 +3216,10 @@
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J68" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="69">
@@ -3212,26 +3227,26 @@
         <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C69" s="1">
-        <v>7016.0</v>
+        <v>7013.0</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E69" s="8">
-        <v>7017.0</v>
+        <v>7014.0</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J69" s="8">
         <v>-1.0</v>
@@ -3242,76 +3257,76 @@
         <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C70" s="1">
-        <v>7017.0</v>
+        <v>7014.0</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E70" s="8">
-        <v>-1.0</v>
+        <v>7015.0</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H70" s="15"/>
       <c r="I70" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J70" s="8">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="C71" s="1">
-        <v>8001.0</v>
+        <v>7015.0</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E71" s="8">
-        <v>8002.0</v>
+        <v>7016.0</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H71" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="H71" s="15"/>
       <c r="I71" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J71" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="C72" s="1">
-        <v>8002.0</v>
+        <v>7016.0</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E72" s="8">
-        <v>8003.0</v>
+        <v>7017.0</v>
       </c>
       <c r="F72" s="15" t="s">
         <v>34</v>
@@ -3319,42 +3334,42 @@
       <c r="G72" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H72" s="17"/>
+      <c r="H72" s="15"/>
       <c r="I72" s="8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J72" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="C73" s="1">
-        <v>8003.0</v>
+        <v>7017.0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E73" s="8">
-        <v>8004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H73" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="H73" s="15"/>
       <c r="I73" s="8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J73" s="8">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="74">
@@ -3365,26 +3380,26 @@
         <v>15</v>
       </c>
       <c r="C74" s="1">
-        <v>8004.0</v>
+        <v>8001.0</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E74" s="8">
-        <v>8005.0</v>
+        <v>8002.0</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J74" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="75">
@@ -3395,26 +3410,26 @@
         <v>15</v>
       </c>
       <c r="C75" s="1">
-        <v>8005.0</v>
+        <v>8002.0</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E75" s="8">
-        <v>8006.0</v>
+        <v>8003.0</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J75" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -3425,23 +3440,21 @@
         <v>15</v>
       </c>
       <c r="C76" s="1">
-        <v>8006.0</v>
+        <v>8003.0</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E76" s="8">
-        <v>-1.0</v>
+        <v>8004.0</v>
       </c>
       <c r="F76" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>122</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H76" s="17"/>
       <c r="I76" s="8" t="s">
         <v>36</v>
       </c>
@@ -3454,29 +3467,29 @@
         <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C77" s="1">
-        <v>8007.0</v>
+        <v>8004.0</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>124</v>
       </c>
       <c r="E77" s="8">
-        <v>8008.0</v>
+        <v>8005.0</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H77" s="17"/>
       <c r="I77" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J77" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -3484,22 +3497,22 @@
         <v>15</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C78" s="1">
-        <v>8008.0</v>
+        <v>8005.0</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>125</v>
       </c>
       <c r="E78" s="8">
-        <v>8009.0</v>
+        <v>8006.0</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="8" t="s">
@@ -3514,24 +3527,26 @@
         <v>15</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="C79" s="1">
-        <v>8009.0</v>
+        <v>8006.0</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>126</v>
       </c>
       <c r="E79" s="8">
-        <v>8010.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F79" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H79" s="17"/>
+        <v>86</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>127</v>
+      </c>
       <c r="I79" s="8" t="s">
         <v>36</v>
       </c>
@@ -3544,26 +3559,26 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C80" s="1">
-        <v>8010.0</v>
+        <v>8007.0</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="E80" s="8">
-        <v>8011.0</v>
+        <v>8008.0</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J80" s="8">
         <v>-1.0</v>
@@ -3574,22 +3589,22 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C81" s="1">
-        <v>8011.0</v>
+        <v>8008.0</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E81" s="8">
-        <v>8012.0</v>
+        <v>8009.0</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="8" t="s">
@@ -3604,29 +3619,29 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C82" s="1">
-        <v>8012.0</v>
+        <v>8009.0</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E82" s="8">
-        <v>8013.0</v>
+        <v>8010.0</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J82" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="83">
@@ -3634,16 +3649,16 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C83" s="1">
-        <v>8013.0</v>
+        <v>8010.0</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="E83" s="8">
-        <v>-1.0</v>
+        <v>8011.0</v>
       </c>
       <c r="F83" s="15" t="s">
         <v>34</v>
@@ -3664,29 +3679,29 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C84" s="1">
-        <v>8014.0</v>
+        <v>8011.0</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E84" s="1">
-        <v>8015.0</v>
+        <v>132</v>
+      </c>
+      <c r="E84" s="8">
+        <v>8012.0</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J84" s="8">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="85">
@@ -3694,29 +3709,29 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C85" s="1">
-        <v>8015.0</v>
+        <v>8012.0</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E85" s="1">
-        <v>8016.0</v>
+        <v>133</v>
+      </c>
+      <c r="E85" s="8">
+        <v>8013.0</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J85" s="8">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -3724,26 +3739,26 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C86" s="1">
-        <v>8016.0</v>
+        <v>8013.0</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E86" s="1">
-        <v>8017.0</v>
+        <v>134</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-1.0</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H86" s="17"/>
       <c r="I86" s="8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J86" s="8">
         <v>-1.0</v>
@@ -3754,29 +3769,29 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C87" s="1">
-        <v>8017.0</v>
+        <v>8014.0</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="E87" s="1">
-        <v>8018.0</v>
+        <v>8015.0</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="H87" s="17"/>
       <c r="I87" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J87" s="8">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
@@ -3784,29 +3799,29 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C88" s="1">
-        <v>8018.0</v>
+        <v>8015.0</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E88" s="1">
-        <v>8019.0</v>
+        <v>8016.0</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J88" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="89">
@@ -3814,22 +3829,22 @@
         <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C89" s="1">
-        <v>8019.0</v>
+        <v>8016.0</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E89" s="1">
-        <v>8020.0</v>
+        <v>8017.0</v>
       </c>
       <c r="F89" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H89" s="17"/>
       <c r="I89" s="8" t="s">
@@ -3844,29 +3859,29 @@
         <v>15</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C90" s="1">
-        <v>8020.0</v>
+        <v>8017.0</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E90" s="1">
-        <v>8021.0</v>
+        <v>8018.0</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H90" s="17"/>
       <c r="I90" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J90" s="8">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="91">
@@ -3874,16 +3889,16 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C91" s="1">
-        <v>8021.0</v>
+        <v>8018.0</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-1.0</v>
+        <v>139</v>
+      </c>
+      <c r="E91" s="1">
+        <v>8019.0</v>
       </c>
       <c r="F91" s="15" t="s">
         <v>34</v>
@@ -3893,7 +3908,7 @@
       </c>
       <c r="H91" s="17"/>
       <c r="I91" s="8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="J91" s="8">
         <v>0.0</v>
@@ -3901,49 +3916,49 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C92" s="1">
-        <v>9001.0</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E92" s="8">
-        <v>9002.0</v>
+        <v>8019.0</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E92" s="1">
+        <v>8020.0</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H92" s="17"/>
       <c r="I92" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J92" s="8">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C93" s="1">
-        <v>9002.0</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E93" s="8">
-        <v>9003.0</v>
+        <v>8020.0</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" s="1">
+        <v>8021.0</v>
       </c>
       <c r="F93" s="15" t="s">
         <v>34</v>
@@ -3956,21 +3971,21 @@
         <v>36</v>
       </c>
       <c r="J93" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C94" s="1">
-        <v>9003.0</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>140</v>
+        <v>8021.0</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="E94" s="8">
         <v>-1.0</v>
@@ -3981,11 +3996,9 @@
       <c r="G94" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H94" s="15" t="s">
-        <v>141</v>
-      </c>
+      <c r="H94" s="17"/>
       <c r="I94" s="8" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J94" s="8">
         <v>0.0</v>
@@ -3996,16 +4009,16 @@
         <v>16</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C95" s="1">
-        <v>9004.0</v>
-      </c>
-      <c r="D95" s="18" t="s">
+        <v>9001.0</v>
+      </c>
+      <c r="D95" s="7" t="s">
         <v>143</v>
       </c>
       <c r="E95" s="8">
-        <v>-1.0</v>
+        <v>9002.0</v>
       </c>
       <c r="F95" s="15" t="s">
         <v>34</v>
@@ -4018,7 +4031,7 @@
         <v>36</v>
       </c>
       <c r="J95" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="96">
@@ -4026,16 +4039,16 @@
         <v>16</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="1">
+        <v>9002.0</v>
+      </c>
+      <c r="D96" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C96" s="1">
-        <v>9005.0</v>
-      </c>
-      <c r="D96" s="18" t="s">
-        <v>145</v>
-      </c>
       <c r="E96" s="8">
-        <v>9006.0</v>
+        <v>9003.0</v>
       </c>
       <c r="F96" s="15" t="s">
         <v>34</v>
@@ -4056,13 +4069,13 @@
         <v>16</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="C97" s="1">
-        <v>9006.0</v>
+        <v>9003.0</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E97" s="8">
         <v>-1.0</v>
@@ -4073,7 +4086,9 @@
       <c r="G97" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H97" s="17"/>
+      <c r="H97" s="15" t="s">
+        <v>146</v>
+      </c>
       <c r="I97" s="8" t="s">
         <v>36</v>
       </c>
@@ -4083,19 +4098,19 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="C98" s="1">
-        <v>10001.0</v>
+        <v>9004.0</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E98" s="8">
-        <v>10002.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F98" s="15" t="s">
         <v>34</v>
@@ -4113,62 +4128,62 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="C99" s="1">
-        <v>10002.0</v>
+        <v>9005.0</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E99" s="8">
-        <v>10003.0</v>
+        <v>9006.0</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H99" s="17"/>
       <c r="I99" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J99" s="8">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="C100" s="1">
-        <v>10003.0</v>
+        <v>9006.0</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E100" s="8">
-        <v>10004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="H100" s="17"/>
       <c r="I100" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J100" s="8">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -4179,26 +4194,26 @@
         <v>18</v>
       </c>
       <c r="C101" s="1">
-        <v>10004.0</v>
+        <v>10001.0</v>
       </c>
       <c r="D101" s="18" t="s">
         <v>152</v>
       </c>
       <c r="E101" s="8">
-        <v>10005.0</v>
+        <v>10002.0</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="H101" s="17"/>
       <c r="I101" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J101" s="8">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -4209,26 +4224,26 @@
         <v>18</v>
       </c>
       <c r="C102" s="1">
-        <v>10005.0</v>
+        <v>10002.0</v>
       </c>
       <c r="D102" s="18" t="s">
         <v>153</v>
       </c>
       <c r="E102" s="8">
-        <v>10006.0</v>
+        <v>10003.0</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="H102" s="17"/>
       <c r="I102" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J102" s="8">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="103">
@@ -4239,26 +4254,26 @@
         <v>18</v>
       </c>
       <c r="C103" s="1">
-        <v>10006.0</v>
+        <v>10003.0</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E103" s="8">
-        <v>10007.0</v>
+        <v>10004.0</v>
       </c>
       <c r="F103" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J103" s="8">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="104">
@@ -4269,26 +4284,26 @@
         <v>18</v>
       </c>
       <c r="C104" s="1">
-        <v>10007.0</v>
+        <v>10004.0</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E104" s="8">
-        <v>10008.0</v>
+        <v>10005.0</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J104" s="8">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="105">
@@ -4299,26 +4314,26 @@
         <v>18</v>
       </c>
       <c r="C105" s="1">
-        <v>10008.0</v>
+        <v>10005.0</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E105" s="8">
-        <v>10009.0</v>
+        <v>10006.0</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J105" s="8">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -4329,26 +4344,26 @@
         <v>18</v>
       </c>
       <c r="C106" s="1">
-        <v>10009.0</v>
+        <v>10006.0</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E106" s="8">
-        <v>10010.0</v>
+        <v>10007.0</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J106" s="8">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="107">
@@ -4359,13 +4374,13 @@
         <v>18</v>
       </c>
       <c r="C107" s="1">
-        <v>10010.0</v>
+        <v>10007.0</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E107" s="8">
-        <v>10011.0</v>
+        <v>10008.0</v>
       </c>
       <c r="F107" s="15" t="s">
         <v>34</v>
@@ -4389,26 +4404,26 @@
         <v>18</v>
       </c>
       <c r="C108" s="1">
-        <v>10011.0</v>
+        <v>10008.0</v>
       </c>
       <c r="D108" s="18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E108" s="8">
-        <v>10012.0</v>
+        <v>10009.0</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H108" s="17"/>
       <c r="I108" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J108" s="8">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="109">
@@ -4419,118 +4434,118 @@
         <v>18</v>
       </c>
       <c r="C109" s="1">
-        <v>10012.0</v>
+        <v>10009.0</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E109" s="8">
-        <v>-1.0</v>
+        <v>10010.0</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>161</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="H109" s="17"/>
       <c r="I109" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J109" s="8">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>162</v>
+      <c r="B110" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C110" s="1">
-        <v>10013.0</v>
+        <v>10010.0</v>
       </c>
       <c r="D110" s="18" t="s">
         <v>163</v>
       </c>
       <c r="E110" s="8">
-        <v>10014.0</v>
+        <v>10011.0</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="H110" s="17"/>
       <c r="I110" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J110" s="8">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>162</v>
+      <c r="B111" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C111" s="1">
-        <v>10014.0</v>
+        <v>10011.0</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>164</v>
       </c>
       <c r="E111" s="8">
-        <v>10015.0</v>
+        <v>10012.0</v>
       </c>
       <c r="F111" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H111" s="17"/>
       <c r="I111" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J111" s="8">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>162</v>
+      <c r="B112" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C112" s="1">
-        <v>10015.0</v>
+        <v>10012.0</v>
       </c>
       <c r="D112" s="18" t="s">
         <v>165</v>
       </c>
       <c r="E112" s="8">
-        <v>10016.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F112" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="H112" s="17"/>
+        <v>154</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="I112" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J112" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="113">
@@ -4538,29 +4553,29 @@
         <v>18</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C113" s="1">
-        <v>10016.0</v>
+        <v>10013.0</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E113" s="8">
-        <v>-1.0</v>
+        <v>10014.0</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="H113" s="17"/>
       <c r="I113" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J113" s="8">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="114">
@@ -4571,26 +4586,26 @@
         <v>167</v>
       </c>
       <c r="C114" s="1">
-        <v>10017.0</v>
+        <v>10014.0</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E114" s="8">
-        <v>10018.0</v>
+        <v>10015.0</v>
       </c>
       <c r="F114" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H114" s="17"/>
       <c r="I114" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J114" s="8">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -4601,26 +4616,26 @@
         <v>167</v>
       </c>
       <c r="C115" s="1">
-        <v>10018.0</v>
+        <v>10015.0</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E115" s="8">
-        <v>10019.0</v>
+        <v>10016.0</v>
       </c>
       <c r="F115" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J115" s="8">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="116">
@@ -4631,26 +4646,26 @@
         <v>167</v>
       </c>
       <c r="C116" s="1">
-        <v>10019.0</v>
+        <v>10016.0</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E116" s="8">
-        <v>10020.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="H116" s="17"/>
       <c r="I116" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J116" s="8">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -4658,106 +4673,106 @@
         <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C117" s="1">
-        <v>10020.0</v>
+        <v>10017.0</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E117" s="8">
-        <v>-1.0</v>
+        <v>10018.0</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="H117" s="17"/>
       <c r="I117" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J117" s="8">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="C118" s="1">
-        <v>11001.0</v>
+        <v>10018.0</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E118" s="8">
-        <v>11002.0</v>
+        <v>10019.0</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J118" s="8">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="C119" s="1">
-        <v>11002.0</v>
+        <v>10019.0</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E119" s="8">
-        <v>11003.0</v>
+        <v>10020.0</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="H119" s="17"/>
       <c r="I119" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J119" s="8">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="C120" s="1">
-        <v>11003.0</v>
+        <v>10020.0</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E120" s="8">
-        <v>11004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>34</v>
@@ -4770,7 +4785,7 @@
         <v>36</v>
       </c>
       <c r="J120" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -4781,26 +4796,26 @@
         <v>20</v>
       </c>
       <c r="C121" s="1">
-        <v>11004.0</v>
+        <v>11001.0</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E121" s="8">
-        <v>11005.0</v>
+        <v>11002.0</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H121" s="17"/>
       <c r="I121" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J121" s="8">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="122">
@@ -4811,13 +4826,13 @@
         <v>20</v>
       </c>
       <c r="C122" s="1">
-        <v>11005.0</v>
+        <v>11002.0</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E122" s="8">
-        <v>11006.0</v>
+        <v>11003.0</v>
       </c>
       <c r="F122" s="15" t="s">
         <v>57</v>
@@ -4830,7 +4845,7 @@
         <v>36</v>
       </c>
       <c r="J122" s="8">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="123">
@@ -4841,26 +4856,26 @@
         <v>20</v>
       </c>
       <c r="C123" s="1">
-        <v>11006.0</v>
+        <v>11003.0</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E123" s="8">
-        <v>11007.0</v>
+        <v>11004.0</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H123" s="17"/>
       <c r="I123" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J123" s="8">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -4871,13 +4886,13 @@
         <v>20</v>
       </c>
       <c r="C124" s="1">
-        <v>11007.0</v>
+        <v>11004.0</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E124" s="8">
-        <v>11008.0</v>
+        <v>11005.0</v>
       </c>
       <c r="F124" s="15" t="s">
         <v>34</v>
@@ -4901,13 +4916,13 @@
         <v>20</v>
       </c>
       <c r="C125" s="1">
-        <v>11008.0</v>
+        <v>11005.0</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E125" s="8">
-        <v>11009.0</v>
+        <v>11006.0</v>
       </c>
       <c r="F125" s="15" t="s">
         <v>57</v>
@@ -4920,7 +4935,7 @@
         <v>36</v>
       </c>
       <c r="J125" s="8">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="126">
@@ -4931,13 +4946,13 @@
         <v>20</v>
       </c>
       <c r="C126" s="1">
-        <v>11009.0</v>
+        <v>11006.0</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E126" s="8">
-        <v>11010.0</v>
+        <v>11007.0</v>
       </c>
       <c r="F126" s="15" t="s">
         <v>57</v>
@@ -4950,7 +4965,7 @@
         <v>36</v>
       </c>
       <c r="J126" s="8">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="127">
@@ -4961,13 +4976,13 @@
         <v>20</v>
       </c>
       <c r="C127" s="1">
-        <v>11010.0</v>
+        <v>11007.0</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E127" s="8">
-        <v>11011.0</v>
+        <v>11008.0</v>
       </c>
       <c r="F127" s="15" t="s">
         <v>34</v>
@@ -4991,13 +5006,13 @@
         <v>20</v>
       </c>
       <c r="C128" s="1">
-        <v>11011.0</v>
+        <v>11008.0</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E128" s="8">
-        <v>-1.0</v>
+        <v>11009.0</v>
       </c>
       <c r="F128" s="15" t="s">
         <v>57</v>
@@ -5005,14 +5020,12 @@
       <c r="G128" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H128" s="15" t="s">
-        <v>183</v>
-      </c>
+      <c r="H128" s="17"/>
       <c r="I128" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J128" s="8">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="129">
@@ -5020,16 +5033,16 @@
         <v>20</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="C129" s="1">
-        <v>11012.0</v>
+        <v>11009.0</v>
       </c>
       <c r="D129" s="18" t="s">
         <v>185</v>
       </c>
       <c r="E129" s="8">
-        <v>11013.0</v>
+        <v>11010.0</v>
       </c>
       <c r="F129" s="15" t="s">
         <v>57</v>
@@ -5050,29 +5063,29 @@
         <v>20</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="C130" s="1">
-        <v>11013.0</v>
+        <v>11010.0</v>
       </c>
       <c r="D130" s="18" t="s">
         <v>186</v>
       </c>
       <c r="E130" s="8">
-        <v>11014.0</v>
+        <v>11011.0</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J130" s="8">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -5080,10 +5093,10 @@
         <v>20</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="C131" s="1">
-        <v>11014.0</v>
+        <v>11011.0</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>187</v>
@@ -5092,17 +5105,19 @@
         <v>-1.0</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H131" s="17"/>
+        <v>21</v>
+      </c>
+      <c r="H131" s="15" t="s">
+        <v>188</v>
+      </c>
       <c r="I131" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J131" s="8">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="132">
@@ -5110,16 +5125,16 @@
         <v>20</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C132" s="1">
-        <v>11015.0</v>
+        <v>11012.0</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E132" s="8">
-        <v>11016.0</v>
+        <v>11013.0</v>
       </c>
       <c r="F132" s="15" t="s">
         <v>57</v>
@@ -5140,16 +5155,16 @@
         <v>20</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C133" s="1">
-        <v>11016.0</v>
+        <v>11013.0</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E133" s="8">
-        <v>11017.0</v>
+        <v>11014.0</v>
       </c>
       <c r="F133" s="15" t="s">
         <v>57</v>
@@ -5170,13 +5185,13 @@
         <v>20</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C134" s="1">
-        <v>11017.0</v>
+        <v>11014.0</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E134" s="8">
         <v>-1.0</v>
@@ -5197,79 +5212,79 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="C135" s="1">
-        <v>12001.0</v>
+        <v>11015.0</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E135" s="8">
-        <v>12002.0</v>
+        <v>11016.0</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G135" s="16" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J135" s="8">
-        <v>-1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="C136" s="1">
-        <v>12002.0</v>
+        <v>11016.0</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E136" s="8">
-        <v>12003.0</v>
+        <v>11017.0</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H136" s="17"/>
       <c r="I136" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J136" s="8">
-        <v>-1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="C137" s="1">
-        <v>12003.0</v>
+        <v>11017.0</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E137" s="8">
-        <v>12004.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F137" s="15" t="s">
         <v>34</v>
@@ -5282,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="J137" s="8">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
@@ -5293,13 +5308,13 @@
         <v>22</v>
       </c>
       <c r="C138" s="1">
-        <v>12004.0</v>
+        <v>12001.0</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E138" s="8">
-        <v>12005.0</v>
+        <v>12002.0</v>
       </c>
       <c r="F138" s="15" t="s">
         <v>34</v>
@@ -5323,13 +5338,13 @@
         <v>22</v>
       </c>
       <c r="C139" s="1">
-        <v>12005.0</v>
+        <v>12002.0</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E139" s="8">
-        <v>-1.0</v>
+        <v>12003.0</v>
       </c>
       <c r="F139" s="15" t="s">
         <v>34</v>
@@ -5346,13 +5361,94 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="19"/>
+      <c r="A140" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C140" s="1">
+        <v>12003.0</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E140" s="8">
+        <v>12004.0</v>
+      </c>
+      <c r="F140" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G140" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H140" s="17"/>
+      <c r="I140" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J140" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="19"/>
+      <c r="A141" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C141" s="1">
+        <v>12004.0</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="E141" s="8">
+        <v>12005.0</v>
+      </c>
+      <c r="F141" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G141" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H141" s="17"/>
+      <c r="I141" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J141" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="19"/>
+      <c r="A142" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142" s="1">
+        <v>12005.0</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F142" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G142" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H142" s="17"/>
+      <c r="I142" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J142" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="19"/>
@@ -7999,6 +8095,15 @@
     </row>
     <row r="1024">
       <c r="A1024" s="19"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="19"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="19"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -8043,7 +8148,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>57</v>
@@ -8063,7 +8168,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>57</v>
@@ -8083,7 +8188,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>57</v>
@@ -8103,7 +8208,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>57</v>
@@ -8123,7 +8228,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>57</v>
@@ -8143,13 +8248,13 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
@@ -8163,13 +8268,13 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
@@ -8183,13 +8288,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -8203,7 +8308,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>34</v>
@@ -8223,13 +8328,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
@@ -8243,7 +8348,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>57</v>
@@ -8263,13 +8368,13 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -150,7 +150,7 @@
     <t>윽!</t>
   </si>
   <si>
-    <t>나 뭔가 잘못 선택한 걸까...?</t>
+    <t>이런 생각을 하면 안되나...?</t>
   </si>
   <si>
     <t>뭐야 이꽃...?</t>
@@ -477,7 +477,7 @@
     <t>N009_1</t>
   </si>
   <si>
-    <t>아무리 오래되도.. 잘 안잊혀지네..</t>
+    <t>아무리 오래돼도.. 잘 안 잊히네..</t>
   </si>
   <si>
     <t>어서 잠이나 자자..</t>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="227">
   <si>
     <t>NpcID</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>서린이 방 침대</t>
+  </si>
+  <si>
+    <t>N013</t>
+  </si>
+  <si>
+    <t>2스테이지 문</t>
+  </si>
+  <si>
+    <t>N014</t>
+  </si>
+  <si>
+    <t>벚꽃 나무</t>
   </si>
   <si>
     <t>NpcEventID</t>
@@ -633,6 +645,45 @@
   </si>
   <si>
     <t>어서 잠이나 자야지...</t>
+  </si>
+  <si>
+    <t>왜 이런곳에 문이 있는거지..?</t>
+  </si>
+  <si>
+    <t>비밀번호로 여는 문이네...</t>
+  </si>
+  <si>
+    <t>비밀번호가.. 어디 적혀있을까?</t>
+  </si>
+  <si>
+    <t>한번 찾아봐야겠다..</t>
+  </si>
+  <si>
+    <t>벚꽃이네..?
+오랜만에 보는 거 같은데.. 진짜 이쁘다..</t>
+  </si>
+  <si>
+    <t>어...? 그러고보니...</t>
+  </si>
+  <si>
+    <t>지금이 봄이던가..?</t>
+  </si>
+  <si>
+    <t>C011</t>
+  </si>
+  <si>
+    <t>N014_0</t>
+  </si>
+  <si>
+    <t>뭐지..? 지금 벚꽃이 필리가 없잖아..
+나한테 왜 이러는 거야...</t>
+  </si>
+  <si>
+    <t>N014_1</t>
+  </si>
+  <si>
+    <t>그렇지?
+분명 봄이었던 거 같아..</t>
   </si>
   <si>
     <t>......................</t>
@@ -840,7 +891,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J142" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J152" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1159,6 +1210,22 @@
         <v>23</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1179,31 +1246,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -1217,19 +1284,19 @@
         <v>1001.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1">
         <v>1002.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1">
         <v>-1.0</v>
@@ -1246,19 +1313,19 @@
         <v>1002.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1">
         <v>1003.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J3" s="1">
         <v>-1.0</v>
@@ -1275,22 +1342,22 @@
         <v>1003.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1">
         <v>-1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J4" s="1">
         <v>-1.0</v>
@@ -1301,26 +1368,26 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1">
         <v>1004.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1">
         <v>1005.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J5" s="1">
         <v>-1.0</v>
@@ -1331,26 +1398,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1">
         <v>1005.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1">
         <v>-1.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1">
         <v>-1.0</v>
@@ -1361,26 +1428,26 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1">
         <v>1006.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1">
         <v>1007.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J7" s="1">
         <v>-1.0</v>
@@ -1391,26 +1458,26 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1">
         <v>1007.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1">
         <v>-1.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J8" s="1">
         <v>-1.0</v>
@@ -1427,19 +1494,19 @@
         <v>2001.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
         <v>2002.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J9" s="1">
         <v>-1.0</v>
@@ -1456,19 +1523,19 @@
         <v>2002.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1">
         <v>2003.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>-1.0</v>
@@ -1485,22 +1552,22 @@
         <v>2003.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1">
         <v>-1.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1">
         <v>-1.0</v>
@@ -1511,26 +1578,26 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1">
         <v>2004.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1">
         <v>2005.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J12" s="1">
         <v>2.0</v>
@@ -1541,26 +1608,26 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1">
         <v>2005.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1">
         <v>-1.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1">
         <v>0.0</v>
@@ -1571,26 +1638,26 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1">
         <v>2006.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1">
         <v>-1.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J14" s="1">
         <v>-1.0</v>
@@ -1607,20 +1674,20 @@
         <v>3001.0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E15" s="8">
         <v>3002.0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J15" s="10">
         <v>0.0</v>
@@ -1637,20 +1704,20 @@
         <v>3002.0</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E16" s="12">
         <v>3003.0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
         <v>-1.0</v>
@@ -1667,20 +1734,20 @@
         <v>3003.0</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E17" s="8">
         <v>3004.0</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J17" s="10">
         <v>4.0</v>
@@ -1697,20 +1764,20 @@
         <v>3004.0</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E18" s="12">
         <v>3005.0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
         <v>-1.0</v>
@@ -1727,20 +1794,20 @@
         <v>3005.0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E19" s="8">
         <v>3006.0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J19" s="10">
         <v>0.0</v>
@@ -1757,20 +1824,20 @@
         <v>3006.0</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E20" s="12">
         <v>3007.0</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J20" s="14">
         <v>0.0</v>
@@ -1787,20 +1854,20 @@
         <v>3007.0</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E21" s="8">
         <v>3008.0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J21" s="10">
         <v>-1.0</v>
@@ -1817,20 +1884,20 @@
         <v>3008.0</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E22" s="12">
         <v>3009.0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J22" s="14">
         <v>2.0</v>
@@ -1847,20 +1914,20 @@
         <v>3009.0</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E23" s="8">
         <v>3010.0</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J23" s="10">
         <v>-1.0</v>
@@ -1877,20 +1944,20 @@
         <v>3010.0</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E24" s="12">
         <v>3011.0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J24" s="14">
         <v>4.0</v>
@@ -1907,20 +1974,20 @@
         <v>3011.0</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E25" s="8">
         <v>3012.0</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J25" s="10">
         <v>-1.0</v>
@@ -1937,20 +2004,20 @@
         <v>3012.0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E26" s="12">
         <v>3013.0</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J26" s="14">
         <v>4.0</v>
@@ -1967,20 +2034,20 @@
         <v>3013.0</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E27" s="8">
         <v>3014.0</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J27" s="10">
         <v>-1.0</v>
@@ -1997,20 +2064,20 @@
         <v>3014.0</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E28" s="12">
         <v>3015.0</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J28" s="14">
         <v>0.0</v>
@@ -2027,20 +2094,20 @@
         <v>3015.0</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E29" s="8">
         <v>3016.0</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J29" s="10">
         <v>-1.0</v>
@@ -2057,20 +2124,20 @@
         <v>3016.0</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E30" s="12">
         <v>3017.0</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J30" s="14">
         <v>0.0</v>
@@ -2087,20 +2154,20 @@
         <v>3017.0</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E31" s="8">
         <v>-1.0</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J31" s="10">
         <v>-1.0</v>
@@ -2117,20 +2184,20 @@
         <v>4001.0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E32" s="8">
         <v>4002.0</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J32" s="8">
         <v>4.0</v>
@@ -2147,22 +2214,22 @@
         <v>4002.0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E33" s="8">
         <v>-1.0</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J33" s="8">
         <v>0.0</v>
@@ -2173,26 +2240,26 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1">
         <v>4003.0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E34" s="8">
         <v>4004.0</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H34" s="15"/>
       <c r="I34" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J34" s="8">
         <v>2.0</v>
@@ -2203,26 +2270,26 @@
         <v>8</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>4004.0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E35" s="8">
         <v>-1.0</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H35" s="15"/>
       <c r="I35" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J35" s="8">
         <v>0.0</v>
@@ -2233,26 +2300,26 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>4005.0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E36" s="8">
         <v>-1.0</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J36" s="8">
         <v>0.0</v>
@@ -2269,20 +2336,20 @@
         <v>5001.0</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E37" s="8">
         <v>5002.0</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J37" s="10">
         <v>0.0</v>
@@ -2299,20 +2366,20 @@
         <v>5002.0</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E38" s="12">
         <v>5003.0</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J38" s="14">
         <v>0.0</v>
@@ -2329,20 +2396,20 @@
         <v>5003.0</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E39" s="10">
         <v>-1.0</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J39" s="10">
         <v>0.0</v>
@@ -2359,20 +2426,20 @@
         <v>6001.0</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E40" s="8">
         <v>6002.0</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J40" s="8">
         <v>0.0</v>
@@ -2389,20 +2456,20 @@
         <v>6002.0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E41" s="8">
         <v>6003.0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J41" s="8">
         <v>0.0</v>
@@ -2419,20 +2486,20 @@
         <v>6003.0</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E42" s="8">
         <v>6004.0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J42" s="8">
         <v>-1.0</v>
@@ -2449,20 +2516,20 @@
         <v>6004.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E43" s="8">
         <v>6005.0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J43" s="8">
         <v>0.0</v>
@@ -2479,20 +2546,20 @@
         <v>6005.0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E44" s="8">
         <v>6006.0</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J44" s="8">
         <v>-1.0</v>
@@ -2509,20 +2576,20 @@
         <v>6006.0</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E45" s="8">
         <v>6007.0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J45" s="8">
         <v>0.0</v>
@@ -2539,20 +2606,20 @@
         <v>6007.0</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E46" s="8">
         <v>6008.0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J46" s="8">
         <v>-1.0</v>
@@ -2569,20 +2636,20 @@
         <v>6008.0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E47" s="8">
         <v>6009.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J47" s="8">
         <v>0.0</v>
@@ -2599,22 +2666,22 @@
         <v>6009.0</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E48" s="8">
         <v>-1.0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J48" s="8">
         <v>-1.0</v>
@@ -2625,26 +2692,26 @@
         <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1">
         <v>6010.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E49" s="8">
         <v>6011.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J49" s="8">
         <v>-1.0</v>
@@ -2655,26 +2722,26 @@
         <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C50" s="1">
         <v>6011.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E50" s="8">
         <v>6012.0</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J50" s="8">
         <v>0.0</v>
@@ -2685,26 +2752,26 @@
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C51" s="1">
         <v>6012.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E51" s="8">
         <v>6013.0</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J51" s="8">
         <v>-1.0</v>
@@ -2715,26 +2782,26 @@
         <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1">
         <v>6013.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E52" s="8">
         <v>-1.0</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J52" s="8">
         <v>-1.0</v>
@@ -2745,26 +2812,26 @@
         <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C53" s="1">
         <v>6014.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E53" s="8">
         <v>6015.0</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J53" s="8">
         <v>3.0</v>
@@ -2775,26 +2842,26 @@
         <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C54" s="1">
         <v>6015.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E54" s="8">
         <v>6016.0</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H54" s="15"/>
       <c r="I54" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J54" s="8">
         <v>-1.0</v>
@@ -2805,26 +2872,26 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1">
         <v>6016.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E55" s="8">
         <v>6017.0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H55" s="15"/>
       <c r="I55" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J55" s="8">
         <v>-1.0</v>
@@ -2835,26 +2902,26 @@
         <v>12</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C56" s="1">
         <v>6017.0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E56" s="8">
         <v>-1.0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H56" s="15"/>
       <c r="I56" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J56" s="8">
         <v>1.0</v>
@@ -2871,20 +2938,20 @@
         <v>7001.0</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E57" s="8">
         <v>7002.0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H57" s="17"/>
       <c r="I57" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J57" s="8">
         <v>-1.0</v>
@@ -2901,20 +2968,20 @@
         <v>7002.0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E58" s="8">
         <v>7003.0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J58" s="8">
         <v>0.0</v>
@@ -2931,20 +2998,20 @@
         <v>7003.0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E59" s="8">
         <v>7004.0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J59" s="8">
         <v>-1.0</v>
@@ -2961,20 +3028,20 @@
         <v>7004.0</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E60" s="8">
         <v>7005.0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H60" s="15"/>
       <c r="I60" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J60" s="8">
         <v>0.0</v>
@@ -2991,20 +3058,20 @@
         <v>7005.0</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E61" s="8">
         <v>7006.0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J61" s="8">
         <v>-1.0</v>
@@ -3021,20 +3088,20 @@
         <v>7006.0</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E62" s="8">
         <v>7007.0</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J62" s="8">
         <v>0.0</v>
@@ -3051,20 +3118,20 @@
         <v>7007.0</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E63" s="8">
         <v>7008.0</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J63" s="8">
         <v>-1.0</v>
@@ -3081,22 +3148,22 @@
         <v>7008.0</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E64" s="8">
         <v>-1.0</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J64" s="8">
         <v>0.0</v>
@@ -3107,26 +3174,26 @@
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C65" s="1">
         <v>7009.0</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E65" s="8">
         <v>7010.0</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J65" s="8">
         <v>3.0</v>
@@ -3137,26 +3204,26 @@
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C66" s="1">
         <v>7010.0</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E66" s="8">
         <v>7011.0</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J66" s="8">
         <v>-1.0</v>
@@ -3167,26 +3234,26 @@
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C67" s="1">
         <v>7011.0</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E67" s="8">
         <v>7012.0</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J67" s="8">
         <v>0.0</v>
@@ -3197,26 +3264,26 @@
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C68" s="1">
         <v>7012.0</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E68" s="8">
         <v>-1.0</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J68" s="8">
         <v>1.0</v>
@@ -3227,26 +3294,26 @@
         <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C69" s="1">
         <v>7013.0</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E69" s="8">
         <v>7014.0</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J69" s="8">
         <v>-1.0</v>
@@ -3257,26 +3324,26 @@
         <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C70" s="1">
         <v>7014.0</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E70" s="8">
         <v>7015.0</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H70" s="15"/>
       <c r="I70" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J70" s="8">
         <v>-1.0</v>
@@ -3287,26 +3354,26 @@
         <v>14</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C71" s="1">
         <v>7015.0</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E71" s="8">
         <v>7016.0</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H71" s="15"/>
       <c r="I71" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J71" s="8">
         <v>0.0</v>
@@ -3317,26 +3384,26 @@
         <v>14</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C72" s="1">
         <v>7016.0</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E72" s="8">
         <v>7017.0</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H72" s="15"/>
       <c r="I72" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J72" s="8">
         <v>-1.0</v>
@@ -3347,26 +3414,26 @@
         <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C73" s="1">
         <v>7017.0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E73" s="8">
         <v>-1.0</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H73" s="15"/>
       <c r="I73" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J73" s="8">
         <v>2.0</v>
@@ -3383,20 +3450,20 @@
         <v>8001.0</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E74" s="8">
         <v>8002.0</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J74" s="8">
         <v>-1.0</v>
@@ -3413,20 +3480,20 @@
         <v>8002.0</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E75" s="8">
         <v>8003.0</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J75" s="8">
         <v>0.0</v>
@@ -3443,20 +3510,20 @@
         <v>8003.0</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E76" s="8">
         <v>8004.0</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H76" s="17"/>
       <c r="I76" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J76" s="8">
         <v>-1.0</v>
@@ -3473,20 +3540,20 @@
         <v>8004.0</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E77" s="8">
         <v>8005.0</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H77" s="17"/>
       <c r="I77" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J77" s="8">
         <v>0.0</v>
@@ -3503,20 +3570,20 @@
         <v>8005.0</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E78" s="8">
         <v>8006.0</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J78" s="8">
         <v>-1.0</v>
@@ -3533,22 +3600,22 @@
         <v>8006.0</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E79" s="8">
         <v>-1.0</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J79" s="8">
         <v>-1.0</v>
@@ -3559,26 +3626,26 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C80" s="1">
         <v>8007.0</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E80" s="8">
         <v>8008.0</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J80" s="8">
         <v>-1.0</v>
@@ -3589,26 +3656,26 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C81" s="1">
         <v>8008.0</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E81" s="8">
         <v>8009.0</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J81" s="8">
         <v>-1.0</v>
@@ -3619,26 +3686,26 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C82" s="1">
         <v>8009.0</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E82" s="8">
         <v>8010.0</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J82" s="8">
         <v>-1.0</v>
@@ -3649,26 +3716,26 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C83" s="1">
         <v>8010.0</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E83" s="8">
         <v>8011.0</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J83" s="8">
         <v>-1.0</v>
@@ -3679,26 +3746,26 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C84" s="1">
         <v>8011.0</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E84" s="8">
         <v>8012.0</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J84" s="8">
         <v>-1.0</v>
@@ -3709,26 +3776,26 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C85" s="1">
         <v>8012.0</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E85" s="8">
         <v>8013.0</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J85" s="8">
         <v>0.0</v>
@@ -3739,26 +3806,26 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C86" s="1">
         <v>8013.0</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E86" s="8">
         <v>-1.0</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H86" s="17"/>
       <c r="I86" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J86" s="8">
         <v>-1.0</v>
@@ -3769,26 +3836,26 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C87" s="1">
         <v>8014.0</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E87" s="1">
         <v>8015.0</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H87" s="17"/>
       <c r="I87" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J87" s="8">
         <v>2.0</v>
@@ -3799,26 +3866,26 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C88" s="1">
         <v>8015.0</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E88" s="1">
         <v>8016.0</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J88" s="8">
         <v>-1.0</v>
@@ -3829,26 +3896,26 @@
         <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C89" s="1">
         <v>8016.0</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E89" s="1">
         <v>8017.0</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H89" s="17"/>
       <c r="I89" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J89" s="8">
         <v>-1.0</v>
@@ -3859,26 +3926,26 @@
         <v>15</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C90" s="1">
         <v>8017.0</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E90" s="1">
         <v>8018.0</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H90" s="17"/>
       <c r="I90" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J90" s="8">
         <v>-1.0</v>
@@ -3889,26 +3956,26 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C91" s="1">
         <v>8018.0</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E91" s="1">
         <v>8019.0</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H91" s="17"/>
       <c r="I91" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J91" s="8">
         <v>0.0</v>
@@ -3919,26 +3986,26 @@
         <v>15</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C92" s="1">
         <v>8019.0</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E92" s="1">
         <v>8020.0</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H92" s="17"/>
       <c r="I92" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J92" s="8">
         <v>-1.0</v>
@@ -3949,26 +4016,26 @@
         <v>15</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C93" s="1">
         <v>8020.0</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E93" s="1">
         <v>8021.0</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H93" s="17"/>
       <c r="I93" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J93" s="8">
         <v>1.0</v>
@@ -3979,26 +4046,26 @@
         <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C94" s="1">
         <v>8021.0</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E94" s="8">
         <v>-1.0</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H94" s="17"/>
       <c r="I94" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J94" s="8">
         <v>0.0</v>
@@ -4015,20 +4082,20 @@
         <v>9001.0</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E95" s="8">
         <v>9002.0</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H95" s="17"/>
       <c r="I95" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J95" s="8">
         <v>1.0</v>
@@ -4045,20 +4112,20 @@
         <v>9002.0</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E96" s="8">
         <v>9003.0</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H96" s="17"/>
       <c r="I96" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J96" s="8">
         <v>0.0</v>
@@ -4075,22 +4142,22 @@
         <v>9003.0</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E97" s="8">
         <v>-1.0</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J97" s="8">
         <v>0.0</v>
@@ -4101,26 +4168,26 @@
         <v>16</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C98" s="1">
         <v>9004.0</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E98" s="8">
         <v>-1.0</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H98" s="17"/>
       <c r="I98" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J98" s="8">
         <v>0.0</v>
@@ -4131,26 +4198,26 @@
         <v>16</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C99" s="1">
         <v>9005.0</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E99" s="8">
         <v>9006.0</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H99" s="17"/>
       <c r="I99" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J99" s="8">
         <v>0.0</v>
@@ -4161,26 +4228,26 @@
         <v>16</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C100" s="1">
         <v>9006.0</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E100" s="8">
         <v>-1.0</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H100" s="17"/>
       <c r="I100" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J100" s="8">
         <v>0.0</v>
@@ -4197,20 +4264,20 @@
         <v>10001.0</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E101" s="8">
         <v>10002.0</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H101" s="17"/>
       <c r="I101" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J101" s="8">
         <v>0.0</v>
@@ -4227,20 +4294,20 @@
         <v>10002.0</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E102" s="8">
         <v>10003.0</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H102" s="17"/>
       <c r="I102" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J102" s="8">
         <v>2.0</v>
@@ -4257,20 +4324,20 @@
         <v>10003.0</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E103" s="8">
         <v>10004.0</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J103" s="8">
         <v>4.0</v>
@@ -4287,20 +4354,20 @@
         <v>10004.0</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E104" s="8">
         <v>10005.0</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J104" s="8">
         <v>5.0</v>
@@ -4317,20 +4384,20 @@
         <v>10005.0</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E105" s="8">
         <v>10006.0</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J105" s="8">
         <v>1.0</v>
@@ -4347,20 +4414,20 @@
         <v>10006.0</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E106" s="8">
         <v>10007.0</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J106" s="8">
         <v>3.0</v>
@@ -4377,20 +4444,20 @@
         <v>10007.0</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E107" s="8">
         <v>10008.0</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J107" s="8">
         <v>1.0</v>
@@ -4407,20 +4474,20 @@
         <v>10008.0</v>
       </c>
       <c r="D108" s="18" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E108" s="8">
         <v>10009.0</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H108" s="17"/>
       <c r="I108" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J108" s="8">
         <v>2.0</v>
@@ -4437,20 +4504,20 @@
         <v>10009.0</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E109" s="8">
         <v>10010.0</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H109" s="17"/>
       <c r="I109" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J109" s="8">
         <v>6.0</v>
@@ -4467,20 +4534,20 @@
         <v>10010.0</v>
       </c>
       <c r="D110" s="18" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E110" s="8">
         <v>10011.0</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H110" s="17"/>
       <c r="I110" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J110" s="8">
         <v>1.0</v>
@@ -4497,20 +4564,20 @@
         <v>10011.0</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E111" s="8">
         <v>10012.0</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H111" s="17"/>
       <c r="I111" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J111" s="8">
         <v>4.0</v>
@@ -4527,22 +4594,22 @@
         <v>10012.0</v>
       </c>
       <c r="D112" s="18" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E112" s="8">
         <v>-1.0</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J112" s="8">
         <v>3.0</v>
@@ -4553,26 +4620,26 @@
         <v>18</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C113" s="1">
         <v>10013.0</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E113" s="8">
         <v>10014.0</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H113" s="17"/>
       <c r="I113" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J113" s="8">
         <v>3.0</v>
@@ -4583,26 +4650,26 @@
         <v>18</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C114" s="1">
         <v>10014.0</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E114" s="8">
         <v>10015.0</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H114" s="17"/>
       <c r="I114" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J114" s="8">
         <v>2.0</v>
@@ -4613,26 +4680,26 @@
         <v>18</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C115" s="1">
         <v>10015.0</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E115" s="8">
         <v>10016.0</v>
       </c>
       <c r="F115" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J115" s="8">
         <v>1.0</v>
@@ -4643,26 +4710,26 @@
         <v>18</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C116" s="1">
         <v>10016.0</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E116" s="8">
         <v>-1.0</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H116" s="17"/>
       <c r="I116" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J116" s="8">
         <v>1.0</v>
@@ -4673,26 +4740,26 @@
         <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C117" s="1">
         <v>10017.0</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E117" s="8">
         <v>10018.0</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H117" s="17"/>
       <c r="I117" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J117" s="8">
         <v>6.0</v>
@@ -4703,26 +4770,26 @@
         <v>18</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C118" s="1">
         <v>10018.0</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E118" s="8">
         <v>10019.0</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J118" s="8">
         <v>7.0</v>
@@ -4733,26 +4800,26 @@
         <v>18</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C119" s="1">
         <v>10019.0</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E119" s="8">
         <v>10020.0</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H119" s="17"/>
       <c r="I119" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J119" s="8">
         <v>5.0</v>
@@ -4763,26 +4830,26 @@
         <v>18</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C120" s="1">
         <v>10020.0</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E120" s="8">
         <v>-1.0</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H120" s="17"/>
       <c r="I120" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J120" s="8">
         <v>1.0</v>
@@ -4799,20 +4866,20 @@
         <v>11001.0</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E121" s="8">
         <v>11002.0</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G121" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H121" s="17"/>
       <c r="I121" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J121" s="8">
         <v>10.0</v>
@@ -4829,20 +4896,20 @@
         <v>11002.0</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E122" s="8">
         <v>11003.0</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G122" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H122" s="17"/>
       <c r="I122" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J122" s="8">
         <v>10.0</v>
@@ -4859,20 +4926,20 @@
         <v>11003.0</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E123" s="8">
         <v>11004.0</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H123" s="17"/>
       <c r="I123" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J123" s="8">
         <v>0.0</v>
@@ -4889,20 +4956,20 @@
         <v>11004.0</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E124" s="8">
         <v>11005.0</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H124" s="17"/>
       <c r="I124" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J124" s="8">
         <v>0.0</v>
@@ -4919,20 +4986,20 @@
         <v>11005.0</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E125" s="8">
         <v>11006.0</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G125" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H125" s="17"/>
       <c r="I125" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J125" s="8">
         <v>11.0</v>
@@ -4949,20 +5016,20 @@
         <v>11006.0</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E126" s="8">
         <v>11007.0</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G126" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H126" s="17"/>
       <c r="I126" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J126" s="8">
         <v>11.0</v>
@@ -4979,20 +5046,20 @@
         <v>11007.0</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E127" s="8">
         <v>11008.0</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J127" s="8">
         <v>0.0</v>
@@ -5009,20 +5076,20 @@
         <v>11008.0</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E128" s="8">
         <v>11009.0</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G128" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H128" s="17"/>
       <c r="I128" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J128" s="8">
         <v>9.0</v>
@@ -5039,20 +5106,20 @@
         <v>11009.0</v>
       </c>
       <c r="D129" s="18" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E129" s="8">
         <v>11010.0</v>
       </c>
       <c r="F129" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G129" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J129" s="8">
         <v>9.0</v>
@@ -5069,20 +5136,20 @@
         <v>11010.0</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E130" s="8">
         <v>11011.0</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J130" s="8">
         <v>0.0</v>
@@ -5099,22 +5166,22 @@
         <v>11011.0</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E131" s="8">
         <v>-1.0</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G131" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J131" s="8">
         <v>8.0</v>
@@ -5125,26 +5192,26 @@
         <v>20</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C132" s="1">
         <v>11012.0</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E132" s="8">
         <v>11013.0</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G132" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H132" s="17"/>
       <c r="I132" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J132" s="8">
         <v>9.0</v>
@@ -5155,26 +5222,26 @@
         <v>20</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C133" s="1">
         <v>11013.0</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E133" s="8">
         <v>11014.0</v>
       </c>
       <c r="F133" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G133" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H133" s="17"/>
       <c r="I133" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J133" s="8">
         <v>9.0</v>
@@ -5185,26 +5252,26 @@
         <v>20</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C134" s="1">
         <v>11014.0</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E134" s="8">
         <v>-1.0</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J134" s="8">
         <v>1.0</v>
@@ -5215,26 +5282,26 @@
         <v>20</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C135" s="1">
         <v>11015.0</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E135" s="8">
         <v>11016.0</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G135" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J135" s="8">
         <v>9.0</v>
@@ -5245,26 +5312,26 @@
         <v>20</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C136" s="1">
         <v>11016.0</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E136" s="8">
         <v>11017.0</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G136" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H136" s="17"/>
       <c r="I136" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J136" s="8">
         <v>9.0</v>
@@ -5275,26 +5342,26 @@
         <v>20</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C137" s="1">
         <v>11017.0</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E137" s="8">
         <v>-1.0</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H137" s="17"/>
       <c r="I137" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J137" s="8">
         <v>1.0</v>
@@ -5311,20 +5378,20 @@
         <v>12001.0</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E138" s="8">
         <v>12002.0</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J138" s="8">
         <v>-1.0</v>
@@ -5341,20 +5408,20 @@
         <v>12002.0</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E139" s="8">
         <v>12003.0</v>
       </c>
       <c r="F139" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H139" s="17"/>
       <c r="I139" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J139" s="8">
         <v>-1.0</v>
@@ -5371,20 +5438,20 @@
         <v>12003.0</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E140" s="8">
         <v>12004.0</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H140" s="17"/>
       <c r="I140" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J140" s="8">
         <v>-1.0</v>
@@ -5401,20 +5468,20 @@
         <v>12004.0</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E141" s="8">
         <v>12005.0</v>
       </c>
       <c r="F141" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G141" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H141" s="17"/>
       <c r="I141" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J141" s="8">
         <v>-1.0</v>
@@ -5431,54 +5498,326 @@
         <v>12005.0</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E142" s="8">
         <v>-1.0</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H142" s="17"/>
       <c r="I142" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J142" s="8">
         <v>-1.0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="19"/>
+      <c r="A143" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="1">
+        <v>13001.0</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="E143" s="8">
+        <v>13002.0</v>
+      </c>
+      <c r="F143" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G143" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H143" s="17"/>
+      <c r="I143" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J143" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="19"/>
+      <c r="A144" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" s="1">
+        <v>13002.0</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="E144" s="8">
+        <v>13003.0</v>
+      </c>
+      <c r="F144" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G144" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H144" s="17"/>
+      <c r="I144" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J144" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="19"/>
+      <c r="A145" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="1">
+        <v>13003.0</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E145" s="8">
+        <v>13004.0</v>
+      </c>
+      <c r="F145" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H145" s="17"/>
+      <c r="I145" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J145" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="19"/>
+      <c r="A146" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="1">
+        <v>13004.0</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F146" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G146" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H146" s="17"/>
+      <c r="I146" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J146" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="19"/>
+      <c r="A147" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" s="1">
+        <v>14001.0</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E147" s="8">
+        <v>14002.0</v>
+      </c>
+      <c r="F147" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H147" s="17"/>
+      <c r="I147" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J147" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="19"/>
+      <c r="A148" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="1">
+        <v>14002.0</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E148" s="8">
+        <v>14003.0</v>
+      </c>
+      <c r="F148" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G148" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148" s="17"/>
+      <c r="I148" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J148" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="19"/>
+      <c r="A149" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="1">
+        <v>14003.0</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="E149" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G149" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H149" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J149" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="19"/>
+      <c r="A150" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C150" s="1">
+        <v>14004.0</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E150" s="8">
+        <v>14005.0</v>
+      </c>
+      <c r="F150" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G150" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H150" s="17"/>
+      <c r="I150" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J150" s="8">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="19"/>
+      <c r="A151" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C151" s="1">
+        <v>14005.0</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F151" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G151" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151" s="17"/>
+      <c r="I151" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J151" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="19"/>
+      <c r="A152" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C152" s="1">
+        <v>14006.0</v>
+      </c>
+      <c r="D152" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E152" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G152" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H152" s="17"/>
+      <c r="I152" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J152" s="8">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="19"/>
@@ -8128,19 +8467,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -8148,16 +8487,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -8168,16 +8507,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -8188,16 +8527,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -8208,16 +8547,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -8228,16 +8567,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1">
         <v>-1.0</v>
@@ -8248,16 +8587,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1">
         <v>-1.0</v>
@@ -8268,16 +8607,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1">
         <v>-1.0</v>
@@ -8288,16 +8627,16 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1">
         <v>-1.0</v>
@@ -8308,16 +8647,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F10" s="1">
         <v>-1.0</v>
@@ -8328,16 +8667,16 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1">
         <v>-1.0</v>
@@ -8348,16 +8687,16 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F12" s="1">
         <v>-1.0</v>
@@ -8368,18 +8707,38 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="227">
   <si>
     <t>NpcID</t>
   </si>
@@ -8724,7 +8724,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>218</v>
@@ -8733,12 +8733,32 @@
         <v>61</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="1">
         <v>-1.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="NPC" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="NpcDialog" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="NpcReDialog" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="NPC" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="NpcDialog" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="NpcReDialog" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="231">
   <si>
     <t>NpcID</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>벚꽃 나무</t>
+  </si>
+  <si>
+    <t>N015</t>
+  </si>
+  <si>
+    <t>3스테이지 서린이 방 책상</t>
   </si>
   <si>
     <t>NpcEventID</t>
@@ -684,6 +690,12 @@
   <si>
     <t>그렇지?
 분명 봄이었던 거 같아..</t>
+  </si>
+  <si>
+    <t>어...? 분명 여기에 일기장을 뒀는데...</t>
+  </si>
+  <si>
+    <t>여기에 없으면... 어디에 있는 거지..?</t>
   </si>
   <si>
     <t>......................</t>
@@ -803,9 +815,6 @@
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -816,6 +825,9 @@
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -890,8 +902,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J152" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D15:J156" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1226,6 +1242,14 @@
         <v>27</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1246,31 +1270,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
@@ -1284,19 +1308,19 @@
         <v>1001.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1">
         <v>1002.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1">
         <v>-1.0</v>
@@ -1313,19 +1337,19 @@
         <v>1002.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1">
         <v>1003.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1">
         <v>-1.0</v>
@@ -1342,22 +1366,22 @@
         <v>1003.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1">
         <v>-1.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1">
         <v>-1.0</v>
@@ -1368,29 +1392,29 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1">
         <v>1004.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
         <v>1005.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J5" s="1">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -1398,29 +1422,29 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1">
         <v>1005.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>-1.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1">
-        <v>-1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -1428,29 +1452,29 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <v>1006.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1">
         <v>1007.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7" s="1">
-        <v>-1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="8">
@@ -1458,29 +1482,29 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1">
         <v>1007.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1">
         <v>-1.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1">
-        <v>-1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9">
@@ -1494,19 +1518,19 @@
         <v>2001.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1">
         <v>2002.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J9" s="1">
         <v>-1.0</v>
@@ -1523,19 +1547,19 @@
         <v>2002.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1">
         <v>2003.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J10" s="1">
         <v>-1.0</v>
@@ -1552,22 +1576,22 @@
         <v>2003.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1">
         <v>-1.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J11" s="1">
         <v>-1.0</v>
@@ -1578,29 +1602,29 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C12" s="1">
         <v>2004.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1">
         <v>2005.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="13">
@@ -1608,29 +1632,29 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1">
         <v>2005.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1">
         <v>-1.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J13" s="1">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="14">
@@ -1638,29 +1662,29 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1">
         <v>2006.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1">
         <v>-1.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J14" s="1">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -1674,23 +1698,23 @@
         <v>3001.0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" s="8">
         <v>3002.0</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0.0</v>
+        <v>42</v>
+      </c>
+      <c r="J15" s="8">
+        <v>4.0</v>
       </c>
     </row>
     <row r="16">
@@ -1703,23 +1727,23 @@
       <c r="C16" s="6">
         <v>3002.0</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="D16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="11">
         <v>3003.0</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="F16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="H16" s="10"/>
+      <c r="I16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="13">
         <v>-1.0</v>
       </c>
     </row>
@@ -1734,23 +1758,23 @@
         <v>3003.0</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E17" s="8">
         <v>3004.0</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="10">
-        <v>4.0</v>
+        <v>42</v>
+      </c>
+      <c r="J17" s="8">
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
@@ -1763,23 +1787,23 @@
       <c r="C18" s="6">
         <v>3004.0</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="11">
+        <v>3005.0</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="12">
-        <v>3005.0</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>-1.0</v>
       </c>
     </row>
@@ -1794,22 +1818,22 @@
         <v>3005.0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="8">
         <v>3006.0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H19" s="7"/>
-      <c r="I19" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J19" s="10">
+      <c r="I19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="14">
         <v>0.0</v>
       </c>
     </row>
@@ -1823,24 +1847,24 @@
       <c r="C20" s="6">
         <v>3006.0</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="D20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="11">
         <v>3007.0</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.0</v>
+      <c r="F20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="11">
+        <v>5.0</v>
       </c>
     </row>
     <row r="21">
@@ -1854,22 +1878,22 @@
         <v>3007.0</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" s="8">
         <v>3008.0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H21" s="7"/>
-      <c r="I21" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="10">
+      <c r="I21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -1883,24 +1907,24 @@
       <c r="C22" s="6">
         <v>3008.0</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="12">
+      <c r="D22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="11">
         <v>3009.0</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="14">
-        <v>2.0</v>
+      <c r="F22" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="11">
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1914,22 +1938,22 @@
         <v>3009.0</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E23" s="8">
         <v>3010.0</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H23" s="7"/>
-      <c r="I23" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" s="10">
+      <c r="I23" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -1943,23 +1967,23 @@
       <c r="C24" s="6">
         <v>3010.0</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="12">
+      <c r="D24" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="11">
         <v>3011.0</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="14">
+      <c r="F24" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" s="13">
         <v>4.0</v>
       </c>
     </row>
@@ -1974,22 +1998,22 @@
         <v>3011.0</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25" s="8">
         <v>3012.0</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H25" s="7"/>
-      <c r="I25" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="10">
+      <c r="I25" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -2003,23 +2027,23 @@
       <c r="C26" s="6">
         <v>3012.0</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="12">
+      <c r="D26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="11">
         <v>3013.0</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="14">
+      <c r="F26" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="13">
         <v>4.0</v>
       </c>
     </row>
@@ -2034,22 +2058,22 @@
         <v>3013.0</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E27" s="8">
         <v>3014.0</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H27" s="7"/>
-      <c r="I27" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="10">
+      <c r="I27" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -2063,24 +2087,24 @@
       <c r="C28" s="6">
         <v>3014.0</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="12">
+      <c r="D28" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="11">
         <v>3015.0</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="14">
-        <v>0.0</v>
+      <c r="F28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="11">
+        <v>4.0</v>
       </c>
     </row>
     <row r="29">
@@ -2094,22 +2118,22 @@
         <v>3015.0</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E29" s="8">
         <v>3016.0</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H29" s="7"/>
-      <c r="I29" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J29" s="10">
+      <c r="I29" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -2123,24 +2147,24 @@
       <c r="C30" s="6">
         <v>3016.0</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="12">
+      <c r="D30" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="11">
         <v>3017.0</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="14">
-        <v>0.0</v>
+      <c r="F30" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="11">
+        <v>4.0</v>
       </c>
     </row>
     <row r="31">
@@ -2154,22 +2178,22 @@
         <v>3017.0</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E31" s="8">
         <v>-1.0</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H31" s="7"/>
-      <c r="I31" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J31" s="10">
+      <c r="I31" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" s="14">
         <v>-1.0</v>
       </c>
     </row>
@@ -2184,20 +2208,20 @@
         <v>4001.0</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E32" s="8">
         <v>4002.0</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J32" s="8">
         <v>4.0</v>
@@ -2214,22 +2238,22 @@
         <v>4002.0</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E33" s="8">
         <v>-1.0</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J33" s="8">
         <v>0.0</v>
@@ -2240,29 +2264,29 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1">
         <v>4003.0</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E34" s="8">
         <v>4004.0</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H34" s="15"/>
       <c r="I34" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J34" s="8">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="35">
@@ -2270,29 +2294,29 @@
         <v>8</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1">
         <v>4004.0</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E35" s="8">
         <v>-1.0</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H35" s="15"/>
       <c r="I35" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J35" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="36">
@@ -2300,26 +2324,26 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1">
         <v>4005.0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E36" s="8">
         <v>-1.0</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J36" s="8">
         <v>0.0</v>
@@ -2336,23 +2360,23 @@
         <v>5001.0</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E37" s="8">
         <v>5002.0</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J37" s="10">
-        <v>0.0</v>
+        <v>42</v>
+      </c>
+      <c r="J37" s="8">
+        <v>5.0</v>
       </c>
     </row>
     <row r="38">
@@ -2365,23 +2389,23 @@
       <c r="C38" s="6">
         <v>5002.0</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E38" s="12">
+      <c r="D38" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="11">
         <v>5003.0</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J38" s="14">
+      <c r="F38" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -2396,22 +2420,22 @@
         <v>5003.0</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="10">
+        <v>88</v>
+      </c>
+      <c r="E39" s="14">
         <v>-1.0</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="10">
+        <v>42</v>
+      </c>
+      <c r="J39" s="14">
         <v>0.0</v>
       </c>
     </row>
@@ -2426,20 +2450,20 @@
         <v>6001.0</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E40" s="8">
         <v>6002.0</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J40" s="8">
         <v>0.0</v>
@@ -2456,20 +2480,20 @@
         <v>6002.0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E41" s="8">
         <v>6003.0</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J41" s="8">
         <v>0.0</v>
@@ -2486,20 +2510,20 @@
         <v>6003.0</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="8">
         <v>6004.0</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J42" s="8">
         <v>-1.0</v>
@@ -2516,23 +2540,23 @@
         <v>6004.0</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" s="8">
         <v>6005.0</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J43" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="44">
@@ -2546,20 +2570,20 @@
         <v>6005.0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E44" s="8">
         <v>6006.0</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J44" s="8">
         <v>-1.0</v>
@@ -2576,20 +2600,20 @@
         <v>6006.0</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E45" s="8">
         <v>6007.0</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J45" s="8">
         <v>0.0</v>
@@ -2606,20 +2630,20 @@
         <v>6007.0</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E46" s="8">
         <v>6008.0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J46" s="8">
         <v>-1.0</v>
@@ -2636,20 +2660,20 @@
         <v>6008.0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E47" s="8">
         <v>6009.0</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J47" s="8">
         <v>0.0</v>
@@ -2666,22 +2690,22 @@
         <v>6009.0</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E48" s="8">
         <v>-1.0</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J48" s="8">
         <v>-1.0</v>
@@ -2692,26 +2716,26 @@
         <v>12</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C49" s="1">
         <v>6010.0</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="8">
         <v>6011.0</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J49" s="8">
         <v>-1.0</v>
@@ -2722,26 +2746,26 @@
         <v>12</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C50" s="1">
         <v>6011.0</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E50" s="8">
         <v>6012.0</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J50" s="8">
         <v>0.0</v>
@@ -2752,26 +2776,26 @@
         <v>12</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1">
         <v>6012.0</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E51" s="8">
         <v>6013.0</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J51" s="8">
         <v>-1.0</v>
@@ -2782,26 +2806,26 @@
         <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C52" s="1">
         <v>6013.0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E52" s="8">
         <v>-1.0</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J52" s="8">
         <v>-1.0</v>
@@ -2812,29 +2836,29 @@
         <v>12</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C53" s="1">
         <v>6014.0</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E53" s="8">
         <v>6015.0</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J53" s="8">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="54">
@@ -2842,26 +2866,26 @@
         <v>12</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C54" s="1">
         <v>6015.0</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E54" s="8">
         <v>6016.0</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H54" s="15"/>
       <c r="I54" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J54" s="8">
         <v>-1.0</v>
@@ -2872,26 +2896,26 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1">
         <v>6016.0</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E55" s="8">
         <v>6017.0</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H55" s="15"/>
       <c r="I55" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J55" s="8">
         <v>-1.0</v>
@@ -2902,26 +2926,26 @@
         <v>12</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C56" s="1">
         <v>6017.0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E56" s="8">
         <v>-1.0</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H56" s="15"/>
       <c r="I56" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J56" s="8">
         <v>1.0</v>
@@ -2938,20 +2962,20 @@
         <v>7001.0</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E57" s="8">
         <v>7002.0</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H57" s="17"/>
       <c r="I57" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J57" s="8">
         <v>-1.0</v>
@@ -2968,20 +2992,20 @@
         <v>7002.0</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E58" s="8">
         <v>7003.0</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J58" s="8">
         <v>0.0</v>
@@ -2998,20 +3022,20 @@
         <v>7003.0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E59" s="8">
         <v>7004.0</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J59" s="8">
         <v>-1.0</v>
@@ -3028,20 +3052,20 @@
         <v>7004.0</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E60" s="8">
         <v>7005.0</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H60" s="15"/>
       <c r="I60" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J60" s="8">
         <v>0.0</v>
@@ -3058,20 +3082,20 @@
         <v>7005.0</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E61" s="8">
         <v>7006.0</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J61" s="8">
         <v>-1.0</v>
@@ -3088,20 +3112,20 @@
         <v>7006.0</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E62" s="8">
         <v>7007.0</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J62" s="8">
         <v>0.0</v>
@@ -3118,20 +3142,20 @@
         <v>7007.0</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E63" s="8">
         <v>7008.0</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J63" s="8">
         <v>-1.0</v>
@@ -3148,25 +3172,25 @@
         <v>7008.0</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E64" s="8">
         <v>-1.0</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="I64" s="10" t="s">
-        <v>62</v>
+        <v>117</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="J64" s="8">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="65">
@@ -3174,26 +3198,26 @@
         <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C65" s="1">
         <v>7009.0</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E65" s="8">
         <v>7010.0</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J65" s="8">
         <v>3.0</v>
@@ -3204,26 +3228,26 @@
         <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C66" s="1">
         <v>7010.0</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E66" s="8">
         <v>7011.0</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J66" s="8">
         <v>-1.0</v>
@@ -3234,29 +3258,29 @@
         <v>14</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C67" s="1">
         <v>7011.0</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E67" s="8">
         <v>7012.0</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J67" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="68">
@@ -3264,26 +3288,26 @@
         <v>14</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C68" s="1">
         <v>7012.0</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E68" s="8">
         <v>-1.0</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J68" s="8">
         <v>1.0</v>
@@ -3294,26 +3318,26 @@
         <v>14</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C69" s="1">
         <v>7013.0</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E69" s="8">
         <v>7014.0</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J69" s="8">
         <v>-1.0</v>
@@ -3324,26 +3348,26 @@
         <v>14</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C70" s="1">
         <v>7014.0</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E70" s="8">
         <v>7015.0</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H70" s="15"/>
       <c r="I70" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J70" s="8">
         <v>-1.0</v>
@@ -3354,26 +3378,26 @@
         <v>14</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C71" s="1">
         <v>7015.0</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E71" s="8">
         <v>7016.0</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H71" s="15"/>
       <c r="I71" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J71" s="8">
         <v>0.0</v>
@@ -3384,26 +3408,26 @@
         <v>14</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C72" s="1">
         <v>7016.0</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E72" s="8">
         <v>7017.0</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H72" s="15"/>
       <c r="I72" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J72" s="8">
         <v>-1.0</v>
@@ -3414,26 +3438,26 @@
         <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C73" s="1">
         <v>7017.0</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E73" s="8">
         <v>-1.0</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H73" s="15"/>
       <c r="I73" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J73" s="8">
         <v>2.0</v>
@@ -3450,20 +3474,20 @@
         <v>8001.0</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E74" s="8">
         <v>8002.0</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J74" s="8">
         <v>-1.0</v>
@@ -3480,23 +3504,23 @@
         <v>8002.0</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E75" s="8">
         <v>8003.0</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J75" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="76">
@@ -3510,20 +3534,20 @@
         <v>8003.0</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E76" s="8">
         <v>8004.0</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H76" s="17"/>
       <c r="I76" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J76" s="8">
         <v>-1.0</v>
@@ -3540,23 +3564,23 @@
         <v>8004.0</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E77" s="8">
         <v>8005.0</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H77" s="17"/>
       <c r="I77" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J77" s="8">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="78">
@@ -3570,20 +3594,20 @@
         <v>8005.0</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E78" s="8">
         <v>8006.0</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H78" s="17"/>
       <c r="I78" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J78" s="8">
         <v>-1.0</v>
@@ -3600,22 +3624,22 @@
         <v>8006.0</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E79" s="8">
         <v>-1.0</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J79" s="8">
         <v>-1.0</v>
@@ -3626,26 +3650,26 @@
         <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C80" s="1">
         <v>8007.0</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E80" s="8">
         <v>8008.0</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J80" s="8">
         <v>-1.0</v>
@@ -3656,26 +3680,26 @@
         <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C81" s="1">
         <v>8008.0</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E81" s="8">
         <v>8009.0</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J81" s="8">
         <v>-1.0</v>
@@ -3686,26 +3710,26 @@
         <v>15</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C82" s="1">
         <v>8009.0</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E82" s="8">
         <v>8010.0</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J82" s="8">
         <v>-1.0</v>
@@ -3716,26 +3740,26 @@
         <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C83" s="1">
         <v>8010.0</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E83" s="8">
         <v>8011.0</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J83" s="8">
         <v>-1.0</v>
@@ -3746,26 +3770,26 @@
         <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C84" s="1">
         <v>8011.0</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E84" s="8">
         <v>8012.0</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J84" s="8">
         <v>-1.0</v>
@@ -3776,26 +3800,26 @@
         <v>15</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C85" s="1">
         <v>8012.0</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E85" s="8">
         <v>8013.0</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J85" s="8">
         <v>0.0</v>
@@ -3806,26 +3830,26 @@
         <v>15</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C86" s="1">
         <v>8013.0</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E86" s="8">
         <v>-1.0</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H86" s="17"/>
       <c r="I86" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J86" s="8">
         <v>-1.0</v>
@@ -3836,26 +3860,26 @@
         <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C87" s="1">
         <v>8014.0</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E87" s="1">
         <v>8015.0</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H87" s="17"/>
       <c r="I87" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J87" s="8">
         <v>2.0</v>
@@ -3866,26 +3890,26 @@
         <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C88" s="1">
         <v>8015.0</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E88" s="1">
         <v>8016.0</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H88" s="17"/>
       <c r="I88" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J88" s="8">
         <v>-1.0</v>
@@ -3896,26 +3920,26 @@
         <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C89" s="1">
         <v>8016.0</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E89" s="1">
         <v>8017.0</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H89" s="17"/>
       <c r="I89" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J89" s="8">
         <v>-1.0</v>
@@ -3926,26 +3950,26 @@
         <v>15</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C90" s="1">
         <v>8017.0</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E90" s="1">
         <v>8018.0</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H90" s="17"/>
       <c r="I90" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J90" s="8">
         <v>-1.0</v>
@@ -3956,29 +3980,29 @@
         <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C91" s="1">
         <v>8018.0</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E91" s="1">
         <v>8019.0</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H91" s="17"/>
       <c r="I91" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J91" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
@@ -3986,26 +4010,26 @@
         <v>15</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C92" s="1">
         <v>8019.0</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E92" s="1">
         <v>8020.0</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H92" s="17"/>
       <c r="I92" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J92" s="8">
         <v>-1.0</v>
@@ -4016,26 +4040,26 @@
         <v>15</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C93" s="1">
         <v>8020.0</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E93" s="1">
         <v>8021.0</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H93" s="17"/>
       <c r="I93" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J93" s="8">
         <v>1.0</v>
@@ -4046,29 +4070,29 @@
         <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C94" s="1">
         <v>8021.0</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E94" s="8">
         <v>-1.0</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H94" s="17"/>
       <c r="I94" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J94" s="8">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="95">
@@ -4082,20 +4106,20 @@
         <v>9001.0</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E95" s="8">
         <v>9002.0</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H95" s="17"/>
       <c r="I95" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J95" s="8">
         <v>1.0</v>
@@ -4111,24 +4135,24 @@
       <c r="C96" s="1">
         <v>9002.0</v>
       </c>
-      <c r="D96" s="11" t="s">
-        <v>148</v>
+      <c r="D96" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="E96" s="8">
         <v>9003.0</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H96" s="17"/>
       <c r="I96" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J96" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="97">
@@ -4142,25 +4166,25 @@
         <v>9003.0</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E97" s="8">
         <v>-1.0</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J97" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="98">
@@ -4168,26 +4192,26 @@
         <v>16</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C98" s="1">
         <v>9004.0</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E98" s="8">
         <v>-1.0</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H98" s="17"/>
       <c r="I98" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J98" s="8">
         <v>0.0</v>
@@ -4198,26 +4222,26 @@
         <v>16</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C99" s="1">
         <v>9005.0</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E99" s="8">
         <v>9006.0</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H99" s="17"/>
       <c r="I99" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J99" s="8">
         <v>0.0</v>
@@ -4228,26 +4252,26 @@
         <v>16</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C100" s="1">
         <v>9006.0</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E100" s="8">
         <v>-1.0</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H100" s="17"/>
       <c r="I100" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J100" s="8">
         <v>0.0</v>
@@ -4264,23 +4288,23 @@
         <v>10001.0</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E101" s="8">
         <v>10002.0</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H101" s="17"/>
       <c r="I101" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J101" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="102">
@@ -4294,20 +4318,20 @@
         <v>10002.0</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E102" s="8">
         <v>10003.0</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H102" s="17"/>
       <c r="I102" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J102" s="8">
         <v>2.0</v>
@@ -4324,20 +4348,20 @@
         <v>10003.0</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E103" s="8">
         <v>10004.0</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J103" s="8">
         <v>4.0</v>
@@ -4354,20 +4378,20 @@
         <v>10004.0</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E104" s="8">
         <v>10005.0</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J104" s="8">
         <v>5.0</v>
@@ -4384,20 +4408,20 @@
         <v>10005.0</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E105" s="8">
         <v>10006.0</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J105" s="8">
         <v>1.0</v>
@@ -4414,20 +4438,20 @@
         <v>10006.0</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E106" s="8">
         <v>10007.0</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J106" s="8">
         <v>3.0</v>
@@ -4444,20 +4468,20 @@
         <v>10007.0</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E107" s="8">
         <v>10008.0</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J107" s="8">
         <v>1.0</v>
@@ -4474,20 +4498,20 @@
         <v>10008.0</v>
       </c>
       <c r="D108" s="18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E108" s="8">
         <v>10009.0</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H108" s="17"/>
       <c r="I108" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J108" s="8">
         <v>2.0</v>
@@ -4504,20 +4528,20 @@
         <v>10009.0</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E109" s="8">
         <v>10010.0</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H109" s="17"/>
       <c r="I109" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J109" s="8">
         <v>6.0</v>
@@ -4534,23 +4558,23 @@
         <v>10010.0</v>
       </c>
       <c r="D110" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E110" s="8">
         <v>10011.0</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H110" s="17"/>
       <c r="I110" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J110" s="8">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
@@ -4564,20 +4588,20 @@
         <v>10011.0</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E111" s="8">
         <v>10012.0</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H111" s="17"/>
       <c r="I111" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J111" s="8">
         <v>4.0</v>
@@ -4594,22 +4618,22 @@
         <v>10012.0</v>
       </c>
       <c r="D112" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E112" s="8">
         <v>-1.0</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J112" s="8">
         <v>3.0</v>
@@ -4620,26 +4644,26 @@
         <v>18</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C113" s="1">
         <v>10013.0</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E113" s="8">
         <v>10014.0</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H113" s="17"/>
       <c r="I113" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J113" s="8">
         <v>3.0</v>
@@ -4650,26 +4674,26 @@
         <v>18</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C114" s="1">
         <v>10014.0</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E114" s="8">
         <v>10015.0</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H114" s="17"/>
       <c r="I114" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J114" s="8">
         <v>2.0</v>
@@ -4680,26 +4704,26 @@
         <v>18</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C115" s="1">
         <v>10015.0</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E115" s="8">
         <v>10016.0</v>
       </c>
       <c r="F115" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J115" s="8">
         <v>1.0</v>
@@ -4710,26 +4734,26 @@
         <v>18</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C116" s="1">
         <v>10016.0</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E116" s="8">
         <v>-1.0</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H116" s="17"/>
       <c r="I116" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J116" s="8">
         <v>1.0</v>
@@ -4740,26 +4764,26 @@
         <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C117" s="1">
         <v>10017.0</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E117" s="8">
         <v>10018.0</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H117" s="17"/>
       <c r="I117" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J117" s="8">
         <v>6.0</v>
@@ -4770,26 +4794,26 @@
         <v>18</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C118" s="1">
         <v>10018.0</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E118" s="8">
         <v>10019.0</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J118" s="8">
         <v>7.0</v>
@@ -4800,26 +4824,26 @@
         <v>18</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C119" s="1">
         <v>10019.0</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E119" s="8">
         <v>10020.0</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H119" s="17"/>
       <c r="I119" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J119" s="8">
         <v>5.0</v>
@@ -4830,29 +4854,29 @@
         <v>18</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C120" s="1">
         <v>10020.0</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E120" s="8">
         <v>-1.0</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H120" s="17"/>
       <c r="I120" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J120" s="8">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="121">
@@ -4866,20 +4890,20 @@
         <v>11001.0</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E121" s="8">
         <v>11002.0</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G121" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H121" s="17"/>
       <c r="I121" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J121" s="8">
         <v>10.0</v>
@@ -4896,20 +4920,20 @@
         <v>11002.0</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E122" s="8">
         <v>11003.0</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G122" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H122" s="17"/>
       <c r="I122" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J122" s="8">
         <v>10.0</v>
@@ -4926,23 +4950,23 @@
         <v>11003.0</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E123" s="8">
         <v>11004.0</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H123" s="17"/>
       <c r="I123" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J123" s="8">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="124">
@@ -4956,23 +4980,23 @@
         <v>11004.0</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E124" s="8">
         <v>11005.0</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H124" s="17"/>
       <c r="I124" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J124" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="125">
@@ -4986,20 +5010,20 @@
         <v>11005.0</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E125" s="8">
         <v>11006.0</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G125" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H125" s="17"/>
       <c r="I125" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J125" s="8">
         <v>11.0</v>
@@ -5016,20 +5040,20 @@
         <v>11006.0</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E126" s="8">
         <v>11007.0</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G126" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H126" s="17"/>
       <c r="I126" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J126" s="8">
         <v>11.0</v>
@@ -5046,23 +5070,23 @@
         <v>11007.0</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E127" s="8">
         <v>11008.0</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J127" s="8">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -5076,20 +5100,20 @@
         <v>11008.0</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E128" s="8">
         <v>11009.0</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G128" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H128" s="17"/>
       <c r="I128" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J128" s="8">
         <v>9.0</v>
@@ -5106,20 +5130,20 @@
         <v>11009.0</v>
       </c>
       <c r="D129" s="18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E129" s="8">
         <v>11010.0</v>
       </c>
       <c r="F129" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G129" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J129" s="8">
         <v>9.0</v>
@@ -5136,20 +5160,20 @@
         <v>11010.0</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E130" s="8">
         <v>11011.0</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J130" s="8">
         <v>0.0</v>
@@ -5166,22 +5190,22 @@
         <v>11011.0</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E131" s="8">
         <v>-1.0</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G131" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J131" s="8">
         <v>8.0</v>
@@ -5192,26 +5216,26 @@
         <v>20</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C132" s="1">
         <v>11012.0</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E132" s="8">
         <v>11013.0</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G132" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H132" s="17"/>
       <c r="I132" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J132" s="8">
         <v>9.0</v>
@@ -5222,26 +5246,26 @@
         <v>20</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C133" s="1">
         <v>11013.0</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E133" s="8">
         <v>11014.0</v>
       </c>
       <c r="F133" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G133" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H133" s="17"/>
       <c r="I133" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J133" s="8">
         <v>9.0</v>
@@ -5252,29 +5276,29 @@
         <v>20</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C134" s="1">
         <v>11014.0</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E134" s="8">
         <v>-1.0</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J134" s="8">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="135">
@@ -5282,26 +5306,26 @@
         <v>20</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C135" s="1">
         <v>11015.0</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E135" s="8">
         <v>11016.0</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G135" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J135" s="8">
         <v>9.0</v>
@@ -5312,26 +5336,26 @@
         <v>20</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C136" s="1">
         <v>11016.0</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E136" s="8">
         <v>11017.0</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G136" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H136" s="17"/>
       <c r="I136" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J136" s="8">
         <v>9.0</v>
@@ -5342,26 +5366,26 @@
         <v>20</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C137" s="1">
         <v>11017.0</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E137" s="8">
         <v>-1.0</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H137" s="17"/>
       <c r="I137" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J137" s="8">
         <v>1.0</v>
@@ -5378,20 +5402,20 @@
         <v>12001.0</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E138" s="8">
         <v>12002.0</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J138" s="8">
         <v>-1.0</v>
@@ -5408,20 +5432,20 @@
         <v>12002.0</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E139" s="8">
         <v>12003.0</v>
       </c>
       <c r="F139" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H139" s="17"/>
       <c r="I139" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J139" s="8">
         <v>-1.0</v>
@@ -5438,20 +5462,20 @@
         <v>12003.0</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E140" s="8">
         <v>12004.0</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H140" s="17"/>
       <c r="I140" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J140" s="8">
         <v>-1.0</v>
@@ -5468,20 +5492,20 @@
         <v>12004.0</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E141" s="8">
         <v>12005.0</v>
       </c>
       <c r="F141" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G141" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H141" s="17"/>
       <c r="I141" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J141" s="8">
         <v>-1.0</v>
@@ -5498,20 +5522,20 @@
         <v>12005.0</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E142" s="8">
         <v>-1.0</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H142" s="17"/>
       <c r="I142" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J142" s="8">
         <v>-1.0</v>
@@ -5528,23 +5552,23 @@
         <v>13001.0</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E143" s="8">
         <v>13002.0</v>
       </c>
       <c r="F143" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G143" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H143" s="17"/>
       <c r="I143" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J143" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="144">
@@ -5558,20 +5582,20 @@
         <v>13002.0</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E144" s="8">
         <v>13003.0</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G144" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H144" s="17"/>
       <c r="I144" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J144" s="8">
         <v>0.0</v>
@@ -5588,20 +5612,20 @@
         <v>13003.0</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E145" s="8">
         <v>13004.0</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G145" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H145" s="17"/>
       <c r="I145" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J145" s="8">
         <v>0.0</v>
@@ -5618,20 +5642,20 @@
         <v>13004.0</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E146" s="8">
         <v>-1.0</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G146" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H146" s="17"/>
       <c r="I146" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J146" s="8">
         <v>0.0</v>
@@ -5648,20 +5672,20 @@
         <v>14001.0</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E147" s="8">
         <v>14002.0</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G147" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H147" s="17"/>
       <c r="I147" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J147" s="8">
         <v>-1.0</v>
@@ -5678,20 +5702,20 @@
         <v>14002.0</v>
       </c>
       <c r="D148" s="18" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E148" s="8">
         <v>14003.0</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G148" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H148" s="17"/>
       <c r="I148" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J148" s="8">
         <v>-1.0</v>
@@ -5708,22 +5732,22 @@
         <v>14003.0</v>
       </c>
       <c r="D149" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E149" s="8">
         <v>-1.0</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G149" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H149" s="15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J149" s="8">
         <v>-1.0</v>
@@ -5734,26 +5758,26 @@
         <v>26</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C150" s="1">
         <v>14004.0</v>
       </c>
       <c r="D150" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E150" s="8">
         <v>14005.0</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G150" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H150" s="17"/>
       <c r="I150" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J150" s="8">
         <v>2.0</v>
@@ -5764,29 +5788,29 @@
         <v>26</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C151" s="1">
         <v>14005.0</v>
       </c>
       <c r="D151" s="18" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E151" s="8">
         <v>-1.0</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H151" s="17"/>
       <c r="I151" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J151" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="152">
@@ -5794,42 +5818,108 @@
         <v>26</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C152" s="1">
         <v>14006.0</v>
       </c>
       <c r="D152" s="18" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E152" s="8">
         <v>-1.0</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G152" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H152" s="17"/>
       <c r="I152" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J152" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="19"/>
+      <c r="A153" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C153" s="1">
+        <v>15001.0</v>
+      </c>
+      <c r="D153" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="E153" s="8">
+        <v>15002.0</v>
+      </c>
+      <c r="F153" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H153" s="17"/>
+      <c r="I153" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J153" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="19"/>
+      <c r="A154" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C154" s="1">
+        <v>15002.0</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-1.0</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H154" s="17"/>
+      <c r="I154" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J154" s="8">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="19"/>
+      <c r="A155" s="5"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="17"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
     </row>
     <row r="156">
-      <c r="A156" s="19"/>
+      <c r="A156" s="5"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="15"/>
+      <c r="G156" s="16"/>
+      <c r="H156" s="17"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
     </row>
     <row r="157">
       <c r="A157" s="19"/>
@@ -8467,19 +8557,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
@@ -8487,16 +8577,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -8507,16 +8597,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -8527,16 +8617,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1">
         <v>-1.0</v>
@@ -8547,16 +8637,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1">
         <v>-1.0</v>
@@ -8567,16 +8657,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1">
         <v>-1.0</v>
@@ -8587,16 +8677,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1">
         <v>-1.0</v>
@@ -8607,16 +8697,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1">
         <v>-1.0</v>
@@ -8627,16 +8717,16 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" s="1">
         <v>-1.0</v>
@@ -8647,16 +8737,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" s="1">
         <v>-1.0</v>
@@ -8667,16 +8757,16 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F11" s="1">
         <v>-1.0</v>
@@ -8687,16 +8777,16 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1">
         <v>-1.0</v>
@@ -8707,16 +8797,16 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1">
         <v>-1.0</v>
@@ -8727,16 +8817,16 @@
         <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1">
         <v>-1.0</v>
@@ -8747,16 +8837,16 @@
         <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1">
         <v>-1.0</v>

--- a/Assets/02Script/Table/NpcTable.xlsx
+++ b/Assets/02Script/Table/NpcTable.xlsx
@@ -90,7 +90,7 @@
     <t>N013</t>
   </si>
   <si>
-    <t>2스테이지 문</t>
+    <t>의문의 문</t>
   </si>
   <si>
     <t>N014</t>
@@ -8823,7 +8823,7 @@
         <v>63</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>42</v>
